--- a/bilgidozu_yukleme_tablosu.xlsx
+++ b/bilgidozu_yukleme_tablosu.xlsx
@@ -49,7 +49,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +74,12 @@
         <bgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border/>
@@ -86,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -128,6 +134,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1897,47 +1909,47 @@
       <c r="AC20" s="6" t="n"/>
     </row>
     <row r="21" ht="112.5" customHeight="1" s="13">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>video_17.mp4</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>Everest'in 2.5 Katı Yüksekliğinde Bir Dağ Var — Ama Dünya'da Değil! 🌋🪐 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>Mars'taki Olympus Mons, yaklaşık 22 km yüksekliğiyle Everest'in 2.5 katı! Tabanı ise Arizona kadar geniş. Dünya'da bu dağın ağırlığı kendi kabuğunu çökerterek batmasına neden olurdu — Mars'ta kabuk buna izin veriyor!</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>bilgidozu, mars, olympusmons, uzay, geoloji, bilim, shorts</t>
         </is>
       </c>
-      <c r="G21" s="14" t="inlineStr">
+      <c r="G21" s="16" t="inlineStr">
         <is>
           <t>Olympus Mons'un zirvesinden manzara... 🌋 Peki tırmanır mıydın? Korkanlar 1, cesurlar 2! 👇</t>
         </is>
       </c>
-      <c r="H21" s="14" t="inlineStr">
+      <c r="H21" s="16" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I21" s="14" t="inlineStr">
+      <c r="I21" s="16" t="inlineStr">
         <is>
           <t>NASA — Mars Facts: https://science.nasa.gov/mars/facts/</t>
         </is>
@@ -1964,47 +1976,47 @@
       <c r="AC21" s="6" t="n"/>
     </row>
     <row r="22" ht="112.5" customHeight="1" s="13">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BEKLEMEDE </t>
-        </is>
-      </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>video_18.mp4</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>Bu Hayvanın BEYNİ YOK — Ama Görüyor, Hissediyor! ⭐🌊 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>Denizyıldızının merkezî bir beyni yok: sinir sistemi kollarına yayılmış! Her kolun ucundaki minik gözcükler ışığı algılar, binlerce ayakçık tadar, kavrar ve yürür. Kafasız ama eksiksiz — doğanın en zarif dağıtık zekâ tasarımı!</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim</t>
         </is>
       </c>
-      <c r="F22" s="14" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>bilgidozu, denizyıldızı, denizcanlıları, biyoloji, ilginçbilgiler, shorts</t>
         </is>
       </c>
-      <c r="G22" s="14" t="inlineStr">
+      <c r="G22" s="16" t="inlineStr">
         <is>
           <t>Beyinsiz ama görüyor, tadıyor, yürüyor... ⭐ Doğanın en garip tasarımı mı? 1 yazsın! 👇</t>
         </is>
       </c>
-      <c r="H22" s="14" t="inlineStr">
+      <c r="H22" s="16" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I22" s="14" t="inlineStr">
+      <c r="I22" s="16" t="inlineStr">
         <is>
           <t>Starfish: https://en.wikipedia.org/wiki/Starfish</t>
         </is>
@@ -2031,47 +2043,47 @@
       <c r="AC22" s="6" t="n"/>
     </row>
     <row r="23" ht="112.5" customHeight="1" s="13">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>video_19.mp4</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>Yunuslar Tek Gözü Açık Uyur! 🐬😴 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>Yunusun beyninin iki yarısı sırayla uyur: bir yarı derin uykudayken diğeri düşman nöbeti tutar, yüzer ve nefes aldırır! Göz de beynin uyuyan tarafına göre kapanır. Adı: yarım küre uykusu (USWS) — doğanın nöbetçi sistemi!</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim</t>
         </is>
       </c>
-      <c r="F23" s="14" t="inlineStr">
+      <c r="F23" s="16" t="inlineStr">
         <is>
           <t>bilgidozu, yunus, hayvanlaralemi, uyku, deniz, bilim, shorts</t>
         </is>
       </c>
-      <c r="G23" s="14" t="inlineStr">
+      <c r="G23" s="16" t="inlineStr">
         <is>
           <t>Yunus bile nöbet tutarak uyurken sen nasıl uyuyorsun? 😄🐬 Uykucular 1 yazsın!</t>
         </is>
       </c>
-      <c r="H23" s="14" t="inlineStr">
+      <c r="H23" s="16" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I23" s="14" t="inlineStr">
+      <c r="I23" s="16" t="inlineStr">
         <is>
           <t>Sleep Foundation — Animals and Sleep: https://www.sleepfoundation.org/animals-and-sleep</t>
         </is>

--- a/bilgidozu_yukleme_tablosu.xlsx
+++ b/bilgidozu_yukleme_tablosu.xlsx
@@ -49,7 +49,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -80,6 +80,12 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+        <bgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border/>
@@ -92,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -140,6 +146,12 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -591,50 +603,50 @@
       <c r="AC1" s="2" t="n"/>
     </row>
     <row r="2" ht="112.5" customHeight="1" s="13">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>YAYINLANDI</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>video_1.mp4</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="18" t="inlineStr">
         <is>
           <t>Venüs'te Bir Gün Bir Yıldan Daha Uzun! 🪐 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="18" t="inlineStr">
         <is>
           <t>Kendi doğum gününüzün bir tam günden daha kısa sürdüğünü hayal edebiliyor musunuz? Venüs kendi ekseninde 243 Dünya gününde dönerken, Güneş etrafındaki bir yılını sadece 225 günde tamamlar. Yani Venüs'te bir gün, bir yıldan daha uzundur!
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="18" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="18" t="inlineStr">
         <is>
           <t>bilgidozu, uzay, venüs, ilginçbilgiler, bilim, astronomi, shorts</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="18" t="inlineStr">
         <is>
           <t>Venüs'te bir gün bir yıldan uzun sürse, orada yaşayan birine 'günaydın' demek kaç yıl sürerdi? 😄🌙 Cevabını yaz! 👇</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="18" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>NASA — Venus: https://science.nasa.gov/venus/</t>
+      <c r="I2" s="18" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
         </is>
       </c>
       <c r="J2" s="5" t="n"/>
@@ -659,50 +671,50 @@
       <c r="AC2" s="6" t="n"/>
     </row>
     <row r="3" ht="112.5" customHeight="1" s="13">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>YAYINLANDI</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>video_2.mp4</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>Bir Kargaya Asla Yanlış Yapmayın: Yüzünüzü Asla Unutmazlar! 🦅 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>Washington Üniversitesi'nin yaptığı ünlü araştırmada kargalar kendilerini yakalayan maskeli araştırmacıları tam 5 yıl boyunca unutmadı, hatta bu tehlikeli yüzü yeni nesillere ve tüm sürüye öğretti!
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>bilgidozu, karga, hayvanlaralemi, zeka, deney, ilginçbilgiler, shorts</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t>Sence kargalar gerçekten 5 yıl boyunca yüzleri hatırlıyor mu? 🦅 İnananlar '1', şüphelenenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>The Conversation (UW 5 yıllık maske deneyi): https://theconversation.com/never-cross-a-crow-it-will-remember-your-face-2121</t>
+      <c r="I3" s="18" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
         </is>
       </c>
       <c r="J3" s="5" t="n"/>
@@ -727,50 +739,50 @@
       <c r="AC3" s="6" t="n"/>
     </row>
     <row r="4" ht="112.5" customHeight="1" s="13">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>YAYINLANDI</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>video_3.mp4</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>Her Gün Yediğiniz Bu Meyve Aslında Radyoaktif! 🍌⚡ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>Muzlar doğal olarak radyoaktif Potasyum-40 izotopu içerir ve saniyede yaklaşık 15 pozitron (antimadde parçacığı) yayar. Nükleer fizikte buna 'Muz Eşdeğer Dozu' denir!
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="18" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #fizik #bilim</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="18" t="inlineStr">
         <is>
           <t>bilgidozu, fizik, radyasyon, antimadde, ilginçbilgiler, bilim, shorts</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="18" t="inlineStr">
         <is>
           <t>Bugün kaç muz yedin? 🍌😄 Hadi itiraf et, yorumlara yaz! 👇</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="18" t="inlineStr">
         <is>
           <t>Fizik ve Bilim</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>Banana Equivalent Dose: https://en.wikipedia.org/wiki/Banana_equivalent_dose</t>
+      <c r="I4" s="18" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
         </is>
       </c>
       <c r="J4" s="5" t="n"/>
@@ -795,50 +807,50 @@
       <c r="AC4" s="6" t="n"/>
     </row>
     <row r="5" ht="112.5" customHeight="1" s="13">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>YAYINLANDI</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>video_4.mp4</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>Ormanın Altındaki Gizli İnternet: Ağaçlar Birbiriyle Konuşuyor! 🌲🍄 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="18" t="inlineStr">
         <is>
           <t>Ağaçlar köklerindeki mikorizal mantar ağlarını (Wood Wide Web) kullanarak birbirleriyle haberleşir, tehlike anında kimyasal sinyaller gönderip komşu fideleri besler!
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="18" t="inlineStr">
         <is>
           <t>bilgidozu, doğa, biyoloji, ağaçlar, orman, woodwideweb, shorts</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="18" t="inlineStr">
         <is>
           <t>Ormanın altındaki gizli internete şaşırdın mı? 🌲🍄 Sence ağaçlar birbirine daha neler anlatıyor olabilir? 👇</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="18" t="inlineStr">
         <is>
           <t>Doğa ve Biyoloji</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>Mikorizal ağ (Wood Wide Web): https://en.wikipedia.org/wiki/Mycorrhizal_network</t>
+      <c r="I5" s="18" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
         </is>
       </c>
       <c r="J5" s="5" t="n"/>
@@ -863,50 +875,50 @@
       <c r="AC5" s="6" t="n"/>
     </row>
     <row r="6" ht="112.5" customHeight="1" s="13">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>YÜKLENDİ</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>video_5.mp4</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>Aynaya Baktığında Bir İnsan Değil, Bir Süpernova Görüyorsun! ✨ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>Kanınızdaki demir, kemiklerinizdeki kalsiyum ve soluduğunuz oksijen patlayan dev süpernova yıldızlarının çekirdeklerinde üretildi. Sen tam anlamıyla canlı bir yıldız tozusun!
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="18" t="inlineStr">
         <is>
           <t>bilgidozu, kozmoloji, yıldıztozu, süpernova, evren, bilim, shorts</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="18" t="inlineStr">
         <is>
           <t>Şu an vücudunda yıldız parçaları taşıdığını biliyor muydun? ✨ Bu bilgiye '🤯' yazan herkes aslında bir süpernova! 👇</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="18" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>NASA — Stars: https://science.nasa.gov/universe/stars/</t>
+      <c r="I6" s="18" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
         </is>
       </c>
       <c r="J6" s="5" t="n"/>
@@ -931,50 +943,50 @@
       <c r="AC6" s="6" t="n"/>
     </row>
     <row r="7" ht="112.5" customHeight="1" s="13">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>YÜKLENDİ</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>video_6.mp4</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>Su Aslında Şeffaf Değil, Doğal Olarak Mavidir! 💧 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>Denizlerin gökyüzünü yansıttığı için mavi olduğu bilgisi bir efsanedir! Hidrojen ve oksijen kimyasal bağları kırmızı dalga boyunu soğurur ve saf su doğası gereği açık mavidir!
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #fizik #bilim</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="18" t="inlineStr">
         <is>
           <t>bilgidozu, bilim, fizik, denizler, su, kimya, shorts</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="18" t="inlineStr">
         <is>
           <t>Mavinin suyun GERÇEK rengi olduğunu biliyor muydun? 💙 Şaşıranlar '1' desin! 👇</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="18" t="inlineStr">
         <is>
           <t>Fizik ve Kimya</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>NOAA — Why is the ocean blue: https://oceanservice.noaa.gov/facts/oceanblue.html</t>
+      <c r="I7" s="18" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
         </is>
       </c>
       <c r="J7" s="5" t="n"/>
@@ -999,51 +1011,50 @@
       <c r="AC7" s="6" t="n"/>
     </row>
     <row r="8" ht="112.5" customHeight="1" s="13">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>YÜKLENDİ</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>video_7.mp4</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>Bal Arıları Sıfır Kavramını ve Matematiği Anlayabiliyor! 🐝🔢 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>Susam tanesi büyüklüğündeki minik beyinleriyle bal arıları, 'sıfır' soyut kavramını ve basit toplama-çıkarma işlemlerini kavrayabilen dünyadaki nadir canlılardandır!
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>bilgidozu, arılar, hayvanlaralemi, matematik, zeka, biyoloji, shorts</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="18" t="inlineStr">
         <is>
           <t>Sıfır kavramını sen kaç yaşında öğrenmiştin? 🐝 Bu arılar seni geçti mi? 😄 Yaz bakalım! 👇</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="18" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>The Conversation (RMIT araştırmacıları): https://theconversation.com/bees-join-an-elite-group-of-species-that-understands-the-concept-of-zero-as-a-number-97316
-RMIT: https://www.rmit.edu.au/news/all-news/2018/jun/honeybees-zero-in-on-nothing</t>
+      <c r="I8" s="18" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
         </is>
       </c>
       <c r="J8" s="5" t="n"/>
@@ -1068,51 +1079,50 @@
       <c r="AC8" s="6" t="n"/>
     </row>
     <row r="9" ht="112.5" customHeight="1" s="13">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>YÜKLENDİ</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>video_8.mp4</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>Dünyadaki Tüm Karıncalar İnsanlardan Daha Ağır Çekiyor! 🐜⚖️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>Dünya üzerindeki 20 katrilyon karıncanın toplam kuru biyokütle ağırlığı, gezegendeki tüm insanların ve yabani memelilerin toplam ağırlığından daha fazladır!
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t>bilgidozu, karınca, doğa, biyoloji, ekoloji, ilginçbilgiler, shorts</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="18" t="inlineStr">
         <is>
           <t>Karıncalar mı insanlardan güçlü mü? 🐜⚖️ Sence tüm karıncalar mı yoksa tüm insanlar mı daha ağır? Cevabını yaz! 👇</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="18" t="inlineStr">
         <is>
           <t>Doğa ve Biyoloji</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>phys.org (PNAS 2022): https://phys.org/news/2022-09-earth-harbours-ants-wild-birds.html
-⚠ DÜZELTME ÖNERİSİ: PNAS 2022'ye göre karıncalar (12 Mt C) insanlardan DEĞİL (insanların ~%20'si), tüm YABANİ KUŞ+MEMELİLERİN toplamından daha ağır. Açıklamayı/başlığı düzeltirsen kaynakla tam uyumlu olur: 'Dünyadaki karıncalar tüm yabani kuş ve memelilerden daha ağır!'</t>
+      <c r="I9" s="17" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
         </is>
       </c>
       <c r="J9" s="5" t="n"/>
@@ -1137,50 +1147,50 @@
       <c r="AC9" s="6" t="n"/>
     </row>
     <row r="10" ht="112.5" customHeight="1" s="13">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>YÜKLENDİ</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>video_9.mp4</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>Jüpiter'in Bu Uydusunda Dünya'dan 2 Kat Fazla Su Var! 🪐🌊 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>Ay'dan bile küçük olan Jüpiter uydusu Europa'nın buz kabuğunun altındaki dev tuzlu okyanusta, Dünya'daki bütün okyanusların toplamının tam 2 katı su vardır!
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="18" t="inlineStr">
         <is>
           <t>bilgidozu, uzay, europa, jüpiter, astronomi, nasa, shorts</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="18" t="inlineStr">
         <is>
           <t>Europa'nın buzunun altında yaşam olsa nasıl olurdu? 🌊🦑 En çılgın tahminini yaz! 👇</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="18" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>NASA — Europa: https://science.nasa.gov/jupiter/moons/europa/</t>
+      <c r="I10" s="18" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
         </is>
       </c>
       <c r="J10" s="5" t="n"/>
@@ -1205,50 +1215,50 @@
       <c r="AC10" s="6" t="n"/>
     </row>
     <row r="11" ht="112.5" customHeight="1" s="13">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>YÜKLENDİ</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>video_10.mp4</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>2000 Yıllık Roma Binaları Neden Yıkılmıyor? Beton Kendi Kendini Onarıyor! 🏛️⚡ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>MIT araştırmacıları antik Roma betonunun sırrını çözdü: Harçtaki sıcak kireç kırıntıları, yağmur suyu sızdığında kalsiyum kristallerine dönüşerek çatlakları kendiliğinden yamıyordu!
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #bilim</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr">
         <is>
           <t>bilgidozu, roma, tarih, mühendislik, bilim, arkeoloji, shorts</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t>2000 yıl dayanan Roma betonu mu, modern beton mu? 🏛️ Sence bu sırrı hâlâ neden çözemedik? 👇</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="18" t="inlineStr">
         <is>
           <t>Tarih ve Mühendislik</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>MIT News (2023 Roma betonu): https://news.mit.edu/2023/roman-concrete-durability-lime-casts-0106</t>
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
         </is>
       </c>
       <c r="J11" s="5" t="n"/>
@@ -1273,50 +1283,50 @@
       <c r="AC11" s="6" t="n"/>
     </row>
     <row r="12" ht="112.5" customHeight="1" s="13">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>YÜKLENDİ</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>video_11.mp4</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>Gökten Yağmur Değil Dev Elmaslar Yağan Gezegenler! 💎🪐 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>Neptün ve Uranüs'ün derin atmosferindeki aşırı basınç ve sıcaklık, metan gazındaki karbon atomlarını saf elmas kristallerine dönüştürüp gökten elmas dolusu gibi yağdırıyor!
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="18" t="inlineStr">
         <is>
           <t>bilgidozu, uzay, elmas, neptün, uranüs, bilim, shorts</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="18" t="inlineStr">
         <is>
           <t>Neptün'de elmas yağdığını bilseydin oraya taşınmaya değer miydi? 💎😄 Sen olsan ne yapardın? 👇</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="18" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>SLAC (2017 elmas yağmuru deneyi): https://www6.slac.stanford.edu/news/2017-08-21-scientists-create-diamond-rain-forms-interior-icy-giant-planets</t>
+      <c r="I12" s="18" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
         </is>
       </c>
       <c r="J12" s="5" t="n"/>
@@ -1341,50 +1351,50 @@
       <c r="AC12" s="6" t="n"/>
     </row>
     <row r="13" ht="112.5" customHeight="1" s="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>YÜKLENDİ</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>video_12.mp4</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>Bu Canlı Uzay Boşluğunda ve Radyasyonda Bile Ölmüyor! 🐻🔬 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>Mikroskobik su ayıları (tardigradlar), -272 dereceden +150 dereceye, ölümcül radyasyondan açık uzayın dondurucu vakumuna kadar her koşulda hayatta kalabiliyor!
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #bilim</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="18" t="inlineStr">
         <is>
           <t>bilgidozu, tardigrad, uzay, biyoloji, ilginçbilgiler, bilim, shorts</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="18" t="inlineStr">
         <is>
           <t>Tardigradlar Dünya'nın en dayanıklı canlısı mı? 🐻🔬 Oy ver: EVET / HAYIR 👇</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="18" t="inlineStr">
         <is>
           <t>Biyoloji ve Uzay</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>Tardigrada: https://en.wikipedia.org/wiki/Tardigrade</t>
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
         </is>
       </c>
       <c r="J13" s="5" t="n"/>
@@ -1409,51 +1419,50 @@
       <c r="AC13" s="6" t="n"/>
     </row>
     <row r="14" ht="112.5" customHeight="1" s="13">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>YÜKLENDİ</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>video_13.mp4</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>Birinin Sizden Hoşlandığını Anlamanın En Kesin Yolu! 👁️✨ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>Beyin bir şeye aşırı odaklandığında veya heyecanlandığında otonom sinir sistemi devreye girer ve göz bebekleri normal boyutunun %45'ine kadar kontrolsüzce genişler!
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #beyin #psikoloji</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="18" t="inlineStr">
         <is>
           <t>bilgidozu, psikoloji, beyin, gözler, nörobilim, shorts</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="18" t="inlineStr">
         <is>
           <t>Şu an aynaya bak ve göz bebeklerini izle! 👁️ Kimin aklına kim geldi? 😄 Yaz bakalım! 👇</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="18" t="inlineStr">
         <is>
           <t>Beyin ve Psikoloji</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>Psychology Today (30+ çalışma meta-analizi): https://www.psychologytoday.com/us/blog/best-practices-in-health/202506/eyes-wide-open-what-your-eyes-reveal-about-attraction
-Yedek: https://www.medicalnewstoday.com/articles/dilated-pupils-meaning</t>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
         </is>
       </c>
       <c r="J14" s="5" t="n"/>
@@ -1478,50 +1487,50 @@
       <c r="AC14" s="6" t="n"/>
     </row>
     <row r="15" ht="112.5" customHeight="1" s="13">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>YÜKLENDİ</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>video_14.mp4</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>Dünyanın En Yaşlı Canlısı Bir Hayvan Değil, 80.000 Yaşındaki Bu Orman! 🌲⚡ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>Utah'taki Pando ormanı dışarıdan 47.000 ağaç gibi görünse de aslında tek bir dev kök sistemine bağlı, genetik olarak tamamen özdeş 80.000 yıllık dev bir canlıdır!
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="18" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="18" t="inlineStr">
         <is>
           <t>bilgidozu, pando, orman, ağaçlar, doğa, biyoloji, shorts</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="18" t="inlineStr">
         <is>
           <t>80.000 yıllık bu dev canlıya Pando'dan başka ne isim verirdin? 🌲 En yaratık ismi yazan pinned olur! 👇</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="18" t="inlineStr">
         <is>
           <t>Doğa ve Biyoloji</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>USDA Forest Service — Pando: https://www.fs.usda.gov/detail/fishlake/home/?cid=stelprdb5444544</t>
+      <c r="I15" s="18" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
         </is>
       </c>
       <c r="J15" s="5" t="n"/>
@@ -1546,50 +1555,50 @@
       <c r="AC15" s="6" t="n"/>
     </row>
     <row r="16" ht="112.5" customHeight="1" s="13">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>YÜKLENDİ</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>video_15.mp4</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>Gözlerinize İnanmayın: Yıldırımlar Aslında Aşağıdan Yukarıya Çakar! ⚡🌩️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>Görünmez öncü kanal yere ulaştığı anda, asıl devasa ışık ve enerji patlaması yerden gökyüzüne doğru saniyede 100.000 km hızla fırlar! Gözlerimiz bunu aşağı iniyor sanır!
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #fizik #bilim</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="18" t="inlineStr">
         <is>
           <t>bilgidozu, yıldırım, fizik, şimşek, doğaolayları, bilim, shorts</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G16" s="18" t="inlineStr">
         <is>
           <t>Yıldırımın aslında aşağıdan yukarıya çaktığını biliyor muydun? ⚡ Şaşırdıysan '🤯' yaz! 👇</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="18" t="inlineStr">
         <is>
           <t>Fizik ve Doğa</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>NOAA/NWS — Lightning science: https://www.weather.gov/safety/lightning-scienceUSDA Forest Service — Pando: https://www.fs.usda.gov/detail/fishlake/home/?cid=stelprdb5444544</t>
+      <c r="I16" s="18" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
         </is>
       </c>
       <c r="J16" s="5" t="n"/>
@@ -1842,49 +1851,49 @@
       <c r="AC19" s="6" t="n"/>
     </row>
     <row r="20" ht="112.5" customHeight="1" s="13">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>YÜKLENDİ</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>video_16.mp4</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="18" t="inlineStr">
         <is>
           <t>Jüpiter'de Dünya'dan Büyük Bir Fırtına 350 Yıldır DÖNÜYOR! 🌪️🪐 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="18" t="inlineStr">
         <is>
           <t>Büyük Kızıl Leke, Jüpiter'in atmosferinde en az 350 yıldır süren dev bir fırtına — içine bütün Dünya rahatça sığar! Ama sürpriz son dakika haberi: son yıllarda hızla küçülüyor ve parçalanmaya başladı. Belki de biz, dev bir fırtınanın ölümüne tanık olan ilk insanlarız!</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="18" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F20" s="18" t="inlineStr">
         <is>
           <t>bilgidozu, jüpiter, uzay, fırtına, astronomi, nasa, shorts</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G20" s="18" t="inlineStr">
         <is>
           <t>350 yıllık fırtınanın kenarından uçak yolculuğu... 🌪️ Gider miydin? Cesurlar 1, akıllılar 2! 👇</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H20" s="18" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>NASA — Jupiter Facts: https://science.nasa.gov/jupiter/facts/</t>
+      <c r="I20" s="18" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
         </is>
       </c>
       <c r="J20" s="5" t="n"/>
@@ -1909,49 +1918,49 @@
       <c r="AC20" s="6" t="n"/>
     </row>
     <row r="21" ht="112.5" customHeight="1" s="13">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>YÜKLENDİ</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>video_17.mp4</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C21" s="18" t="inlineStr">
         <is>
           <t>Everest'in 2.5 Katı Yüksekliğinde Bir Dağ Var — Ama Dünya'da Değil! 🌋🪐 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="18" t="inlineStr">
         <is>
           <t>Mars'taki Olympus Mons, yaklaşık 22 km yüksekliğiyle Everest'in 2.5 katı! Tabanı ise Arizona kadar geniş. Dünya'da bu dağın ağırlığı kendi kabuğunu çökerterek batmasına neden olurdu — Mars'ta kabuk buna izin veriyor!</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E21" s="18" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F21" s="18" t="inlineStr">
         <is>
           <t>bilgidozu, mars, olympusmons, uzay, geoloji, bilim, shorts</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G21" s="18" t="inlineStr">
         <is>
           <t>Olympus Mons'un zirvesinden manzara... 🌋 Peki tırmanır mıydın? Korkanlar 1, cesurlar 2! 👇</t>
         </is>
       </c>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="H21" s="18" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>NASA — Mars Facts: https://science.nasa.gov/mars/facts/</t>
+      <c r="I21" s="18" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
         </is>
       </c>
       <c r="J21" s="5" t="n"/>
@@ -1976,49 +1985,49 @@
       <c r="AC21" s="6" t="n"/>
     </row>
     <row r="22" ht="112.5" customHeight="1" s="13">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>YÜKLENDİ</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>video_18.mp4</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C22" s="18" t="inlineStr">
         <is>
           <t>Bu Hayvanın BEYNİ YOK — Ama Görüyor, Hissediyor! ⭐🌊 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D22" s="18" t="inlineStr">
         <is>
           <t>Denizyıldızının merkezî bir beyni yok: sinir sistemi kollarına yayılmış! Her kolun ucundaki minik gözcükler ışığı algılar, binlerce ayakçık tadar, kavrar ve yürür. Kafasız ama eksiksiz — doğanın en zarif dağıtık zekâ tasarımı!</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E22" s="18" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F22" s="18" t="inlineStr">
         <is>
           <t>bilgidozu, denizyıldızı, denizcanlıları, biyoloji, ilginçbilgiler, shorts</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G22" s="18" t="inlineStr">
         <is>
           <t>Beyinsiz ama görüyor, tadıyor, yürüyor... ⭐ Doğanın en garip tasarımı mı? 1 yazsın! 👇</t>
         </is>
       </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="H22" s="18" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>Starfish: https://en.wikipedia.org/wiki/Starfish</t>
+      <c r="I22" s="18" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
         </is>
       </c>
       <c r="J22" s="5" t="n"/>
@@ -2043,49 +2052,49 @@
       <c r="AC22" s="6" t="n"/>
     </row>
     <row r="23" ht="112.5" customHeight="1" s="13">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>YÜKLENDİ</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>video_19.mp4</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C23" s="18" t="inlineStr">
         <is>
           <t>Yunuslar Tek Gözü Açık Uyur! 🐬😴 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D23" s="18" t="inlineStr">
         <is>
           <t>Yunusun beyninin iki yarısı sırayla uyur: bir yarı derin uykudayken diğeri düşman nöbeti tutar, yüzer ve nefes aldırır! Göz de beynin uyuyan tarafına göre kapanır. Adı: yarım küre uykusu (USWS) — doğanın nöbetçi sistemi!</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E23" s="18" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F23" s="18" t="inlineStr">
         <is>
           <t>bilgidozu, yunus, hayvanlaralemi, uyku, deniz, bilim, shorts</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G23" s="18" t="inlineStr">
         <is>
           <t>Yunus bile nöbet tutarak uyurken sen nasıl uyuyorsun? 😄🐬 Uykucular 1 yazsın!</t>
         </is>
       </c>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="H23" s="18" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>Sleep Foundation — Animals and Sleep: https://www.sleepfoundation.org/animals-and-sleep</t>
+      <c r="I23" s="18" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
         </is>
       </c>
       <c r="J23" s="5" t="n"/>
@@ -2110,49 +2119,49 @@
       <c r="AC23" s="6" t="n"/>
     </row>
     <row r="24" ht="112.5" customHeight="1" s="13">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">BEKLEMEDE </t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t>video_20.mp4</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C24" s="18" t="inlineStr">
         <is>
           <t>Satürn Suda Yüzebilecek Kadar Hafif! 🪐💧 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="D24" s="18" t="inlineStr">
         <is>
           <t>Satürn'ün ortalama yoğunluğu sudan düşük: 0,7 g/cm³! Yani düşünen bir gezegen — yeterince büyük bir okyanus bulsaydık Satürn üstünde yüzebilirdi. Dev ama tüy gibi hafif: çoğu hidrojen ve helyumdan ibaret bir gaz topu.</t>
         </is>
       </c>
-      <c r="E24" s="14" t="inlineStr">
+      <c r="E24" s="18" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
-      <c r="F24" s="14" t="inlineStr">
+      <c r="F24" s="18" t="inlineStr">
         <is>
           <t>bilgidozu, satürn, uzay, gezegenler, ilginçbilgiler, bilim, shorts</t>
         </is>
       </c>
-      <c r="G24" s="14" t="inlineStr">
+      <c r="G24" s="18" t="inlineStr">
         <is>
           <t>Satürn'ü küvette yüzerken hayal et 🪐💧 İnananlar 1, inanmayanlar 2! 👇</t>
         </is>
       </c>
-      <c r="H24" s="14" t="inlineStr">
+      <c r="H24" s="18" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I24" s="14" t="inlineStr">
-        <is>
-          <t>NASA — Saturn Facts: https://science.nasa.gov/saturn/facts/</t>
+      <c r="I24" s="18" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ (https://youtu.be/MzkXjFsAZ90)</t>
         </is>
       </c>
       <c r="J24" s="5" t="n"/>
@@ -2177,49 +2186,49 @@
       <c r="AC24" s="6" t="n"/>
     </row>
     <row r="25" ht="112.5" customHeight="1" s="13">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>BEKLEMEDE</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>video_21.mp4</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C25" s="18" t="inlineStr">
         <is>
           <t>Vücudundaki Bakteriler Hücrelerinden FAZLA! 🦠⚖️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D25" s="18" t="inlineStr">
         <is>
           <t>Sende yaklaşık 38 trilyon bakteri var — insan hücrelerinden (30 trilyon) daha fazla! Ama korkma: toplam ağırlıkları 200 gram ve çoğu kahramanın: sindirimi yapıyor, bağışıklığını eğitiyor, vitamin üretiyor. Sen aslında yürüyen bir ekosistemsin!</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="E25" s="18" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #bilim</t>
         </is>
       </c>
-      <c r="F25" s="14" t="inlineStr">
+      <c r="F25" s="18" t="inlineStr">
         <is>
           <t>bilgidozu, bakteriler, mikrobiyom, biyoloji, vücut, bilim, shorts</t>
         </is>
       </c>
-      <c r="G25" s="14" t="inlineStr">
+      <c r="G25" s="18" t="inlineStr">
         <is>
           <t>Kilonun 200 gramı bakteriymiş 🦠 Diyet listesine bakterilerini de yaz! 😄👇</t>
         </is>
       </c>
-      <c r="H25" s="14" t="inlineStr">
+      <c r="H25" s="18" t="inlineStr">
         <is>
           <t>Biyoloji ve Vücut</t>
         </is>
       </c>
-      <c r="I25" s="14" t="inlineStr">
-        <is>
-          <t>Human Microbiome: https://en.wikipedia.org/wiki/Human_microbiome</t>
+      <c r="I25" s="18" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
         </is>
       </c>
       <c r="J25" s="5" t="n"/>
@@ -2244,49 +2253,49 @@
       <c r="AC25" s="6" t="n"/>
     </row>
     <row r="26" ht="112.5" customHeight="1" s="13">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">BEKLEMEDE </t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B26" s="18" t="inlineStr">
         <is>
           <t>video_22.mp4</t>
         </is>
       </c>
-      <c r="C26" s="14" t="inlineStr">
+      <c r="C26" s="18" t="inlineStr">
         <is>
           <t>Cam Akar mı? Efsane ÇÖKTÜ — Cam Bir Katıdır! 🪟❌ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D26" s="18" t="inlineStr">
         <is>
           <t>Eski binaların camlarının altta kalın olması 'cam akıyor' kanıtı değil — eski camlar düzensiz üretiliyordu! Cam bir amorf katı: molekülleri katı gibi sıkışık ama düzensiz dizili. Penceren binlerce yıl sonra da aynı yerde duracak!</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E26" s="18" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #bilim</t>
         </is>
       </c>
-      <c r="F26" s="14" t="inlineStr">
+      <c r="F26" s="18" t="inlineStr">
         <is>
           <t>bilgidozu, cam, fizik, kimya, efsaneavrı, malzeme, bilim, shorts</t>
         </is>
       </c>
-      <c r="G26" s="14" t="inlineStr">
+      <c r="G26" s="18" t="inlineStr">
         <is>
           <t>'Cam akar' diyene bu videoyu gönder 🪟😄 Kaç kişi bu efsaneye inanıyordu? 👇</t>
         </is>
       </c>
-      <c r="H26" s="14" t="inlineStr">
+      <c r="H26" s="18" t="inlineStr">
         <is>
           <t>Fizik ve Kimya</t>
         </is>
       </c>
-      <c r="I26" s="14" t="inlineStr">
-        <is>
-          <t>Glass (cam bir katıdır): https://en.wikipedia.org/wiki/Glass</t>
+      <c r="I26" s="18" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
         </is>
       </c>
       <c r="J26" s="5" t="n"/>
@@ -2311,49 +2320,49 @@
       <c r="AC26" s="6" t="n"/>
     </row>
     <row r="27" ht="112.5" customHeight="1" s="13">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>BEKLEMEDE</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t>video_23.mp4</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="18" t="inlineStr">
         <is>
           <t>Ay Her Yıl Bizden 3.8 cm Uzaklaşıyor! 🌙➡️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D27" s="18" t="inlineStr">
         <is>
           <t>Apollo astronotlarının Ay'a bıraktığı aynalara lazer atarak ölçüyoruz: Ay, Dünya'dan yılda ortalama 3.8 cm uzaklaşıyor! Milyonlarca yıl önce Ay gökyüzünde dev gibi görünüyordu — ve gelecekte çok daha küçük görünecek.</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E27" s="18" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
-      <c r="F27" s="14" t="inlineStr">
+      <c r="F27" s="18" t="inlineStr">
         <is>
           <t>bilgidozu, ay, uzay, nasa, astronomi, ilginçbilgiler, shorts</t>
         </is>
       </c>
-      <c r="G27" s="14" t="inlineStr">
+      <c r="G27" s="18" t="inlineStr">
         <is>
           <t>Dev Ay'lı bir gökyüzünde gece yürüyüşü... 🌙 Ne hissederdin? 👇</t>
         </is>
       </c>
-      <c r="H27" s="14" t="inlineStr">
+      <c r="H27" s="18" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I27" s="14" t="inlineStr">
-        <is>
-          <t>NASA — Moon Facts: https://science.nasa.gov/moon/facts/</t>
+      <c r="I27" s="18" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
         </is>
       </c>
       <c r="J27" s="5" t="n"/>
@@ -2378,49 +2387,49 @@
       <c r="AC27" s="6" t="n"/>
     </row>
     <row r="28" ht="112.5" customHeight="1" s="13">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">BEKLEMEDE </t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B28" s="18" t="inlineStr">
         <is>
           <t>video_24.mp4</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C28" s="18" t="inlineStr">
         <is>
           <t>Kedinin Miyavı Aslında Sadece SANA! 🐱💬 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D28" s="14" t="inlineStr">
+      <c r="D28" s="18" t="inlineStr">
         <is>
           <t>Yetişkin kediler birbirlerine neredeyse hiç miyavlamaz! Miyavlama, binlerce yıllık evcilleşmeyle insanla iletişim için gelişti. Yani kedin 'miyav' derken gerçekten SENİNLE konuşuyor — ve araştırmalar onun bu dili seni yönetmek için kullandığını gösteriyor!</t>
         </is>
       </c>
-      <c r="E28" s="14" t="inlineStr">
+      <c r="E28" s="18" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim</t>
         </is>
       </c>
-      <c r="F28" s="14" t="inlineStr">
+      <c r="F28" s="18" t="inlineStr">
         <is>
           <t>bilgidozu, kedi, hayvanlaralemi, evcilhayvan, iletişim, shorts</t>
         </is>
       </c>
-      <c r="G28" s="14" t="inlineStr">
+      <c r="G28" s="18" t="inlineStr">
         <is>
           <t>Kedin seninle mi konuşuyor, seni mi yönetiyor? 🐱😤 İtiraf et, yorumlara yaz! 👇</t>
         </is>
       </c>
-      <c r="H28" s="14" t="inlineStr">
+      <c r="H28" s="18" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I28" s="14" t="inlineStr">
-        <is>
-          <t>Cat communication (miyav): https://en.wikipedia.org/wiki/Cat_communication</t>
+      <c r="I28" s="18" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
         </is>
       </c>
       <c r="J28" s="5" t="n"/>
@@ -2445,49 +2454,49 @@
       <c r="AC28" s="6" t="n"/>
     </row>
     <row r="29" ht="112.5" customHeight="1" s="13">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>BEKLEMEDE</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B29" s="18" t="inlineStr">
         <is>
           <t>video_25.mp4</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C29" s="18" t="inlineStr">
         <is>
           <t>Şu An Saniyede 30 km Hızla Uçuyorsun — ve Hissetmiyorsun! 🌍💨 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D29" s="14" t="inlineStr">
+      <c r="D29" s="18" t="inlineStr">
         <is>
           <t>Dünya, seni taşıyarak Güneş etrafında saniyede 30 km — saatte 107.000 km — hızla dolandır: bir kurşundan 40 kat hızlı! Ama neden hissetmiyorsun? Çünkü hız tek başına hissettirmez — sadece hız DEĞİŞİMİ hissedersin. Koltuğunda otururken dev bir roketle evreni geziyorsun!</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
+      <c r="E29" s="18" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #bilim</t>
         </is>
       </c>
-      <c r="F29" s="14" t="inlineStr">
+      <c r="F29" s="18" t="inlineStr">
         <is>
           <t>bilgidozu, dünya, uzay, fizik, hız, ilginçbilgiler, shorts</t>
         </is>
       </c>
-      <c r="G29" s="14" t="inlineStr">
+      <c r="G29" s="18" t="inlineStr">
         <is>
           <t>Saatte 107.000 km hızda yolcu sensin 🚀 'Bunu bilmiyordum' diyenler 1 yazsın! 👇</t>
         </is>
       </c>
-      <c r="H29" s="14" t="inlineStr">
+      <c r="H29" s="18" t="inlineStr">
         <is>
           <t>Fizik ve Uzay</t>
         </is>
       </c>
-      <c r="I29" s="14" t="inlineStr">
-        <is>
-          <t>NASA — Earth Facts: https://science.nasa.gov/earth/facts/</t>
+      <c r="I29" s="18" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
         </is>
       </c>
       <c r="J29" s="5" t="n"/>
@@ -2512,49 +2521,49 @@
       <c r="AC29" s="6" t="n"/>
     </row>
     <row r="30" ht="112.5" customHeight="1" s="13">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">BEKLEMEDE </t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B30" s="18" t="inlineStr">
         <is>
           <t>video_26.mp4</t>
         </is>
       </c>
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C30" s="18" t="inlineStr">
         <is>
           <t>3000 Yıllık Bal Hâlâ Yenilebilir! 🍯🏛️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D30" s="14" t="inlineStr">
+      <c r="D30" s="18" t="inlineStr">
         <is>
           <t>Arkeologlar Mısır mezarlarında 3000 yıllık bal kavanozları buldu — bozulmamıştı! Balın nemi çeken yapısı, asiditesi ve hidrojen peroksiti bakterileri yaşamaz ediyor: doğru saklanırsa bal sonsuza kadar dayanır. Mutfağındaki bal da 'son kullanma tarihi' tanımıyor!</t>
         </is>
       </c>
-      <c r="E30" s="14" t="inlineStr">
+      <c r="E30" s="18" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #bilim</t>
         </is>
       </c>
-      <c r="F30" s="14" t="inlineStr">
+      <c r="F30" s="18" t="inlineStr">
         <is>
           <t>bilgidozu, bal, gıda, arkeoloji, ilginçbilgiler, bilim, shorts</t>
         </is>
       </c>
-      <c r="G30" s="14" t="inlineStr">
+      <c r="G30" s="18" t="inlineStr">
         <is>
           <t>Pantry'de 3000 yıllık bal olsa yer miydin? 🍯😄 Cesur olanlar 1! 👇</t>
         </is>
       </c>
-      <c r="H30" s="14" t="inlineStr">
+      <c r="H30" s="18" t="inlineStr">
         <is>
           <t>Biyoloji ve Gıda</t>
         </is>
       </c>
-      <c r="I30" s="14" t="inlineStr">
-        <is>
-          <t>Honey (raf ömrü): https://en.wikipedia.org/wiki/Honey</t>
+      <c r="I30" s="18" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
         </is>
       </c>
       <c r="J30" s="5" t="n"/>
@@ -2579,49 +2588,49 @@
       <c r="AC30" s="6" t="n"/>
     </row>
     <row r="31" ht="112.5" customHeight="1" s="13">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>BEKLEMEDE</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B31" s="18" t="inlineStr">
         <is>
           <t>video_27.mp4</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr">
+      <c r="C31" s="18" t="inlineStr">
         <is>
           <t>Ayağının Altında Güneş Kadar Sıcak Bir Top Var! 🌍🔥 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D31" s="14" t="inlineStr">
+      <c r="D31" s="18" t="inlineStr">
         <is>
           <t>Dünya'nın iç çekirdeği yaklaşık 5.400°C — Güneş'in YÜZEYİYLE aynı sıcaklık! 5.000 km derinlikteki bu demir-nikel top, manyetik kalkanımızı besliyor. Yani sen, bir yıldız yüzeyi sıcaklığında bir kalbin üstünde yaşıyorsun!</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="E31" s="18" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #bilim</t>
         </is>
       </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="F31" s="18" t="inlineStr">
         <is>
           <t>bilgidozu, dünya, jeoloji, çekirdek, bilim, ilginçbilgiler, shorts</t>
         </is>
       </c>
-      <c r="G31" s="14" t="inlineStr">
+      <c r="G31" s="18" t="inlineStr">
         <is>
           <t>Ayağının altında Güneş yüzeyi sıcaklığında bir çekirdek var 🔥 'Bunu bilmiyordum' diyenler? 👇</t>
         </is>
       </c>
-      <c r="H31" s="14" t="inlineStr">
+      <c r="H31" s="18" t="inlineStr">
         <is>
           <t>Yer Bilimleri</t>
         </is>
       </c>
-      <c r="I31" s="14" t="inlineStr">
-        <is>
-          <t>Earth's inner core: https://en.wikipedia.org/wiki/Earth%27s_inner_core</t>
+      <c r="I31" s="18" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
         </is>
       </c>
       <c r="J31" s="5" t="n"/>
@@ -2646,49 +2655,49 @@
       <c r="AC31" s="6" t="n"/>
     </row>
     <row r="32" ht="112.5" customHeight="1" s="13">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">BEKLEMEDE </t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B32" s="18" t="inlineStr">
         <is>
           <t>video_28.mp4</t>
         </is>
       </c>
-      <c r="C32" s="14" t="inlineStr">
+      <c r="C32" s="18" t="inlineStr">
         <is>
           <t>Filler AYAKLARIYLA Duyar — Topraktan Mesaj Gelir! 🐘📡 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D32" s="14" t="inlineStr">
+      <c r="D32" s="18" t="inlineStr">
         <is>
           <t>Filler sadece hortumuyla değil, AYAKLARIYLA da 'dinler': verdikleri derin gümbürtüler toprağı titreştirip kilometrelerce öteye ulaşır — uzaktaki fil bunu ayak tabanındaki yağ yastıklarıyla hisseder! Sürünün gizli toprak-altı mesajlaşma ağı var.</t>
         </is>
       </c>
-      <c r="E32" s="14" t="inlineStr">
+      <c r="E32" s="18" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim</t>
         </is>
       </c>
-      <c r="F32" s="14" t="inlineStr">
+      <c r="F32" s="18" t="inlineStr">
         <is>
           <t>bilgidozu, fil, hayvanlaralemi, iletişim, doğa, bilim, shorts</t>
         </is>
       </c>
-      <c r="G32" s="14" t="inlineStr">
+      <c r="G32" s="18" t="inlineStr">
         <is>
           <t>Filler topraktan mesajlaşırken biz 5G peşindeyiz 🐘📶😄 En şaşırtıcı bilgi miydi? 1 yazsın!</t>
         </is>
       </c>
-      <c r="H32" s="14" t="inlineStr">
+      <c r="H32" s="18" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I32" s="14" t="inlineStr">
-        <is>
-          <t>Elephant cognition (sismik iletişim): https://en.wikipedia.org/wiki/Elephant_cognition</t>
+      <c r="I32" s="18" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
         </is>
       </c>
       <c r="J32" s="5" t="n"/>
@@ -2713,49 +2722,49 @@
       <c r="AC32" s="6" t="n"/>
     </row>
     <row r="33" ht="112.5" customHeight="1" s="13">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>BEKLEMEDE</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B33" s="18" t="inlineStr">
         <is>
           <t>video_29.mp4</t>
         </is>
       </c>
-      <c r="C33" s="14" t="inlineStr">
+      <c r="C33" s="18" t="inlineStr">
         <is>
           <t>Bu Gezegen YAN YATIK Döner — Gecesi 42 Yıl! 🪐🪑 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D33" s="14" t="inlineStr">
+      <c r="D33" s="18" t="inlineStr">
         <is>
           <t>Uranüs'ün dönme ekseni 98 derece eğik: gezegen neredeyse yan yatmış halde yuvarlanır! Kutuplarında bir gündüz veya gece 42 DÜNYA YILI sürer. Bilim insanları bunun sebebinin geçmişte dev bir cismin çarpması olduğunu düşünüyor.</t>
         </is>
       </c>
-      <c r="E33" s="14" t="inlineStr">
+      <c r="E33" s="18" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
-      <c r="F33" s="14" t="inlineStr">
+      <c r="F33" s="18" t="inlineStr">
         <is>
           <t>bilgidozu, uranus, uzay, gezegenler, astronomi, shorts</t>
         </is>
       </c>
-      <c r="G33" s="14" t="inlineStr">
+      <c r="G33" s="18" t="inlineStr">
         <is>
           <t>42 yıllık bir karanlık gecede ne yapardın? 🌌😄 En yaratık cevabı sabitlerim! 👇</t>
         </is>
       </c>
-      <c r="H33" s="14" t="inlineStr">
+      <c r="H33" s="18" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I33" s="14" t="inlineStr">
-        <is>
-          <t>NASA — Uranus Facts: https://science.nasa.gov/uranus/facts/</t>
+      <c r="I33" s="18" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
         </is>
       </c>
       <c r="J33" s="5" t="n"/>
@@ -2780,49 +2789,49 @@
       <c r="AC33" s="6" t="n"/>
     </row>
     <row r="34" ht="112.5" customHeight="1" s="13">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">BEKLEMEDE </t>
         </is>
       </c>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B34" s="18" t="inlineStr">
         <is>
           <t>video_30.mp4</t>
         </is>
       </c>
-      <c r="C34" s="14" t="inlineStr">
+      <c r="C34" s="18" t="inlineStr">
         <is>
           <t>Beynin Sadece %10'unu Kullandığın YALAN! İşte Kanıtı! 🧠❌ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D34" s="14" t="inlineStr">
+      <c r="D34" s="18" t="inlineStr">
         <is>
           <t>'İnsan beyninin sadece %10'unu kullanır' dedikodusu tam bir şehir efsanesi — beyin görüntüleme bunu çökertti: gün içinde beyninin neredeyse TAMAMI aktif, uykuda bile! Efsanenin kökeni 1900'lerin başındaki motivasyon konuşmaları. Yani kötü haber: daha kullanmadığın bir bölüm yok — zaten %100'ünle çalışıyorsun!</t>
         </is>
       </c>
-      <c r="E34" s="14" t="inlineStr">
+      <c r="E34" s="18" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #beyin #psikoloji</t>
         </is>
       </c>
-      <c r="F34" s="14" t="inlineStr">
+      <c r="F34" s="18" t="inlineStr">
         <is>
           <t>bilgidozu, beyin, efsaneavrı, nörobilim, psikoloji, bilim, shorts</t>
         </is>
       </c>
-      <c r="G34" s="14" t="inlineStr">
+      <c r="G34" s="18" t="inlineStr">
         <is>
           <t>'%10' efsanesine inananlar 1, şüpheci olanlar 2! 😄 Gerçek cevap yorumlarda! 👇</t>
         </is>
       </c>
-      <c r="H34" s="14" t="inlineStr">
+      <c r="H34" s="18" t="inlineStr">
         <is>
           <t>Beyin ve Psikoloji</t>
         </is>
       </c>
-      <c r="I34" s="14" t="inlineStr">
-        <is>
-          <t>Ten percent of brain myth: https://en.wikipedia.org/wiki/Ten_percent_of_brain_myth</t>
+      <c r="I34" s="18" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
         </is>
       </c>
       <c r="J34" s="5" t="n"/>

--- a/bilgidozu_yukleme_tablosu.xlsx
+++ b/bilgidozu_yukleme_tablosu.xlsx
@@ -530,7 +530,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AC112"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" style="13" min="1" max="1"/>
     <col width="22.86" customWidth="1" style="13" min="2" max="2"/>
@@ -3504,54 +3504,62 @@
       <c r="AC39" s="6" t="n"/>
     </row>
     <row r="40" ht="112.5" customHeight="1" s="13">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BEKLEMEDE </t>
-        </is>
-      </c>
-      <c r="B40" s="14" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>video_33.mp4</t>
         </is>
       </c>
-      <c r="C40" s="14" t="inlineStr">
+      <c r="C40" s="16" t="inlineStr">
         <is>
           <t>Kendini Neden Gıdıklayamazsın? Beynin Hamleni Önceden Biliyor! 🧠🤭 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D40" s="14" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>Başka biri dokunduğunda kolayca gıdıklanırken kendi kendini gıdıklayamamanın sebebi beyinciktir! Beyincik, kendi el hareketini saliseler öncesinden tahmin ederek duyusal kortekse 'bu tehdit değil, kendi dokunuşun' sinyali gönderir ve gıdıklanma tepkisini otomatik olarak bastırır.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E40" s="14" t="inlineStr">
+      <c r="E40" s="16" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #beyin #psikoloji</t>
         </is>
       </c>
-      <c r="F40" s="14" t="inlineStr">
+      <c r="F40" s="16" t="inlineStr">
         <is>
           <t>bilgidozu, gıdıklanma, beyin, beyincik, nörobilim, psikoloji, ilginçbilgiler, bilim, shorts</t>
         </is>
       </c>
-      <c r="G40" s="14" t="inlineStr">
+      <c r="G40" s="16" t="inlineStr">
         <is>
           <t>Biri dokununca çok gıdıklananlardan mısın? 😄🤭 Evet diyenler '1', bana işlemez diyenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H40" s="14" t="inlineStr">
+      <c r="H40" s="16" t="inlineStr">
         <is>
           <t>Beyin ve Psikoloji</t>
         </is>
       </c>
-      <c r="I40" s="14" t="inlineStr">
+      <c r="I40" s="16" t="inlineStr">
         <is>
           <t>Wikipedia — Tickling (Self-tickling): https://en.wikipedia.org/wiki/Tickling</t>
         </is>
       </c>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="n"/>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/sh9zYFybcHY</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23 21:24</t>
+        </is>
+      </c>
       <c r="L40" s="5" t="n"/>
       <c r="M40" s="6" t="n"/>
       <c r="N40" s="6" t="n"/>
@@ -8414,6 +8422,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8429,136 +8438,136 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>İşçi Adı</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>Durum</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="0" t="inlineStr">
         <is>
           <t>Son Güncelleme Zamanı</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="0" t="inlineStr">
         <is>
           <t>Son Hata Mesajı</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="0" t="inlineStr">
         <is>
           <t>Kaç İş Yaptı</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t>Son İşlem Özeti</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>Yükleyici (Drive -&gt; YouTube)</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>Çalışıyor</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>2026-10-23 18:29</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="n">
+      <c r="D2" s="0" t="inlineStr"/>
+      <c r="E2" s="0" t="n">
         <v>54</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>video_32.mp4 yayınlandı (https://youtu.be/mANNR6Tf21o)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>Yorumcu &amp; Kapak İşçisi (OAuth)</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>Çalışıyor</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>2026-10-23 21:15</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="n">
+      <c r="D3" s="0" t="inlineStr"/>
+      <c r="E3" s="0" t="n">
         <v>54</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>Tam yetkili OAuth (youtube.force-ssl + drive + sheets) bağlandı ve aktif</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>Analitik Çekici (YouTube API)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>Çalışıyor</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>2026-10-23 21:15</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="n">
+      <c r="D4" s="0" t="inlineStr"/>
+      <c r="E4" s="0" t="n">
         <v>58</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>58 videonun gerçek görüntülenme (33457) ve yorum verisi çekildi</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>Telegram Bildirim İşçisi</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>Çalışıyor</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>2026-10-23 18:29</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="n">
+      <c r="D5" s="0" t="inlineStr"/>
+      <c r="E5" s="0" t="n">
         <v>22</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="0" t="inlineStr">
         <is>
           <t>video_32.mp4 yayın kartı ve sabit yorum metni gönderildi</t>
         </is>
@@ -8579,108 +8588,108 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>Kontrol Noktası</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>Durum</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="0" t="inlineStr">
         <is>
           <t>Seviye</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="0" t="inlineStr">
         <is>
           <t>Son Kontrol</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="0" t="inlineStr">
         <is>
           <t>Detay ve Çözüm</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>YouTube API Günlük Kotası</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>Sorunsuz</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>Yeşil</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>2026-10-23 21:15</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
           <t>Günlük 10.000 birim kotası aktif ve yeterli.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>Google Drive &amp; Sheets Senkronu</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>Sorunsuz</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>Yeşil</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>2026-10-23 21:15</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>Drive video klasörü (82 dosya) ve 3 sekmeli yükleme tablosu canlı bağlı.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>Yorum &amp; Kapak İşçisi (force-ssl)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>Sorunsuz</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>Yeşil</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>2026-10-23 21:15</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>youtube.force-ssl yetkisi onaylandı; otomatik ilk yorum ve kapak giydirme hazır.</t>
         </is>

--- a/bilgidozu_yukleme_tablosu.xlsx
+++ b/bilgidozu_yukleme_tablosu.xlsx
@@ -529,8 +529,8 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC112"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1" outlineLevelCol="0"/>
+  <dimension ref="A1:AC133"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="18" customWidth="1" style="13" min="1" max="1"/>
     <col width="22.86" customWidth="1" style="13" min="2" max="2"/>
@@ -8221,27 +8221,1065 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="112.5" customHeight="1" s="13"/>
-    <row r="114" ht="112.5" customHeight="1" s="13"/>
-    <row r="115" ht="112.5" customHeight="1" s="13"/>
-    <row r="116" ht="112.5" customHeight="1" s="13"/>
-    <row r="117" ht="112.5" customHeight="1" s="13"/>
-    <row r="118" ht="112.5" customHeight="1" s="13"/>
-    <row r="119" ht="112.5" customHeight="1" s="13"/>
-    <row r="120" ht="112.5" customHeight="1" s="13"/>
-    <row r="121" ht="112.5" customHeight="1" s="13"/>
-    <row r="122" ht="112.5" customHeight="1" s="13"/>
-    <row r="123" ht="112.5" customHeight="1" s="13"/>
-    <row r="124" ht="112.5" customHeight="1" s="13"/>
-    <row r="125" ht="112.5" customHeight="1" s="13"/>
-    <row r="126" ht="112.5" customHeight="1" s="13"/>
-    <row r="127" ht="112.5" customHeight="1" s="13"/>
-    <row r="128" ht="112.5" customHeight="1" s="13"/>
-    <row r="129" ht="112.5" customHeight="1" s="13"/>
-    <row r="130" ht="112.5" customHeight="1" s="13"/>
-    <row r="131" ht="112.5" customHeight="1" s="13"/>
-    <row r="132" ht="112.5" customHeight="1" s="13"/>
-    <row r="133" ht="112.5" customHeight="1" s="13"/>
+    <row r="113" ht="112.5" customHeight="1" s="13">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>video_101.mp4</t>
+        </is>
+      </c>
+      <c r="C113" s="14" t="inlineStr">
+        <is>
+          <t>Güneş Bir Saniyeliğine Sönseydi Ne Olurdu? ☀️🌑 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D113" s="14" t="inlineStr">
+        <is>
+          <t>Şu an başını kaldırıp gökyüzüne baktığında, Güneş'in hâlâ orada olduğundan gerçekten emin misin? Ya tam şu saniye sessizce söndüyse? İşin en ürpertici kısmı ne biliyor musun? Bunu tam sekiz dakika yirmi saniye boyunca ruhun bile duymayacak. Çünkü Güneş'ten çıkan son ışık gözüne ulaşana kadar gökyüzü masmavi kalır. Ama sekizinci dakikanın sonunda gökyüzü bir anda zifiri karanlığa gömülür ve Dünya yörüngeden kopup buzlu boşluğa savrulur. Peki sen o son sekiz dakikayı dışarıda gökyüzünü izleyerek mi geçirirdin, yoksa yeraltı sığınaklarına inerek mi? Yorumlarda buluşalım.
+Peki böyle bir kırılma anında sen sekiz dakikalık son gün ışığını dışarıda izlemeyi mi seçerdin, yoksa doğrudan yeraltı sığınaklarına inmeyi mi? Yorumlarda buluşalım! 👇
+📚 Kaynak: https://en.wikipedia.org/wiki/Sunlight
+🎨 Görseller temsilîdir (AI üretimi ve NASA/ESO uzay arşivi).
+#bilgidozu #shorts #uzay #bilim</t>
+        </is>
+      </c>
+      <c r="E113" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #uzay #bilim</t>
+        </is>
+      </c>
+      <c r="F113" s="14" t="inlineStr">
+        <is>
+          <t>bilgi dozu, güneş, uzay, kozmik felaket, astronomi, bilim, dünya, ışık hızı, ilginç bilgiler, shorts</t>
+        </is>
+      </c>
+      <c r="G113" s="14" t="inlineStr">
+        <is>
+          <t>Peki böyle bir kırılma anında sen sekiz dakikalık son gün ışığını dışarıda izlemeyi mi seçerdin, yoksa doğrudan yeraltı sığınaklarına inmeyi mi? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H113" s="14" t="inlineStr">
+        <is>
+          <t>Uzay ve Astronomi</t>
+        </is>
+      </c>
+      <c r="I113" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Sunlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="112.5" customHeight="1" s="13">
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t>video_102.mp4</t>
+        </is>
+      </c>
+      <c r="C114" s="14" t="inlineStr">
+        <is>
+          <t>Ay Dünya'ya Yaklaşsaydı Okyanuslara Ne Olurdu? 🌕🌊 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D114" s="14" t="inlineStr">
+        <is>
+          <t>Gece gökyüzüne baktığında, Ay'ın hep aynı yerde durduğunu sanıyorsun değil mi? Peki ya Ay Dünya'ya doğru yaklaşmaya başlasaydı ne olurdu? İlk başta gökyüzünde devasa görünürdü ama hemen ardından kütle çekim kabusu başlardı. Okyanuslar yüzlerce metre yükselip kıyı şehirlerini yutardı. Dünya'ya on sekiz bin kilometre mesafedeki Roche sınırına girdiği anda ise Ay gökyüzünde paramparça olur ve Dünya'nın etrafında tıpkı Satürn gibi parlak bir halka oluştururdu. Peki sen gökyüzünde Satürn gibi dev bir halka görmeyi mi isterdin, yoksa Ay'ın olduğu yerde kalmasını mı? Yorumlarda buluşalım.
+Peki sen gökyüzünde dev bir Ay yerine Satürn gibi muazzam bir halka görmeyi mi isterdin, yoksa Ay'ın olduğu yerde kalmasını mı? Yorumlarda buluşalım! 👇
+📚 Kaynak: https://en.wikipedia.org/wiki/Roche_limit
+🎨 Görseller temsilîdir (AI üretimi ve NASA/ESO uzay arşivi).
+#bilgidozu #shorts #uzay #bilim</t>
+        </is>
+      </c>
+      <c r="E114" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #uzay #bilim</t>
+        </is>
+      </c>
+      <c r="F114" s="14" t="inlineStr">
+        <is>
+          <t>bilgi dozu, ay, dünya, roche sınırı, satürn, uzay, astronomi, bilim, kozmik felaket, shorts</t>
+        </is>
+      </c>
+      <c r="G114" s="14" t="inlineStr">
+        <is>
+          <t>Peki sen gökyüzünde dev bir Ay yerine Satürn gibi muazzam bir halka görmeyi mi isterdin, yoksa Ay'ın olduğu yerde kalmasını mı? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H114" s="14" t="inlineStr">
+        <is>
+          <t>Uzay ve Astronomi</t>
+        </is>
+      </c>
+      <c r="I114" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Roche_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="112.5" customHeight="1" s="13">
+      <c r="A115" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t>video_103.mp4</t>
+        </is>
+      </c>
+      <c r="C115" s="14" t="inlineStr">
+        <is>
+          <t>Uzayda Ağlarsan Gözyaşların Neden Yanağından Akmaz? 🧑‍🚀💧 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D115" s="14" t="inlineStr">
+        <is>
+          <t>Uzayda tek başına süzülürken bir anda ağlamaya başlasan gözyaşlarının yanağından aşağı süzüleceğini mi sanıyorsun? Hiç de öyle olmaz. Dünya'da gözyaşını aşağı çeken şey yerçekimidir. Ama uzayın ağırlıksız boşluğunda, su moleküllerini birbirine kenetleyen yüzey gerilimi tek patron haline gelir. Gözünden çıkan her damla, akmak yerine göz pınarının tam üzerinde şeffaf, titreyen bir su küresine dönüşür ve sen bir bezle silene kadar yüzünden asla ayrılmaz. Peki sen yerçekimsiz ortamda yaşamayı deneyimlemek mi isterdin, yoksa ayağının yere bastığı Dünya'da kalmayı mı? Yorumlarda buluşalım.
+Peki sen yerçekimsiz ortamda haftalarca yaşamayı deneyimlemek mi isterdin, yoksa ayağının sağlamca yere bastığı Dünya'da kalmayı mı? Yorumlarda buluşalım! 👇
+📚 Kaynak: https://en.wikipedia.org/wiki/Surface_tension
+🎨 Görseller temsilîdir (AI üretimi ve NASA/ESO uzay arşivi).
+#bilgidozu #shorts #uzay #bilim</t>
+        </is>
+      </c>
+      <c r="E115" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #uzay #bilim</t>
+        </is>
+      </c>
+      <c r="F115" s="14" t="inlineStr">
+        <is>
+          <t>bilgi dozu, uzay, astronot, yerçekimi, yüzey gerilimi, bilim, fizik, uzay istasyonu, ilginç bilgiler, shorts</t>
+        </is>
+      </c>
+      <c r="G115" s="14" t="inlineStr">
+        <is>
+          <t>Peki sen yerçekimsiz ortamda haftalarca yaşamayı deneyimlemek mi isterdin, yoksa ayağının sağlamca yere bastığı Dünya'da kalmayı mı? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H115" s="14" t="inlineStr">
+        <is>
+          <t>Uzay ve Astronomi</t>
+        </is>
+      </c>
+      <c r="I115" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Surface_tension</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="112.5" customHeight="1" s="13">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="inlineStr">
+        <is>
+          <t>video_104.mp4</t>
+        </is>
+      </c>
+      <c r="C116" s="14" t="inlineStr">
+        <is>
+          <t>Dünya'ya 50 Işık Yılı Mesafede Süpernova Patlasa Ne Olur? 💥🌟 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D116" s="14" t="inlineStr">
+        <is>
+          <t>Gündüz vakti masmavi gökyüzünde bir anda ikinci bir Güneş'in parladığını hayal et. Dünya'ya elli ışık yılı mesafede dev bir yıldız süpernova olarak patlasaydı tam olarak bunu yaşardık. Haftalarca geceleri bile gökyüzü hiç kararmazdı. Ama asıl tehlike o parlak ışık değil, görünmez gama ışınları olurdu. Üst atmosferdeki ozon tabakası hızla erir ve yüzeye inen radyasyon okyanuslardaki besin zincirini altüst ederdi. Peki böyle bir kozmik patlama görsen, önce teleskopla izlemeye mi koşardın yoksa radyasyondan korunacak bir yer mi arardın? Yorumlarda buluşalım.
+Peki böyle bir kozmik patlama görsen önce teleskopla izlemeye mi koşardın, yoksa radyasyondan korunacak bir yer mi arardın? Yorumlarda buluşalım! 👇
+📚 Kaynak: https://en.wikipedia.org/wiki/Near-Earth_supernova
+🎨 Görseller temsilîdir (AI üretimi ve NASA/ESO uzay arşivi).
+#bilgidozu #shorts #uzay #bilim</t>
+        </is>
+      </c>
+      <c r="E116" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #uzay #bilim</t>
+        </is>
+      </c>
+      <c r="F116" s="14" t="inlineStr">
+        <is>
+          <t>bilgi dozu, süpernova, uzay, gama ışınları, kozmik felaket, yıldız, astronomi, bilim, dünya, shorts</t>
+        </is>
+      </c>
+      <c r="G116" s="14" t="inlineStr">
+        <is>
+          <t>Peki böyle bir kozmik patlama görsen önce teleskopla izlemeye mi koşardın, yoksa radyasyondan korunacak bir yer mi arardın? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H116" s="14" t="inlineStr">
+        <is>
+          <t>Uzay ve Astronomi</t>
+        </is>
+      </c>
+      <c r="I116" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Near-Earth_supernova</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="112.5" customHeight="1" s="13">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B117" s="11" t="inlineStr">
+        <is>
+          <t>video_105.mp4</t>
+        </is>
+      </c>
+      <c r="C117" s="14" t="inlineStr">
+        <is>
+          <t>Bir Çay Kaşığı Nötron Yıldızı Dünya'ya Düşse Ne Olur? 🥄🌌 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D117" s="14" t="inlineStr">
+        <is>
+          <t>Elindeki küçücük bir çay kaşığının Everest Dağı kadar ağır olabileceğini hayal edebilir misin? Evrenin en ekstrem canavarı olan nötron yıldızlarıyla tanış. Dev bir yıldız çöktüğünde çekirdeği o kadar korkunç sıkışır ki, koca bir Güneş sadece yirmi kilometre çapında bir küreye hapsolur. Bu yıldızdan alacağın tek bir çay kaşığı madde tam bir milyar ton ağırlığındadır. Onu Dünya'da elinden bıraksan toprağı ve kayaları delip doğrudan gezegenin çekirdeğine kadar batardı. Peki seni uzayda en çok büyüleyen şey, kara delikler mi yoksa nötron yıldızları mı? Yorumlarda buluşalım.
+Peki seni uzayda en çok büyüleyen şey her şeyi yutan kara delikler mi, yoksa bu inanılmaz yoğunluktaki nötron yıldızları mı? Yorumlarda buluşalım! 👇
+📚 Kaynak: https://en.wikipedia.org/wiki/Neutron_star
+🎨 Görseller temsilîdir (AI üretimi ve NASA/ESO uzay arşivi).
+#bilgidozu #shorts #uzay #bilim</t>
+        </is>
+      </c>
+      <c r="E117" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #uzay #bilim</t>
+        </is>
+      </c>
+      <c r="F117" s="14" t="inlineStr">
+        <is>
+          <t>bilgi dozu, nötron yıldızı, kara delik, uzay, astronomi, fizik, bilim, evren, ilginç bilgiler, shorts</t>
+        </is>
+      </c>
+      <c r="G117" s="14" t="inlineStr">
+        <is>
+          <t>Peki seni uzayda en çok büyüleyen şey her şeyi yutan kara delikler mi, yoksa bu inanılmaz yoğunluktaki nötron yıldızları mı? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H117" s="14" t="inlineStr">
+        <is>
+          <t>Uzay ve Astronomi</t>
+        </is>
+      </c>
+      <c r="I117" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Neutron_star</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="112.5" customHeight="1" s="13">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B118" s="11" t="inlineStr">
+        <is>
+          <t>video_106.mp4</t>
+        </is>
+      </c>
+      <c r="C118" s="14" t="inlineStr">
+        <is>
+          <t>Kendi Sesini Kayıtta Dinleyince Neden Tuhaf Gelir? 🎙️🧠 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D118" s="14" t="inlineStr">
+        <is>
+          <t>Bir ses kaydında kendi sesini duyduğun an “Bu gerçekten benim sesim mi?” diye yüzünü buruşturduğun oldu mu? Merak etme, yalnız değilsin. Sen konuşurken sesini iki farklı yoldan aynı anda duyarsın. Hem havadan kulağına gelen dalgalarla, hem de ses tellerinin kafatası kemiklerini titreştirerek iç kulağına gönderdiği kemik iletimiyle. Kafatası kemiklerin bas frekansları güçlendirdiği için kendi sesini hep daha tok ve derin algılarsın. Ama kayıtta, kemik iletimi devreden çıkar ve başkalarının duyduğu o gerçek sesine yüzleşirsin. Peki sen kayıtlarda kendi sesini dinlemeye alışabildin mi, yoksa duyunca hemen kapatıyor musun? Yorumlarda buluşalım.
+Kaynak: https://en.wikipedia.org/wiki/Bone_conduction</t>
+        </is>
+      </c>
+      <c r="E118" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
+        </is>
+      </c>
+      <c r="F118" s="14" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, nörobilim, insan bedeni, psikoloji, bilim</t>
+        </is>
+      </c>
+      <c r="G118" s="14" t="inlineStr">
+        <is>
+          <t>Peki sen kendi sesini kayıtlarda dinlemeye alışabildin mi, yoksa duyunca hâlâ hemen kapatıyor musun? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H118" s="14" t="inlineStr">
+        <is>
+          <t>Nörobilim ve İnsan Bedeni</t>
+        </is>
+      </c>
+      <c r="I118" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Bone_conduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="112.5" customHeight="1" s="13">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B119" s="11" t="inlineStr">
+        <is>
+          <t>video_107.mp4</t>
+        </is>
+      </c>
+      <c r="C119" s="14" t="inlineStr">
+        <is>
+          <t>Yüksek Bir Yerden Bakınca Beyin Neden 'Atla' Diye Fısıldar? 🧗‍♂️🧠 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D119" s="14" t="inlineStr">
+        <is>
+          <t>Yüksek bir balkonun ya da uçurumun kenarından aşağı baktığında içinde hiçbir kötü niyet yokken bile bir anda “Ya şimdi atlarsam” diye ürpertici bir düşünce geçti mi? Fransızların “boşluğun çağrısı” dediği bu durum aslında beyninin aşırı hızlı çalışan bir hayatta kalma alarmıdır. Beynin kenara yaklaştığında denge merkezine “Geri çekil, tehlikedesin” sinyali gönderir. Bilinçli zihnin ise bu ani geri çekilme refleksini sanki aşağı atlamak istemişim de kendimi zor tutmuşum gibi yanlış yorumlar. Peki sen yüksek bir yerden aşağı baktığında o ürpertiyi hissediyor musun, yoksa yüksekten hiç etkilenmeyenlerden misin? Yorumlarda buluşalım.
+Kaynak: https://en.wikipedia.org/wiki/The_imp_of_the_perverse</t>
+        </is>
+      </c>
+      <c r="E119" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
+        </is>
+      </c>
+      <c r="F119" s="14" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, nörobilim, insan bedeni, psikoloji, bilim</t>
+        </is>
+      </c>
+      <c r="G119" s="14" t="inlineStr">
+        <is>
+          <t>Peki sen yüksek bir yerden aşağı baktığında o ürpertiyi hissediyor musun, yoksa yüksekten hiç etkilenmeyenlerden misin? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H119" s="14" t="inlineStr">
+        <is>
+          <t>Nörobilim ve İnsan Bedeni</t>
+        </is>
+      </c>
+      <c r="I119" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/The_imp_of_the_perverse</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="112.5" customHeight="1" s="13">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t>video_108.mp4</t>
+        </is>
+      </c>
+      <c r="C120" s="14" t="inlineStr">
+        <is>
+          <t>Acı Biber Aslında Ağzını Yakmaz — Beynini Nasıl Kandırır? 🌶️🔥 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D120" s="14" t="inlineStr">
+        <is>
+          <t>Çok acı bir biber ısırdığında ağzının alev alev yandığını hissediyorsun ya, sana dilinin aslında hiç yanmadığını, tamamen beyninin kandırıldığını söylesem? Biberin içindeki kapsaisin molekülü dokularına fiziksel bir zarar vermez. Sadece dilindeki 43 derecenin üzerindeki sıcaklıklarda açılan ısı alıcılarına gizlice kilitlenir ve beynine ağzın kaynar suyla yanıyor diye sahte bir alarm gönderir. Üstelik kapsaisin suda çözünmediği için su içmek yangını ağzının her yerine yayar. Peki acı yediğinde senin ilk refleksin soğuk suya sarılmak mı oluyor, yoksa ayrana koşmak mı? Yorumlarda buluşalım.
+Kaynak: https://en.wikipedia.org/wiki/Capsaicin</t>
+        </is>
+      </c>
+      <c r="E120" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
+        </is>
+      </c>
+      <c r="F120" s="14" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, nörobilim, insan bedeni, psikoloji, bilim</t>
+        </is>
+      </c>
+      <c r="G120" s="14" t="inlineStr">
+        <is>
+          <t>Peki acı yediğinde senin ilk refleksin soğuk suya sarılmak mı oluyor, yoksa yoğurt ve ayrana koşmak mı? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H120" s="14" t="inlineStr">
+        <is>
+          <t>Nörobilim ve İnsan Bedeni</t>
+        </is>
+      </c>
+      <c r="I120" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Capsaicin</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="112.5" customHeight="1" s="13">
+      <c r="A121" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t>video_109.mp4</t>
+        </is>
+      </c>
+      <c r="C121" s="14" t="inlineStr">
+        <is>
+          <t>Soğukta Dişlerin Neden İrade Dışı Takırdar? 🥶🦷 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D121" s="14" t="inlineStr">
+        <is>
+          <t>Dondurucu bir soğukta dışarı çıktığında, ne kadar sıkmaya çalışırsan çalış, dişlerinin kendi kendine takırdadığı oldu mu? Bunu durduramazsın. Çünkü o an kontrol beynindeki hipotalamus adlı gizli termostata geçer. İç sıcaklığın milimetrik olarak düştüğü anda, beynin kaslarını saniyede defalarca kasılıp gevşemeye zorlayarak acil ısı üretir. Çene kasların vücudunun en güçlü ve beynine en yakın kas grubu olduğu için bu titreme en şiddetli orada hissedilir ve dişlerin birbirine vurur. Peki sen dondurucu kış soğuğuna daha kolay dayananlardan mısın, yoksa yaz sıcağını tercih edenlerden mi? Yorumlarda buluşalım.
+Kaynak: https://en.wikipedia.org/wiki/Shivering</t>
+        </is>
+      </c>
+      <c r="E121" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
+        </is>
+      </c>
+      <c r="F121" s="14" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, nörobilim, insan bedeni, psikoloji, bilim</t>
+        </is>
+      </c>
+      <c r="G121" s="14" t="inlineStr">
+        <is>
+          <t>Peki sen dondurucu kış soğuğuna daha kolay dayananlardan mısın, yoksa kavurucu yaz sıcağını tercih edenlerden mi? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H121" s="14" t="inlineStr">
+        <is>
+          <t>Nörobilim ve İnsan Bedeni</t>
+        </is>
+      </c>
+      <c r="I121" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Shivering</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="112.5" customHeight="1" s="13">
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B122" s="11" t="inlineStr">
+        <is>
+          <t>video_110.mp4</t>
+        </is>
+      </c>
+      <c r="C122" s="14" t="inlineStr">
+        <is>
+          <t>Utandığında Neden Sadece Yüzün ve Kulakların Kızarır? 😳🧠 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D122" s="14" t="inlineStr">
+        <is>
+          <t>Herkesin içinde bir anda utandığında neden kolların değil de sadece yanakların ve kulakların alev alev kızarır? Üstelik sakın kızarma dedikçe daha da kıpkırmızı olursun. Charles Darwin'in tüm duyguların en insaniye olanı dediği bu tepki vücudunun gizli dürüstlük mekanizmasıdır. Utandığın saniye beynin ani bir adrenalin salgılar ve sadece yüzündeki özel kılcal damarlar genişleyerek cildinin altına sıcak kan hücum eder. Evrimsel olarak bu tek kelime etmeden çevrendekilere hata yaptım ve farkındayım demenin sessiz yoludur. Peki sen utandığında sakin kalabilenlerden misin, yoksa saniyesinde kızaranlardan mı? Yorumlarda buluşalım.
+Kaynak: https://en.wikipedia.org/wiki/Blushing</t>
+        </is>
+      </c>
+      <c r="E122" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
+        </is>
+      </c>
+      <c r="F122" s="14" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, nörobilim, insan bedeni, psikoloji, bilim</t>
+        </is>
+      </c>
+      <c r="G122" s="14" t="inlineStr">
+        <is>
+          <t>Peki sen utandığında rengini belli etmeden sakin kalabilenlerden misin, yoksa saniyesinde pancar gibi kızaranlardan mı? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H122" s="14" t="inlineStr">
+        <is>
+          <t>Nörobilim ve İnsan Bedeni</t>
+        </is>
+      </c>
+      <c r="I122" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Blushing</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="112.5" customHeight="1" s="13">
+      <c r="A123" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B123" s="11" t="inlineStr">
+        <is>
+          <t>video_111.mp4</t>
+        </is>
+      </c>
+      <c r="C123" s="14" t="inlineStr">
+        <is>
+          <t>Dünya'nın En Issız Noktası Point Nemo: En Yakın İnsanlar Uzayda! 🌊🛰️ #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D123" s="14" t="inlineStr">
+        <is>
+          <t>Dünya üzerinde öyle ıssız bir nokta var ki, orada bir tekneyle mahsur kalsan sana en yakın insanlar Dünya'da değil, uzayda olurdu. Güney Pasifik Okyanusu'nun ortasındaki Point Nemo ile tanış. Burası en yakın kara parçasına tam 2.688 kilometre uzaklıktadır. Buna karşılık, Uluslararası Uzay İstasyonu başının sadece 400 kilometre üzerinden geçer. Yani gökyüzündeki astronotlar, sana karadaki insanlardan tam 6 kat daha yakındır. Uzay ajansları da ömrü biten uyduları bu dev su mezarlığına düşürür. Peki sen böyle mutlak bir sessizliğin ortasında tek başına bir gece geçirmeye cesaret edebilir miydin, yoksa kıyıdan asla ayrılmaz mıydın? Yorumlarda buluşalım!
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+Kaynak: https://en.wikipedia.org/wiki/Pole_of_inaccessibility
+#bilgidozu #shorts #doğa #okyanus #coğrafya #bilim</t>
+        </is>
+      </c>
+      <c r="E123" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #doğa #okyanus #coğrafya #bilim</t>
+        </is>
+      </c>
+      <c r="F123" s="14" t="inlineStr">
+        <is>
+          <t>bilgidozu, point nemo, güney pasifik, dünyanın en ıssız noktası, uydu mezarlığı, uluslararası uzay istasyonu, coğrafya, doğa, bilim, shorts</t>
+        </is>
+      </c>
+      <c r="G123" s="14" t="inlineStr">
+        <is>
+          <t>Peki sen böyle mutlak bir sessizliğin ortasında tek başına bir gece geçirmeye cesaret edebilir miydin, yoksa kıyıdan asla ayrılmaz mıydın? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H123" s="14" t="inlineStr">
+        <is>
+          <t>Doğa ve Hayvanlar</t>
+        </is>
+      </c>
+      <c r="I123" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Pole_of_inaccessibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="112.5" customHeight="1" s="13">
+      <c r="A124" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B124" s="11" t="inlineStr">
+        <is>
+          <t>video_112.mp4</t>
+        </is>
+      </c>
+      <c r="C124" s="14" t="inlineStr">
+        <is>
+          <t>Antarktika'daki Buzuldan Neden Kan Kırmızısı Şelale Akıyor? 🧊🩸 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D124" s="14" t="inlineStr">
+        <is>
+          <t>Antarktika'nın bembeyaz, dondurucu buzullarının arasından bir anda kıpkırmızı, kan renginde bir şelalenin aktığını görsen ne düşünürdün? Taylor Buzulu'ndaki bu ürpertici manzaranın sebebi kan ya da yosun değil, tam 5 milyon yıl önce buzulun 400 metre altına hapsolmuş antik bir yeraltı gölü. Bu gizli gölün suyu okyanuslardan 3 kat daha tuzlu olduğu için dondurucu soğukta bile asla donmuyor. İçindeki yoğun demir, buzulun çatlaklarından sızıp milyonlarca yıl sonra ilk kez havadaki oksijenle temas ettiği anda saniyeler içinde paslanarak kıpkırmızı bir şelaleye dönüşüyor. Peki sen Antarktika'daki bu gizemli buzulun yanına gitmeyi mi seçerdin, yoksa sıcak bir tropik adada kalmayı mı? Yorumlarda buluşalım!
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+Kaynak: https://en.wikipedia.org/wiki/Blood_Falls
+#bilgidozu #shorts #antarktika #doğa #coğrafya #bilim</t>
+        </is>
+      </c>
+      <c r="E124" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #antarktika #doğa #coğrafya #bilim</t>
+        </is>
+      </c>
+      <c r="F124" s="14" t="inlineStr">
+        <is>
+          <t>bilgidozu, kan şelalesi, blood falls, antarktika, taylor buzulu, doğa olayları, coğrafya, bilim, shorts</t>
+        </is>
+      </c>
+      <c r="G124" s="14" t="inlineStr">
+        <is>
+          <t>Peki sen Antarktika'daki bu gizemli buzulun yanına gitmeyi mi seçerdin, yoksa sıcak bir tropik adada kalmayı mı? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H124" s="14" t="inlineStr">
+        <is>
+          <t>Doğa ve Hayvanlar</t>
+        </is>
+      </c>
+      <c r="I124" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Blood_Falls</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="112.5" customHeight="1" s="13">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B125" s="11" t="inlineStr">
+        <is>
+          <t>video_113.mp4</t>
+        </is>
+      </c>
+      <c r="C125" s="14" t="inlineStr">
+        <is>
+          <t>5,5 Milyon Yıldır Güneş Görmeyen Mühürlü Mağara: Movile! 🕳️🕷️ #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D125" s="14" t="inlineStr">
+        <is>
+          <t>Tam 5,5 milyon yıl boyunca güneş ışığının tek bir zerresini bile görmemiş, mühürlü bir yeraltı dünyasının kapısını açtığını hayal et. Romanya'da tesadüfen keşfedilen Movile Mağarası, dış dünyadan tamamen kopuk bambaşka bir gezegen gibi. İçerideki havada oksijen normalin yarısından bile az, atmosferi ise zehirli hidrojen sülfür ve karbondioksitle dolu. Güneş ışığı olmadığı için buradaki yaşam tamamen kimyasal enerjiyle ayakta kalıyor ve içeride gözleri yok olmuş, sadece buraya özgü 30'dan fazla gizemli canlı türü yaşıyor. Peki özel bir oksijen tüpüyle bu karanlık mağaraya inme şansın olsa içeri adım atar mıydın, yoksa kapısını mühürlü mü bırakırdın? Yorumlarda buluşalım!
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+Kaynak: https://en.wikipedia.org/wiki/Movile_Cave
+#bilgidozu #shorts #mağara #doğa #biyoloji #bilim</t>
+        </is>
+      </c>
+      <c r="E125" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #mağara #doğa #biyoloji #bilim</t>
+        </is>
+      </c>
+      <c r="F125" s="14" t="inlineStr">
+        <is>
+          <t>bilgidozu, movile mağarası, mühürlü mağara, romanya, kemosentez, gizemli yerler, doğa, bilim, shorts</t>
+        </is>
+      </c>
+      <c r="G125" s="14" t="inlineStr">
+        <is>
+          <t>Peki özel bir oksijen tüpüyle bu karanlık mağaraya inme şansın olsa içeri adım atar mıydın, yoksa kapısını mühürlü mü bırakırdın? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H125" s="14" t="inlineStr">
+        <is>
+          <t>Doğa ve Hayvanlar</t>
+        </is>
+      </c>
+      <c r="I125" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Movile_Cave</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="112.5" customHeight="1" s="13">
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B126" s="11" t="inlineStr">
+        <is>
+          <t>video_114.mp4</t>
+        </is>
+      </c>
+      <c r="C126" s="14" t="inlineStr">
+        <is>
+          <t>Dallol Volkanı: Dünya Üzerindeki En Asidik ve Renkli Cehennem! 🌋🧪 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D126" s="14" t="inlineStr">
+        <is>
+          <t>Şu gördüğün neon sarısı ve zümrüt yeşili göller başka bir gezegene değil, Dünya üzerindeki en tehlikeli cehenneme ait. Etiyopya'daki Danakil Çöküntüsü'nde yer alan Dallol Volkanı, deniz seviyesinin 48 metre altında kaynayan dev bir kimya laboratuvarı gibidir. Yerin altındaki kızgın magma, kalın tuz ve kükürt yataklarıyla buluştuğunda, yüzeye akü asidinden bile daha yakıcı kaynar sular ve zehirli klor gazları fışkırır. Burada maskesiz uzun süre nefes almak bile imkânsızdır. Peki sen uzaylı bir gezegeni andıran bu yeri uzaktan dronelarla izlemeyi mi seçerdin, yoksa özel koruyucu kıyafetle yanına kadar yürümeyi mi? Yorumlarda buluşalım!
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+Kaynak: https://en.wikipedia.org/wiki/Dallol_(hydrothermal_system)
+#bilgidozu #shorts #volkan #doğa #coğrafya #bilim</t>
+        </is>
+      </c>
+      <c r="E126" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #volkan #doğa #coğrafya #bilim</t>
+        </is>
+      </c>
+      <c r="F126" s="14" t="inlineStr">
+        <is>
+          <t>bilgidozu, dallol volkanı, danakil çöküntüsü, etiyopya, asit gölleri, ekstrem doğa, coğrafya, bilim, shorts</t>
+        </is>
+      </c>
+      <c r="G126" s="14" t="inlineStr">
+        <is>
+          <t>Peki sen uzaylı bir gezegeni andıran bu yeri uzaktan dronelarla izlemeyi mi seçerdin, yoksa özel koruyucu kıyafetle yanına kadar yürümeyi mi? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H126" s="14" t="inlineStr">
+        <is>
+          <t>Doğa ve Hayvanlar</t>
+        </is>
+      </c>
+      <c r="I126" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Dallol_(hydrothermal_system)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="112.5" customHeight="1" s="13">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B127" s="11" t="inlineStr">
+        <is>
+          <t>video_115.mp4</t>
+        </is>
+      </c>
+      <c r="C127" s="14" t="inlineStr">
+        <is>
+          <t>Yerin 2.224 Metre Altında Ne Var? Dünya'nın En Derin Mağarası! 🧗‍♂️🌑 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D127" s="14" t="inlineStr">
+        <is>
+          <t>Yerin tam 2.224 metre altına, yani üst üste dizilmiş 7 Eyfel Kulesi derinliğine karanlık bir kuyudan indiğini hayal et. Kafkas Dağları'ndaki Krubera Mağarası, Dünya'nın bilinen en derin uçurumlarından biridir. Buraya inen mağaracıların en dibe ulaşması haftalar sürer ve içeride yeraltı şelaleleriyle buz gibi su tünelleri vardır. En şaşırtıcı olanı ise, 2.000 metre derinlikteki o dondurucu ve ışıksız sularda bile dış dünyayı hiç görmemiş şeffaf canlıların yaşamaya devam etmesidir. Peki sana sınırsız ekipman verilse okyanusun en derin çukuruna dalmayı mı seçerdin, yoksa Dünya'nın en derin mağarasına inmeyi mi? Yorumlarda buluşalım!
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+Kaynak: https://en.wikipedia.org/wiki/Krubera_Cave
+#bilgidozu #shorts #mağara #doğa #keşif #bilim</t>
+        </is>
+      </c>
+      <c r="E127" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #mağara #doğa #keşif #bilim</t>
+        </is>
+      </c>
+      <c r="F127" s="14" t="inlineStr">
+        <is>
+          <t>bilgidozu, krubera mağarası, dünyanın en derin mağarası, kafkas dağları, mağaracılık, doğa, coğrafya, bilim, shorts</t>
+        </is>
+      </c>
+      <c r="G127" s="14" t="inlineStr">
+        <is>
+          <t>Peki sana sınırsız ekipman verilse okyanusun en derin çukuruna dalmayı mı seçerdin, yoksa Dünya'nın en derin mağarasına inmeyi mi? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H127" s="14" t="inlineStr">
+        <is>
+          <t>Doğa ve Hayvanlar</t>
+        </is>
+      </c>
+      <c r="I127" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Krubera_Cave</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="112.5" customHeight="1" s="13">
+      <c r="A128" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B128" s="11" t="inlineStr">
+        <is>
+          <t>video_116.mp4</t>
+        </is>
+      </c>
+      <c r="C128" s="14" t="inlineStr">
+        <is>
+          <t>2.100 Yıllık Batıktan Çıkan İlk Analog Bilgisayar: Antikythera! ⚙️🏛️ #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D128" s="14" t="inlineStr">
+        <is>
+          <t>Denizin dibinde iki bin yıl boyunca paslanmış bir Yunan batığından, modern saatler kadar karmaşık dişlilere sahip antik bir bilgisayar çıktığını biliyor muydun?
+Peki sence antik dünyada bunun gibi henüz keşfedemediğimiz başka yüksek teknolojiler de var mıdır, yoksa bu tek bir dahinin eseri miydi? Yorumlarda buluşalım! 👇
+📚 Kaynak: https://en.wikipedia.org/wiki/Antikythera_mechanism
+🎨 Görseller temsilîdir (AI üretimi).
+#bilgidozu #shorts #tarih #arkeoloji #bilim</t>
+        </is>
+      </c>
+      <c r="E128" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #tarih #arkeoloji #bilim</t>
+        </is>
+      </c>
+      <c r="F128" s="14" t="inlineStr">
+        <is>
+          <t>bilgi dozu, antik mühendislik, tarih, arkeoloji, gizemli yapılar, bilim, shorts</t>
+        </is>
+      </c>
+      <c r="G128" s="14" t="inlineStr">
+        <is>
+          <t>Peki sence antik dünyada bunun gibi henüz keşfedemediğimiz başka yüksek teknolojiler de var mıdır, yoksa bu tek bir dahinin eseri miydi? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H128" s="14" t="inlineStr">
+        <is>
+          <t>Tarih ve Antik Mühendislik</t>
+        </is>
+      </c>
+      <c r="I128" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Antikythera_mechanism</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="112.5" customHeight="1" s="13">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B129" s="11" t="inlineStr">
+        <is>
+          <t>video_117.mp4</t>
+        </is>
+      </c>
+      <c r="C129" s="14" t="inlineStr">
+        <is>
+          <t>Derinkuyu Yeraltı Şehri: 20 Bin Kişi Yerin Altında Nasıl Nefes Aldı? 🏺🕯️ #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D129" s="14" t="inlineStr">
+        <is>
+          <t>Kapadokya'nın altında, yirmi bin insanın hayvanları ve erzaklarıyla birlikte haftalarca hiç yeryüzüne çıkmadan yaşayabildiği sekiz katlı dev bir yeraltı şehri var: Derinkuyu.
+Peki sen tehlike anında haftalarca böyle bir yeraltı şehrinde yaşayabilir miydin, yoksa kapalı alanda daralır mıydın? Yorumlarda buluşalım! 👇
+📚 Kaynak: https://en.wikipedia.org/wiki/Derinkuyu_underground_city
+🎨 Görseller temsilîdir (AI üretimi).
+#bilgidozu #shorts #tarih #arkeoloji #bilim</t>
+        </is>
+      </c>
+      <c r="E129" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #tarih #arkeoloji #bilim</t>
+        </is>
+      </c>
+      <c r="F129" s="14" t="inlineStr">
+        <is>
+          <t>bilgi dozu, antik mühendislik, tarih, arkeoloji, gizemli yapılar, bilim, shorts</t>
+        </is>
+      </c>
+      <c r="G129" s="14" t="inlineStr">
+        <is>
+          <t>Peki sen tehlike anında haftalarca böyle bir yeraltı şehrinde yaşayabilir miydin, yoksa kapalı alanda daralır mıydın? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H129" s="14" t="inlineStr">
+        <is>
+          <t>Tarih ve Antik Mühendislik</t>
+        </is>
+      </c>
+      <c r="I129" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Derinkuyu_underground_city</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="112.5" customHeight="1" s="13">
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B130" s="11" t="inlineStr">
+        <is>
+          <t>video_118.mp4</t>
+        </is>
+      </c>
+      <c r="C130" s="14" t="inlineStr">
+        <is>
+          <t>Voynich El Yazması: 600 Yıldır Kimsenin Okuyamadığı Şifreli Kitap! 📜🔍 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D130" s="14" t="inlineStr">
+        <is>
+          <t>Dünyanın en iyi şifre çözücüleri, dilbilimcileri ve yapay zekâları bir araya geldi ama altı yüz yıllık bu kitabın tek bir cümlesini bile okuyamadı: Voynich El Yazması.
+Peki sence bu kitap unutulmuş gizli bir bilimin şifreli kaydı mı, yoksa tarihin en zekice kurgulanmış bilmecesi mi? Yorumlarda buluşalım! 👇
+📚 Kaynak: https://en.wikipedia.org/wiki/Voynich_manuscript
+🎨 Görseller temsilîdir (AI üretimi).
+#bilgidozu #shorts #tarih #arkeoloji #bilim</t>
+        </is>
+      </c>
+      <c r="E130" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #tarih #arkeoloji #bilim</t>
+        </is>
+      </c>
+      <c r="F130" s="14" t="inlineStr">
+        <is>
+          <t>bilgi dozu, antik mühendislik, tarih, arkeoloji, gizemli yapılar, bilim, shorts</t>
+        </is>
+      </c>
+      <c r="G130" s="14" t="inlineStr">
+        <is>
+          <t>Peki sence bu kitap unutulmuş gizli bir bilimin şifreli kaydı mı, yoksa tarihin en zekice kurgulanmış bilmecesi mi? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H130" s="14" t="inlineStr">
+        <is>
+          <t>Tarih ve Antik Mühendislik</t>
+        </is>
+      </c>
+      <c r="I130" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Voynich_manuscript</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="112.5" customHeight="1" s="13">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B131" s="11" t="inlineStr">
+        <is>
+          <t>video_119.mp4</t>
+        </is>
+      </c>
+      <c r="C131" s="14" t="inlineStr">
+        <is>
+          <t>Puma Punku H-Blokları: Jilet Bile Girmeyen Antik Taşların Sırrı! 🪨📐 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D131" s="14" t="inlineStr">
+        <is>
+          <t>Deniz seviyesinden üç bin sekiz yüz metre yüksekte, aralarına jilet bile girmeyecek kadar kusursuz kesilmiş yüz tonluk taş bloklar düşün: Puma Punku.
+Peki sence antik ustalar bu kusursuz taş işçiliğini sabırlı el aletleriyle mi başardı, yoksa bugün unuttuğumuz özel bir teknikleri mi vardı? Yorumlarda buluşalım! 👇
+📚 Kaynak: https://en.wikipedia.org/wiki/Pumapunku
+🎨 Görseller temsilîdir (AI üretimi).
+#bilgidozu #shorts #tarih #arkeoloji #bilim</t>
+        </is>
+      </c>
+      <c r="E131" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #tarih #arkeoloji #bilim</t>
+        </is>
+      </c>
+      <c r="F131" s="14" t="inlineStr">
+        <is>
+          <t>bilgi dozu, antik mühendislik, tarih, arkeoloji, gizemli yapılar, bilim, shorts</t>
+        </is>
+      </c>
+      <c r="G131" s="14" t="inlineStr">
+        <is>
+          <t>Peki sence antik ustalar bu kusursuz taş işçiliğini sabırlı el aletleriyle mi başardı, yoksa bugün unuttuğumuz özel bir teknikleri mi vardı? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H131" s="14" t="inlineStr">
+        <is>
+          <t>Tarih ve Antik Mühendislik</t>
+        </is>
+      </c>
+      <c r="I131" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Pumapunku</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="112.5" customHeight="1" s="13">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B132" s="11" t="inlineStr">
+        <is>
+          <t>video_120.mp4</t>
+        </is>
+      </c>
+      <c r="C132" s="14" t="inlineStr">
+        <is>
+          <t>Babil'in Asma Bahçeleri Gerçekte Babil'de Değil Miydi? 🌿🏛️ #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D132" s="14" t="inlineStr">
+        <is>
+          <t>Dünyanın Yedi Harikası'ndan biri sayılan Babil'in Asma Bahçeleri'nin aslında hiçbir zaman Babil'de olmadığını duysan ne derdin?
+Peki sen geçmişe gidebilsen önce bu efsanevi Asma Bahçeleri'ni mi görmek isterdin, yoksa İskenderiye Kütüphanesi'ni mi? Yorumlarda buluşalım! 👇
+📚 Kaynak: https://en.wikipedia.org/wiki/Hanging_Gardens_of_Babylon
+🎨 Görseller temsilîdir (AI üretimi).
+#bilgidozu #shorts #tarih #arkeoloji #bilim</t>
+        </is>
+      </c>
+      <c r="E132" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #tarih #arkeoloji #bilim</t>
+        </is>
+      </c>
+      <c r="F132" s="14" t="inlineStr">
+        <is>
+          <t>bilgi dozu, antik mühendislik, tarih, arkeoloji, gizemli yapılar, bilim, shorts</t>
+        </is>
+      </c>
+      <c r="G132" s="14" t="inlineStr">
+        <is>
+          <t>Peki sen geçmişe gidebilsen önce bu efsanevi Asma Bahçeleri'ni mi görmek isterdin, yoksa İskenderiye Kütüphanesi'ni mi? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H132" s="14" t="inlineStr">
+        <is>
+          <t>Tarih ve Antik Mühendislik</t>
+        </is>
+      </c>
+      <c r="I132" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Hanging_Gardens_of_Babylon</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="112.5" customHeight="1" s="13">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B133" s="11" t="inlineStr">
+        <is>
+          <t>uzun_video_13.mp4</t>
+        </is>
+      </c>
+      <c r="C133" s="14" t="inlineStr">
+        <is>
+          <t>Beyninin Senden Gizlediği 3 Otomatik Hile (Kendi Sesin, Boşluğun Çağrısı ve Sahte Acı) 🧠🔒 #bilgidozu</t>
+        </is>
+      </c>
+      <c r="D133" s="14" t="inlineStr">
+        <is>
+          <t>Beyninin senden gizlediği 3 otomatik hileyi tek bir merak yolculuğunda inceliyoruz:
+1 · Kendi Sesin Neden Kayıtta Yabancı Gelir? (Kafatası Kemik İletimi)
+2 · Yüksek Bir Yerden Bakınca Beyin Neden 'Atla' Diye Fısıldar? (Boşluğun Çağrısı)
+3 · Acı Biber Aslında Ağzını Yakmaz — Beynini Nasıl Kandırır? (Kapsaisin &amp; TRPV1)
+Bu 3 beyin hilesinden seni en çok şaşırtan hangisi oldu: Kendi sesinin kemik iletimi mi, yüksek yerdeki Boşluğun Çağrısı mı, yoksa acı biberin sahte yanık alarmı mı? Yorumlarda buluşalım! 👇
+📚 Kaynaklar:
+https://en.wikipedia.org/wiki/Bone_conduction
+https://en.wikipedia.org/wiki/The_imp_of_the_perverse
+https://en.wikipedia.org/wiki/Capsaicin
+🎨 Görseller temsilîdir (AI üretimi).
+#bilgidozu #bilim #psikoloji #nörobilim #insanbedeni</t>
+        </is>
+      </c>
+      <c r="E133" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #bilim #psikoloji #nörobilim #insanbedeni</t>
+        </is>
+      </c>
+      <c r="F133" s="14" t="inlineStr">
+        <is>
+          <t>bilgi dozu, nörobilim, psikoloji, insan beyni, kemik iletimi, kapsaisin, bilim, belgesel</t>
+        </is>
+      </c>
+      <c r="G133" s="14" t="inlineStr">
+        <is>
+          <t>Bu 3 beyin hilesinden seni en çok şaşırtan hangisi oldu: Kendi sesinin kemik iletimi mi, yüksek yerdeki Boşluğun Çağrısı mı, yoksa acı biberin sahte yanık alarmı mı? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H133" s="14" t="inlineStr">
+        <is>
+          <t>Uzun — Nörobilim ve Psikoloji</t>
+        </is>
+      </c>
+      <c r="I133" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Bone_conduction
+https://en.wikipedia.org/wiki/The_imp_of_the_perverse
+https://en.wikipedia.org/wiki/Capsaicin</t>
+        </is>
+      </c>
+    </row>
     <row r="134" ht="112.5" customHeight="1" s="13"/>
     <row r="135" ht="112.5" customHeight="1" s="13"/>
     <row r="136" ht="112.5" customHeight="1" s="13"/>

--- a/bilgidozu_yukleme_tablosu.xlsx
+++ b/bilgidozu_yukleme_tablosu.xlsx
@@ -530,7 +530,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AC133"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" style="13" min="1" max="1"/>
     <col width="22.86" customWidth="1" style="13" min="2" max="2"/>
@@ -3582,7 +3582,7 @@
     <row r="41" ht="112.5" customHeight="1" s="13">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>BEKLEMEDE</t>
+          <t>YÜKLENDİ</t>
         </is>
       </c>
       <c r="B41" s="14" t="inlineStr">
@@ -3626,8 +3626,16 @@
           <t>Wikipedia — Hypnic jerk: https://en.wikipedia.org/wiki/Hypnic_jerk</t>
         </is>
       </c>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="5" t="n"/>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/tCuQNw_V74I</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-24 14:24</t>
+        </is>
+      </c>
       <c r="L41" s="5" t="n"/>
       <c r="M41" s="6" t="n"/>
       <c r="N41" s="6" t="n"/>
@@ -9520,16 +9528,16 @@
       </c>
       <c r="C2" s="0" t="inlineStr">
         <is>
-          <t>2026-10-23 18:29</t>
+          <t>2026-10-24 14:24</t>
         </is>
       </c>
       <c r="D2" s="0" t="inlineStr"/>
       <c r="E2" s="0" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F2" s="0" t="inlineStr">
         <is>
-          <t>video_32.mp4 yayınlandı (https://youtu.be/mANNR6Tf21o)</t>
+          <t>video_34.mp4 yayınlandı (https://youtu.be/tCuQNw_V74I)</t>
         </is>
       </c>
     </row>
@@ -9546,16 +9554,16 @@
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>2026-10-23 21:15</t>
+          <t>2026-10-24 14:24</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr"/>
       <c r="E3" s="0" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t>Tam yetkili OAuth (youtube.force-ssl + drive + sheets) bağlandı ve aktif</t>
+          <t>video_34.mp4 sabit yorumu otomatik atıldı (ID: Ugzvwaj5XgX3cgIfA8R4AaABAg)</t>
         </is>
       </c>
     </row>
@@ -9572,16 +9580,16 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>2026-10-23 21:15</t>
+          <t>2026-10-24 14:24</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr"/>
       <c r="E4" s="0" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>58 videonun gerçek görüntülenme (33457) ve yorum verisi çekildi</t>
+          <t>34.276 görüntülenme ve 494 beğeni verisi çekildi</t>
         </is>
       </c>
     </row>
@@ -9598,16 +9606,16 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>2026-10-23 18:29</t>
+          <t>2026-10-24 14:24</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr"/>
       <c r="E5" s="0" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>video_32.mp4 yayın kartı ve sabit yorum metni gönderildi</t>
+          <t>video_34.mp4 yayın kartı ve sabit yorum metni gönderildi</t>
         </is>
       </c>
     </row>
@@ -9670,7 +9678,7 @@
       </c>
       <c r="D2" s="0" t="inlineStr">
         <is>
-          <t>2026-10-23 21:15</t>
+          <t>2026-10-24 14:24</t>
         </is>
       </c>
       <c r="E2" s="0" t="inlineStr">
@@ -9697,12 +9705,12 @@
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>2026-10-23 21:15</t>
+          <t>2026-10-24 14:24</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>Drive video klasörü (82 dosya) ve 3 sekmeli yükleme tablosu canlı bağlı.</t>
+          <t>Ana Drive klasörü (1MBjwKp1DXoxLiCAkds84MowZAFMOK7Br), KAPAKLAR klasörü ve 3 sekmeli baslik.xlsx canlı bağlı.</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9732,7 @@
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>2026-10-23 21:15</t>
+          <t>2026-10-24 14:24</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">

--- a/bilgidozu_yukleme_tablosu.xlsx
+++ b/bilgidozu_yukleme_tablosu.xlsx
@@ -673,7 +673,7 @@
       </c>
       <c r="I2" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>NASA — Venus: https://science.nasa.gov/venus/</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I3" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>The Conversation (UW 5 yıllık maske deneyi): https://theconversation.com/never-cross-a-crow-it-will-remember-your-face-2121</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="I4" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>Banana Equivalent Dose: https://en.wikipedia.org/wiki/Banana_equivalent_dose</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="I5" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>Mikorizal ağ (Wood Wide Web): https://en.wikipedia.org/wiki/Mycorrhizal_network</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="I6" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>NASA — Stars: https://science.nasa.gov/universe/stars/</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="I7" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>NOAA — Why is the ocean blue: https://oceanservice.noaa.gov/facts/oceanblue.html</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="I8" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>The Conversation (RMIT araştırmacıları): https://theconversation.com/bees-join-an-elite-group-of-species-that-understands-the-concept-of-zero-as-a-number-97316 RMIT: https://www.rmit.edu.au/news/all-news/2018/jun/honeybees-zero-in-on-nothing</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="I9" s="17" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>phys.org (PNAS 2022): https://phys.org/news/2022-09-earth-harbours-ants-wild-birds.html</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="I10" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>NASA — Europa: https://science.nasa.gov/jupiter/moons/europa/</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="I11" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>MIT News (2023 Roma betonu): https://news.mit.edu/2023/roman-concrete-durability-lime-casts-0106</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="I12" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>SLAC (2017 elmas yağmuru deneyi): https://www6.slac.stanford.edu/news/2017-08-21-scientists-create-diamond-rain-forms-interior-icy-giant-planets</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="I13" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>Tardigrada: https://en.wikipedia.org/wiki/Tardigrade</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="I14" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>Psychology Today (30+ çalışma meta-analizi): https://www.psychologytoday.com/us/blog/best-practices-in-health/202506/eyes-wide-open-what-your-eyes-reveal-about-attraction Yedek: https://www.medicalnewstoday.com/articles/dilated-pupils-meaning</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="I15" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>USDA Forest Service — Pando: https://www.fs.usda.gov/detail/fishlake/home/?cid=stelprdb5444544</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="I16" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>NOAA / NWS — Lightning Science: https://www.weather.gov/safety/lightning-science</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -1879,9 +1879,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>NASA Venus: https://science.nasa.gov/venus/
-SLAC elmas yağmuru: https://www6.slac.stanford.edu/news/2017-08-21-scientists-create-diamond-rain-forms-interior-icy-giant-planets
-NASA Europa: https://science.nasa.gov/jupiter/moons/europa/</t>
+          <t>NASA Venus: https://science.nasa.gov/venus/ SLAC elmas yağmuru: https://www6.slac.stanford.edu/news/2017-08-21-scientists-create-diamond-rain-forms-interior-icy-giant-planets NASA Europa: https://science.nasa.gov/jupiter/moons/europa/</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1967,9 +1965,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>The Conversation karga: https://theconversation.com/never-cross-a-crow-it-will-remember-your-face-2121
-The Conversation arılar: https://theconversation.com/bees-join-an-elite-group-of-species-that-understands-the-concept-of-zero-as-a-number-97316
-USDA Pando: https://www.fs.usda.gov/detail/fishlake/home/?cid=stelprdb5444544</t>
+          <t>The Conversation karga: https://theconversation.com/never-cross-a-crow-it-will-remember-your-face-2121 The Conversation arılar: https://theconversation.com/bees-join-an-elite-group-of-species-that-understands-the-concept-of-zero-as-a-number-97316 USDA Pando: https://www.fs.usda.gov/detail/fishlake/home/?cid=stelprdb5444544</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -2055,9 +2051,7 @@
       </c>
       <c r="I19" s="14" t="inlineStr">
         <is>
-          <t>Görünmez Goril: https://en.wikipedia.org/wiki/The_Invisible_Gorilla
-Kapı Eşiği Etkisi: https://en.wikipedia.org/wiki/Doorway_effect
-Özgür İrade Nörobilimi: https://en.wikipedia.org/wiki/Neuroscience_of_free_will</t>
+          <t>Görünmez Goril: https://en.wikipedia.org/wiki/The_Invisible_Gorilla Kapı Eşiği Etkisi: https://en.wikipedia.org/wiki/Doorway_effect Özgür İrade Nörobilimi: https://en.wikipedia.org/wiki/Neuroscience_of_free_will</t>
         </is>
       </c>
       <c r="J19" s="5" t="n"/>
@@ -2124,7 +2118,7 @@
       </c>
       <c r="I20" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>NASA — Jupiter Facts: https://science.nasa.gov/jupiter/facts/</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
@@ -2203,7 +2197,7 @@
       </c>
       <c r="I21" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>NASA — Mars Facts: https://science.nasa.gov/mars/facts/</t>
         </is>
       </c>
       <c r="J21" s="5" t="n"/>
@@ -2270,7 +2264,7 @@
       </c>
       <c r="I22" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>Starfish: https://en.wikipedia.org/wiki/Starfish</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -2349,7 +2343,7 @@
       </c>
       <c r="I23" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>Sleep Foundation — Animals and Sleep: https://www.sleepfoundation.org/animals-and-sleep</t>
         </is>
       </c>
       <c r="J23" s="5" t="n"/>
@@ -2376,7 +2370,7 @@
     <row r="24" ht="112.5" customHeight="1" s="13">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">BEKLEMEDE </t>
+          <t>YÜKLENDİ</t>
         </is>
       </c>
       <c r="B24" s="18" t="inlineStr">
@@ -2416,7 +2410,7 @@
       </c>
       <c r="I24" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ (https://youtu.be/MzkXjFsAZ90)</t>
+          <t>NASA — Saturn Facts: https://science.nasa.gov/saturn/facts/</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
@@ -2495,7 +2489,7 @@
       </c>
       <c r="I25" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>Human Microbiome: https://en.wikipedia.org/wiki/Human_microbiome</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -2574,7 +2568,7 @@
       </c>
       <c r="I26" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>Glass (cam bir katıdır): https://en.wikipedia.org/wiki/Glass</t>
         </is>
       </c>
       <c r="J26" s="5" t="n"/>
@@ -2641,7 +2635,7 @@
       </c>
       <c r="I27" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>NASA — Moon Facts: https://science.nasa.gov/moon/facts/</t>
         </is>
       </c>
       <c r="J27" s="5" t="n"/>
@@ -2708,7 +2702,7 @@
       </c>
       <c r="I28" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>Cat communication (miyav): https://en.wikipedia.org/wiki/Cat_communication</t>
         </is>
       </c>
       <c r="J28" s="5" t="n"/>
@@ -2775,7 +2769,7 @@
       </c>
       <c r="I29" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>NASA — Earth Facts: https://science.nasa.gov/earth/facts/</t>
         </is>
       </c>
       <c r="J29" s="5" t="n"/>
@@ -2842,7 +2836,7 @@
       </c>
       <c r="I30" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>Honey (raf ömrü): https://en.wikipedia.org/wiki/Honey</t>
         </is>
       </c>
       <c r="J30" s="5" t="n"/>
@@ -2909,7 +2903,7 @@
       </c>
       <c r="I31" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>Earth's inner core: https://en.wikipedia.org/wiki/Earth%27s_inner_core</t>
         </is>
       </c>
       <c r="J31" s="5" t="n"/>
@@ -2976,7 +2970,7 @@
       </c>
       <c r="I32" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>Elephant cognition (sismik iletişim): https://en.wikipedia.org/wiki/Elephant_cognition</t>
         </is>
       </c>
       <c r="J32" s="5" t="n"/>
@@ -3043,7 +3037,7 @@
       </c>
       <c r="I33" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>NASA — Uranus Facts: https://science.nasa.gov/uranus/facts/</t>
         </is>
       </c>
       <c r="J33" s="5" t="n"/>
@@ -3110,7 +3104,7 @@
       </c>
       <c r="I34" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>Ten percent of brain myth: https://en.wikipedia.org/wiki/Ten_percent_of_brain_myth</t>
         </is>
       </c>
       <c r="J34" s="5" t="n"/>
@@ -3178,8 +3172,7 @@
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
-          <t>NASA Mars Facts: https://science.nasa.gov/mars/facts/
-NASA Neptune Facts (rüzgarlar): https://science.nasa.gov/neptune/facts/</t>
+          <t>NASA Mars Facts: https://science.nasa.gov/mars/facts/ NASA Neptune Facts (rüzgarlar): https://science.nasa.gov/neptune/facts/</t>
         </is>
       </c>
       <c r="J35" s="5" t="n"/>
@@ -3247,9 +3240,7 @@
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>Turritopsis dohrnii (ölümsüz denizanası): https://en.wikipedia.org/wiki/Turritopsis_dohrnii
-Sleep Foundation (USWS): https://www.sleepfoundation.org/animals-and-sleep
-PBS NOVA (köpek koku): https://www.pbs.org/wgbh/nova/article/dogs-sense-of-smell/</t>
+          <t>Turritopsis dohrnii (ölümsüz denizanası): https://en.wikipedia.org/wiki/Turritopsis_dohrnii Sleep Foundation (USWS): https://www.sleepfoundation.org/animals-and-sleep PBS NOVA (köpek koku): https://www.pbs.org/wgbh/nova/article/dogs-sense-of-smell/</t>
         </is>
       </c>
       <c r="J36" s="5" t="n"/>
@@ -3317,9 +3308,7 @@
       </c>
       <c r="I37" s="14" t="inlineStr">
         <is>
-          <t>McGurk effect: https://en.wikipedia.org/wiki/McGurk_effect
-Olfactory memory (koku-anı): https://en.wikipedia.org/wiki/Olfactory_memory
-Placebo (Harvard Health): https://www.health.harvard.edu/mental-health/the-power-of-the-placebo-effect</t>
+          <t>McGurk effect: https://en.wikipedia.org/wiki/McGurk_effect Olfactory memory (koku-anı): https://en.wikipedia.org/wiki/Olfactory_memory Placebo (Harvard Health): https://www.health.harvard.edu/mental-health/the-power-of-the-placebo-effect</t>
         </is>
       </c>
       <c r="J37" s="5" t="n"/>
@@ -3387,7 +3376,7 @@
       </c>
       <c r="I38" s="16" t="inlineStr">
         <is>
-          <t>YÜKLENDİ (https://youtu.be/c0lcGGWy-hw)</t>
+          <t>Wikipedia — Blind spot (vision): https://en.wikipedia.org/wiki/Blind_spot_(vision)</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
@@ -4453,8 +4442,7 @@
       </c>
       <c r="I53" s="14" t="inlineStr">
         <is>
-          <t>NOAA Ocean Exploration — Bioluminescence: https://oceanexplorer.noaa.gov/facts/bioluminescence.html
-Smithsonian Ocean — Bioluminescence: https://ocean.si.edu/ocean-life/fish/bioluminescence</t>
+          <t>NOAA Ocean Exploration — Bioluminescence: https://oceanexplorer.noaa.gov/facts/bioluminescence.html Smithsonian Ocean — Bioluminescence: https://ocean.si.edu/ocean-life/fish/bioluminescence</t>
         </is>
       </c>
       <c r="J53" s="5" t="n"/>
@@ -5292,7 +5280,7 @@
       </c>
       <c r="I65" s="14" t="inlineStr">
         <is>
-          <t>Kaynak: Wikipedia / MarineBio — Sea Otter Tool Use &amp; Fur Density</t>
+          <t>Wikipedia / MarineBio — Sea Otter Tool Use &amp; Fur Density: https://en.wikipedia.org/wiki/Sea_otter</t>
         </is>
       </c>
       <c r="J65" s="5" t="n"/>
@@ -6552,7 +6540,7 @@
       </c>
       <c r="I83" s="14" t="inlineStr">
         <is>
-          <t>Journal of Voice / Auditory Bone Conduction</t>
+          <t>Journal of Voice / Wikipedia — Auditory Bone Conduction: https://en.wikipedia.org/wiki/Bone_conduction</t>
         </is>
       </c>
       <c r="J83" s="5" t="n"/>
@@ -6694,7 +6682,7 @@
       </c>
       <c r="I85" s="14" t="inlineStr">
         <is>
-          <t>PLOS ONE (2012) — Vailati et al. / Journal of Experimental Biology</t>
+          <t>PLOS ONE (2012) — Vailati et al. (Archerfish Water Jet): https://journals.plos.org/plosone/article?id=10.1371/journal.pone.0047867</t>
         </is>
       </c>
       <c r="J85" s="5" t="n"/>
@@ -6765,7 +6753,7 @@
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>IEEE Electromagnetic Shielding / Faraday Cage</t>
+          <t>IEEE Electromagnetic Shielding / Wikipedia — Faraday Cage: https://en.wikipedia.org/wiki/Faraday_cage</t>
         </is>
       </c>
       <c r="J86" s="5" t="n"/>
@@ -6836,7 +6824,7 @@
       </c>
       <c r="I87" s="14" t="inlineStr">
         <is>
-          <t>NASA Heliophysics / SOHO Solar Acoustics</t>
+          <t>NASA Heliophysics / SOHO — Solar Acoustics: https://sci.esa.int/web/soho/-/30851-solar-interior</t>
         </is>
       </c>
       <c r="J87" s="5" t="n"/>
@@ -6907,7 +6895,7 @@
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>Texas A&amp;M College of Medicine / Autonomic Sneezing Reflex</t>
+          <t>Texas A&amp;M College of Medicine / Wikipedia — Photic &amp; Autonomic Sneezing Reflex: https://en.wikipedia.org/wiki/Sneeze</t>
         </is>
       </c>
       <c r="J88" s="5" t="n"/>
@@ -6978,7 +6966,7 @@
       </c>
       <c r="I89" s="14" t="inlineStr">
         <is>
-          <t>Journal of Archaeological Science (2012) — Lipo &amp; Hunt</t>
+          <t>Journal of Archaeological Science (2012) — Lipo &amp; Hunt (Easter Island Moai): https://en.wikipedia.org/wiki/Moai</t>
         </is>
       </c>
       <c r="J89" s="5" t="n"/>
@@ -7049,7 +7037,7 @@
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>Nature Communications (2019) — de Santana et al.</t>
+          <t>Nature Communications (2019) — de Santana et al. (860V Electric Eel): https://www.nature.com/articles/s41467-019-11622-9</t>
         </is>
       </c>
       <c r="J90" s="5" t="n"/>
@@ -7120,7 +7108,7 @@
       </c>
       <c r="I91" s="14" t="inlineStr">
         <is>
-          <t>ASME A17.1 Escalator Safety Code</t>
+          <t>ASME A17.1 Escalator Safety Code — Escalator Skirt Deflector Brushes: https://en.wikipedia.org/wiki/Escalator</t>
         </is>
       </c>
       <c r="J91" s="5" t="n"/>
@@ -7191,7 +7179,7 @@
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>Nature Astronomy — Diamond Rain on Ice Giants</t>
+          <t>Nature Astronomy / SLAC — Diamond Rain on Ice Giants: https://www6.slac.stanford.edu/news/2017-08-21-scientists-create-diamond-rain-forms-interior-icy-giant-planets</t>
         </is>
       </c>
     </row>
@@ -7242,7 +7230,7 @@
       </c>
       <c r="I93" s="14" t="inlineStr">
         <is>
-          <t>ESA FOTON-M3 Tardigrade Mission</t>
+          <t>ESA FOTON-M3 / Current Biology — Tardigrades in Space: https://en.wikipedia.org/wiki/Tardigrade</t>
         </is>
       </c>
     </row>
@@ -7293,7 +7281,7 @@
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>Hess &amp; Polt — Pupillometry Research</t>
+          <t>Hess &amp; Polt (1960) / Wikipedia — Pupillometry Research: https://en.wikipedia.org/wiki/Pupillometry</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7332,7 @@
       </c>
       <c r="I95" s="14" t="inlineStr">
         <is>
-          <t>US Forest Service — Pando Clonal Colony</t>
+          <t>USDA Forest Service — Pando Clonal Colony: https://www.fs.usda.gov/detail/fishlake/home/?cid=stelprdb5444544</t>
         </is>
       </c>
     </row>
@@ -7395,7 +7383,7 @@
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>NOAA Severe Weather — Return Stroke Physics</t>
+          <t>NOAA Severe Weather — Lightning Return Stroke Physics: https://www.weather.gov/safety/lightning-science</t>
         </is>
       </c>
     </row>
@@ -7446,7 +7434,7 @@
       </c>
       <c r="I97" s="14" t="inlineStr">
         <is>
-          <t>NASA Juno Mission — Great Red Spot</t>
+          <t>NASA Juno Mission — Jupiter Great Red Spot: https://science.nasa.gov/jupiter/facts/</t>
         </is>
       </c>
     </row>
@@ -7497,7 +7485,7 @@
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>NASA Mars Exploration — Olympus Mons</t>
+          <t>NASA Mars Exploration — Olympus Mons: https://science.nasa.gov/mars/facts/</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7536,7 @@
       </c>
       <c r="I99" s="14" t="inlineStr">
         <is>
-          <t>Smithsonian Ocean — Sea Stars Anatomy</t>
+          <t>Smithsonian Ocean / Wikipedia — Sea Stars Anatomy: https://en.wikipedia.org/wiki/Starfish</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7587,7 @@
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>Neuroscience Reviews — Unihemispheric Sleep</t>
+          <t>Sleep Foundation / Wikipedia — Unihemispheric Slow-Wave Sleep: https://en.wikipedia.org/wiki/Unihemispheric_slow-wave_sleep</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7638,7 @@
       </c>
       <c r="I101" s="14" t="inlineStr">
         <is>
-          <t>NASA Cassini Mission — Saturn Planetary Density</t>
+          <t>NASA Cassini Mission — Saturn Planetary Density: https://science.nasa.gov/saturn/facts/</t>
         </is>
       </c>
     </row>
@@ -7701,7 +7689,7 @@
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>PLOS Biology — Human Microbiome Cell Count</t>
+          <t>PLOS Biology (Sender et al., 2016) — Revised Estimates for Human &amp; Bacteria Cells: https://journals.plos.org/plosbiology/article?id=10.1371/journal.pbio.1002533</t>
         </is>
       </c>
     </row>
@@ -7752,7 +7740,7 @@
       </c>
       <c r="I103" s="14" t="inlineStr">
         <is>
-          <t>American Journal of Physics — Cathedral Glass</t>
+          <t>American Journal of Physics (Zanotto, 1998) — Do Cathedral Glasses Flow?: https://en.wikipedia.org/wiki/Glass</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7791,7 @@
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>NASA Lunar Laser Ranging Experiment</t>
+          <t>NASA — Lunar Laser Ranging Experiment: https://science.nasa.gov/moon/facts/</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7842,7 @@
       </c>
       <c r="I105" s="14" t="inlineStr">
         <is>
-          <t>Cornell Feline Health Center — Cat Vocalization</t>
+          <t>Cornell Feline Health Center / Wikipedia — Cat Vocalization: https://en.wikipedia.org/wiki/Cat_communication</t>
         </is>
       </c>
     </row>
@@ -7905,7 +7893,7 @@
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>NASA Earth Fact Sheet — Orbital Velocity</t>
+          <t>NASA Earth Fact Sheet — Orbital Velocity: https://science.nasa.gov/earth/facts/</t>
         </is>
       </c>
     </row>
@@ -7956,7 +7944,7 @@
       </c>
       <c r="I107" s="14" t="inlineStr">
         <is>
-          <t>Smithsonian — Honey's Eternal Shelf Life</t>
+          <t>Smithsonian Magazine — The Science Behind Honey's Eternal Shelf Life: https://en.wikipedia.org/wiki/Honey</t>
         </is>
       </c>
     </row>
@@ -8007,7 +7995,7 @@
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>Science — Earth's Inner Core Temperature</t>
+          <t>Science / Wikipedia — Earth's Inner Core Temperature: https://en.wikipedia.org/wiki/Earth%27s_inner_core</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8046,7 @@
       </c>
       <c r="I109" s="14" t="inlineStr">
         <is>
-          <t>Stanford University — Elephant Seismic Hearing</t>
+          <t>Stanford University / Wikipedia — Elephant Seismic Communication: https://en.wikipedia.org/wiki/Elephant_cognition</t>
         </is>
       </c>
     </row>
@@ -8109,7 +8097,7 @@
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>NASA Uranus Planetary Fact Sheet</t>
+          <t>NASA — Uranus Planetary Fact Sheet: https://science.nasa.gov/uranus/facts/</t>
         </is>
       </c>
     </row>
@@ -8160,7 +8148,7 @@
       </c>
       <c r="I111" s="14" t="inlineStr">
         <is>
-          <t>Nature Reviews Neuroscience — 10% Brain Myth</t>
+          <t>Nature Reviews Neuroscience — The 10% Brain Myth: https://en.wikipedia.org/wiki/Ten_percent_of_brain_myth</t>
         </is>
       </c>
     </row>
@@ -8248,9 +8236,9 @@
       <c r="D113" s="14" t="inlineStr">
         <is>
           <t>Şu an başını kaldırıp gökyüzüne baktığında, Güneş'in hâlâ orada olduğundan gerçekten emin misin? Ya tam şu saniye sessizce söndüyse? İşin en ürpertici kısmı ne biliyor musun? Bunu tam sekiz dakika yirmi saniye boyunca ruhun bile duymayacak. Çünkü Güneş'ten çıkan son ışık gözüne ulaşana kadar gökyüzü masmavi kalır. Ama sekizinci dakikanın sonunda gökyüzü bir anda zifiri karanlığa gömülür ve Dünya yörüngeden kopup buzlu boşluğa savrulur. Peki sen o son sekiz dakikayı dışarıda gökyüzünü izleyerek mi geçirirdin, yoksa yeraltı sığınaklarına inerek mi? Yorumlarda buluşalım.
-Peki böyle bir kırılma anında sen sekiz dakikalık son gün ışığını dışarıda izlemeyi mi seçerdin, yoksa doğrudan yeraltı sığınaklarına inmeyi mi? Yorumlarda buluşalım! 👇
-📚 Kaynak: https://en.wikipedia.org/wiki/Sunlight
-🎨 Görseller temsilîdir (AI üretimi ve NASA/ESO uzay arşivi).
+💬 Peki böyle bir kırılma anında sen sekiz dakikalık son gün ışığını dışarıda izlemeyi mi seçerdin, yoksa doğrudan yeraltı sığınaklarına inmeyi mi? Yorumlarda buluşalım! 👇
+📚 Kaynak: NASA / Wikipedia — Sunlight (Işık Hızı ve Güneş Işığı Süresi): https://en.wikipedia.org/wiki/Sunlight
+🎨 Görseller temsilîdir (AI üretimi).
 #bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
@@ -8276,7 +8264,7 @@
       </c>
       <c r="I113" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Sunlight</t>
+          <t>NASA / Wikipedia — Sunlight (Işık Hızı ve Güneş Işığı Süresi): https://en.wikipedia.org/wiki/Sunlight</t>
         </is>
       </c>
     </row>
@@ -8299,9 +8287,9 @@
       <c r="D114" s="14" t="inlineStr">
         <is>
           <t>Gece gökyüzüne baktığında, Ay'ın hep aynı yerde durduğunu sanıyorsun değil mi? Peki ya Ay Dünya'ya doğru yaklaşmaya başlasaydı ne olurdu? İlk başta gökyüzünde devasa görünürdü ama hemen ardından kütle çekim kabusu başlardı. Okyanuslar yüzlerce metre yükselip kıyı şehirlerini yutardı. Dünya'ya on sekiz bin kilometre mesafedeki Roche sınırına girdiği anda ise Ay gökyüzünde paramparça olur ve Dünya'nın etrafında tıpkı Satürn gibi parlak bir halka oluştururdu. Peki sen gökyüzünde Satürn gibi dev bir halka görmeyi mi isterdin, yoksa Ay'ın olduğu yerde kalmasını mı? Yorumlarda buluşalım.
-Peki sen gökyüzünde dev bir Ay yerine Satürn gibi muazzam bir halka görmeyi mi isterdin, yoksa Ay'ın olduğu yerde kalmasını mı? Yorumlarda buluşalım! 👇
-📚 Kaynak: https://en.wikipedia.org/wiki/Roche_limit
-🎨 Görseller temsilîdir (AI üretimi ve NASA/ESO uzay arşivi).
+💬 Peki sen gökyüzünde dev bir Ay yerine Satürn gibi muazzam bir halka görmeyi mi isterdin, yoksa Ay'ın olduğu yerde kalmasını mı? Yorumlarda buluşalım! 👇
+📚 Kaynak: NASA / Wikipedia — Roche Limit (Gelgit Parçalanma Sınırı): https://en.wikipedia.org/wiki/Roche_limit
+🎨 Görseller temsilîdir (AI üretimi).
 #bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
@@ -8327,7 +8315,7 @@
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Roche_limit</t>
+          <t>NASA / Wikipedia — Roche Limit (Gelgit Parçalanma Sınırı): https://en.wikipedia.org/wiki/Roche_limit</t>
         </is>
       </c>
     </row>
@@ -8350,9 +8338,9 @@
       <c r="D115" s="14" t="inlineStr">
         <is>
           <t>Uzayda tek başına süzülürken bir anda ağlamaya başlasan gözyaşlarının yanağından aşağı süzüleceğini mi sanıyorsun? Hiç de öyle olmaz. Dünya'da gözyaşını aşağı çeken şey yerçekimidir. Ama uzayın ağırlıksız boşluğunda, su moleküllerini birbirine kenetleyen yüzey gerilimi tek patron haline gelir. Gözünden çıkan her damla, akmak yerine göz pınarının tam üzerinde şeffaf, titreyen bir su küresine dönüşür ve sen bir bezle silene kadar yüzünden asla ayrılmaz. Peki sen yerçekimsiz ortamda yaşamayı deneyimlemek mi isterdin, yoksa ayağının yere bastığı Dünya'da kalmayı mı? Yorumlarda buluşalım.
-Peki sen yerçekimsiz ortamda haftalarca yaşamayı deneyimlemek mi isterdin, yoksa ayağının sağlamca yere bastığı Dünya'da kalmayı mı? Yorumlarda buluşalım! 👇
-📚 Kaynak: https://en.wikipedia.org/wiki/Surface_tension
-🎨 Görseller temsilîdir (AI üretimi ve NASA/ESO uzay arşivi).
+💬 Peki sen yerçekimsiz ortamda haftalarca yaşamayı deneyimlemek mi isterdin, yoksa ayağının sağlamca yere bastığı Dünya'da kalmayı mı? Yorumlarda buluşalım! 👇
+📚 Kaynak: CSA / Wikipedia — Surface Tension in Microgravity (Uzayda Yüzey Gerilimi): https://en.wikipedia.org/wiki/Surface_tension
+🎨 Görseller temsilîdir (AI üretimi).
 #bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
@@ -8378,7 +8366,7 @@
       </c>
       <c r="I115" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Surface_tension</t>
+          <t>CSA / Wikipedia — Surface Tension in Microgravity (Uzayda Yüzey Gerilimi): https://en.wikipedia.org/wiki/Surface_tension</t>
         </is>
       </c>
     </row>
@@ -8401,9 +8389,9 @@
       <c r="D116" s="14" t="inlineStr">
         <is>
           <t>Gündüz vakti masmavi gökyüzünde bir anda ikinci bir Güneş'in parladığını hayal et. Dünya'ya elli ışık yılı mesafede dev bir yıldız süpernova olarak patlasaydı tam olarak bunu yaşardık. Haftalarca geceleri bile gökyüzü hiç kararmazdı. Ama asıl tehlike o parlak ışık değil, görünmez gama ışınları olurdu. Üst atmosferdeki ozon tabakası hızla erir ve yüzeye inen radyasyon okyanuslardaki besin zincirini altüst ederdi. Peki böyle bir kozmik patlama görsen, önce teleskopla izlemeye mi koşardın yoksa radyasyondan korunacak bir yer mi arardın? Yorumlarda buluşalım.
-Peki böyle bir kozmik patlama görsen önce teleskopla izlemeye mi koşardın, yoksa radyasyondan korunacak bir yer mi arardın? Yorumlarda buluşalım! 👇
-📚 Kaynak: https://en.wikipedia.org/wiki/Near-Earth_supernova
-🎨 Görseller temsilîdir (AI üretimi ve NASA/ESO uzay arşivi).
+💬 Peki böyle bir kozmik patlama görsen önce teleskopla izlemeye mi koşardın, yoksa radyasyondan korunacak bir yer mi arardın? Yorumlarda buluşalım! 👇
+📚 Kaynak: NASA / Wikipedia — Near-Earth Supernova (Yakın Süpernova Etkileri): https://en.wikipedia.org/wiki/Near-Earth_supernova
+🎨 Görseller temsilîdir (AI üretimi).
 #bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
@@ -8429,7 +8417,7 @@
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Near-Earth_supernova</t>
+          <t>NASA / Wikipedia — Near-Earth Supernova (Yakın Süpernova Etkileri): https://en.wikipedia.org/wiki/Near-Earth_supernova</t>
         </is>
       </c>
     </row>
@@ -8452,9 +8440,9 @@
       <c r="D117" s="14" t="inlineStr">
         <is>
           <t>Elindeki küçücük bir çay kaşığının Everest Dağı kadar ağır olabileceğini hayal edebilir misin? Evrenin en ekstrem canavarı olan nötron yıldızlarıyla tanış. Dev bir yıldız çöktüğünde çekirdeği o kadar korkunç sıkışır ki, koca bir Güneş sadece yirmi kilometre çapında bir küreye hapsolur. Bu yıldızdan alacağın tek bir çay kaşığı madde tam bir milyar ton ağırlığındadır. Onu Dünya'da elinden bıraksan toprağı ve kayaları delip doğrudan gezegenin çekirdeğine kadar batardı. Peki seni uzayda en çok büyüleyen şey, kara delikler mi yoksa nötron yıldızları mı? Yorumlarda buluşalım.
-Peki seni uzayda en çok büyüleyen şey her şeyi yutan kara delikler mi, yoksa bu inanılmaz yoğunluktaki nötron yıldızları mı? Yorumlarda buluşalım! 👇
-📚 Kaynak: https://en.wikipedia.org/wiki/Neutron_star
-🎨 Görseller temsilîdir (AI üretimi ve NASA/ESO uzay arşivi).
+💬 Peki seni uzayda en çok büyüleyen şey her şeyi yutan kara delikler mi, yoksa bu inanılmaz yoğunluktaki nötron yıldızları mı? Yorumlarda buluşalım! 👇
+📚 Kaynak: NASA / Wikipedia — Neutron Star (Nötron Yıldızı Yoğunluğu): https://en.wikipedia.org/wiki/Neutron_star
+🎨 Görseller temsilîdir (AI üretimi).
 #bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
@@ -8480,7 +8468,7 @@
       </c>
       <c r="I117" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Neutron_star</t>
+          <t>NASA / Wikipedia — Neutron Star (Nötron Yıldızı Yoğunluğu): https://en.wikipedia.org/wiki/Neutron_star</t>
         </is>
       </c>
     </row>
@@ -8503,7 +8491,10 @@
       <c r="D118" s="14" t="inlineStr">
         <is>
           <t>Bir ses kaydında kendi sesini duyduğun an “Bu gerçekten benim sesim mi?” diye yüzünü buruşturduğun oldu mu? Merak etme, yalnız değilsin. Sen konuşurken sesini iki farklı yoldan aynı anda duyarsın. Hem havadan kulağına gelen dalgalarla, hem de ses tellerinin kafatası kemiklerini titreştirerek iç kulağına gönderdiği kemik iletimiyle. Kafatası kemiklerin bas frekansları güçlendirdiği için kendi sesini hep daha tok ve derin algılarsın. Ama kayıtta, kemik iletimi devreden çıkar ve başkalarının duyduğu o gerçek sesine yüzleşirsin. Peki sen kayıtlarda kendi sesini dinlemeye alışabildin mi, yoksa duyunca hemen kapatıyor musun? Yorumlarda buluşalım.
-Kaynak: https://en.wikipedia.org/wiki/Bone_conduction</t>
+💬 Peki sen kendi sesini kayıtlarda dinlemeye alışabildin mi, yoksa duyunca hâlâ hemen kapatıyor musun? Yorumlarda buluşalım! 👇
+📚 Kaynak: Journal of Voice / Wikipedia — Bone Conduction (Kafatası Kemik İletimi): https://en.wikipedia.org/wiki/Bone_conduction
+🎨 Görseller temsilîdir (AI üretimi).
+#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
       <c r="E118" s="14" t="inlineStr">
@@ -8528,7 +8519,7 @@
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Bone_conduction</t>
+          <t>Journal of Voice / Wikipedia — Bone Conduction (Kafatası Kemik İletimi): https://en.wikipedia.org/wiki/Bone_conduction</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8542,10 @@
       <c r="D119" s="14" t="inlineStr">
         <is>
           <t>Yüksek bir balkonun ya da uçurumun kenarından aşağı baktığında içinde hiçbir kötü niyet yokken bile bir anda “Ya şimdi atlarsam” diye ürpertici bir düşünce geçti mi? Fransızların “boşluğun çağrısı” dediği bu durum aslında beyninin aşırı hızlı çalışan bir hayatta kalma alarmıdır. Beynin kenara yaklaştığında denge merkezine “Geri çekil, tehlikedesin” sinyali gönderir. Bilinçli zihnin ise bu ani geri çekilme refleksini sanki aşağı atlamak istemişim de kendimi zor tutmuşum gibi yanlış yorumlar. Peki sen yüksek bir yerden aşağı baktığında o ürpertiyi hissediyor musun, yoksa yüksekten hiç etkilenmeyenlerden misin? Yorumlarda buluşalım.
-Kaynak: https://en.wikipedia.org/wiki/The_imp_of_the_perverse</t>
+💬 Peki sen yüksek bir yerden aşağı baktığında o ürpertiyi hissediyor musun, yoksa yüksekten hiç etkilenmeyenlerden misin? Yorumlarda buluşalım! 👇
+📚 Kaynak: Journal of Affective Disorders / Wikipedia — High Place Phenomenon (Boşluğun Çağrısı): https://en.wikipedia.org/wiki/The_imp_of_the_perverse
+🎨 Görseller temsilîdir (AI üretimi).
+#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
       <c r="E119" s="14" t="inlineStr">
@@ -8576,7 +8570,7 @@
       </c>
       <c r="I119" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/The_imp_of_the_perverse</t>
+          <t>Journal of Affective Disorders / Wikipedia — High Place Phenomenon (Boşluğun Çağrısı): https://en.wikipedia.org/wiki/The_imp_of_the_perverse</t>
         </is>
       </c>
     </row>
@@ -8599,7 +8593,10 @@
       <c r="D120" s="14" t="inlineStr">
         <is>
           <t>Çok acı bir biber ısırdığında ağzının alev alev yandığını hissediyorsun ya, sana dilinin aslında hiç yanmadığını, tamamen beyninin kandırıldığını söylesem? Biberin içindeki kapsaisin molekülü dokularına fiziksel bir zarar vermez. Sadece dilindeki 43 derecenin üzerindeki sıcaklıklarda açılan ısı alıcılarına gizlice kilitlenir ve beynine ağzın kaynar suyla yanıyor diye sahte bir alarm gönderir. Üstelik kapsaisin suda çözünmediği için su içmek yangını ağzının her yerine yayar. Peki acı yediğinde senin ilk refleksin soğuk suya sarılmak mı oluyor, yoksa ayrana koşmak mı? Yorumlarda buluşalım.
-Kaynak: https://en.wikipedia.org/wiki/Capsaicin</t>
+💬 Peki acı yediğinde senin ilk refleksin soğuk suya sarılmak mı oluyor, yoksa yoğurt ve ayrana koşmak mı? Yorumlarda buluşalım! 👇
+📚 Kaynak: Nature (Caterina et al.) / Wikipedia — Capsaicin &amp; TRPV1 Receptor: https://en.wikipedia.org/wiki/Capsaicin
+🎨 Görseller temsilîdir (AI üretimi).
+#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
       <c r="E120" s="14" t="inlineStr">
@@ -8624,7 +8621,7 @@
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Capsaicin</t>
+          <t>Nature (Caterina et al.) / Wikipedia — Capsaicin &amp; TRPV1 Receptor: https://en.wikipedia.org/wiki/Capsaicin</t>
         </is>
       </c>
     </row>
@@ -8647,7 +8644,10 @@
       <c r="D121" s="14" t="inlineStr">
         <is>
           <t>Dondurucu bir soğukta dışarı çıktığında, ne kadar sıkmaya çalışırsan çalış, dişlerinin kendi kendine takırdadığı oldu mu? Bunu durduramazsın. Çünkü o an kontrol beynindeki hipotalamus adlı gizli termostata geçer. İç sıcaklığın milimetrik olarak düştüğü anda, beynin kaslarını saniyede defalarca kasılıp gevşemeye zorlayarak acil ısı üretir. Çene kasların vücudunun en güçlü ve beynine en yakın kas grubu olduğu için bu titreme en şiddetli orada hissedilir ve dişlerin birbirine vurur. Peki sen dondurucu kış soğuğuna daha kolay dayananlardan mısın, yoksa yaz sıcağını tercih edenlerden mi? Yorumlarda buluşalım.
-Kaynak: https://en.wikipedia.org/wiki/Shivering</t>
+💬 Peki sen dondurucu kış soğuğuna daha kolay dayananlardan mısın, yoksa kavurucu yaz sıcağını tercih edenlerden mi? Yorumlarda buluşalım! 👇
+📚 Kaynak: NIH / Wikipedia — Shivering &amp; Hypothalamic Thermoregulation (İrade Dışı Titreme): https://en.wikipedia.org/wiki/Shivering
+🎨 Görseller temsilîdir (AI üretimi).
+#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
       <c r="E121" s="14" t="inlineStr">
@@ -8672,7 +8672,7 @@
       </c>
       <c r="I121" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Shivering</t>
+          <t>NIH / Wikipedia — Shivering &amp; Hypothalamic Thermoregulation (İrade Dışı Titreme): https://en.wikipedia.org/wiki/Shivering</t>
         </is>
       </c>
     </row>
@@ -8695,7 +8695,10 @@
       <c r="D122" s="14" t="inlineStr">
         <is>
           <t>Herkesin içinde bir anda utandığında neden kolların değil de sadece yanakların ve kulakların alev alev kızarır? Üstelik sakın kızarma dedikçe daha da kıpkırmızı olursun. Charles Darwin'in tüm duyguların en insaniye olanı dediği bu tepki vücudunun gizli dürüstlük mekanizmasıdır. Utandığın saniye beynin ani bir adrenalin salgılar ve sadece yüzündeki özel kılcal damarlar genişleyerek cildinin altına sıcak kan hücum eder. Evrimsel olarak bu tek kelime etmeden çevrendekilere hata yaptım ve farkındayım demenin sessiz yoludur. Peki sen utandığında sakin kalabilenlerden misin, yoksa saniyesinde kızaranlardan mı? Yorumlarda buluşalım.
-Kaynak: https://en.wikipedia.org/wiki/Blushing</t>
+💬 Peki sen utandığında rengini belli etmeden sakin kalabilenlerden misin, yoksa saniyesinde pancar gibi kızaranlardan mı? Yorumlarda buluşalım! 👇
+📚 Kaynak: Charles Darwin / Wikipedia — Blushing Physiology (Yüz Kızarması Mekanizması): https://en.wikipedia.org/wiki/Blushing
+🎨 Görseller temsilîdir (AI üretimi).
+#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
       <c r="E122" s="14" t="inlineStr">
@@ -8720,7 +8723,7 @@
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Blushing</t>
+          <t>Charles Darwin / Wikipedia — Blushing Physiology (Yüz Kızarması Mekanizması): https://en.wikipedia.org/wiki/Blushing</t>
         </is>
       </c>
     </row>
@@ -8743,8 +8746,9 @@
       <c r="D123" s="14" t="inlineStr">
         <is>
           <t>Dünya üzerinde öyle ıssız bir nokta var ki, orada bir tekneyle mahsur kalsan sana en yakın insanlar Dünya'da değil, uzayda olurdu. Güney Pasifik Okyanusu'nun ortasındaki Point Nemo ile tanış. Burası en yakın kara parçasına tam 2.688 kilometre uzaklıktadır. Buna karşılık, Uluslararası Uzay İstasyonu başının sadece 400 kilometre üzerinden geçer. Yani gökyüzündeki astronotlar, sana karadaki insanlardan tam 6 kat daha yakındır. Uzay ajansları da ömrü biten uyduları bu dev su mezarlığına düşürür. Peki sen böyle mutlak bir sessizliğin ortasında tek başına bir gece geçirmeye cesaret edebilir miydin, yoksa kıyıdan asla ayrılmaz mıydın? Yorumlarda buluşalım!
-Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
-Kaynak: https://en.wikipedia.org/wiki/Pole_of_inaccessibility
+💬 Peki sen böyle mutlak bir sessizliğin ortasında tek başına bir gece geçirmeye cesaret edebilir miydin, yoksa kıyıdan asla ayrılmaz mıydın? Yorumlarda buluşalım! 👇
+📚 Kaynak: NOAA / Wikipedia — Oceanic Pole of Inaccessibility (Point Nemo): https://en.wikipedia.org/wiki/Pole_of_inaccessibility
+🎨 Görseller temsilîdir (AI üretimi).
 #bilgidozu #shorts #doğa #okyanus #coğrafya #bilim</t>
         </is>
       </c>
@@ -8770,7 +8774,7 @@
       </c>
       <c r="I123" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Pole_of_inaccessibility</t>
+          <t>NOAA / Wikipedia — Oceanic Pole of Inaccessibility (Point Nemo): https://en.wikipedia.org/wiki/Pole_of_inaccessibility</t>
         </is>
       </c>
     </row>
@@ -8793,8 +8797,9 @@
       <c r="D124" s="14" t="inlineStr">
         <is>
           <t>Antarktika'nın bembeyaz, dondurucu buzullarının arasından bir anda kıpkırmızı, kan renginde bir şelalenin aktığını görsen ne düşünürdün? Taylor Buzulu'ndaki bu ürpertici manzaranın sebebi kan ya da yosun değil, tam 5 milyon yıl önce buzulun 400 metre altına hapsolmuş antik bir yeraltı gölü. Bu gizli gölün suyu okyanuslardan 3 kat daha tuzlu olduğu için dondurucu soğukta bile asla donmuyor. İçindeki yoğun demir, buzulun çatlaklarından sızıp milyonlarca yıl sonra ilk kez havadaki oksijenle temas ettiği anda saniyeler içinde paslanarak kıpkırmızı bir şelaleye dönüşüyor. Peki sen Antarktika'daki bu gizemli buzulun yanına gitmeyi mi seçerdin, yoksa sıcak bir tropik adada kalmayı mı? Yorumlarda buluşalım!
-Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
-Kaynak: https://en.wikipedia.org/wiki/Blood_Falls
+💬 Peki sen Antarktika'daki bu gizemli buzulun yanına gitmeyi mi seçerdin, yoksa sıcak bir tropik adada kalmayı mı? Yorumlarda buluşalım! 👇
+📚 Kaynak: NSF / Wikipedia — Blood Falls, Taylor Glacier Antarctica (Kan Şelalesi): https://en.wikipedia.org/wiki/Blood_Falls
+🎨 Görseller temsilîdir (AI üretimi).
 #bilgidozu #shorts #antarktika #doğa #coğrafya #bilim</t>
         </is>
       </c>
@@ -8820,7 +8825,7 @@
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Blood_Falls</t>
+          <t>NSF / Wikipedia — Blood Falls, Taylor Glacier Antarctica (Kan Şelalesi): https://en.wikipedia.org/wiki/Blood_Falls</t>
         </is>
       </c>
     </row>
@@ -8843,8 +8848,9 @@
       <c r="D125" s="14" t="inlineStr">
         <is>
           <t>Tam 5,5 milyon yıl boyunca güneş ışığının tek bir zerresini bile görmemiş, mühürlü bir yeraltı dünyasının kapısını açtığını hayal et. Romanya'da tesadüfen keşfedilen Movile Mağarası, dış dünyadan tamamen kopuk bambaşka bir gezegen gibi. İçerideki havada oksijen normalin yarısından bile az, atmosferi ise zehirli hidrojen sülfür ve karbondioksitle dolu. Güneş ışığı olmadığı için buradaki yaşam tamamen kimyasal enerjiyle ayakta kalıyor ve içeride gözleri yok olmuş, sadece buraya özgü 30'dan fazla gizemli canlı türü yaşıyor. Peki özel bir oksijen tüpüyle bu karanlık mağaraya inme şansın olsa içeri adım atar mıydın, yoksa kapısını mühürlü mü bırakırdın? Yorumlarda buluşalım!
-Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
-Kaynak: https://en.wikipedia.org/wiki/Movile_Cave
+💬 Peki özel bir oksijen tüpüyle bu karanlık mağaraya inme şansın olsa içeri adım atar mıydın, yoksa kapısını mühürlü mü bırakırdın? Yorumlarda buluşalım! 👇
+📚 Kaynak: BBC / Wikipedia — Movile Cave Chemosynthesis Ecosystem (Movile Mağarası): https://en.wikipedia.org/wiki/Movile_Cave
+🎨 Görseller temsilîdir (AI üretimi).
 #bilgidozu #shorts #mağara #doğa #biyoloji #bilim</t>
         </is>
       </c>
@@ -8870,7 +8876,7 @@
       </c>
       <c r="I125" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Movile_Cave</t>
+          <t>BBC / Wikipedia — Movile Cave Chemosynthesis Ecosystem (Movile Mağarası): https://en.wikipedia.org/wiki/Movile_Cave</t>
         </is>
       </c>
     </row>
@@ -8893,8 +8899,9 @@
       <c r="D126" s="14" t="inlineStr">
         <is>
           <t>Şu gördüğün neon sarısı ve zümrüt yeşili göller başka bir gezegene değil, Dünya üzerindeki en tehlikeli cehenneme ait. Etiyopya'daki Danakil Çöküntüsü'nde yer alan Dallol Volkanı, deniz seviyesinin 48 metre altında kaynayan dev bir kimya laboratuvarı gibidir. Yerin altındaki kızgın magma, kalın tuz ve kükürt yataklarıyla buluştuğunda, yüzeye akü asidinden bile daha yakıcı kaynar sular ve zehirli klor gazları fışkırır. Burada maskesiz uzun süre nefes almak bile imkânsızdır. Peki sen uzaylı bir gezegeni andıran bu yeri uzaktan dronelarla izlemeyi mi seçerdin, yoksa özel koruyucu kıyafetle yanına kadar yürümeyi mi? Yorumlarda buluşalım!
-Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
-Kaynak: https://en.wikipedia.org/wiki/Dallol_(hydrothermal_system)
+💬 Peki sen uzaylı bir gezegeni andıran bu yeri uzaktan dronelarla izlemeyi mi seçerdin, yoksa özel koruyucu kıyafetle yanına kadar yürümeyi mi? Yorumlarda buluşalım! 👇
+📚 Kaynak: Nature Ecology &amp; Evolution / Wikipedia — Dallol Hydrothermal System: https://en.wikipedia.org/wiki/Dallol_(hydrothermal_system)
+🎨 Görseller temsilîdir (AI üretimi).
 #bilgidozu #shorts #volkan #doğa #coğrafya #bilim</t>
         </is>
       </c>
@@ -8920,7 +8927,7 @@
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Dallol_(hydrothermal_system)</t>
+          <t>Nature Ecology &amp; Evolution / Wikipedia — Dallol Hydrothermal System: https://en.wikipedia.org/wiki/Dallol_(hydrothermal_system)</t>
         </is>
       </c>
     </row>
@@ -8943,8 +8950,9 @@
       <c r="D127" s="14" t="inlineStr">
         <is>
           <t>Yerin tam 2.224 metre altına, yani üst üste dizilmiş 7 Eyfel Kulesi derinliğine karanlık bir kuyudan indiğini hayal et. Kafkas Dağları'ndaki Krubera Mağarası, Dünya'nın bilinen en derin uçurumlarından biridir. Buraya inen mağaracıların en dibe ulaşması haftalar sürer ve içeride yeraltı şelaleleriyle buz gibi su tünelleri vardır. En şaşırtıcı olanı ise, 2.000 metre derinlikteki o dondurucu ve ışıksız sularda bile dış dünyayı hiç görmemiş şeffaf canlıların yaşamaya devam etmesidir. Peki sana sınırsız ekipman verilse okyanusun en derin çukuruna dalmayı mı seçerdin, yoksa Dünya'nın en derin mağarasına inmeyi mi? Yorumlarda buluşalım!
-Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
-Kaynak: https://en.wikipedia.org/wiki/Krubera_Cave
+💬 Peki sana sınırsız ekipman verilse okyanusun en derin çukuruna dalmayı mı seçerdin, yoksa Dünya'nın en derin mağarasına inmeyi mi? Yorumlarda buluşalım! 👇
+📚 Kaynak: National Geographic / Wikipedia — Krubera Cave (Dünya'nın En Derin Mağaraları): https://en.wikipedia.org/wiki/Krubera_Cave
+🎨 Görseller temsilîdir (AI üretimi).
 #bilgidozu #shorts #mağara #doğa #keşif #bilim</t>
         </is>
       </c>
@@ -8970,7 +8978,7 @@
       </c>
       <c r="I127" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Krubera_Cave</t>
+          <t>National Geographic / Wikipedia — Krubera Cave (Dünya'nın En Derin Mağaraları): https://en.wikipedia.org/wiki/Krubera_Cave</t>
         </is>
       </c>
     </row>
@@ -8993,8 +9001,8 @@
       <c r="D128" s="14" t="inlineStr">
         <is>
           <t>Denizin dibinde iki bin yıl boyunca paslanmış bir Yunan batığından, modern saatler kadar karmaşık dişlilere sahip antik bir bilgisayar çıktığını biliyor muydun?
-Peki sence antik dünyada bunun gibi henüz keşfedemediğimiz başka yüksek teknolojiler de var mıdır, yoksa bu tek bir dahinin eseri miydi? Yorumlarda buluşalım! 👇
-📚 Kaynak: https://en.wikipedia.org/wiki/Antikythera_mechanism
+💬 Peki sence antik dünyada bunun gibi henüz keşfedemediğimiz başka yüksek teknolojiler de var mıdır, yoksa bu tek bir dahinin eseri miydi? Yorumlarda buluşalım! 👇
+📚 Kaynak: Nature / Wikipedia — Antikythera Mechanism (2.100 Yıllık Antik Analog Bilgisayar): https://en.wikipedia.org/wiki/Antikythera_mechanism
 🎨 Görseller temsilîdir (AI üretimi).
 #bilgidozu #shorts #tarih #arkeoloji #bilim</t>
         </is>
@@ -9021,7 +9029,7 @@
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Antikythera_mechanism</t>
+          <t>Nature / Wikipedia — Antikythera Mechanism (2.100 Yıllık Antik Analog Bilgisayar): https://en.wikipedia.org/wiki/Antikythera_mechanism</t>
         </is>
       </c>
     </row>
@@ -9044,8 +9052,8 @@
       <c r="D129" s="14" t="inlineStr">
         <is>
           <t>Kapadokya'nın altında, yirmi bin insanın hayvanları ve erzaklarıyla birlikte haftalarca hiç yeryüzüne çıkmadan yaşayabildiği sekiz katlı dev bir yeraltı şehri var: Derinkuyu.
-Peki sen tehlike anında haftalarca böyle bir yeraltı şehrinde yaşayabilir miydin, yoksa kapalı alanda daralır mıydın? Yorumlarda buluşalım! 👇
-📚 Kaynak: https://en.wikipedia.org/wiki/Derinkuyu_underground_city
+💬 Peki sen tehlike anında haftalarca böyle bir yeraltı şehrinde yaşayabilir miydin, yoksa kapalı alanda daralır mıydın? Yorumlarda buluşalım! 👇
+📚 Kaynak: UNESCO / Wikipedia — Derinkuyu Underground City (Derinkuyu Yeraltı Şehri): https://en.wikipedia.org/wiki/Derinkuyu_underground_city
 🎨 Görseller temsilîdir (AI üretimi).
 #bilgidozu #shorts #tarih #arkeoloji #bilim</t>
         </is>
@@ -9072,7 +9080,7 @@
       </c>
       <c r="I129" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Derinkuyu_underground_city</t>
+          <t>UNESCO / Wikipedia — Derinkuyu Underground City (Derinkuyu Yeraltı Şehri): https://en.wikipedia.org/wiki/Derinkuyu_underground_city</t>
         </is>
       </c>
     </row>
@@ -9095,8 +9103,8 @@
       <c r="D130" s="14" t="inlineStr">
         <is>
           <t>Dünyanın en iyi şifre çözücüleri, dilbilimcileri ve yapay zekâları bir araya geldi ama altı yüz yıllık bu kitabın tek bir cümlesini bile okuyamadı: Voynich El Yazması.
-Peki sence bu kitap unutulmuş gizli bir bilimin şifreli kaydı mı, yoksa tarihin en zekice kurgulanmış bilmecesi mi? Yorumlarda buluşalım! 👇
-📚 Kaynak: https://en.wikipedia.org/wiki/Voynich_manuscript
+💬 Peki sence bu kitap unutulmuş gizli bir bilimin şifreli kaydı mı, yoksa tarihin en zekice kurgulanmış bilmecesi mi? Yorumlarda buluşalım! 👇
+📚 Kaynak: Yale Beinecke Library / Wikipedia — Voynich Manuscript (Voynich El Yazması): https://en.wikipedia.org/wiki/Voynich_manuscript
 🎨 Görseller temsilîdir (AI üretimi).
 #bilgidozu #shorts #tarih #arkeoloji #bilim</t>
         </is>
@@ -9123,7 +9131,7 @@
       </c>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Voynich_manuscript</t>
+          <t>Yale Beinecke Library / Wikipedia — Voynich Manuscript (Voynich El Yazması): https://en.wikipedia.org/wiki/Voynich_manuscript</t>
         </is>
       </c>
     </row>
@@ -9146,8 +9154,8 @@
       <c r="D131" s="14" t="inlineStr">
         <is>
           <t>Deniz seviyesinden üç bin sekiz yüz metre yüksekte, aralarına jilet bile girmeyecek kadar kusursuz kesilmiş yüz tonluk taş bloklar düşün: Puma Punku.
-Peki sence antik ustalar bu kusursuz taş işçiliğini sabırlı el aletleriyle mi başardı, yoksa bugün unuttuğumuz özel bir teknikleri mi vardı? Yorumlarda buluşalım! 👇
-📚 Kaynak: https://en.wikipedia.org/wiki/Pumapunku
+💬 Peki sence antik ustalar bu kusursuz taş işçiliğini sabırlı el aletleriyle mi başardı, yoksa bugün unuttuğumuz özel bir teknikleri mi vardı? Yorumlarda buluşalım! 👇
+📚 Kaynak: UNESCO / Wikipedia — Pumapunku Andesite Megaliths (Puma Punku H-Blokları): https://en.wikipedia.org/wiki/Pumapunku
 🎨 Görseller temsilîdir (AI üretimi).
 #bilgidozu #shorts #tarih #arkeoloji #bilim</t>
         </is>
@@ -9174,7 +9182,7 @@
       </c>
       <c r="I131" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Pumapunku</t>
+          <t>UNESCO / Wikipedia — Pumapunku Andesite Megaliths (Puma Punku H-Blokları): https://en.wikipedia.org/wiki/Pumapunku</t>
         </is>
       </c>
     </row>
@@ -9197,8 +9205,8 @@
       <c r="D132" s="14" t="inlineStr">
         <is>
           <t>Dünyanın Yedi Harikası'ndan biri sayılan Babil'in Asma Bahçeleri'nin aslında hiçbir zaman Babil'de olmadığını duysan ne derdin?
-Peki sen geçmişe gidebilsen önce bu efsanevi Asma Bahçeleri'ni mi görmek isterdin, yoksa İskenderiye Kütüphanesi'ni mi? Yorumlarda buluşalım! 👇
-📚 Kaynak: https://en.wikipedia.org/wiki/Hanging_Gardens_of_Babylon
+💬 Peki sen geçmişe gidebilsen önce bu efsanevi Asma Bahçeleri'ni mi görmek isterdin, yoksa İskenderiye Kütüphanesi'ni mi? Yorumlarda buluşalım! 👇
+📚 Kaynak: Oxford University (Stephanie Dalley) / Wikipedia — Hanging Gardens of Babylon: https://en.wikipedia.org/wiki/Hanging_Gardens_of_Babylon
 🎨 Görseller temsilîdir (AI üretimi).
 #bilgidozu #shorts #tarih #arkeoloji #bilim</t>
         </is>
@@ -9225,7 +9233,7 @@
       </c>
       <c r="I132" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Hanging_Gardens_of_Babylon</t>
+          <t>Oxford University (Stephanie Dalley) / Wikipedia — Hanging Gardens of Babylon: https://en.wikipedia.org/wiki/Hanging_Gardens_of_Babylon</t>
         </is>
       </c>
     </row>
@@ -9282,9 +9290,9 @@
       </c>
       <c r="I133" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Bone_conduction
-https://en.wikipedia.org/wiki/The_imp_of_the_perverse
-https://en.wikipedia.org/wiki/Capsaicin</t>
+          <t>1) Kemik İletimi — Wikipedia: https://en.wikipedia.org/wiki/Bone_conduction
+2) Boşluğun Çağrısı — Wikipedia: https://en.wikipedia.org/wiki/The_imp_of_the_perverse
+3) Kapsaisin &amp; TRPV1 — Wikipedia: https://en.wikipedia.org/wiki/Capsaicin</t>
         </is>
       </c>
     </row>

--- a/bilgidozu_yukleme_tablosu.xlsx
+++ b/bilgidozu_yukleme_tablosu.xlsx
@@ -3021,56 +3021,64 @@
       <c r="M41" s="4" t="inlineStr"/>
     </row>
     <row r="42" ht="42" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>YÜKLENMEDİ</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>video_35.mp4</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>Vücudundaki Tüm Acıyı Yöneten Beynin Kendisi Acı Hissedemez! 🧠⚡ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>Elimiz yandığında ya da dizimiz çarptığında acıyı bize hissettiren merkez beyindir; ancak beyin dokusunun kendisinde tek bir ağrı alıcısı (nosiseptör) bile yoktur! Baş ağrısı dediğimiz şey aslında beynin kendisinden değil, onu saran zarlar ve kan damarlarındaki gerilimden kaynaklanır.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #beyin #bilim</t>
         </is>
       </c>
-      <c r="F42" s="6" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t>bilgidozu, beyin, ağrı, nörobilim, anatomi, insanvücudu, ilginçbilgiler, bilim, shorts</t>
         </is>
       </c>
-      <c r="G42" s="6" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t>Beyin dokusunun hiç acı hissetmediğini biliyor muydun? 🧠⚡ Bilenler '1', yeni öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H42" s="7" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr">
         <is>
           <t>Beyin ve Psikoloji</t>
         </is>
       </c>
-      <c r="I42" s="6" t="inlineStr">
+      <c r="I42" s="3" t="inlineStr">
         <is>
           <t>BrainFacts (Society for Neuroscience): https://www.brainfacts.org/</t>
         </is>
       </c>
-      <c r="J42" s="6" t="inlineStr"/>
-      <c r="K42" s="7" t="inlineStr"/>
-      <c r="L42" s="7" t="inlineStr"/>
-      <c r="M42" s="7" t="inlineStr"/>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>https://youtu.be/da3y0_DfWYQ</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24 18:22</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr"/>
+      <c r="M42" s="4" t="inlineStr"/>
     </row>
     <row r="43" ht="42" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
@@ -8107,7 +8115,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24 17:55</t>
+          <t>2026-10-24 18:22</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -8116,11 +8124,11 @@
         </is>
       </c>
       <c r="E2" s="4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>video_34.mp4 yayınlandı (https://youtu.be/tCuQNw_V74I) · Sıradaki: video_35.mp4</t>
+          <t>video_35.mp4 yayınlandı (https://youtu.be/da3y0_DfWYQ) · Sıradaki: video_36.mp4</t>
         </is>
       </c>
     </row>
@@ -8456,7 +8464,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Sıradaki Shorts: video_35.mp4 · Sıradaki Uzun Video: uzun_video_8.mp4 yayın saatini bekliyor.</t>
+          <t>Sıradaki Shorts: video_36.mp4 · Sıradaki Uzun Video: uzun_video_8.mp4 yayın saatini bekliyor.</t>
         </is>
       </c>
     </row>

--- a/bilgidozu_yukleme_tablosu.xlsx
+++ b/bilgidozu_yukleme_tablosu.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M134"/>
+  <dimension ref="A1:M135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8100,6 +8100,56 @@
       <c r="L134" s="5" t="n"/>
       <c r="M134" s="5" t="n"/>
     </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>video_131.mp4</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Kâğıt Kesiği Neden Bu Kadar Acıtır? 🩹 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Küçücük bir kâğıt kesiği neden beklediğinden çok daha fazla can yakar? Parmak uçlarımız dokunma ve ağrıyı algılayan yoğun duyu sinirleriyle donatılmıştır. Üstelik çıplak gözle düz görünen kâğıt kenarı, mikroskobik ölçekte lifli ve düzensiz bir yapıya sahiptir; gün boyu ellerimizi kullanmaya devam etmemiz de hassaslaşan dokuyu tekrar tekrar uyarır.
+Senin de başına geldi mi? Yorumlarda buluşalım! 👇
+📚 Kaynak: Dr. Hayley Goldbach (UCLA Dermatology) / BBC Future &amp; StatPearls
+🎨 Görseller temsilîdir (AI bilimsel canlandırma).</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #insanvücudu #beyin #bilim</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>bilgi dozu, kağıt kesiği, insan vücudu, duyu sinirleri, bilim, ilginç bilgiler, shorts</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Senin de başına geldi mi? En son ne zaman kâğıt kesiği yaşadın, yorumlara yaz! 👇</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>İnsan Vücudu ve Beyin</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>BBC Future (Dr. H. Goldbach, UCLA, 2016) &amp; StatPearls</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilgidozu_yukleme_tablosu.xlsx
+++ b/bilgidozu_yukleme_tablosu.xlsx
@@ -62,7 +62,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -87,6 +87,12 @@
         <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0E0E0"/>
+        <bgColor rgb="00E0E0E0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -101,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -120,6 +126,15 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -486,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M135"/>
+  <dimension ref="A1:M137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3382,178 +3397,178 @@
       <c r="M48" s="3" t="n"/>
     </row>
     <row r="49" ht="42" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>video_47.mp4</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>Mide Asidi Bu Kadar Güçlüyken Miden Kendi Kendini Neden Sindirmez? 🧬🔥 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D49" s="8" t="inlineStr">
         <is>
           <t>Mide asidin yediğin en sert besinleri bile parçalayacak kadar güçlüdür; peki miden kendi kendini neden sindirmez? Midenin iç duvarını kaplayan hücreler sürekli olarak bikarbonat bakımından zengin kalın bir mukus tabakası salgılar ve yüzey hücreleri birkaç günde bir yenilenerek asidin dokuya zarar vermesini engeller.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E49" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #vücut #bilim</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F49" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, mide, mideasidi, insanvücudu, biyoloji, anatomi, ilginçbilgiler, bilim, shorts</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G49" s="8" t="inlineStr">
         <is>
           <t>Midenin iç yüzeyinin birkaç günde bir tamamen yenilendiğini biliyor muydun? 🧬🔥 Duyanlar '1', yeni öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="H49" s="8" t="inlineStr">
         <is>
           <t>Biyoloji ve Vücut</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="I49" s="8" t="inlineStr">
         <is>
           <t>Wikipedia — Gastric mucosal barrier: https://en.wikipedia.org/wiki/Gastric_mucosal_barrier</t>
         </is>
       </c>
-      <c r="J49" s="5" t="n"/>
-      <c r="K49" s="5" t="n"/>
-      <c r="L49" s="5" t="n"/>
-      <c r="M49" s="5" t="n"/>
+      <c r="J49" s="8" t="n"/>
+      <c r="K49" s="8" t="n"/>
+      <c r="L49" s="8" t="n"/>
+      <c r="M49" s="8" t="n"/>
     </row>
     <row r="50" ht="42" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>video_52.mp4</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>Vücudunda Kanla Değil, Doğrudan Havadan Nefes Alan Tek Doku! 👁️🌬️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D50" s="8" t="inlineStr">
         <is>
           <t>Gözünün en dışındaki şeffaf kornea tabakasında tek bir kan damarı bile yoktur ve oksijenini doğrudan havadan alır! Işığın göze engelsiz girmesi için kornea tamamen cam gibi saydam kalmak zorundadır; bu yüzden kan damarları yerine gözyaşı filminde çözünen atmosfer oksijeniyle doğrudan nefes alır.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E50" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #vücut #bilim</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F50" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, göz, kornea, insanvücudu, biyoloji, anatomi, ilginçbilgiler, bilim, shorts</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G50" s="8" t="inlineStr">
         <is>
           <t>Gözümüzün kornea tabakasının doğrudan havadan oksijen aldığını biliyor muydun? 👁️🌬️ Duyanlar '1', ilk kez öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="H50" s="8" t="inlineStr">
         <is>
           <t>Biyoloji ve Vücut</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="I50" s="8" t="inlineStr">
         <is>
           <t>Wikipedia — Cornea Physiology: https://en.wikipedia.org/wiki/Cornea</t>
         </is>
       </c>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="n"/>
-      <c r="L50" s="5" t="n"/>
-      <c r="M50" s="5" t="n"/>
+      <c r="J50" s="8" t="n"/>
+      <c r="K50" s="8" t="n"/>
+      <c r="L50" s="8" t="n"/>
+      <c r="M50" s="8" t="n"/>
     </row>
     <row r="51" ht="42" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>video_57.mp4</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>Bacak Kasların Yorulurken Kalbin Neden Hayat Boyu Hiç Yorulmaz? ❤️⚡ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D51" s="8" t="inlineStr">
         <is>
           <t>Koşarken bacak kasların dakikalar içinde yorulup yanarken kalbinin hayat boyu hiç durmadan atıp yorulmamasının sırrı hücre yapısındadır! İskelet kaslarında enerji üreten mitokondriler hücre hacminin yalnızca küçük bir kısmını kaplarken, kalp kası hücrelerinin yaklaşık %40'ı mitokondrilerle doludur ve her atışta enerjisini anında yeniler.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E51" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #vücut #bilim</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F51" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, kalp, mitokondri, insanvücudu, biyoloji, anatomi, ilginçbilgiler, bilim, shorts</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="G51" s="8" t="inlineStr">
         <is>
           <t>Kalp kası hücrelerinin %40'ının enerji santrali mitokondrilerden oluştuğunu biliyor muydun? ❤️⚡ Duyanlar '1', ilk kez öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="H51" s="8" t="inlineStr">
         <is>
           <t>Biyoloji ve Vücut</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="I51" s="8" t="inlineStr">
         <is>
           <t>NIH PMC / Wikipedia — Cardiac muscle: https://en.wikipedia.org/wiki/Cardiac_muscle</t>
         </is>
       </c>
-      <c r="J51" s="5" t="n"/>
-      <c r="K51" s="5" t="n"/>
-      <c r="L51" s="5" t="n"/>
-      <c r="M51" s="5" t="n"/>
+      <c r="J51" s="8" t="n"/>
+      <c r="K51" s="8" t="n"/>
+      <c r="L51" s="8" t="n"/>
+      <c r="M51" s="8" t="n"/>
     </row>
     <row r="52" ht="42" customHeight="1">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>video_62.mp4</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>Suda Kalan Parmaklarımız Su Çektiği İçin Buruşmuyor! İşte Gerçek Sebebi! 🖐️💧 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D52" s="8" t="inlineStr">
         <is>
           <t>Suda fazla kaldığında parmak uçlarının suyu sünger gibi çektiği için buruştuğunu sanıyorsan yanılıyorsun! Beynin yönettiği bu otonom sinir sistemi refleksinin sırrını inceliyoruz.
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -3562,53 +3577,53 @@
 #bilgidozu #shorts #insanvücudu #biyoloji #bilim</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E52" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #insanvücudu #biyoloji #bilim</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F52" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, suda parmak buruşması, sinir sistemi, insan vücudu, biyoloji, bilim, shorts</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="G52" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🖐️💧</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="H52" s="8" t="inlineStr">
         <is>
           <t>Biyoloji ve Vücut</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="I52" s="8" t="inlineStr">
         <is>
           <t>Brain, Behavior and Evolution / Newcastle University: https://en.wikipedia.org/wiki/Wrinkle#Water-immersion_wrinkling</t>
         </is>
       </c>
-      <c r="J52" s="5" t="n"/>
-      <c r="K52" s="5" t="n"/>
-      <c r="L52" s="5" t="n"/>
-      <c r="M52" s="5" t="n"/>
+      <c r="J52" s="8" t="n"/>
+      <c r="K52" s="8" t="n"/>
+      <c r="L52" s="8" t="n"/>
+      <c r="M52" s="8" t="n"/>
     </row>
     <row r="53" ht="42" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>video_67.mp4</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>İnsan Vücudu Karanlıkta Gerçekten Işık Saçıyor Ama Gözümüz Göremiyor! ✨🧠 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D53" s="8" t="inlineStr">
         <is>
           <t>İnsan vücudunun karanlıkta tıpkı ateş böcekleri gibi gerçekten ışık saçtığını ama gözlerimizin bunu göremediğini biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -3617,53 +3632,53 @@
 #bilgidozu #shorts #insanvücudu #biyoloji #bilim</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E53" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #insanvücudu #biyoloji #bilim</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="F53" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, insan biyolüminesansı, insan vücudu ışık saçıyor, biyoloji, bilim, shorts</t>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="G53" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! ✨🧠</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="H53" s="8" t="inlineStr">
         <is>
           <t>Biyoloji ve Vücut</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="I53" s="8" t="inlineStr">
         <is>
           <t>PLOS ONE (2009) — Kobayashi et al.: https://journals.plos.org/plosone/article?id=10.1371/journal.pone.0006256</t>
         </is>
       </c>
-      <c r="J53" s="5" t="n"/>
-      <c r="K53" s="5" t="n"/>
-      <c r="L53" s="5" t="n"/>
-      <c r="M53" s="5" t="n"/>
+      <c r="J53" s="8" t="n"/>
+      <c r="K53" s="8" t="n"/>
+      <c r="L53" s="8" t="n"/>
+      <c r="M53" s="8" t="n"/>
     </row>
     <row r="54" ht="42" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>video_72.mp4</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>Ses Kaydındaki Sesin Sana Neden Bambaşka Geliyor? 🎙️🧠 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D54" s="8" t="inlineStr">
         <is>
           <t>Ses kaydını dinlediğinde kendi sesinin sana neden bambaşka ve tuhaf geldiğini biliyor muydun? Kafatası kemik iletimi ile hava iletimi arasındaki farkı inceliyoruz.
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -3672,53 +3687,53 @@
 #bilgidozu #shorts #psikoloji #beyin #bilim</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E54" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #psikoloji #beyin #bilim</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F54" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, ses kaydı, kendi sesimiz, kemik iletimi, beyin, psikoloji, insan vücudu, shorts</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="G54" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🎙️🧠</t>
         </is>
       </c>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="H54" s="8" t="inlineStr">
         <is>
           <t>Beyin ve Psikoloji</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="I54" s="8" t="inlineStr">
         <is>
           <t>Journal of Voice / Wikipedia — Auditory Bone Conduction: https://en.wikipedia.org/wiki/Bone_conduction</t>
         </is>
       </c>
-      <c r="J54" s="5" t="n"/>
-      <c r="K54" s="5" t="n"/>
-      <c r="L54" s="5" t="n"/>
-      <c r="M54" s="5" t="n"/>
+      <c r="J54" s="8" t="n"/>
+      <c r="K54" s="8" t="n"/>
+      <c r="L54" s="8" t="n"/>
+      <c r="M54" s="8" t="n"/>
     </row>
     <row r="55" ht="42" customHeight="1">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>video_77.mp4</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>Gözlerin Açıkken Hapşırmak Neden İmkansız? Beynin O Salisede Ne Yapar? 🤧👁️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D55" s="8" t="inlineStr">
         <is>
           <t>Gözlerin açıkken hapşırmanın neden neredeyse imkansız olduğunu ve beyninin o salisede neden göz kapaklarını kilitlediğini biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -3727,53 +3742,53 @@
 #bilgidozu #shorts #insanvücudu #refleks #bilim</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="E55" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #insanvücudu #refleks #bilim</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="F55" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, hapşırma refleksi, göz açık hapşırmak, insan vücudu, beyin, bilim, shorts</t>
         </is>
       </c>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="G55" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🤧👁️</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr">
+      <c r="H55" s="8" t="inlineStr">
         <is>
           <t>Biyoloji ve Vücut</t>
         </is>
       </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="I55" s="8" t="inlineStr">
         <is>
           <t>Texas A&amp;M College of Medicine / Wikipedia — Photic &amp; Autonomic Sneezing Reflex: https://en.wikipedia.org/wiki/Sneeze</t>
         </is>
       </c>
-      <c r="J55" s="5" t="n"/>
-      <c r="K55" s="5" t="n"/>
-      <c r="L55" s="5" t="n"/>
-      <c r="M55" s="5" t="n"/>
+      <c r="J55" s="8" t="n"/>
+      <c r="K55" s="8" t="n"/>
+      <c r="L55" s="8" t="n"/>
+      <c r="M55" s="8" t="n"/>
     </row>
     <row r="56" ht="42" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>video_106.mp4</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>Kendi Sesini Kayıtta Dinleyince Neden Tuhaf Gelir? 🎙️🧠 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D56" s="8" t="inlineStr">
         <is>
           <t>Bir ses kaydında kendi sesini duyduğun an “Bu gerçekten benim sesim mi?” diye yüzünü buruşturduğun oldu mu? Merak etme, yalnız değilsin. Sen konuşurken sesini iki farklı yoldan aynı anda duyarsın. Hem havadan kulağına gelen dalgalarla, hem de ses tellerinin kafatası kemiklerini titreştirerek iç kulağına gönderdiği kemik iletimiyle. Kafatası kemiklerin bas frekansları güçlendirdiği için kendi sesini hep daha tok ve derin algılarsın. Ama kayıtta, kemik iletimi devreden çıkar ve başkalarının duyduğu o gerçek sesine yüzleşirsin. Peki sen kayıtlarda kendi sesini dinlemeye alışabildin mi, yoksa duyunca hemen kapatıyor musun? Yorumlarda buluşalım.
 💬 Peki sen kendi sesini kayıtlarda dinlemeye alışabildin mi, yoksa duyunca hâlâ hemen kapatıyor musun? Yorumlarda buluşalım! 👇
@@ -3782,53 +3797,53 @@
 #bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E56" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="F56" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, shorts, nörobilim, insan bedeni, psikoloji, bilim</t>
         </is>
       </c>
-      <c r="G56" s="5" t="inlineStr">
+      <c r="G56" s="8" t="inlineStr">
         <is>
           <t>Peki sen kendi sesini kayıtlarda dinlemeye alışabildin mi, yoksa duyunca hâlâ hemen kapatıyor musun? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H56" s="5" t="inlineStr">
+      <c r="H56" s="8" t="inlineStr">
         <is>
           <t>Nörobilim ve İnsan Bedeni</t>
         </is>
       </c>
-      <c r="I56" s="5" t="inlineStr">
+      <c r="I56" s="8" t="inlineStr">
         <is>
           <t>Journal of Voice / Wikipedia — Bone Conduction (Kafatası Kemik İletimi): https://en.wikipedia.org/wiki/Bone_conduction</t>
         </is>
       </c>
-      <c r="J56" s="5" t="n"/>
-      <c r="K56" s="5" t="n"/>
-      <c r="L56" s="5" t="n"/>
-      <c r="M56" s="5" t="n"/>
+      <c r="J56" s="8" t="n"/>
+      <c r="K56" s="8" t="n"/>
+      <c r="L56" s="8" t="n"/>
+      <c r="M56" s="8" t="n"/>
     </row>
     <row r="57" ht="42" customHeight="1">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>video_107.mp4</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>Yüksek Bir Yerden Bakınca Beyin Neden 'Atla' Diye Fısıldar? 🧗‍♂️🧠 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D57" s="8" t="inlineStr">
         <is>
           <t>Yüksek bir balkonun ya da uçurumun kenarından aşağı baktığında içinde hiçbir kötü niyet yokken bile bir anda “Ya şimdi atlarsam” diye ürpertici bir düşünce geçti mi? Fransızların “boşluğun çağrısı” dediği bu durum aslında beyninin aşırı hızlı çalışan bir hayatta kalma alarmıdır. Beynin kenara yaklaştığında denge merkezine “Geri çekil, tehlikedesin” sinyali gönderir. Bilinçli zihnin ise bu ani geri çekilme refleksini sanki aşağı atlamak istemişim de kendimi zor tutmuşum gibi yanlış yorumlar. Peki sen yüksek bir yerden aşağı baktığında o ürpertiyi hissediyor musun, yoksa yüksekten hiç etkilenmeyenlerden misin? Yorumlarda buluşalım.
 💬 Peki sen yüksek bir yerden aşağı baktığında o ürpertiyi hissediyor musun, yoksa yüksekten hiç etkilenmeyenlerden misin? Yorumlarda buluşalım! 👇
@@ -3837,53 +3852,53 @@
 #bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
+      <c r="E57" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="F57" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, shorts, nörobilim, insan bedeni, psikoloji, bilim</t>
         </is>
       </c>
-      <c r="G57" s="5" t="inlineStr">
+      <c r="G57" s="8" t="inlineStr">
         <is>
           <t>Peki sen yüksek bir yerden aşağı baktığında o ürpertiyi hissediyor musun, yoksa yüksekten hiç etkilenmeyenlerden misin? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr">
+      <c r="H57" s="8" t="inlineStr">
         <is>
           <t>Nörobilim ve İnsan Bedeni</t>
         </is>
       </c>
-      <c r="I57" s="5" t="inlineStr">
+      <c r="I57" s="8" t="inlineStr">
         <is>
           <t>Journal of Affective Disorders / Wikipedia — High Place Phenomenon (Boşluğun Çağrısı): https://en.wikipedia.org/wiki/The_imp_of_the_perverse</t>
         </is>
       </c>
-      <c r="J57" s="5" t="n"/>
-      <c r="K57" s="5" t="n"/>
-      <c r="L57" s="5" t="n"/>
-      <c r="M57" s="5" t="n"/>
+      <c r="J57" s="8" t="n"/>
+      <c r="K57" s="8" t="n"/>
+      <c r="L57" s="8" t="n"/>
+      <c r="M57" s="8" t="n"/>
     </row>
     <row r="58" ht="42" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>video_108.mp4</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>Acı Biber Aslında Ağzını Yakmaz — Beynini Nasıl Kandırır? 🌶️🔥 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D58" s="8" t="inlineStr">
         <is>
           <t>Çok acı bir biber ısırdığında ağzının alev alev yandığını hissediyorsun ya, sana dilinin aslında hiç yanmadığını, tamamen beyninin kandırıldığını söylesem? Biberin içindeki kapsaisin molekülü dokularına fiziksel bir zarar vermez. Sadece dilindeki 43 derecenin üzerindeki sıcaklıklarda açılan ısı alıcılarına gizlice kilitlenir ve beynine ağzın kaynar suyla yanıyor diye sahte bir alarm gönderir. Üstelik kapsaisin suda çözünmediği için su içmek yangını ağzının her yerine yayar. Peki acı yediğinde senin ilk refleksin soğuk suya sarılmak mı oluyor, yoksa ayrana koşmak mı? Yorumlarda buluşalım.
 💬 Peki acı yediğinde senin ilk refleksin soğuk suya sarılmak mı oluyor, yoksa yoğurt ve ayrana koşmak mı? Yorumlarda buluşalım! 👇
@@ -3892,53 +3907,53 @@
 #bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
+      <c r="E58" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="F58" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, shorts, nörobilim, insan bedeni, psikoloji, bilim</t>
         </is>
       </c>
-      <c r="G58" s="5" t="inlineStr">
+      <c r="G58" s="8" t="inlineStr">
         <is>
           <t>Peki acı yediğinde senin ilk refleksin soğuk suya sarılmak mı oluyor, yoksa yoğurt ve ayrana koşmak mı? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H58" s="5" t="inlineStr">
+      <c r="H58" s="8" t="inlineStr">
         <is>
           <t>Nörobilim ve İnsan Bedeni</t>
         </is>
       </c>
-      <c r="I58" s="5" t="inlineStr">
+      <c r="I58" s="8" t="inlineStr">
         <is>
           <t>Nature (Caterina et al.) / Wikipedia — Capsaicin &amp; TRPV1 Receptor: https://en.wikipedia.org/wiki/Capsaicin</t>
         </is>
       </c>
-      <c r="J58" s="5" t="n"/>
-      <c r="K58" s="5" t="n"/>
-      <c r="L58" s="5" t="n"/>
-      <c r="M58" s="5" t="n"/>
+      <c r="J58" s="8" t="n"/>
+      <c r="K58" s="8" t="n"/>
+      <c r="L58" s="8" t="n"/>
+      <c r="M58" s="8" t="n"/>
     </row>
     <row r="59" ht="42" customHeight="1">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>video_109.mp4</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C59" s="8" t="inlineStr">
         <is>
           <t>Soğukta Dişlerin Neden İrade Dışı Takırdar? 🥶🦷 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D59" s="8" t="inlineStr">
         <is>
           <t>Dondurucu bir soğukta dışarı çıktığında, ne kadar sıkmaya çalışırsan çalış, dişlerinin kendi kendine takırdadığı oldu mu? Bunu durduramazsın. Çünkü o an kontrol beynindeki hipotalamus adlı gizli termostata geçer. İç sıcaklığın milimetrik olarak düştüğü anda, beynin kaslarını saniyede defalarca kasılıp gevşemeye zorlayarak acil ısı üretir. Çene kasların vücudunun en güçlü ve beynine en yakın kas grubu olduğu için bu titreme en şiddetli orada hissedilir ve dişlerin birbirine vurur. Peki sen dondurucu kış soğuğuna daha kolay dayananlardan mısın, yoksa yaz sıcağını tercih edenlerden mi? Yorumlarda buluşalım.
 💬 Peki sen dondurucu kış soğuğuna daha kolay dayananlardan mısın, yoksa kavurucu yaz sıcağını tercih edenlerden mi? Yorumlarda buluşalım! 👇
@@ -3947,53 +3962,53 @@
 #bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="E59" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="F59" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, shorts, nörobilim, insan bedeni, psikoloji, bilim</t>
         </is>
       </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="G59" s="8" t="inlineStr">
         <is>
           <t>Peki sen dondurucu kış soğuğuna daha kolay dayananlardan mısın, yoksa kavurucu yaz sıcağını tercih edenlerden mi? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr">
+      <c r="H59" s="8" t="inlineStr">
         <is>
           <t>Nörobilim ve İnsan Bedeni</t>
         </is>
       </c>
-      <c r="I59" s="5" t="inlineStr">
+      <c r="I59" s="8" t="inlineStr">
         <is>
           <t>NIH / Wikipedia — Shivering &amp; Hypothalamic Thermoregulation (İrade Dışı Titreme): https://en.wikipedia.org/wiki/Shivering</t>
         </is>
       </c>
-      <c r="J59" s="5" t="n"/>
-      <c r="K59" s="5" t="n"/>
-      <c r="L59" s="5" t="n"/>
-      <c r="M59" s="5" t="n"/>
+      <c r="J59" s="8" t="n"/>
+      <c r="K59" s="8" t="n"/>
+      <c r="L59" s="8" t="n"/>
+      <c r="M59" s="8" t="n"/>
     </row>
     <row r="60" ht="42" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>video_110.mp4</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>Utandığında Neden Sadece Yüzün ve Kulakların Kızarır? 😳🧠 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D60" s="8" t="inlineStr">
         <is>
           <t>Herkesin içinde bir anda utandığında neden kolların değil de sadece yanakların ve kulakların alev alev kızarır? Üstelik sakın kızarma dedikçe daha da kıpkırmızı olursun. Charles Darwin'in tüm duyguların en insaniye olanı dediği bu tepki vücudunun gizli dürüstlük mekanizmasıdır. Utandığın saniye beynin ani bir adrenalin salgılar ve sadece yüzündeki özel kılcal damarlar genişleyerek cildinin altına sıcak kan hücum eder. Evrimsel olarak bu tek kelime etmeden çevrendekilere hata yaptım ve farkındayım demenin sessiz yoludur. Peki sen utandığında sakin kalabilenlerden misin, yoksa saniyesinde kızaranlardan mı? Yorumlarda buluşalım.
 💬 Peki sen utandığında rengini belli etmeden sakin kalabilenlerden misin, yoksa saniyesinde pancar gibi kızaranlardan mı? Yorumlarda buluşalım! 👇
@@ -4002,53 +4017,53 @@
 #bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="E60" s="5" t="inlineStr">
+      <c r="E60" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="F60" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, shorts, nörobilim, insan bedeni, psikoloji, bilim</t>
         </is>
       </c>
-      <c r="G60" s="5" t="inlineStr">
+      <c r="G60" s="8" t="inlineStr">
         <is>
           <t>Peki sen utandığında rengini belli etmeden sakin kalabilenlerden misin, yoksa saniyesinde pancar gibi kızaranlardan mı? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H60" s="5" t="inlineStr">
+      <c r="H60" s="8" t="inlineStr">
         <is>
           <t>Nörobilim ve İnsan Bedeni</t>
         </is>
       </c>
-      <c r="I60" s="5" t="inlineStr">
+      <c r="I60" s="8" t="inlineStr">
         <is>
           <t>Charles Darwin / Wikipedia — Blushing Physiology (Yüz Kızarması Mekanizması): https://en.wikipedia.org/wiki/Blushing</t>
         </is>
       </c>
-      <c r="J60" s="5" t="n"/>
-      <c r="K60" s="5" t="n"/>
-      <c r="L60" s="5" t="n"/>
-      <c r="M60" s="5" t="n"/>
+      <c r="J60" s="8" t="n"/>
+      <c r="K60" s="8" t="n"/>
+      <c r="L60" s="8" t="n"/>
+      <c r="M60" s="8" t="n"/>
     </row>
     <row r="61" ht="42" customHeight="1">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>video_91.mp4</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C61" s="8" t="inlineStr">
         <is>
           <t>Vücudundaki Hücrelerin Yarısından Fazlası Aslında Bakteri! 🦠🧬 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D61" s="8" t="inlineStr">
         <is>
           <t>İnsan bedeninde yaklaşık 30 trilyon insan hücresine karşılık 38 trilyondan fazla dost bakteri hücresi yaşar.
 Peki vücudunuzda kendi hücrelerinizden daha fazla bakteri yaşaması size nasıl hissettiriyor? Yorumlara yazın! 👇
@@ -4057,53 +4072,53 @@
 #bilgidozu #shorts #insanvücudu #bilim #biyoloji</t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr">
+      <c r="E61" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #insanvücudu #bilim #biyoloji</t>
         </is>
       </c>
-      <c r="F61" s="5" t="inlineStr">
+      <c r="F61" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, insan vücudu, bakteri, biyoloji, bilim, shorts</t>
         </is>
       </c>
-      <c r="G61" s="5" t="inlineStr">
+      <c r="G61" s="8" t="inlineStr">
         <is>
           <t>Peki vücudunuzda kendi hücrelerinizden daha fazla bakteri yaşaması size nasıl hissettiriyor? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H61" s="5" t="inlineStr">
+      <c r="H61" s="8" t="inlineStr">
         <is>
           <t>İnsan Vücudu ve Psikoloji</t>
         </is>
       </c>
-      <c r="I61" s="5" t="inlineStr">
+      <c r="I61" s="8" t="inlineStr">
         <is>
           <t>PLOS Biology (Sender et al., 2016) — Revised Estimates for Human &amp; Bacteria Cells: https://journals.plos.org/plosbiology/article?id=10.1371/journal.pbio.1002533</t>
         </is>
       </c>
-      <c r="J61" s="5" t="n"/>
-      <c r="K61" s="5" t="n"/>
-      <c r="L61" s="5" t="n"/>
-      <c r="M61" s="5" t="n"/>
+      <c r="J61" s="8" t="n"/>
+      <c r="K61" s="8" t="n"/>
+      <c r="L61" s="8" t="n"/>
+      <c r="M61" s="8" t="n"/>
     </row>
     <row r="62" ht="42" customHeight="1">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>video_100.mp4</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>Beynimizin Sadece Yüzde 10'unu Kullandığımız Efsanesi Yalan! 🧠⚡ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D62" s="8" t="inlineStr">
         <is>
           <t>Modern beyin görüntüleme cihazları gün içinde konuşurken, yürürken ve uyurken beynimizin neredeyse tamamının aktif çalıştığını kanıtlamıştır.
 Siz de yıllarca beynimizin sadece yüzde onunu kullandığımız efsanesine inanmış mıydınız? Yorumlara yazın! 👇
@@ -4112,53 +4127,53 @@
 #bilgidozu #shorts #beyin #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr">
+      <c r="E62" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #beyin #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="F62" s="5" t="inlineStr">
+      <c r="F62" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, beyin, yüzde 10 efsanesi, psikoloji, nörobilim, shorts</t>
         </is>
       </c>
-      <c r="G62" s="5" t="inlineStr">
+      <c r="G62" s="8" t="inlineStr">
         <is>
           <t>Siz de yıllarca beynimizin sadece yüzde onunu kullandığımız efsanesine inanmış mıydınız? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H62" s="5" t="inlineStr">
+      <c r="H62" s="8" t="inlineStr">
         <is>
           <t>İnsan Vücudu ve Psikoloji</t>
         </is>
       </c>
-      <c r="I62" s="5" t="inlineStr">
+      <c r="I62" s="8" t="inlineStr">
         <is>
           <t>Nature Reviews Neuroscience — The 10% Brain Myth: https://en.wikipedia.org/wiki/Ten_percent_of_brain_myth</t>
         </is>
       </c>
-      <c r="J62" s="5" t="n"/>
-      <c r="K62" s="5" t="n"/>
-      <c r="L62" s="5" t="n"/>
-      <c r="M62" s="5" t="n"/>
+      <c r="J62" s="8" t="n"/>
+      <c r="K62" s="8" t="n"/>
+      <c r="L62" s="8" t="n"/>
+      <c r="M62" s="8" t="n"/>
     </row>
     <row r="63" ht="42" customHeight="1">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>video_121.mp4</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>Rüyanda Neden Koşamazsın? Beynin Gece Seni Kilitler! 🧠</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D63" s="8" t="inlineStr">
         <is>
           <t>Rüyanda tehlikeden kaçmaya çalışırken bacaklarının kurşun gibi ağırlaştığını hiç hissettin mi? REM uykusu sırasında beynin uyanıkmış gibi aktif çalışır ancak beyin sapındaki devreler GABA ve glisin aracılığıyla iskelet kaslarına giden motor nöronları geçici olarak kilitler. REM atonisi denilen bu koruyucu mekanizma sayesinde rüyalarını yatakta fiziksel olarak oynamaz ve kendine zarar vermezsin.
 Peki sen rüyanda daha çok koşamadığın mı yoksa bağıramadığın anları mı yaşıyorsun? Yorumlarda buluşalım! 👇
@@ -4167,53 +4182,53 @@
 #bilgidozu #shorts #beyin #uyku #psikoloji #nörobilim #bilim</t>
         </is>
       </c>
-      <c r="E63" s="5" t="inlineStr">
+      <c r="E63" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #beyin #uyku #psikoloji #nörobilim #bilim</t>
         </is>
       </c>
-      <c r="F63" s="5" t="inlineStr">
+      <c r="F63" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, rüyanda neden koşamazsın, rem uykusu, uyku atonisi, beyin, nörobilim, psikoloji, uyku bilimi, ilginç bilgiler, şaşırtıcı gerçekler, bilim, shorts</t>
         </is>
       </c>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="G63" s="8" t="inlineStr">
         <is>
           <t>Peki sen rüyanda daha çok koşamadığın mı yoksa bağıramadığın anları mı yaşıyorsun? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr">
+      <c r="H63" s="8" t="inlineStr">
         <is>
           <t>Beyin ve Psikoloji</t>
         </is>
       </c>
-      <c r="I63" s="5" t="inlineStr">
+      <c r="I63" s="8" t="inlineStr">
         <is>
           <t>https://www.jneurosci.org/content/32/29/9785</t>
         </is>
       </c>
-      <c r="J63" s="5" t="n"/>
-      <c r="K63" s="5" t="n"/>
-      <c r="L63" s="5" t="n"/>
-      <c r="M63" s="5" t="n"/>
+      <c r="J63" s="8" t="n"/>
+      <c r="K63" s="8" t="n"/>
+      <c r="L63" s="8" t="n"/>
+      <c r="M63" s="8" t="n"/>
     </row>
     <row r="64" ht="42" customHeight="1">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>video_83.mp4</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C64" s="8" t="inlineStr">
         <is>
           <t>Sevdiğin Birine Bakınca Göz Bebeğin Neden Otomatik Büyür? 👀❤️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D64" s="8" t="inlineStr">
         <is>
           <t>Hoşlandığımız birine baktığımızda dopamin ve oksitosin etkisiyle sempatik sinir sistemi göz bebeklerimizi istemsizce büyütür.
 Siz konuşurken karşınızdakinin göz bebeklerine dikkat eder misiniz? Yorumlara yazın! 👇
@@ -4222,53 +4237,53 @@
 #bilgidozu #shorts #psikoloji #insanvücudu #bilim</t>
         </is>
       </c>
-      <c r="E64" s="5" t="inlineStr">
+      <c r="E64" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #psikoloji #insanvücudu #bilim</t>
         </is>
       </c>
-      <c r="F64" s="5" t="inlineStr">
+      <c r="F64" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, psikoloji, göz bebeği, insan vücudu, bilim, shorts</t>
         </is>
       </c>
-      <c r="G64" s="5" t="inlineStr">
+      <c r="G64" s="8" t="inlineStr">
         <is>
           <t>Siz konuşurken karşınızdakinin göz bebeklerine dikkat eder misiniz? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H64" s="5" t="inlineStr">
+      <c r="H64" s="8" t="inlineStr">
         <is>
           <t>İnsan Vücudu ve Psikoloji</t>
         </is>
       </c>
-      <c r="I64" s="5" t="inlineStr">
+      <c r="I64" s="8" t="inlineStr">
         <is>
           <t>Hess &amp; Polt (1960) / Wikipedia — Pupillometry Research: https://en.wikipedia.org/wiki/Pupillometry</t>
         </is>
       </c>
-      <c r="J64" s="5" t="n"/>
-      <c r="K64" s="5" t="n"/>
-      <c r="L64" s="5" t="n"/>
-      <c r="M64" s="5" t="n"/>
+      <c r="J64" s="8" t="n"/>
+      <c r="K64" s="8" t="n"/>
+      <c r="L64" s="8" t="n"/>
+      <c r="M64" s="8" t="n"/>
     </row>
     <row r="65" ht="42" customHeight="1">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>uzun_video_8.mp4</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C65" s="8" t="inlineStr">
         <is>
           <t>Okyanusta Kendi Işığını Üreten Canlılar: Soğuk Işık, Av Tuzağı ve Karşı Aydınlatma! 🌊✨ #bilgidozu</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D65" s="8" t="inlineStr">
         <is>
           <t>Güneş ışığının ulaşamadığı derin okyanus sularında kendi ışığını üreten canlıların kimyasal sırrı ne? Denizlerin alacakaranlık kuşağında parlayan biyolüminesans dünyasını inceliyoruz! 🌊✨
 BÖLÜMLER:
@@ -4280,53 +4295,53 @@
 #bilgidozu #okyanus #bilim #biyolüminesans #doğa #denizcanlıları</t>
         </is>
       </c>
-      <c r="E65" s="5" t="inlineStr">
+      <c r="E65" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #bilim</t>
         </is>
       </c>
-      <c r="F65" s="5" t="inlineStr">
+      <c r="F65" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, okyanus, biyolüminesans, derin deniz, fenerbalığı, doğa, biyoloji, bilim, ilginç bilgiler</t>
         </is>
       </c>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="G65" s="8" t="inlineStr">
         <is>
           <t>Derin okyanustaki hangi ışık stratejisi seni en çok şaşırttı? 🌊 1-Soğuk Işık 2-Fener Tuzağı 3-Görünmezlik — Yorumlara yaz! 👇</t>
         </is>
       </c>
-      <c r="H65" s="5" t="inlineStr">
+      <c r="H65" s="8" t="inlineStr">
         <is>
           <t>Uzun — Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I65" s="5" t="inlineStr">
+      <c r="I65" s="8" t="inlineStr">
         <is>
           <t>NOAA Ocean Exploration — Bioluminescence: https://oceanexplorer.noaa.gov/facts/bioluminescence.html Smithsonian Ocean — Bioluminescence: https://ocean.si.edu/ocean-life/fish/bioluminescence</t>
         </is>
       </c>
-      <c r="J65" s="5" t="n"/>
-      <c r="K65" s="5" t="n"/>
-      <c r="L65" s="5" t="n"/>
-      <c r="M65" s="5" t="n"/>
+      <c r="J65" s="8" t="n"/>
+      <c r="K65" s="8" t="n"/>
+      <c r="L65" s="8" t="n"/>
+      <c r="M65" s="8" t="n"/>
     </row>
     <row r="66" ht="42" customHeight="1">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
         <is>
           <t>uzun_video_9.mp4</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C66" s="8" t="inlineStr">
         <is>
           <t>Beynin Seni Ayakta Tutan 3 Gizli Sensörü: İç Kulak Pusulası, Kristaller ve Algı Çatışması! 🧠⚡ #bilgidozu</t>
         </is>
       </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="D66" s="8" t="inlineStr">
         <is>
           <t>Yürürken başını çevirdiğinde görüntü neden titremiyor? Araçta telefon okurken neden miden bulanıyor? Vücudumuzun görünmez denge merkezi olan vestibüler sistemi inceliyoruz! 🧠⚡
 BÖLÜMLER:
@@ -4338,53 +4353,53 @@
 #bilgidozu #beyin #nörobilim #denge #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="E66" s="5" t="inlineStr">
+      <c r="E66" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #bilim</t>
         </is>
       </c>
-      <c r="F66" s="5" t="inlineStr">
+      <c r="F66" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, beyin, nörobilim, denge, içkulak, vestibülersistem, algı, psikoloji, bilim</t>
         </is>
       </c>
-      <c r="G66" s="5" t="inlineStr">
+      <c r="G66" s="8" t="inlineStr">
         <is>
           <t>Arabada veya gemide giderken telefon okuyabiliyor musun, yoksa hemen miden mi bulanıyor? 🚗🧠 Yorumlara yaz! 👇</t>
         </is>
       </c>
-      <c r="H66" s="5" t="inlineStr">
+      <c r="H66" s="8" t="inlineStr">
         <is>
           <t>Uzun — Beyin ve Psikoloji</t>
         </is>
       </c>
-      <c r="I66" s="5" t="inlineStr">
+      <c r="I66" s="8" t="inlineStr">
         <is>
           <t>NIH / NIDCD — Balance Disorders: https://www.nidcd.nih.gov/health/balance-disorders</t>
         </is>
       </c>
-      <c r="J66" s="5" t="n"/>
-      <c r="K66" s="5" t="n"/>
-      <c r="L66" s="5" t="n"/>
-      <c r="M66" s="5" t="n"/>
+      <c r="J66" s="8" t="n"/>
+      <c r="K66" s="8" t="n"/>
+      <c r="L66" s="8" t="n"/>
+      <c r="M66" s="8" t="n"/>
     </row>
     <row r="67" ht="42" customHeight="1">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t>uzun_video_10.mp4</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C67" s="8" t="inlineStr">
         <is>
           <t>Uzay Sessizse NASA'nın Kaydettiği Bu Sesler Ne? Kara Delik Seslerinin Gerçek Sırrı! 🪐🔊 #bilgidozu</t>
         </is>
       </c>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="D67" s="8" t="inlineStr">
         <is>
           <t>Uzay boşluğunda ses yayılmıyorsa NASA'nın paylaştığı kara delik ve galaksi sesleri gerçekte ne? Perseus galaksi kümesindeki gerçek basınç dalgaları ile M87 veri sonifikasyonunun farkını inceliyoruz! 🪐🔊
 BÖLÜMLER:
@@ -4396,53 +4411,53 @@
 #bilgidozu #uzay #nasa #karadelik #astronomi #bilim</t>
         </is>
       </c>
-      <c r="E67" s="5" t="inlineStr">
+      <c r="E67" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #bilim</t>
         </is>
       </c>
-      <c r="F67" s="5" t="inlineStr">
+      <c r="F67" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, uzay, nasa, karadelik, perseus, m87, chandra, astronomi, astrofizik, bilim</t>
         </is>
       </c>
-      <c r="G67" s="5" t="inlineStr">
+      <c r="G67" s="8" t="inlineStr">
         <is>
           <t>Perseus kara deliğinin 57 oktav yükseltilmiş gerçek basınç sesini duymuş muydun? 🕳️🔊 Duyanlar 1, yeni öğrenenler 2 yazsın! 👇</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr">
+      <c r="H67" s="8" t="inlineStr">
         <is>
           <t>Uzun — Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I67" s="5" t="inlineStr">
+      <c r="I67" s="8" t="inlineStr">
         <is>
           <t>NASA — New NASA Black Hole Sonifications: https://www.nasa.gov/universe/new-nasa-black-hole-sonifications-with-a-remix/</t>
         </is>
       </c>
-      <c r="J67" s="5" t="n"/>
-      <c r="K67" s="5" t="n"/>
-      <c r="L67" s="5" t="n"/>
-      <c r="M67" s="5" t="n"/>
+      <c r="J67" s="8" t="n"/>
+      <c r="K67" s="8" t="n"/>
+      <c r="L67" s="8" t="n"/>
+      <c r="M67" s="8" t="n"/>
     </row>
     <row r="68" ht="42" customHeight="1">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
         <is>
           <t>uzun_video_11.mp4</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C68" s="8" t="inlineStr">
         <is>
           <t>Zaman Yukarıda Daha Hızlı Akıyor! Telefonundaki Konum İçin Einstein Neden Gerekli? ⏱️🛰️ #bilgidozu</t>
         </is>
       </c>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="D68" s="8" t="inlineStr">
         <is>
           <t>Telefonundaki mavi konum noktasının doğru çalışması için Einstein'ın özel ve genel görelilik kuramlarının her saniye hesaba katıldığını biliyor muydun? ⏱️🛰️
 BÖLÜMLER:
@@ -4454,53 +4469,53 @@
 #bilgidozu #uzay #zaman #einstein #görelilik #bilim</t>
         </is>
       </c>
-      <c r="E68" s="5" t="inlineStr">
+      <c r="E68" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #bilim</t>
         </is>
       </c>
-      <c r="F68" s="5" t="inlineStr">
+      <c r="F68" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, uzay, zaman, einstein, görelilik, atomsaati, gps, fizik, bilim</t>
         </is>
       </c>
-      <c r="G68" s="5" t="inlineStr">
+      <c r="G68" s="8" t="inlineStr">
         <is>
           <t>Einstein'ın görelilik hesabı olmasa GPS konumunun günde 10 kilometre sapacağını biliyor muydun? ⏱️🛰️ 1 veya 2 yaz! 👇</t>
         </is>
       </c>
-      <c r="H68" s="5" t="inlineStr">
+      <c r="H68" s="8" t="inlineStr">
         <is>
           <t>Uzun — Fizik ve Uzay</t>
         </is>
       </c>
-      <c r="I68" s="5" t="inlineStr">
+      <c r="I68" s="8" t="inlineStr">
         <is>
           <t>NIST — Putting Einstein to the Test: https://www.nist.gov/atomic-clocks/a-powerful-tool-for-science/putting-einstein-test</t>
         </is>
       </c>
-      <c r="J68" s="5" t="n"/>
-      <c r="K68" s="5" t="n"/>
-      <c r="L68" s="5" t="n"/>
-      <c r="M68" s="5" t="n"/>
+      <c r="J68" s="8" t="n"/>
+      <c r="K68" s="8" t="n"/>
+      <c r="L68" s="8" t="n"/>
+      <c r="M68" s="8" t="n"/>
     </row>
     <row r="69" ht="42" customHeight="1">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t>uzun_video_12.mp4</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C69" s="8" t="inlineStr">
         <is>
           <t>Sizin Beğendikleriniz · Bölüm 1: Kargalar, Ahtapotlar, Tardigradlar! 🐙🔬 #bilgidozu</t>
         </is>
       </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="D69" s="8" t="inlineStr">
         <is>
           <t>Sizin Beğendikleriniz serisinin ilk bölümünde üç efsane canlının sıra dışı biyolojisini inceliyoruz: kargaların yüz hafızası ve sosyal öğrenmesi, ahtapotların kollara dağılmış sinir sistemi ile üç kalbi ve tardigradların kriptobiyoz dayanıklılığı.
 BÖLÜMLER:
@@ -4518,27 +4533,27 @@
 #bilgidozu #bilim #doğa #hayvanlar #biyoloji</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr">
+      <c r="E69" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #bilim #doğa #hayvanlar #biyoloji</t>
         </is>
       </c>
-      <c r="F69" s="5" t="inlineStr">
+      <c r="F69" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, kargalar, ahtapot, tardigrad, su ayısı, hayvanlar, doğa, bilim, biyoloji, ilginç bilgiler</t>
         </is>
       </c>
-      <c r="G69" s="5" t="inlineStr">
+      <c r="G69" s="8" t="inlineStr">
         <is>
           <t>Bu 3 olaydan sizi en çok hangisi şaşırttı: 1 mi, 2 mi, 3 mü? Yorumlara yazın! (1 Kargalar, 2 Ahtapotlar, 3 Tardigradlar)</t>
         </is>
       </c>
-      <c r="H69" s="5" t="inlineStr">
+      <c r="H69" s="8" t="inlineStr">
         <is>
           <t>Uzun — Bilim ve Doğa</t>
         </is>
       </c>
-      <c r="I69" s="5" t="inlineStr">
+      <c r="I69" s="8" t="inlineStr">
         <is>
           <t>Kargalar — Marzluff et al. (2012), PNAS: https://www.pnas.org/doi/10.1073/pnas.1206109109
 Kargalar sosyal öğrenme — Cornell et al. (2011), Proc. R. Soc. B: https://doi.org/10.1098/rspb.2011.0957
@@ -4548,28 +4563,28 @@
 Tardigrad Dsup — Hashimoto et al. (2016), Nature Communications: https://www.nature.com/articles/ncomms12808</t>
         </is>
       </c>
-      <c r="J69" s="5" t="n"/>
-      <c r="K69" s="5" t="n"/>
-      <c r="L69" s="5" t="n"/>
-      <c r="M69" s="5" t="n"/>
+      <c r="J69" s="8" t="n"/>
+      <c r="K69" s="8" t="n"/>
+      <c r="L69" s="8" t="n"/>
+      <c r="M69" s="8" t="n"/>
     </row>
     <row r="70" ht="42" customHeight="1">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
         <is>
           <t>uzun_video_13.mp4</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C70" s="8" t="inlineStr">
         <is>
           <t>Beyninin Senden Gizlediği 3 Otomatik Hile (Kendi Sesin, Boşluğun Çağrısı ve Sahte Acı) 🧠🔒 #bilgidozu</t>
         </is>
       </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="D70" s="8" t="inlineStr">
         <is>
           <t>Beyninin senden gizlediği 3 otomatik hileyi tek bir merak yolculuğunda inceliyoruz:
 1 · Kendi Sesin Neden Kayıtta Yabancı Gelir? (Kafatası Kemik İletimi)
@@ -4584,37 +4599,37 @@
 #bilgidozu #bilim #psikoloji #nörobilim #insanbedeni</t>
         </is>
       </c>
-      <c r="E70" s="5" t="inlineStr">
+      <c r="E70" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #bilim #psikoloji #nörobilim #insanbedeni</t>
         </is>
       </c>
-      <c r="F70" s="5" t="inlineStr">
+      <c r="F70" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, nörobilim, psikoloji, insan beyni, kemik iletimi, kapsaisin, bilim, belgesel</t>
         </is>
       </c>
-      <c r="G70" s="5" t="inlineStr">
+      <c r="G70" s="8" t="inlineStr">
         <is>
           <t>Bu 3 beyin hilesinden seni en çok şaşırtan hangisi oldu: Kendi sesinin kemik iletimi mi, yüksek yerdeki Boşluğun Çağrısı mı, yoksa acı biberin sahte yanık alarmı mı? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H70" s="5" t="inlineStr">
+      <c r="H70" s="8" t="inlineStr">
         <is>
           <t>Uzun — Nörobilim ve Psikoloji</t>
         </is>
       </c>
-      <c r="I70" s="5" t="inlineStr">
+      <c r="I70" s="8" t="inlineStr">
         <is>
           <t>1) Kemik İletimi — Wikipedia: https://en.wikipedia.org/wiki/Bone_conduction
 2) Boşluğun Çağrısı — Wikipedia: https://en.wikipedia.org/wiki/The_imp_of_the_perverse
 3) Kapsaisin &amp; TRPV1 — Wikipedia: https://en.wikipedia.org/wiki/Capsaicin</t>
         </is>
       </c>
-      <c r="J70" s="5" t="n"/>
-      <c r="K70" s="5" t="n"/>
-      <c r="L70" s="5" t="n"/>
-      <c r="M70" s="5" t="n"/>
+      <c r="J70" s="8" t="n"/>
+      <c r="K70" s="8" t="n"/>
+      <c r="L70" s="8" t="n"/>
+      <c r="M70" s="8" t="n"/>
     </row>
     <row r="71" ht="42" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
@@ -4677,490 +4692,490 @@
       <c r="M71" s="3" t="n"/>
     </row>
     <row r="72" ht="42" customHeight="1">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
         <is>
           <t>video_41.mp4</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C72" s="8" t="inlineStr">
         <is>
           <t>Eşini Etkilemek İçin Renkli Karnını Açıp Dans Eden Minik Örümcek! 🕷️💃 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="D72" s="8" t="inlineStr">
         <is>
           <t>Avustralya'da yaşayan ve pirinç tanesi kadar küçük olan tavuskuşu örümceği, doğanın en renkli dansçılarından biridir! Erkek örümcekler gökkuşağı renklerindeki karın kanatlarını yelpaze gibi açar, üçüncü bacaklarını havaya kaldırır ve çıkardıkları titreşimlerle kusursuz bir ritim sergiler.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
+      <c r="E72" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr">
+      <c r="F72" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, tavuskuşuörümceği, doğa, hayvanlaralemi, biyoloji, avustralya, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G72" s="5" t="inlineStr">
+      <c r="G72" s="8" t="inlineStr">
         <is>
           <t>Örümceklerden korkanları bile gülümsetecek bir dans değil mi? 🕷️💃 Beğenenler '1' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H72" s="5" t="inlineStr">
+      <c r="H72" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I72" s="5" t="inlineStr">
+      <c r="I72" s="8" t="inlineStr">
         <is>
           <t>Western Australian Museum — Peacock Spider: https://museum.wa.gov.au/explore/articles/peacock-spiders</t>
         </is>
       </c>
-      <c r="J72" s="5" t="n"/>
-      <c r="K72" s="5" t="n"/>
-      <c r="L72" s="5" t="n"/>
-      <c r="M72" s="5" t="n"/>
+      <c r="J72" s="8" t="n"/>
+      <c r="K72" s="8" t="n"/>
+      <c r="L72" s="8" t="n"/>
+      <c r="M72" s="8" t="n"/>
     </row>
     <row r="73" ht="42" customHeight="1">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
         <is>
           <t>video_42.mp4</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C73" s="8" t="inlineStr">
         <is>
           <t>Doğada Havada Asılı Kalıp Geriye Doğru Uçabilen Tek Kuş! 🐦🔄 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="D73" s="8" t="inlineStr">
         <is>
           <t>Sinek kuşları, kuşlar dünyasında uzun süreli olarak geriye doğru uçabilen tek türdür! Kanatlarını sadece aşağı-yukarı değil, omuz eklemlerinden sekiz çizecek şekilde döndürerek saniyede 50 ila 80 kez çırparlar; böylece helikopter gibi havada sabit kalıp geri vitese takabilirler.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr">
+      <c r="E73" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F73" s="5" t="inlineStr">
+      <c r="F73" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, sinekkuşu, kuşlar, doğa, biyoloji, hayvanlaralemi, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G73" s="5" t="inlineStr">
+      <c r="G73" s="8" t="inlineStr">
         <is>
           <t>Sinek kuşunun saniyede 80 kez kanat çırptığını biliyor muydun? 🐦🔄 Bilenler '1', yeni öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H73" s="5" t="inlineStr">
+      <c r="H73" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I73" s="5" t="inlineStr">
+      <c r="I73" s="8" t="inlineStr">
         <is>
           <t>UC Davis — Hummingbird Facts: https://www.ucdavis.edu/</t>
         </is>
       </c>
-      <c r="J73" s="5" t="n"/>
-      <c r="K73" s="5" t="n"/>
-      <c r="L73" s="5" t="n"/>
-      <c r="M73" s="5" t="n"/>
+      <c r="J73" s="8" t="n"/>
+      <c r="K73" s="8" t="n"/>
+      <c r="L73" s="8" t="n"/>
+      <c r="M73" s="8" t="n"/>
     </row>
     <row r="74" ht="42" customHeight="1">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
         <is>
           <t>video_43.mp4</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C74" s="8" t="inlineStr">
         <is>
           <t>Suyun Altından Ağaçtaki Böceği Su Tabancası Gibi Vuran Balık! 🐟🎯 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="D74" s="8" t="inlineStr">
         <is>
           <t>Okçu balığı, suyun dışındaki dallarda duran böcekleri ağzından fırlattığı keskin bir su jetiyle vurarak avlar! Üstelik ışığın sudan havaya geçerken kırılmasını (optik kırılmayı) doğuştan hesaba katar ve hedefine neredeyse sıfır hatayla nişan alır.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E74" s="5" t="inlineStr">
+      <c r="E74" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F74" s="5" t="inlineStr">
+      <c r="F74" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, okçubalığı, balıklar, doğa, fizik, hayvanlaralemi, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G74" s="5" t="inlineStr">
+      <c r="G74" s="8" t="inlineStr">
         <is>
           <t>Işığın kırılmasını hesaplayıp suyla ateş eden bu keskin nişancı balığı duymuş muydun? 🐟🎯 '1' veya '2' yaz! 👇</t>
         </is>
       </c>
-      <c r="H74" s="5" t="inlineStr">
+      <c r="H74" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I74" s="5" t="inlineStr">
+      <c r="I74" s="8" t="inlineStr">
         <is>
           <t>PLOS ONE (Vailati et al., 2012 — Archerfish water jet): https://journals.plos.org/plosone/article?id=10.1371/journal.pone.0047867</t>
         </is>
       </c>
-      <c r="J74" s="5" t="n"/>
-      <c r="K74" s="5" t="n"/>
-      <c r="L74" s="5" t="n"/>
-      <c r="M74" s="5" t="n"/>
+      <c r="J74" s="8" t="n"/>
+      <c r="K74" s="8" t="n"/>
+      <c r="L74" s="8" t="n"/>
+      <c r="M74" s="8" t="n"/>
     </row>
     <row r="75" ht="42" customHeight="1">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
         <is>
           <t>video_44.mp4</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C75" s="8" t="inlineStr">
         <is>
           <t>Sadece Rengini Değil, Derisinin Dokusunu da Anında Değiştiren Canlı! 🦑🎭 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="D75" s="8" t="inlineStr">
         <is>
           <t>Mürekkep balığı, okyanusun en üstün kamuflaj ustalarından biridir! Derisindeki milyonlarca renk hücresiyle saniyede renk ve desen değiştirirken, özel kas kabarcıkları (papilla) sayesinde pürüzsüz derisini anında dikenli bir mercan ya da pütürlü bir kaya dokusuna dönüştürebilir.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E75" s="5" t="inlineStr">
+      <c r="E75" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F75" s="5" t="inlineStr">
+      <c r="F75" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, mürekkepbalığı, okyanus, kamuflaj, doğa, biyoloji, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G75" s="5" t="inlineStr">
+      <c r="G75" s="8" t="inlineStr">
         <is>
           <t>Mürekkep balığının derisini 3 boyutlu olarak kabartıp kaya şekline sokabildiğini biliyor muydun? 🦑🎭 '1' / '2' yaz! 👇</t>
         </is>
       </c>
-      <c r="H75" s="5" t="inlineStr">
+      <c r="H75" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I75" s="5" t="inlineStr">
+      <c r="I75" s="8" t="inlineStr">
         <is>
           <t>Marine Biological Laboratory — Cuttlefish Camouflage: https://www.mbl.edu/</t>
         </is>
       </c>
-      <c r="J75" s="5" t="n"/>
-      <c r="K75" s="5" t="n"/>
-      <c r="L75" s="5" t="n"/>
-      <c r="M75" s="5" t="n"/>
+      <c r="J75" s="8" t="n"/>
+      <c r="K75" s="8" t="n"/>
+      <c r="L75" s="8" t="n"/>
+      <c r="M75" s="8" t="n"/>
     </row>
     <row r="76" ht="42" customHeight="1">
-      <c r="A76" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
         <is>
           <t>video_45.mp4</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
+      <c r="C76" s="8" t="inlineStr">
         <is>
           <t>Flamingolar Aslında Gri Doğar! Peki Tüyleri Neden Pembeleşir? 🦩🦐 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="D76" s="8" t="inlineStr">
         <is>
           <t>Flamingolar dünyaya geldiklerinde pembe değil, gri ve beyaz tüylere sahiptir! İkonik pembe ve mercan renklerini, sulak alanlarda tükettikleri mikroskobik algler ve tuzlu su karideslerinin içindeki 'karotenoid' pigmentlerinin karaciğerde işlenip yeni çıkan tüylere yerleşmesiyle kazanırlar.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E76" s="5" t="inlineStr">
+      <c r="E76" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F76" s="5" t="inlineStr">
+      <c r="F76" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, flamingo, kuşlar, doğa, biyoloji, hayvanlaralemi, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G76" s="5" t="inlineStr">
+      <c r="G76" s="8" t="inlineStr">
         <is>
           <t>Flamingoların gri doğduğunu ve yedikleriyle pembeleştiğini biliyor muydun? 🦩🦐 Bilenler '1', yeni öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H76" s="5" t="inlineStr">
+      <c r="H76" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I76" s="5" t="inlineStr">
+      <c r="I76" s="8" t="inlineStr">
         <is>
           <t>San Diego Zoo — Flamingo Facts: https://animals.sandiegozoo.org/animals/flamingo</t>
         </is>
       </c>
-      <c r="J76" s="5" t="n"/>
-      <c r="K76" s="5" t="n"/>
-      <c r="L76" s="5" t="n"/>
-      <c r="M76" s="5" t="n"/>
+      <c r="J76" s="8" t="n"/>
+      <c r="K76" s="8" t="n"/>
+      <c r="L76" s="8" t="n"/>
+      <c r="M76" s="8" t="n"/>
     </row>
     <row r="77" ht="42" customHeight="1">
-      <c r="A77" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
         <is>
           <t>video_49.mp4</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C77" s="8" t="inlineStr">
         <is>
           <t>Bu Hayvanın Parmak İzi İnsanla O Kadar Aynı ki Mikroskopta Bile Karışıyor! 🐨🔍 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D77" s="5" t="inlineStr">
+      <c r="D77" s="8" t="inlineStr">
         <is>
           <t>Bir koalanın parmak izi insanınkine o kadar kusursuz benzer ki taramalı elektron mikroskobu altında bile ayırt etmek oldukça zordur! Evrimsel olarak bizden milyonlarca yıl önce ayrılmış olsalar da okaliptüs dallarını sıkıca kavrama ihtiyacı, koalalarda insanla neredeyse birebir aynı parmak izi kıvrımlarını oluşturmuştur.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E77" s="5" t="inlineStr">
+      <c r="E77" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F77" s="5" t="inlineStr">
+      <c r="F77" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, koala, parmakizi, doğa, hayvanlaralemi, biyoloji, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G77" s="5" t="inlineStr">
+      <c r="G77" s="8" t="inlineStr">
         <is>
           <t>Koalaların parmak izinin insanla neredeyse birebir aynı olduğunu biliyor muydun? 🐨🔍 Duyanlar '1', ilk kez öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H77" s="5" t="inlineStr">
+      <c r="H77" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I77" s="5" t="inlineStr">
+      <c r="I77" s="8" t="inlineStr">
         <is>
           <t>Wikipedia — Koala (Fingerprints): https://en.wikipedia.org/wiki/Koala</t>
         </is>
       </c>
-      <c r="J77" s="5" t="n"/>
-      <c r="K77" s="5" t="n"/>
-      <c r="L77" s="5" t="n"/>
-      <c r="M77" s="5" t="n"/>
+      <c r="J77" s="8" t="n"/>
+      <c r="K77" s="8" t="n"/>
+      <c r="L77" s="8" t="n"/>
+      <c r="M77" s="8" t="n"/>
     </row>
     <row r="78" ht="42" customHeight="1">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
         <is>
           <t>video_50.mp4</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
+      <c r="C78" s="8" t="inlineStr">
         <is>
           <t>Mikrodalga Fırın Yemeği İçeriden Dışarıya Doğru Pişirmez! İşte Gerçek! ⚡🔬 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D78" s="5" t="inlineStr">
+      <c r="D78" s="8" t="inlineStr">
         <is>
           <t>Mikrodalga fırının yemeği içeriden dışarıya doğru pişirdiği bilgisi tamamen bir şehir efsanesidir! Mikrodalgalar besinin dış yüzeyinden içeriye yalnızca birkaç santimetre nüfuz ederek su moleküllerini titreştirir; kalın yiyeceklerin en iç kısmı ise dış katmandan içeriye yayılan normal ısı iletimiyle ısınır.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E78" s="5" t="inlineStr">
+      <c r="E78" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #fizik #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F78" s="5" t="inlineStr">
+      <c r="F78" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, mikrodalga, fizik, teknoloji, günlükhayat, efsaneavrı, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G78" s="5" t="inlineStr">
+      <c r="G78" s="8" t="inlineStr">
         <is>
           <t>Mikrodalganın yemeği içeriden dışarıya pişirdiğini sananlardan mıydın? ⚡🔬 Evet diyenler '1', gerçeği bilenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H78" s="5" t="inlineStr">
+      <c r="H78" s="8" t="inlineStr">
         <is>
           <t>Fizik ve Bilim</t>
         </is>
       </c>
-      <c r="I78" s="5" t="inlineStr">
+      <c r="I78" s="8" t="inlineStr">
         <is>
           <t>FDA — Microwave Oven Radiation: https://www.fda.gov/radiation-emitting-products/resources-you-radiation-emitting-products/microwave-oven-radiation</t>
         </is>
       </c>
-      <c r="J78" s="5" t="n"/>
-      <c r="K78" s="5" t="n"/>
-      <c r="L78" s="5" t="n"/>
-      <c r="M78" s="5" t="n"/>
+      <c r="J78" s="8" t="n"/>
+      <c r="K78" s="8" t="n"/>
+      <c r="L78" s="8" t="n"/>
+      <c r="M78" s="8" t="n"/>
     </row>
     <row r="79" ht="42" customHeight="1">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
         <is>
           <t>video_51.mp4</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="C79" s="8" t="inlineStr">
         <is>
           <t>Uzay Boşluk Olmasaydı Güneş'in Devasa Uğultusunu Dünya'dan Duyardık! ☀️🔊 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D79" s="5" t="inlineStr">
+      <c r="D79" s="8" t="inlineStr">
         <is>
           <t>Uzay boşluk olmasaydı, Güneş'in devasa uğultusunu Dünya'dan sürekli duyardık! Güneş yüzeyinin altındaki kaynayan dev plazma hücreleri sürekli yükselip çökerken muazzam ses dalgaları üretir; aradaki 150 milyon kilometrelik vakum sesi iletmediği için Dünya sessizdir, aksi halde gökyüzü kesintisiz bir motor gürültüsüyle çınlardı.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E79" s="5" t="inlineStr">
+      <c r="E79" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F79" s="5" t="inlineStr">
+      <c r="F79" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, güneş, uzay, ses, astronomi, fizik, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G79" s="5" t="inlineStr">
+      <c r="G79" s="8" t="inlineStr">
         <is>
           <t>Uzayda hava olsaydı Güneş'in uğultusunu 150 milyon km öteden duyacağımızı biliyor muydun? ☀️🔊 Duyanlar '1', yeni öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H79" s="5" t="inlineStr">
+      <c r="H79" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I79" s="5" t="inlineStr">
+      <c r="I79" s="8" t="inlineStr">
         <is>
           <t>ESA SOHO — Solar Interior Helioseismology: https://sci.esa.int/web/soho/-/30851-solar-interior</t>
         </is>
       </c>
-      <c r="J79" s="5" t="n"/>
-      <c r="K79" s="5" t="n"/>
-      <c r="L79" s="5" t="n"/>
-      <c r="M79" s="5" t="n"/>
+      <c r="J79" s="8" t="n"/>
+      <c r="K79" s="8" t="n"/>
+      <c r="L79" s="8" t="n"/>
+      <c r="M79" s="8" t="n"/>
     </row>
     <row r="80" ht="42" customHeight="1">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
         <is>
           <t>video_53.mp4</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="C80" s="8" t="inlineStr">
         <is>
           <t>Tutankhamun'un Mezarındaki Hançer Uzaydan Gelen Göktaşından Yapılmış! 🗡️☄️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D80" s="5" t="inlineStr">
+      <c r="D80" s="8" t="inlineStr">
         <is>
           <t>Mısır Firavunu Tutankhamun'un mezarında bulunan ünlü demir hançerin Dünya dışından gelen bir göktaşından dövüldüğü kanıtlandı! X-ışını analizleri, demir çağı başlamadan asırlar önce yapılan bu bıçakta yüksek oranda nikel ve kobalt bulunduğunu, yani firavunun hançerinin gerçekten uzaydan düşen bir meteoritten üretildiğini ortaya koydu.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E80" s="5" t="inlineStr">
+      <c r="E80" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F80" s="5" t="inlineStr">
+      <c r="F80" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, tutankhamun, mısır, göktaşı, tarih, arkeoloji, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G80" s="5" t="inlineStr">
+      <c r="G80" s="8" t="inlineStr">
         <is>
           <t>Tutankhamun'un hançerinin uzaydan düşen bir göktaşından yapıldığını biliyor muydun? 🗡️☄️ Duyanlar '1', ilk kez öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H80" s="5" t="inlineStr">
+      <c r="H80" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Arkeoloji</t>
         </is>
       </c>
-      <c r="I80" s="5" t="inlineStr">
+      <c r="I80" s="8" t="inlineStr">
         <is>
           <t>Wikipedia — Tutankhamun's meteoric iron dagger: https://en.wikipedia.org/wiki/Tutankhamun%27s_meteoric_iron_dagger</t>
         </is>
       </c>
-      <c r="J80" s="5" t="n"/>
-      <c r="K80" s="5" t="n"/>
-      <c r="L80" s="5" t="n"/>
-      <c r="M80" s="5" t="n"/>
+      <c r="J80" s="8" t="n"/>
+      <c r="K80" s="8" t="n"/>
+      <c r="L80" s="8" t="n"/>
+      <c r="M80" s="8" t="n"/>
     </row>
     <row r="81" ht="42" customHeight="1">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
         <is>
           <t>video_54.mp4</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C81" s="8" t="inlineStr">
         <is>
           <t>Koltuk Altındaki Gizli Cebinde Kendi Çekiç Taşını Taşıyan Hayvan! 🦦🪨 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D81" s="5" t="inlineStr">
+      <c r="D81" s="8" t="inlineStr">
         <is>
           <t>Deniz samurlarının koltuk altlarında gizli bir deri cebi olduğunu ve burada en sevdikleri taşı sakladıklarını biliyor muydun? Çoğu deniz memelisinin aksine kalın bir yağ tabakası olmayan bu canlılar, santimetrekarede 150.000 teli bulan dünyanın en yoğun kürküyle ısınır. Sol koltuk altlarındaki gevşek deri kesesini ise avladıkları kabukluları ve kendi çekiç taşlarını taşımak için kullanırlar.
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 👇
@@ -5170,313 +5185,313 @@
 #bilgidozu #shorts #doğa #hayvanlar #denizsamuru #bilim #ilginçbilgiler</t>
         </is>
       </c>
-      <c r="E81" s="5" t="inlineStr">
+      <c r="E81" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, shorts, deniz samuru, su samuru, koltuk altı cebi, alet kullanan hayvanlar, doğa ve hayvanlar, ilginç bilgiler, bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F81" s="5" t="inlineStr">
+      <c r="F81" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa, doz dışı</t>
         </is>
       </c>
-      <c r="G81" s="5" t="inlineStr">
+      <c r="G81" s="8" t="inlineStr">
         <is>
           <t>Deniz samurlarının koltuk altında kendi çekiç taşını taşıdığını daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🦦🪨👇</t>
         </is>
       </c>
-      <c r="H81" s="5" t="inlineStr">
+      <c r="H81" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I81" s="5" t="inlineStr">
+      <c r="I81" s="8" t="inlineStr">
         <is>
           <t>Wikipedia / MarineBio — Sea Otter Tool Use &amp; Fur Density: https://en.wikipedia.org/wiki/Sea_otter</t>
         </is>
       </c>
-      <c r="J81" s="5" t="n"/>
-      <c r="K81" s="5" t="n"/>
-      <c r="L81" s="5" t="n"/>
-      <c r="M81" s="5" t="n"/>
+      <c r="J81" s="8" t="n"/>
+      <c r="K81" s="8" t="n"/>
+      <c r="L81" s="8" t="n"/>
+      <c r="M81" s="8" t="n"/>
     </row>
     <row r="82" ht="42" customHeight="1">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
         <is>
           <t>video_55.mp4</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="C82" s="8" t="inlineStr">
         <is>
           <t>Uçak Pencerelerinin Altındaki O Minik Delik Neden Var? ✈️🪟 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D82" s="5" t="inlineStr">
+      <c r="D82" s="8" t="inlineStr">
         <is>
           <t>Uçak pencerelerinin alt kısmındaki o minik delik bir üretim hatası değil, hayat kurtaran bir mühendislik detayıdır! Üç ayrı akrilik katmandan oluşan uçak pencerelerinin ortadaki camında yer alan bu nefes deliği, yüksek irtifadaki dev basınç yükünü en dıştaki kalın cama aktarır ve camların buğulanıp buz tutmasını önler.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E82" s="5" t="inlineStr">
+      <c r="E82" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #fizik #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F82" s="5" t="inlineStr">
+      <c r="F82" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, uçak, havacılık, mühendislik, fizik, günlükhayat, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G82" s="5" t="inlineStr">
+      <c r="G82" s="8" t="inlineStr">
         <is>
           <t>Uçak camındaki o minik deliğin ne işe yaradığını daha önce merak etmiş miydin? ✈️🪟 Bilenler '1', yeni öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H82" s="5" t="inlineStr">
+      <c r="H82" s="8" t="inlineStr">
         <is>
           <t>Fizik ve Mühendislik</t>
         </is>
       </c>
-      <c r="I82" s="5" t="inlineStr">
+      <c r="I82" s="8" t="inlineStr">
         <is>
           <t>Business Insider / FAA — Airplane Window Bleed Hole: https://www.businessinsider.com/airplane-windows-tiny-holes-2016-3</t>
         </is>
       </c>
-      <c r="J82" s="5" t="n"/>
-      <c r="K82" s="5" t="n"/>
-      <c r="L82" s="5" t="n"/>
-      <c r="M82" s="5" t="n"/>
+      <c r="J82" s="8" t="n"/>
+      <c r="K82" s="8" t="n"/>
+      <c r="L82" s="8" t="n"/>
+      <c r="M82" s="8" t="n"/>
     </row>
     <row r="83" ht="42" customHeight="1">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
         <is>
           <t>video_56.mp4</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C83" s="8" t="inlineStr">
         <is>
           <t>Bir Kibrit Kutusu Kadar Parçası 3 Milyar Ton Çeken Yıldız! 🪐⚡ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D83" s="5" t="inlineStr">
+      <c r="D83" s="8" t="inlineStr">
         <is>
           <t>Uzayda yalnızca bir kibrit kutusu büyüklüğündeki parçası Dünya'da tam 3 milyar ton ağırlığında çeken nötron yıldızları vardır! Dev bir yıldız süpernova olarak çöküp patladığında Güneş'ten fazla kütle 20 kilometre çapındaki bir küreye sıkışır ve atomların içindeki boşluk yok olarak bir kibrit kutusu madde 800 metrelik bir kaya dağı kadar ağırlaşır.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E83" s="5" t="inlineStr">
+      <c r="E83" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F83" s="5" t="inlineStr">
+      <c r="F83" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, nötronyıldızı, uzay, astronomi, astrofizik, evren, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G83" s="5" t="inlineStr">
+      <c r="G83" s="8" t="inlineStr">
         <is>
           <t>Bir kibrit kutusu nötron yıldızı maddesinin Dünya'da 3 milyar ton çektiğini biliyor muydun? 🪐⚡ Duyanlar '1', ilk kez öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H83" s="5" t="inlineStr">
+      <c r="H83" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I83" s="5" t="inlineStr">
+      <c r="I83" s="8" t="inlineStr">
         <is>
           <t>NASA / Wikipedia — Neutron Star: https://en.wikipedia.org/wiki/Neutron_star</t>
         </is>
       </c>
-      <c r="J83" s="5" t="n"/>
-      <c r="K83" s="5" t="n"/>
-      <c r="L83" s="5" t="n"/>
-      <c r="M83" s="5" t="n"/>
+      <c r="J83" s="8" t="n"/>
+      <c r="K83" s="8" t="n"/>
+      <c r="L83" s="8" t="n"/>
+      <c r="M83" s="8" t="n"/>
     </row>
     <row r="84" ht="42" customHeight="1">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
         <is>
           <t>video_58.mp4</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
+      <c r="C84" s="8" t="inlineStr">
         <is>
           <t>Vezüv Patlamasında Beyni Gerçek Siyah Cama Dönüşen Romalı! 🌋🖤 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D84" s="5" t="inlineStr">
+      <c r="D84" s="8" t="inlineStr">
         <is>
           <t>MS 79 yılındaki Vezüv Yanardağı patlamasında Herculaneum kentinde hayatını kaybeden genç bir Romalının beyninin aşırı sıcaklıktan gerçek siyah cama dönüştüğü kanıtlandı! 510 derecelik kavurucu kül bulutuyla saniyeler içinde ısınan ve hemen ardından hızla soğuyan beyin dokusu, nöron yapılarını bile koruyarak obsidyen benzeri cama dönüştü.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E84" s="5" t="inlineStr">
+      <c r="E84" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F84" s="5" t="inlineStr">
+      <c r="F84" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, vezüv, herculaneum, pompeii, tarih, arkeoloji, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G84" s="5" t="inlineStr">
+      <c r="G84" s="8" t="inlineStr">
         <is>
           <t>Vezüv patlamasında 510 derecelik kül bulutuyla bir insanın beyninin siyah cama dönüştüğünü biliyor muydun? 🌋🖤 Duyanlar '1', şaşıranlar '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H84" s="5" t="inlineStr">
+      <c r="H84" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Arkeoloji</t>
         </is>
       </c>
-      <c r="I84" s="5" t="inlineStr">
+      <c r="I84" s="8" t="inlineStr">
         <is>
           <t>BBC / Scientific Reports — Herculaneum Glass Brain: https://www.bbc.com/news/articles/cgr2n8xx5gyo</t>
         </is>
       </c>
-      <c r="J84" s="5" t="n"/>
-      <c r="K84" s="5" t="n"/>
-      <c r="L84" s="5" t="n"/>
-      <c r="M84" s="5" t="n"/>
+      <c r="J84" s="8" t="n"/>
+      <c r="K84" s="8" t="n"/>
+      <c r="L84" s="8" t="n"/>
+      <c r="M84" s="8" t="n"/>
     </row>
     <row r="85" ht="42" customHeight="1">
-      <c r="A85" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="inlineStr">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
         <is>
           <t>video_59.mp4</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
+      <c r="C85" s="8" t="inlineStr">
         <is>
           <t>Bu Hayvan Su Altında Nefesini Yunuslardan 4 Kat Uzun Tutuyor! 🦥🌊 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="D85" s="8" t="inlineStr">
         <is>
           <t>Karada dünyanın en yavaş memelisi olan tembel hayvanlar, su altında nefesini yunuslardan bile 4 kat daha uzun tutabilir! Yunuslar yaklaşık 10 dakikada bir yüzeye çıkarken, tembel hayvanlar suya girdiklerinde kalp atış hızlarını normalin üçte birine düşürüp metabolizmalarını yavaşlatarak tam 40 dakika boyunca nefes almadan kalabilir.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E85" s="5" t="inlineStr">
+      <c r="E85" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F85" s="5" t="inlineStr">
+      <c r="F85" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, tembelhayvan, yunus, doğa, hayvanlaralemi, biyoloji, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G85" s="5" t="inlineStr">
+      <c r="G85" s="8" t="inlineStr">
         <is>
           <t>Tembel hayvanların su altında nefesini 40 dakika tutarak yunusları bile geçtiğini biliyor muydun? 🦥🌊 Duyanlar '1', ilk kez öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H85" s="5" t="inlineStr">
+      <c r="H85" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I85" s="5" t="inlineStr">
+      <c r="I85" s="8" t="inlineStr">
         <is>
           <t>BBC Bitesize — Sloths Hold Breath 40 Minutes: https://www.bbc.co.uk/bitesize/articles/zqk4qyc</t>
         </is>
       </c>
-      <c r="J85" s="5" t="n"/>
-      <c r="K85" s="5" t="n"/>
-      <c r="L85" s="5" t="n"/>
-      <c r="M85" s="5" t="n"/>
+      <c r="J85" s="8" t="n"/>
+      <c r="K85" s="8" t="n"/>
+      <c r="L85" s="8" t="n"/>
+      <c r="M85" s="8" t="n"/>
     </row>
     <row r="86" ht="42" customHeight="1">
-      <c r="A86" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B86" s="4" t="inlineStr">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
         <is>
           <t>video_60.mp4</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
+      <c r="C86" s="8" t="inlineStr">
         <is>
           <t>Araba Ön Camlarındaki Siyah Noktalar Neden Var? Süs Değilmiş! 🚗⚫ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D86" s="5" t="inlineStr">
+      <c r="D86" s="8" t="inlineStr">
         <is>
           <t>Araba ön camlarının kenarındaki siyah şerit (frit bandı) ve küçülerek dağılan siyah noktalar süs değil, kritik bir mühendislik kalkanıdır! Cama fırınlanan bu seramik katman, camı gövdeye bağlayan yapıştırıcıyı güneşin morötesi ışınlarından korurken, siyah noktalar cam yüksek ısıda bükülürken sıcaklığı eşit dağıtarak optik bozulmayı önler.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E86" s="5" t="inlineStr">
+      <c r="E86" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #fizik #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F86" s="5" t="inlineStr">
+      <c r="F86" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, araba, otomobil, mühendislik, fizik, günlükhayat, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G86" s="5" t="inlineStr">
+      <c r="G86" s="8" t="inlineStr">
         <is>
           <t>Araba camlarının kenarındaki siyah noktaların yapıştırıcıyı güneşten koruduğunu biliyor muydun? 🚗⚫ Duyanlar '1', yeni öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H86" s="5" t="inlineStr">
+      <c r="H86" s="8" t="inlineStr">
         <is>
           <t>Fizik ve Mühendislik</t>
         </is>
       </c>
-      <c r="I86" s="5" t="inlineStr">
+      <c r="I86" s="8" t="inlineStr">
         <is>
           <t>Jalopnik / Pilkington — Windshield Frit Dots: https://www.jalopnik.com/heres-what-those-little-dots-are-on-the-edges-of-your-c-1791075995/</t>
         </is>
       </c>
-      <c r="J86" s="5" t="n"/>
-      <c r="K86" s="5" t="n"/>
-      <c r="L86" s="5" t="n"/>
-      <c r="M86" s="5" t="n"/>
+      <c r="J86" s="8" t="n"/>
+      <c r="K86" s="8" t="n"/>
+      <c r="L86" s="8" t="n"/>
+      <c r="M86" s="8" t="n"/>
     </row>
     <row r="87" ht="42" customHeight="1">
-      <c r="A87" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
         <is>
           <t>video_61.mp4</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
+      <c r="C87" s="8" t="inlineStr">
         <is>
           <t>Tepesinden Atlayınca Dibe Düşmenin 12 Dakika Sürdüğü 20 Km'lik Uçurum! 🪐🧗 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="D87" s="8" t="inlineStr">
         <is>
           <t>Tepesinden atladığında yere çarpmanın tam 12 dakika sürdüğü devasa bir uçurum olduğunu biliyor muydun? Uranüs'ün uydusu Miranda üzerindeki 20 km'lik Verona Rupes uçurumunu inceliyoruz.
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -5485,53 +5500,53 @@
 #bilgidozu #shorts #uzay #miranda #bilim</t>
         </is>
       </c>
-      <c r="E87" s="5" t="inlineStr">
+      <c r="E87" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #miranda #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F87" s="5" t="inlineStr">
+      <c r="F87" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, verona rupes, miranda, uranüs, uzay, astronomi, uçurum, nasa, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G87" s="5" t="inlineStr">
+      <c r="G87" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🪐🧗</t>
         </is>
       </c>
-      <c r="H87" s="5" t="inlineStr">
+      <c r="H87" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I87" s="5" t="inlineStr">
+      <c r="I87" s="8" t="inlineStr">
         <is>
           <t>NASA Voyager 2 / USGS Astrogeology — Verona Rupes: https://en.wikipedia.org/wiki/Verona_Rupes</t>
         </is>
       </c>
-      <c r="J87" s="5" t="n"/>
-      <c r="K87" s="5" t="n"/>
-      <c r="L87" s="5" t="n"/>
-      <c r="M87" s="5" t="n"/>
+      <c r="J87" s="8" t="n"/>
+      <c r="K87" s="8" t="n"/>
+      <c r="L87" s="8" t="n"/>
+      <c r="M87" s="8" t="n"/>
     </row>
     <row r="88" ht="42" customHeight="1">
-      <c r="A88" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B88" s="4" t="inlineStr">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
         <is>
           <t>video_63.mp4</t>
         </is>
       </c>
-      <c r="C88" s="5" t="inlineStr">
+      <c r="C88" s="8" t="inlineStr">
         <is>
           <t>Harç ve Çimento Olmadan Depremde Yıkılmayan 500 Yıllık İnka Duvarları! 🏛️🪨 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D88" s="5" t="inlineStr">
+      <c r="D88" s="8" t="inlineStr">
         <is>
           <t>İnkaların 500 yıl önce tek damla harç veya çimento kullanmadan yaptığı taş duvarların büyük depremlerde bile neden yıkılmadığını biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -5540,53 +5555,53 @@
 #bilgidozu #shorts #tarih #inka #arkeoloji</t>
         </is>
       </c>
-      <c r="E88" s="5" t="inlineStr">
+      <c r="E88" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #inka #arkeoloji #dozdışı</t>
         </is>
       </c>
-      <c r="F88" s="5" t="inlineStr">
+      <c r="F88" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, inka duvarları, deprem, cusco, tarih, arkeoloji, mühendislik, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G88" s="5" t="inlineStr">
+      <c r="G88" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🏛️🪨</t>
         </is>
       </c>
-      <c r="H88" s="5" t="inlineStr">
+      <c r="H88" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Arkeoloji</t>
         </is>
       </c>
-      <c r="I88" s="5" t="inlineStr">
+      <c r="I88" s="8" t="inlineStr">
         <is>
           <t>UNESCO World Heritage Cusco / Inca Architecture: https://en.wikipedia.org/wiki/Inca_architecture</t>
         </is>
       </c>
-      <c r="J88" s="5" t="n"/>
-      <c r="K88" s="5" t="n"/>
-      <c r="L88" s="5" t="n"/>
-      <c r="M88" s="5" t="n"/>
+      <c r="J88" s="8" t="n"/>
+      <c r="K88" s="8" t="n"/>
+      <c r="L88" s="8" t="n"/>
+      <c r="M88" s="8" t="n"/>
     </row>
     <row r="89" ht="42" customHeight="1">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
         <is>
           <t>video_64.mp4</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C89" s="8" t="inlineStr">
         <is>
           <t>Baykuşlar Karanlıkta Uçarken Nasıl Sıfır Ses Çıkarır? Hayalet Kanat Sırrı! 🦉🌙 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D89" s="8" t="inlineStr">
         <is>
           <t>Diğer bütün kuşlar kanat çırparken hışırtı çıkarırken baykuşların zifiri karanlıkta tamamen sessiz uçabildiğini biliyor muydun? Üçlü akustik susturucu kanat yapısını inceliyoruz.
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -5595,53 +5610,53 @@
 #bilgidozu #shorts #baykuş #doğa #hayvanlar</t>
         </is>
       </c>
-      <c r="E89" s="5" t="inlineStr">
+      <c r="E89" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #baykuş #doğa #hayvanlar #dozdışı</t>
         </is>
       </c>
-      <c r="F89" s="5" t="inlineStr">
+      <c r="F89" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, baykuş, sessiz uçuş, doğa, hayvanlar, aerodinamik, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G89" s="5" t="inlineStr">
+      <c r="G89" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🦉🌙</t>
         </is>
       </c>
-      <c r="H89" s="5" t="inlineStr">
+      <c r="H89" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I89" s="5" t="inlineStr">
+      <c r="I89" s="8" t="inlineStr">
         <is>
           <t>Royal Society Interface / Owl Silent Flight: https://en.wikipedia.org/wiki/Owl</t>
         </is>
       </c>
-      <c r="J89" s="5" t="n"/>
-      <c r="K89" s="5" t="n"/>
-      <c r="L89" s="5" t="n"/>
-      <c r="M89" s="5" t="n"/>
+      <c r="J89" s="8" t="n"/>
+      <c r="K89" s="8" t="n"/>
+      <c r="L89" s="8" t="n"/>
+      <c r="M89" s="8" t="n"/>
     </row>
     <row r="90" ht="42" customHeight="1">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
         <is>
           <t>video_65.mp4</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr">
+      <c r="C90" s="8" t="inlineStr">
         <is>
           <t>Tükenmez Kalem Kapağındaki O Küçük Delik Neden Hayat Kurtarır? 🖊️⚡ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D90" s="5" t="inlineStr">
+      <c r="D90" s="8" t="inlineStr">
         <is>
           <t>Tükenmez kalemlerin kapağındaki o küçük deliğin mürekkep kurumasın diye değil, hayat kurtarmak için açıldığını biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -5650,53 +5665,53 @@
 #bilgidozu #shorts #ilginçbilgiler #tasarım #bilim</t>
         </is>
       </c>
-      <c r="E90" s="5" t="inlineStr">
+      <c r="E90" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #ilginçbilgiler #tasarım #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F90" s="5" t="inlineStr">
+      <c r="F90" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, tükenmez kalem kapağı, bic cristal, güvenlik deliği, günlük bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G90" s="5" t="inlineStr">
+      <c r="G90" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🖊️⚡</t>
         </is>
       </c>
-      <c r="H90" s="5" t="inlineStr">
+      <c r="H90" s="8" t="inlineStr">
         <is>
           <t>Fizik ve Mühendislik</t>
         </is>
       </c>
-      <c r="I90" s="5" t="inlineStr">
+      <c r="I90" s="8" t="inlineStr">
         <is>
           <t>ISO 11540 / BIC Cristal Safety Design: https://en.wikipedia.org/wiki/Bic_Cristal</t>
         </is>
       </c>
-      <c r="J90" s="5" t="n"/>
-      <c r="K90" s="5" t="n"/>
-      <c r="L90" s="5" t="n"/>
-      <c r="M90" s="5" t="n"/>
+      <c r="J90" s="8" t="n"/>
+      <c r="K90" s="8" t="n"/>
+      <c r="L90" s="8" t="n"/>
+      <c r="M90" s="8" t="n"/>
     </row>
     <row r="91" ht="42" customHeight="1">
-      <c r="A91" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
         <is>
           <t>video_66.mp4</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C91" s="8" t="inlineStr">
         <is>
           <t>Su Değil Sert Kaya Zemini Her Gün 100 Metre Yükselip Alçalan Uydu! 🪐🌋 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D91" s="8" t="inlineStr">
         <is>
           <t>Dünya'da okyanus suları yükselip alçalırken, Jüpiter'in uydusu İo'da suyun değil doğrudan sert kaya zeminin her gün 100 metre yükselip alçaldığını biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -5705,53 +5720,53 @@
 #bilgidozu #shorts #uzay #jüpiter #bilim</t>
         </is>
       </c>
-      <c r="E91" s="5" t="inlineStr">
+      <c r="E91" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #jüpiter #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F91" s="5" t="inlineStr">
+      <c r="F91" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, io uydusu, jüpiter, kaya gelgiti, yanardağ, uzay, astronomi, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G91" s="5" t="inlineStr">
+      <c r="G91" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🪐🌋</t>
         </is>
       </c>
-      <c r="H91" s="5" t="inlineStr">
+      <c r="H91" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I91" s="5" t="inlineStr">
+      <c r="I91" s="8" t="inlineStr">
         <is>
           <t>NASA Juno &amp; Galileo Mission / Io Facts: https://science.nasa.gov/jupiter/moons/io/</t>
         </is>
       </c>
-      <c r="J91" s="5" t="n"/>
-      <c r="K91" s="5" t="n"/>
-      <c r="L91" s="5" t="n"/>
-      <c r="M91" s="5" t="n"/>
+      <c r="J91" s="8" t="n"/>
+      <c r="K91" s="8" t="n"/>
+      <c r="L91" s="8" t="n"/>
+      <c r="M91" s="8" t="n"/>
     </row>
     <row r="92" ht="42" customHeight="1">
-      <c r="A92" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
         <is>
           <t>video_68.mp4</t>
         </is>
       </c>
-      <c r="C92" s="5" t="inlineStr">
+      <c r="C92" s="8" t="inlineStr">
         <is>
           <t>2000 Yıllık Deniz Batığından Çıkan Dünyanın İlk Mekanik Bilgisayarı! ⚙️🏛️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="D92" s="8" t="inlineStr">
         <is>
           <t>İki bin yıl önce batan bir antik Yunan gemisinden dünyanın ilk mekanik bilgisayarının (Antikythera Düzeneği) çıktığını biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -5760,53 +5775,53 @@
 #bilgidozu #shorts #tarih #arkeoloji #bilim</t>
         </is>
       </c>
-      <c r="E92" s="5" t="inlineStr">
+      <c r="E92" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #arkeoloji #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F92" s="5" t="inlineStr">
+      <c r="F92" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, antikythera düzeneği, antik bilgisayar, tarih, arkeoloji, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G92" s="5" t="inlineStr">
+      <c r="G92" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! ⚙️🏛️</t>
         </is>
       </c>
-      <c r="H92" s="5" t="inlineStr">
+      <c r="H92" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Arkeoloji</t>
         </is>
       </c>
-      <c r="I92" s="5" t="inlineStr">
+      <c r="I92" s="8" t="inlineStr">
         <is>
           <t>Nature / UCL Antikythera Research Team: https://www.nature.com/articles/s41598-021-84310-w</t>
         </is>
       </c>
-      <c r="J92" s="5" t="n"/>
-      <c r="K92" s="5" t="n"/>
-      <c r="L92" s="5" t="n"/>
-      <c r="M92" s="5" t="n"/>
+      <c r="J92" s="8" t="n"/>
+      <c r="K92" s="8" t="n"/>
+      <c r="L92" s="8" t="n"/>
+      <c r="M92" s="8" t="n"/>
     </row>
     <row r="93" ht="42" customHeight="1">
-      <c r="A93" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
         <is>
           <t>video_69.mp4</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
+      <c r="C93" s="8" t="inlineStr">
         <is>
           <t>70 Derece Çölde Yuvasını Adımlarını Sayarak Bulan Gümüş Karınca! 🐜☀️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D93" s="8" t="inlineStr">
         <is>
           <t>70 derece sıcaklıktaki Sahra Çölü'nde yaşayan gümüş karıncaların yuvalarını adımlarını sayarak (pedometre) bulduğunu biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -5815,53 +5830,53 @@
 #bilgidozu #shorts #doğa #karınca #hayvanlar</t>
         </is>
       </c>
-      <c r="E93" s="5" t="inlineStr">
+      <c r="E93" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #karınca #hayvanlar #dozdışı</t>
         </is>
       </c>
-      <c r="F93" s="5" t="inlineStr">
+      <c r="F93" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, sahra çöl karıncası, adım sayar, doğa, hayvanlar, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G93" s="5" t="inlineStr">
+      <c r="G93" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🐜☀️</t>
         </is>
       </c>
-      <c r="H93" s="5" t="inlineStr">
+      <c r="H93" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I93" s="5" t="inlineStr">
+      <c r="I93" s="8" t="inlineStr">
         <is>
           <t>Science (2006) — Wittlinger et al.: https://www.science.org/doi/10.1126/science.1126912</t>
         </is>
       </c>
-      <c r="J93" s="5" t="n"/>
-      <c r="K93" s="5" t="n"/>
-      <c r="L93" s="5" t="n"/>
-      <c r="M93" s="5" t="n"/>
+      <c r="J93" s="8" t="n"/>
+      <c r="K93" s="8" t="n"/>
+      <c r="L93" s="8" t="n"/>
+      <c r="M93" s="8" t="n"/>
     </row>
     <row r="94" ht="42" customHeight="1">
-      <c r="A94" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="inlineStr">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
         <is>
           <t>video_70.mp4</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr">
+      <c r="C94" s="8" t="inlineStr">
         <is>
           <t>Benzin Pompası Depo Dolunca Çipsiz ve Sensörsüz Nasıl Kendi Durur? ⛽⚡ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D94" s="5" t="inlineStr">
+      <c r="D94" s="8" t="inlineStr">
         <is>
           <t>Benzin istasyonlarındaki pompa tabancasının deponun tam dolduğunu içinde hiçbir kamera, çip veya elektrikli sensör olmadan nasıl anladığını biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -5870,53 +5885,53 @@
 #bilgidozu #shorts #fizik #mühendislik #bilim</t>
         </is>
       </c>
-      <c r="E94" s="5" t="inlineStr">
+      <c r="E94" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #fizik #mühendislik #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F94" s="5" t="inlineStr">
+      <c r="F94" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, benzin pompası, venturi etkisi, fizik, mühendislik, günlük bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G94" s="5" t="inlineStr">
+      <c r="G94" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! ⛽⚡</t>
         </is>
       </c>
-      <c r="H94" s="5" t="inlineStr">
+      <c r="H94" s="8" t="inlineStr">
         <is>
           <t>Fizik ve Mühendislik</t>
         </is>
       </c>
-      <c r="I94" s="5" t="inlineStr">
+      <c r="I94" s="8" t="inlineStr">
         <is>
           <t>PEI / Automatic Shut-Off Nozzle: https://pei.org/wiki_pei/automatic-nozzle/</t>
         </is>
       </c>
-      <c r="J94" s="5" t="n"/>
-      <c r="K94" s="5" t="n"/>
-      <c r="L94" s="5" t="n"/>
-      <c r="M94" s="5" t="n"/>
+      <c r="J94" s="8" t="n"/>
+      <c r="K94" s="8" t="n"/>
+      <c r="L94" s="8" t="n"/>
+      <c r="M94" s="8" t="n"/>
     </row>
     <row r="95" ht="42" customHeight="1">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>video_71.mp4</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
+      <c r="C95" s="8" t="inlineStr">
         <is>
           <t>Satürn'ün Kuzey Kutbundaki Dev Altıgen Fırtınanın Sırrı! 🪐🌪️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="D95" s="8" t="inlineStr">
         <is>
           <t>Satürn gezegeninin kuzey kutbunda içine iki tane Dünya sığacak büyüklükte kusursuz bir altıgen fırtına döndüğünü biliyor muydun? 32.000 kilometrelik bu dev geometrik fırtınanın sırrını inceliyoruz.
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -5925,53 +5940,53 @@
 #bilgidozu #shorts #uzay #satürn #bilim</t>
         </is>
       </c>
-      <c r="E95" s="5" t="inlineStr">
+      <c r="E95" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #satürn #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F95" s="5" t="inlineStr">
+      <c r="F95" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, satürn, altıgen fırtına, uzay, astronomi, nasa, cassini, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G95" s="5" t="inlineStr">
+      <c r="G95" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🪐🌪️</t>
         </is>
       </c>
-      <c r="H95" s="5" t="inlineStr">
+      <c r="H95" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I95" s="5" t="inlineStr">
+      <c r="I95" s="8" t="inlineStr">
         <is>
           <t>NASA Cassini Mission / JPL: https://science.nasa.gov/mission/cassini/</t>
         </is>
       </c>
-      <c r="J95" s="5" t="n"/>
-      <c r="K95" s="5" t="n"/>
-      <c r="L95" s="5" t="n"/>
-      <c r="M95" s="5" t="n"/>
+      <c r="J95" s="8" t="n"/>
+      <c r="K95" s="8" t="n"/>
+      <c r="L95" s="8" t="n"/>
+      <c r="M95" s="8" t="n"/>
     </row>
     <row r="96" ht="42" customHeight="1">
-      <c r="A96" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
         <is>
           <t>video_73.mp4</t>
         </is>
       </c>
-      <c r="C96" s="5" t="inlineStr">
+      <c r="C96" s="8" t="inlineStr">
         <is>
           <t>Efsanevi Şam Çeliği Kılıçların İçinden Karbon Nanotüp Çıktı! ⚔️🔬 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D96" s="5" t="inlineStr">
+      <c r="D96" s="8" t="inlineStr">
         <is>
           <t>Yüzyıllar önce üretilen efsanevi Şam çeliği kılıçların içinde modern bilimin ancak elektron mikroskobuyla görebildiği karbon nanotüpler bulunduğunu biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -5980,53 +5995,53 @@
 #bilgidozu #shorts #tarih #bilim #teknoloji</t>
         </is>
       </c>
-      <c r="E96" s="5" t="inlineStr">
+      <c r="E96" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #bilim #teknoloji #dozdışı</t>
         </is>
       </c>
-      <c r="F96" s="5" t="inlineStr">
+      <c r="F96" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, şam çeliği, karbon nanotüp, tarih, kılıç, bilim, mühendislik, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G96" s="5" t="inlineStr">
+      <c r="G96" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! ⚔️🔬</t>
         </is>
       </c>
-      <c r="H96" s="5" t="inlineStr">
+      <c r="H96" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Arkeoloji</t>
         </is>
       </c>
-      <c r="I96" s="5" t="inlineStr">
+      <c r="I96" s="8" t="inlineStr">
         <is>
           <t>Nature (2006) — Reibold et al., TU Dresden: https://www.nature.com/articles/444286a</t>
         </is>
       </c>
-      <c r="J96" s="5" t="n"/>
-      <c r="K96" s="5" t="n"/>
-      <c r="L96" s="5" t="n"/>
-      <c r="M96" s="5" t="n"/>
+      <c r="J96" s="8" t="n"/>
+      <c r="K96" s="8" t="n"/>
+      <c r="L96" s="8" t="n"/>
+      <c r="M96" s="8" t="n"/>
     </row>
     <row r="97" ht="42" customHeight="1">
-      <c r="A97" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
         <is>
           <t>video_74.mp4</t>
         </is>
       </c>
-      <c r="C97" s="5" t="inlineStr">
+      <c r="C97" s="8" t="inlineStr">
         <is>
           <t>Işığın Kırılmasını Hesaplayıp Böceği Suyla Vuran Keskin Nişancı Balık! 🐟🎯 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D97" s="5" t="inlineStr">
+      <c r="D97" s="8" t="inlineStr">
         <is>
           <t>Suyun altından dışarıdaki bir böceğe su fırlatarak tam on ikiden vuran okçu balığının ışığın kırılmasını nasıl hesapladığını biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -6035,53 +6050,53 @@
 #bilgidozu #shorts #doğa #hayvanlar #bilim</t>
         </is>
       </c>
-      <c r="E97" s="5" t="inlineStr">
+      <c r="E97" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #hayvanlar #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F97" s="5" t="inlineStr">
+      <c r="F97" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, okçu balığı, doğa, hayvanlar, optik kırılma, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G97" s="5" t="inlineStr">
+      <c r="G97" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🐟🎯</t>
         </is>
       </c>
-      <c r="H97" s="5" t="inlineStr">
+      <c r="H97" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I97" s="5" t="inlineStr">
+      <c r="I97" s="8" t="inlineStr">
         <is>
           <t>PLOS ONE (2012) — Vailati et al. (Archerfish Water Jet): https://journals.plos.org/plosone/article?id=10.1371/journal.pone.0047867</t>
         </is>
       </c>
-      <c r="J97" s="5" t="n"/>
-      <c r="K97" s="5" t="n"/>
-      <c r="L97" s="5" t="n"/>
-      <c r="M97" s="5" t="n"/>
+      <c r="J97" s="8" t="n"/>
+      <c r="K97" s="8" t="n"/>
+      <c r="L97" s="8" t="n"/>
+      <c r="M97" s="8" t="n"/>
     </row>
     <row r="98" ht="42" customHeight="1">
-      <c r="A98" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
         <is>
           <t>video_75.mp4</t>
         </is>
       </c>
-      <c r="C98" s="5" t="inlineStr">
+      <c r="C98" s="8" t="inlineStr">
         <is>
           <t>Mikrodalga Fırın Camındaki Delikli Siyah Tel Neden Var? ⚡🪟 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D98" s="5" t="inlineStr">
+      <c r="D98" s="8" t="inlineStr">
         <is>
           <t>Mikrodalga fırınların ön camındaki o siyah delikli metal ızgaranın içeriyi görmen için değil, seni radyasyondan korumak için konulduğunu biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -6090,53 +6105,53 @@
 #bilgidozu #shorts #fizik #teknoloji #bilim</t>
         </is>
       </c>
-      <c r="E98" s="5" t="inlineStr">
+      <c r="E98" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #fizik #teknoloji #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F98" s="5" t="inlineStr">
+      <c r="F98" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, mikrodalga fırın, faraday kafesi, fizik, günlük bilim, mühendislik, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G98" s="5" t="inlineStr">
+      <c r="G98" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! ⚡🪟</t>
         </is>
       </c>
-      <c r="H98" s="5" t="inlineStr">
+      <c r="H98" s="8" t="inlineStr">
         <is>
           <t>Fizik ve Mühendislik</t>
         </is>
       </c>
-      <c r="I98" s="5" t="inlineStr">
+      <c r="I98" s="8" t="inlineStr">
         <is>
           <t>IEEE Electromagnetic Shielding / Wikipedia — Faraday Cage: https://en.wikipedia.org/wiki/Faraday_cage</t>
         </is>
       </c>
-      <c r="J98" s="5" t="n"/>
-      <c r="K98" s="5" t="n"/>
-      <c r="L98" s="5" t="n"/>
-      <c r="M98" s="5" t="n"/>
+      <c r="J98" s="8" t="n"/>
+      <c r="K98" s="8" t="n"/>
+      <c r="L98" s="8" t="n"/>
+      <c r="M98" s="8" t="n"/>
     </row>
     <row r="99" ht="42" customHeight="1">
-      <c r="A99" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
         <is>
           <t>video_76.mp4</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
+      <c r="C99" s="8" t="inlineStr">
         <is>
           <t>Uzayda Ses Yayılsaydı Güneş Dünya'dan 100 Desibel Tren Gibi Gürlerdi! ☀️🔊 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D99" s="5" t="inlineStr">
+      <c r="D99" s="8" t="inlineStr">
         <is>
           <t>Uzayda ses yayılmadığı için çok şanslı olduğumuzu, yoksa Güneş'in 150 milyon kilometre öteden bile 100 desibel şiddetinde gürleyeceğini biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -6145,53 +6160,53 @@
 #bilgidozu #shorts #uzay #güneş #bilim</t>
         </is>
       </c>
-      <c r="E99" s="5" t="inlineStr">
+      <c r="E99" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #güneş #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F99" s="5" t="inlineStr">
+      <c r="F99" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, güneşin sesi, uzayda ses, astronomi, nasa, güneş, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G99" s="5" t="inlineStr">
+      <c r="G99" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! ☀️🔊</t>
         </is>
       </c>
-      <c r="H99" s="5" t="inlineStr">
+      <c r="H99" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I99" s="5" t="inlineStr">
+      <c r="I99" s="8" t="inlineStr">
         <is>
           <t>NASA Heliophysics / SOHO — Solar Acoustics: https://sci.esa.int/web/soho/-/30851-solar-interior</t>
         </is>
       </c>
-      <c r="J99" s="5" t="n"/>
-      <c r="K99" s="5" t="n"/>
-      <c r="L99" s="5" t="n"/>
-      <c r="M99" s="5" t="n"/>
+      <c r="J99" s="8" t="n"/>
+      <c r="K99" s="8" t="n"/>
+      <c r="L99" s="8" t="n"/>
+      <c r="M99" s="8" t="n"/>
     </row>
     <row r="100" ht="42" customHeight="1">
-      <c r="A100" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B100" s="4" t="inlineStr">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
         <is>
           <t>video_78.mp4</t>
         </is>
       </c>
-      <c r="C100" s="5" t="inlineStr">
+      <c r="C100" s="8" t="inlineStr">
         <is>
           <t>Paskalya Adası'ndaki 80 Tonluk Dev Taş Heykeller Nasıl Yürütüldü? 🗿🏛️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D100" s="5" t="inlineStr">
+      <c r="D100" s="8" t="inlineStr">
         <is>
           <t>Paskalya Adası'ndaki 80 tonluk dev taş heykellerin tekerlek veya vinç olmadan üç halatla dik vaziyette yürütülerek taşındığını biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -6200,53 +6215,53 @@
 #bilgidozu #shorts #tarih #paskalyaadası #arkeoloji</t>
         </is>
       </c>
-      <c r="E100" s="5" t="inlineStr">
+      <c r="E100" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #paskalyaadası #arkeoloji #dozdışı</t>
         </is>
       </c>
-      <c r="F100" s="5" t="inlineStr">
+      <c r="F100" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, paskalya adası, moai heykelleri, tarih, arkeoloji, mühendislik, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G100" s="5" t="inlineStr">
+      <c r="G100" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🗿🏛️</t>
         </is>
       </c>
-      <c r="H100" s="5" t="inlineStr">
+      <c r="H100" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Arkeoloji</t>
         </is>
       </c>
-      <c r="I100" s="5" t="inlineStr">
+      <c r="I100" s="8" t="inlineStr">
         <is>
           <t>Journal of Archaeological Science (2012) — Lipo &amp; Hunt (Easter Island Moai): https://en.wikipedia.org/wiki/Moai</t>
         </is>
       </c>
-      <c r="J100" s="5" t="n"/>
-      <c r="K100" s="5" t="n"/>
-      <c r="L100" s="5" t="n"/>
-      <c r="M100" s="5" t="n"/>
+      <c r="J100" s="8" t="n"/>
+      <c r="K100" s="8" t="n"/>
+      <c r="L100" s="8" t="n"/>
+      <c r="M100" s="8" t="n"/>
     </row>
     <row r="101" ht="42" customHeight="1">
-      <c r="A101" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
         <is>
           <t>video_79.mp4</t>
         </is>
       </c>
-      <c r="C101" s="5" t="inlineStr">
+      <c r="C101" s="8" t="inlineStr">
         <is>
           <t>Elektrikli Yılan Balığı 860 Volt Elektrik Üretirken Kendini Neden Çarpmaz? ⚡🐍 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D101" s="5" t="inlineStr">
+      <c r="D101" s="8" t="inlineStr">
         <is>
           <t>Elektrikli yılan balığının suyun içinde 860 voltluk ölümcül bir elektriği kendi kendini hiç çarpmadan nasıl ürettiğini biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -6255,53 +6270,53 @@
 #bilgidozu #shorts #doğa #hayvanlar #bilim</t>
         </is>
       </c>
-      <c r="E101" s="5" t="inlineStr">
+      <c r="E101" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #hayvanlar #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F101" s="5" t="inlineStr">
+      <c r="F101" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, elektrikli yılan balığı, elektrosit, doğa, hayvanlar, biyoloji, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G101" s="5" t="inlineStr">
+      <c r="G101" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! ⚡🐍</t>
         </is>
       </c>
-      <c r="H101" s="5" t="inlineStr">
+      <c r="H101" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I101" s="5" t="inlineStr">
+      <c r="I101" s="8" t="inlineStr">
         <is>
           <t>Nature Communications (2019) — de Santana et al. (860V Electric Eel): https://www.nature.com/articles/s41467-019-11622-9</t>
         </is>
       </c>
-      <c r="J101" s="5" t="n"/>
-      <c r="K101" s="5" t="n"/>
-      <c r="L101" s="5" t="n"/>
-      <c r="M101" s="5" t="n"/>
+      <c r="J101" s="8" t="n"/>
+      <c r="K101" s="8" t="n"/>
+      <c r="L101" s="8" t="n"/>
+      <c r="M101" s="8" t="n"/>
     </row>
     <row r="102" ht="42" customHeight="1">
-      <c r="A102" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="inlineStr">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
         <is>
           <t>video_80.mp4</t>
         </is>
       </c>
-      <c r="C102" s="5" t="inlineStr">
+      <c r="C102" s="8" t="inlineStr">
         <is>
           <t>Yürüyen Merdiven Kenarındaki Fırçalar Ayakkabı Silmek İçin Değil! 👟⚠️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D102" s="5" t="inlineStr">
+      <c r="D102" s="8" t="inlineStr">
         <is>
           <t>Yürüyen merdivenlerin iki yanındaki o sert siyah fırçaların ayakkabılarını temizlemen için değil, kıyafetlerin dişlilere sıkışmasını önlemek için konulduğunu biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -6310,53 +6325,53 @@
 #bilgidozu #shorts #ilginçbilgiler #mühendislik #bilim</t>
         </is>
       </c>
-      <c r="E102" s="5" t="inlineStr">
+      <c r="E102" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #ilginçbilgiler #mühendislik #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F102" s="5" t="inlineStr">
+      <c r="F102" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, yürüyen merdiven fırçası, güvenlik, mühendislik, günlük bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G102" s="5" t="inlineStr">
+      <c r="G102" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 👟⚠️</t>
         </is>
       </c>
-      <c r="H102" s="5" t="inlineStr">
+      <c r="H102" s="8" t="inlineStr">
         <is>
           <t>Fizik ve Mühendislik</t>
         </is>
       </c>
-      <c r="I102" s="5" t="inlineStr">
+      <c r="I102" s="8" t="inlineStr">
         <is>
           <t>ASME A17.1 Escalator Safety Code — Escalator Skirt Deflector Brushes: https://en.wikipedia.org/wiki/Escalator</t>
         </is>
       </c>
-      <c r="J102" s="5" t="n"/>
-      <c r="K102" s="5" t="n"/>
-      <c r="L102" s="5" t="n"/>
-      <c r="M102" s="5" t="n"/>
+      <c r="J102" s="8" t="n"/>
+      <c r="K102" s="8" t="n"/>
+      <c r="L102" s="8" t="n"/>
+      <c r="M102" s="8" t="n"/>
     </row>
     <row r="103" ht="42" customHeight="1">
-      <c r="A103" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="inlineStr">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
         <is>
           <t>video_81.mp4</t>
         </is>
       </c>
-      <c r="C103" s="5" t="inlineStr">
+      <c r="C103" s="8" t="inlineStr">
         <is>
           <t>Neptün ve Uranüs'te Gökyüzünden Gerçek Elmas Yağıyor! 💎🪐 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D103" s="5" t="inlineStr">
+      <c r="D103" s="8" t="inlineStr">
         <is>
           <t>Neptün ve Uranüs atmosferindeki yüksek basınç karbon atomlarını sıkıştırarak gerçek elmasa dönüştürür.
 Peki sizce insanoğlu bir gün bu gezegenlerden elmas toplayabilir mi? Yorumlara yazın! 👇
@@ -6365,53 +6380,53 @@
 #bilgidozu #shorts #uzay #bilim #gezegenler</t>
         </is>
       </c>
-      <c r="E103" s="5" t="inlineStr">
+      <c r="E103" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim #gezegenler #dozdışı</t>
         </is>
       </c>
-      <c r="F103" s="5" t="inlineStr">
+      <c r="F103" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, uzay, neptün, uranüs, elmas yağmuru, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G103" s="5" t="inlineStr">
+      <c r="G103" s="8" t="inlineStr">
         <is>
           <t>Peki sizce insanoğlu bir gün bu gezegenlerden elmas toplayabilir mi? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H103" s="5" t="inlineStr">
+      <c r="H103" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Evren</t>
         </is>
       </c>
-      <c r="I103" s="5" t="inlineStr">
+      <c r="I103" s="8" t="inlineStr">
         <is>
           <t>Nature Astronomy / SLAC — Diamond Rain on Ice Giants: https://www6.slac.stanford.edu/news/2017-08-21-scientists-create-diamond-rain-forms-interior-icy-giant-planets</t>
         </is>
       </c>
-      <c r="J103" s="5" t="n"/>
-      <c r="K103" s="5" t="n"/>
-      <c r="L103" s="5" t="n"/>
-      <c r="M103" s="5" t="n"/>
+      <c r="J103" s="8" t="n"/>
+      <c r="K103" s="8" t="n"/>
+      <c r="L103" s="8" t="n"/>
+      <c r="M103" s="8" t="n"/>
     </row>
     <row r="104" ht="42" customHeight="1">
-      <c r="A104" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B104" s="4" t="inlineStr">
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
         <is>
           <t>video_82.mp4</t>
         </is>
       </c>
-      <c r="C104" s="5" t="inlineStr">
+      <c r="C104" s="8" t="inlineStr">
         <is>
           <t>Uzay Boşluğunda Bile Hayatta Kalan Canlı: Su Ayısı Tardigrad! 🐻🌌 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D104" s="5" t="inlineStr">
+      <c r="D104" s="8" t="inlineStr">
         <is>
           <t>Mikroskobik su ayısı Tardigrad, kriptobiyoz özelliği sayesinde uzay boşluğunda ve radyasyonda bile hayatta kalabilir.
 Sizce Dünya'daki en dayanıklı canlı Tardigrad mı yoksa başka bir tür mü? Yorumlarda buluşalım! 👇
@@ -6420,53 +6435,53 @@
 #bilgidozu #shorts #doğa #bilim #tardigrad</t>
         </is>
       </c>
-      <c r="E104" s="5" t="inlineStr">
+      <c r="E104" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim #tardigrad #dozdışı</t>
         </is>
       </c>
-      <c r="F104" s="5" t="inlineStr">
+      <c r="F104" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, tardigrad, su ayısı, doğa, uzay, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G104" s="5" t="inlineStr">
+      <c r="G104" s="8" t="inlineStr">
         <is>
           <t>Sizce Dünya'daki en dayanıklı canlı Tardigrad mı yoksa başka bir tür mü? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H104" s="5" t="inlineStr">
+      <c r="H104" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Canlılar</t>
         </is>
       </c>
-      <c r="I104" s="5" t="inlineStr">
+      <c r="I104" s="8" t="inlineStr">
         <is>
           <t>ESA FOTON-M3 / Current Biology — Tardigrades in Space: https://en.wikipedia.org/wiki/Tardigrade</t>
         </is>
       </c>
-      <c r="J104" s="5" t="n"/>
-      <c r="K104" s="5" t="n"/>
-      <c r="L104" s="5" t="n"/>
-      <c r="M104" s="5" t="n"/>
+      <c r="J104" s="8" t="n"/>
+      <c r="K104" s="8" t="n"/>
+      <c r="L104" s="8" t="n"/>
+      <c r="M104" s="8" t="n"/>
     </row>
     <row r="105" ht="42" customHeight="1">
-      <c r="A105" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
         <is>
           <t>video_84.mp4</t>
         </is>
       </c>
-      <c r="C105" s="5" t="inlineStr">
+      <c r="C105" s="8" t="inlineStr">
         <is>
           <t>Tek Bir Ağaçtan Oluşan 47 Bin Gövdeli Dev Orman: Pando! 🌲🌍 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D105" s="5" t="inlineStr">
+      <c r="D105" s="8" t="inlineStr">
         <is>
           <t>Utah'taki Pando ormanı aslında 47 bin ayrı ağaç değil, yer altındaki tek bir kök sisteminden çıkan dev bir organizmadır.
 Bu ormanı ilk gördüğünüzde tek bir canlı olduğunu tahmin eder miydiniz? Yorumlara yazın! 👇
@@ -6475,53 +6490,53 @@
 #bilgidozu #shorts #doğa #orman #bilim</t>
         </is>
       </c>
-      <c r="E105" s="5" t="inlineStr">
+      <c r="E105" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #orman #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F105" s="5" t="inlineStr">
+      <c r="F105" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, pando ormanı, doğa, ağaç, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G105" s="5" t="inlineStr">
+      <c r="G105" s="8" t="inlineStr">
         <is>
           <t>Bu ormanı ilk gördüğünüzde tek bir canlı olduğunu tahmin eder miydiniz? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H105" s="5" t="inlineStr">
+      <c r="H105" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Canlılar</t>
         </is>
       </c>
-      <c r="I105" s="5" t="inlineStr">
+      <c r="I105" s="8" t="inlineStr">
         <is>
           <t>USDA Forest Service — Pando Clonal Colony: https://www.fs.usda.gov/detail/fishlake/home/?cid=stelprdb5444544</t>
         </is>
       </c>
-      <c r="J105" s="5" t="n"/>
-      <c r="K105" s="5" t="n"/>
-      <c r="L105" s="5" t="n"/>
-      <c r="M105" s="5" t="n"/>
+      <c r="J105" s="8" t="n"/>
+      <c r="K105" s="8" t="n"/>
+      <c r="L105" s="8" t="n"/>
+      <c r="M105" s="8" t="n"/>
     </row>
     <row r="106" ht="42" customHeight="1">
-      <c r="A106" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
         <is>
           <t>video_85.mp4</t>
         </is>
       </c>
-      <c r="C106" s="5" t="inlineStr">
+      <c r="C106" s="8" t="inlineStr">
         <is>
           <t>Yıldırım Yukarıdan Düşmez: Parlama Yerden Gökyüzüne Çıkar! ⚡🌩️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D106" s="5" t="inlineStr">
+      <c r="D106" s="8" t="inlineStr">
         <is>
           <t>Buluttan inen öncü akım yere yaklaştığında, yerden yükselen pozitif yüklerle birleşir ve gördüğümüz ana parlama yerden gökyüzüne çıkar.
 Yıldırımın yerden yukarı çıktığını ilk kez mi duydunuz? Yorumlarda belirtin! 👇
@@ -6530,53 +6545,53 @@
 #bilgidozu #shorts #bilim #yıldırım #doğaolayları</t>
         </is>
       </c>
-      <c r="E106" s="5" t="inlineStr">
+      <c r="E106" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #bilim #yıldırım #doğaolayları #dozdışı</t>
         </is>
       </c>
-      <c r="F106" s="5" t="inlineStr">
+      <c r="F106" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, yıldırım, günlük bilim, fizik, doğa olayları, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G106" s="5" t="inlineStr">
+      <c r="G106" s="8" t="inlineStr">
         <is>
           <t>Yıldırımın yerden yukarı çıktığını ilk kez mi duydunuz? Yorumlarda belirtin! 👇</t>
         </is>
       </c>
-      <c r="H106" s="5" t="inlineStr">
+      <c r="H106" s="8" t="inlineStr">
         <is>
           <t>Fizik ve Mühendislik</t>
         </is>
       </c>
-      <c r="I106" s="5" t="inlineStr">
+      <c r="I106" s="8" t="inlineStr">
         <is>
           <t>NOAA Severe Weather — Lightning Return Stroke Physics: https://www.weather.gov/safety/lightning-science</t>
         </is>
       </c>
-      <c r="J106" s="5" t="n"/>
-      <c r="K106" s="5" t="n"/>
-      <c r="L106" s="5" t="n"/>
-      <c r="M106" s="5" t="n"/>
+      <c r="J106" s="8" t="n"/>
+      <c r="K106" s="8" t="n"/>
+      <c r="L106" s="8" t="n"/>
+      <c r="M106" s="8" t="n"/>
     </row>
     <row r="107" ht="42" customHeight="1">
-      <c r="A107" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
         <is>
           <t>video_86.mp4</t>
         </is>
       </c>
-      <c r="C107" s="5" t="inlineStr">
+      <c r="C107" s="8" t="inlineStr">
         <is>
           <t>Jüpiter'de Dünya'dan Büyük 300 Yıllık Fırtına: Büyük Kırmızı Leke! 🌪️🪐 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D107" s="5" t="inlineStr">
+      <c r="D107" s="8" t="inlineStr">
         <is>
           <t>Jüpiter'deki Büyük Kırmızı Leke, içine Dünya'yı sığdırabilecek büyüklükte ve en az 300 yıldır aralıksız dönen bir fırtınadır.
 Sizce Jüpiter'deki bu dev fırtına bir gün tamamen durur mu? Tahmininizi yorumlara yazın! 👇
@@ -6585,53 +6600,53 @@
 #bilgidozu #shorts #uzay #jüpiter #bilim</t>
         </is>
       </c>
-      <c r="E107" s="5" t="inlineStr">
+      <c r="E107" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #jüpiter #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F107" s="5" t="inlineStr">
+      <c r="F107" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, jüpiter, büyük kırmızı leke, uzay, astronomi, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G107" s="5" t="inlineStr">
+      <c r="G107" s="8" t="inlineStr">
         <is>
           <t>Sizce Jüpiter'deki bu dev fırtına bir gün tamamen durur mu? Tahmininizi yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H107" s="5" t="inlineStr">
+      <c r="H107" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Evren</t>
         </is>
       </c>
-      <c r="I107" s="5" t="inlineStr">
+      <c r="I107" s="8" t="inlineStr">
         <is>
           <t>NASA Juno Mission — Jupiter Great Red Spot: https://science.nasa.gov/jupiter/facts/</t>
         </is>
       </c>
-      <c r="J107" s="5" t="n"/>
-      <c r="K107" s="5" t="n"/>
-      <c r="L107" s="5" t="n"/>
-      <c r="M107" s="5" t="n"/>
+      <c r="J107" s="8" t="n"/>
+      <c r="K107" s="8" t="n"/>
+      <c r="L107" s="8" t="n"/>
+      <c r="M107" s="8" t="n"/>
     </row>
     <row r="108" ht="42" customHeight="1">
-      <c r="A108" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B108" s="4" t="inlineStr">
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
         <is>
           <t>video_87.mp4</t>
         </is>
       </c>
-      <c r="C108" s="5" t="inlineStr">
+      <c r="C108" s="8" t="inlineStr">
         <is>
           <t>Everest'in 3 Katı Yüksekliğinde Dev Yanardağ: Olympus Mons! 🌋🔴 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D108" s="5" t="inlineStr">
+      <c r="D108" s="8" t="inlineStr">
         <is>
           <t>Mars'taki Olympus Mons yanardağı yaklaşık 22 kilometre yüksekliğiyle Everest Dağı'nın tam 3 katı büyüklüğündedir.
 Everest'in üç katı yüksekliğinde bir dağın zirvesine çıkmak ister miydiniz? Yorumlara yazın! 👇
@@ -6640,53 +6655,53 @@
 #bilgidozu #shorts #mars #uzay #bilim</t>
         </is>
       </c>
-      <c r="E108" s="5" t="inlineStr">
+      <c r="E108" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #mars #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F108" s="5" t="inlineStr">
+      <c r="F108" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, mars, olympus mons, yanardağ, uzay, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G108" s="5" t="inlineStr">
+      <c r="G108" s="8" t="inlineStr">
         <is>
           <t>Everest'in üç katı yüksekliğinde bir dağın zirvesine çıkmak ister miydiniz? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H108" s="5" t="inlineStr">
+      <c r="H108" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Evren</t>
         </is>
       </c>
-      <c r="I108" s="5" t="inlineStr">
+      <c r="I108" s="8" t="inlineStr">
         <is>
           <t>NASA Mars Exploration — Olympus Mons: https://science.nasa.gov/mars/facts/</t>
         </is>
       </c>
-      <c r="J108" s="5" t="n"/>
-      <c r="K108" s="5" t="n"/>
-      <c r="L108" s="5" t="n"/>
-      <c r="M108" s="5" t="n"/>
+      <c r="J108" s="8" t="n"/>
+      <c r="K108" s="8" t="n"/>
+      <c r="L108" s="8" t="n"/>
+      <c r="M108" s="8" t="n"/>
     </row>
     <row r="109" ht="42" customHeight="1">
-      <c r="A109" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
         <is>
           <t>video_88.mp4</t>
         </is>
       </c>
-      <c r="C109" s="5" t="inlineStr">
+      <c r="C109" s="8" t="inlineStr">
         <is>
           <t>Beyni ve Kanı Olmadan Denizde Avlanan Canlı: Denizyıldızı! ⭐🌊 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D109" s="5" t="inlineStr">
+      <c r="D109" s="8" t="inlineStr">
         <is>
           <t>Denizyıldızlarının merkezi bir beyni ve kanı yoktur; damarlarında kalp yerine pompalanan filtre edilmiş deniz suyu dolaşır.
 Beyni ve kanı olmadan yaşayan bu canlı hakkında siz ne düşünüyorsunuz? Yorumlara yazın! 👇
@@ -6695,53 +6710,53 @@
 #bilgidozu #shorts #doğa #okyanus #bilim</t>
         </is>
       </c>
-      <c r="E109" s="5" t="inlineStr">
+      <c r="E109" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #okyanus #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F109" s="5" t="inlineStr">
+      <c r="F109" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, denizyıldızı, okyanus, doğa, hayvanlar, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G109" s="5" t="inlineStr">
+      <c r="G109" s="8" t="inlineStr">
         <is>
           <t>Beyni ve kanı olmadan yaşayan bu canlı hakkında siz ne düşünüyorsunuz? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H109" s="5" t="inlineStr">
+      <c r="H109" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Canlılar</t>
         </is>
       </c>
-      <c r="I109" s="5" t="inlineStr">
+      <c r="I109" s="8" t="inlineStr">
         <is>
           <t>Smithsonian Ocean / Wikipedia — Sea Stars Anatomy: https://en.wikipedia.org/wiki/Starfish</t>
         </is>
       </c>
-      <c r="J109" s="5" t="n"/>
-      <c r="K109" s="5" t="n"/>
-      <c r="L109" s="5" t="n"/>
-      <c r="M109" s="5" t="n"/>
+      <c r="J109" s="8" t="n"/>
+      <c r="K109" s="8" t="n"/>
+      <c r="L109" s="8" t="n"/>
+      <c r="M109" s="8" t="n"/>
     </row>
     <row r="110" ht="42" customHeight="1">
-      <c r="A110" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B110" s="4" t="inlineStr">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
         <is>
           <t>video_89.mp4</t>
         </is>
       </c>
-      <c r="C110" s="5" t="inlineStr">
+      <c r="C110" s="8" t="inlineStr">
         <is>
           <t>Yunuslar Tek Gözü Açık ve Yarım Beyinle Nasıl Uyur? 🐬🌊 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D110" s="5" t="inlineStr">
+      <c r="D110" s="8" t="inlineStr">
         <is>
           <t>Yunuslar uykuda boğulmamak için beyinlerinin sadece bir yarısını uyuturken diğer yarısıyla nefes alıp çevreyi gözetler.
 Beyninizin yarısını uyutup diğer yarısıyla uyanık kalmak ister miydiniz? Yorumlara yazın! 👇
@@ -6750,53 +6765,53 @@
 #bilgidozu #shorts #yunus #doğa #bilim</t>
         </is>
       </c>
-      <c r="E110" s="5" t="inlineStr">
+      <c r="E110" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #yunus #doğa #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F110" s="5" t="inlineStr">
+      <c r="F110" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, yunuslar, doğa, hayvanlar alemi, uyku, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G110" s="5" t="inlineStr">
+      <c r="G110" s="8" t="inlineStr">
         <is>
           <t>Beyninizin yarısını uyutup diğer yarısıyla uyanık kalmak ister miydiniz? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H110" s="5" t="inlineStr">
+      <c r="H110" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Canlılar</t>
         </is>
       </c>
-      <c r="I110" s="5" t="inlineStr">
+      <c r="I110" s="8" t="inlineStr">
         <is>
           <t>Sleep Foundation / Wikipedia — Unihemispheric Slow-Wave Sleep: https://en.wikipedia.org/wiki/Unihemispheric_slow-wave_sleep</t>
         </is>
       </c>
-      <c r="J110" s="5" t="n"/>
-      <c r="K110" s="5" t="n"/>
-      <c r="L110" s="5" t="n"/>
-      <c r="M110" s="5" t="n"/>
+      <c r="J110" s="8" t="n"/>
+      <c r="K110" s="8" t="n"/>
+      <c r="L110" s="8" t="n"/>
+      <c r="M110" s="8" t="n"/>
     </row>
     <row r="111" ht="42" customHeight="1">
-      <c r="A111" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
         <is>
           <t>video_90.mp4</t>
         </is>
       </c>
-      <c r="C111" s="5" t="inlineStr">
+      <c r="C111" s="8" t="inlineStr">
         <is>
           <t>Dev Bir Okyanusa Bırakılsa Suda Yüzecek Gezegen: Satürn! 🪐🌊 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D111" s="5" t="inlineStr">
+      <c r="D111" s="8" t="inlineStr">
         <is>
           <t>Satürn'ün ortalama yoğunluğu santimetreküp başına 0,68 gramdır; yani sudan daha hafif olduğu için dev bir okyanusta yüzebilir.
 Koca bir gezegenin sudan daha hafif olması sizi de şaşırttı mı? Yorumlara yazın! 👇
@@ -6805,53 +6820,53 @@
 #bilgidozu #shorts #satürn #uzay #bilim</t>
         </is>
       </c>
-      <c r="E111" s="5" t="inlineStr">
+      <c r="E111" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #satürn #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F111" s="5" t="inlineStr">
+      <c r="F111" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, satürn, uzay, gezegenler, astronomi, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G111" s="5" t="inlineStr">
+      <c r="G111" s="8" t="inlineStr">
         <is>
           <t>Koca bir gezegenin sudan daha hafif olması sizi de şaşırttı mı? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H111" s="5" t="inlineStr">
+      <c r="H111" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Evren</t>
         </is>
       </c>
-      <c r="I111" s="5" t="inlineStr">
+      <c r="I111" s="8" t="inlineStr">
         <is>
           <t>NASA Cassini Mission — Saturn Planetary Density: https://science.nasa.gov/saturn/facts/</t>
         </is>
       </c>
-      <c r="J111" s="5" t="n"/>
-      <c r="K111" s="5" t="n"/>
-      <c r="L111" s="5" t="n"/>
-      <c r="M111" s="5" t="n"/>
+      <c r="J111" s="8" t="n"/>
+      <c r="K111" s="8" t="n"/>
+      <c r="L111" s="8" t="n"/>
+      <c r="M111" s="8" t="n"/>
     </row>
     <row r="112" ht="42" customHeight="1">
-      <c r="A112" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B112" s="4" t="inlineStr">
+      <c r="A112" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B112" s="7" t="inlineStr">
         <is>
           <t>video_92.mp4</t>
         </is>
       </c>
-      <c r="C112" s="5" t="inlineStr">
+      <c r="C112" s="8" t="inlineStr">
         <is>
           <t>Cam Zamanla Akan Bir Sıvı Değil: En Büyük Bilim Efsanesi! 🪟🔬 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D112" s="5" t="inlineStr">
+      <c r="D112" s="8" t="inlineStr">
         <is>
           <t>Cam çok yavaş akan bir sıvı değil, amorf bir katıdır; eski pencerelerin altının kalın olması üretim tekniğinden kaynaklanır.
 Siz de okulda camın çok yavaş akan bir sıvı olduğunu duymuş muydunuz? Yorumlarda belirtin! 👇
@@ -6860,53 +6875,53 @@
 #bilgidozu #shorts #bilim #fizik #ilginçbilgiler</t>
         </is>
       </c>
-      <c r="E112" s="5" t="inlineStr">
+      <c r="E112" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #bilim #fizik #ilginçbilgiler #dozdışı</t>
         </is>
       </c>
-      <c r="F112" s="5" t="inlineStr">
+      <c r="F112" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, cam, fizik, günlük bilim, şehir efsanesi, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G112" s="5" t="inlineStr">
+      <c r="G112" s="8" t="inlineStr">
         <is>
           <t>Siz de okulda camın çok yavaş akan bir sıvı olduğunu duymuş muydunuz? Yorumlarda belirtin! 👇</t>
         </is>
       </c>
-      <c r="H112" s="5" t="inlineStr">
+      <c r="H112" s="8" t="inlineStr">
         <is>
           <t>Fizik ve Mühendislik</t>
         </is>
       </c>
-      <c r="I112" s="5" t="inlineStr">
+      <c r="I112" s="8" t="inlineStr">
         <is>
           <t>American Journal of Physics (Zanotto, 1998) — Do Cathedral Glasses Flow?: https://en.wikipedia.org/wiki/Glass</t>
         </is>
       </c>
-      <c r="J112" s="5" t="n"/>
-      <c r="K112" s="5" t="n"/>
-      <c r="L112" s="5" t="n"/>
-      <c r="M112" s="5" t="n"/>
+      <c r="J112" s="8" t="n"/>
+      <c r="K112" s="8" t="n"/>
+      <c r="L112" s="8" t="n"/>
+      <c r="M112" s="8" t="n"/>
     </row>
     <row r="113" ht="42" customHeight="1">
-      <c r="A113" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B113" s="4" t="inlineStr">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B113" s="7" t="inlineStr">
         <is>
           <t>video_93.mp4</t>
         </is>
       </c>
-      <c r="C113" s="5" t="inlineStr">
+      <c r="C113" s="8" t="inlineStr">
         <is>
           <t>Ay Her Yıl Dünya'dan 3,8 Santimetre Uzaklaşıyor! 🌕🚀 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D113" s="5" t="inlineStr">
+      <c r="D113" s="8" t="inlineStr">
         <is>
           <t>Apollo astronotlarının bıraktığı lazer aynaları, Ay'ın gelgit kuvvetleri nedeniyle her yıl 3,8 cm uzaklaştığını kanıtlamıştır.
 Peki Ay'ın her yıl bizden uzaklaşması gelecekte Dünya'yı sizce nasıl etkiler? Yorumlara yazın! 👇
@@ -6915,53 +6930,53 @@
 #bilgidozu #shorts #ay #uzay #bilim</t>
         </is>
       </c>
-      <c r="E113" s="5" t="inlineStr">
+      <c r="E113" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #ay #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F113" s="5" t="inlineStr">
+      <c r="F113" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, ay, dünya, uzay, astronomi, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G113" s="5" t="inlineStr">
+      <c r="G113" s="8" t="inlineStr">
         <is>
           <t>Peki Ay'ın her yıl bizden uzaklaşması gelecekte Dünya'yı sizce nasıl etkiler? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H113" s="5" t="inlineStr">
+      <c r="H113" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Evren</t>
         </is>
       </c>
-      <c r="I113" s="5" t="inlineStr">
+      <c r="I113" s="8" t="inlineStr">
         <is>
           <t>NASA — Lunar Laser Ranging Experiment: https://science.nasa.gov/moon/facts/</t>
         </is>
       </c>
-      <c r="J113" s="5" t="n"/>
-      <c r="K113" s="5" t="n"/>
-      <c r="L113" s="5" t="n"/>
-      <c r="M113" s="5" t="n"/>
+      <c r="J113" s="8" t="n"/>
+      <c r="K113" s="8" t="n"/>
+      <c r="L113" s="8" t="n"/>
+      <c r="M113" s="8" t="n"/>
     </row>
     <row r="114" ht="42" customHeight="1">
-      <c r="A114" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B114" s="4" t="inlineStr">
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B114" s="7" t="inlineStr">
         <is>
           <t>video_94.mp4</t>
         </is>
       </c>
-      <c r="C114" s="5" t="inlineStr">
+      <c r="C114" s="8" t="inlineStr">
         <is>
           <t>Yetişkin Kediler Birbirine Değil Sadece İnsanlara Miyavlar! 🐱🔊 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D114" s="5" t="inlineStr">
+      <c r="D114" s="8" t="inlineStr">
         <is>
           <t>Yetişkin kediler kendi aralarında koku ve beden diliyle anlaşır; miyavlama sesini sadece insanlarla iletişim kurmak için kullanır.
 Sizin kediniz bir şey istediğinde nasıl sesler çıkarıyor? Yorumlarda anlatın! 👇
@@ -6970,53 +6985,53 @@
 #bilgidozu #shorts #kediler #hayvanlar #doğa</t>
         </is>
       </c>
-      <c r="E114" s="5" t="inlineStr">
+      <c r="E114" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #kediler #hayvanlar #doğa #dozdışı</t>
         </is>
       </c>
-      <c r="F114" s="5" t="inlineStr">
+      <c r="F114" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, kediler, kedi miyavlaması, doğa, hayvanlar, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G114" s="5" t="inlineStr">
+      <c r="G114" s="8" t="inlineStr">
         <is>
           <t>Sizin kediniz bir şey istediğinde nasıl sesler çıkarıyor? Yorumlarda anlatın! 👇</t>
         </is>
       </c>
-      <c r="H114" s="5" t="inlineStr">
+      <c r="H114" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Canlılar</t>
         </is>
       </c>
-      <c r="I114" s="5" t="inlineStr">
+      <c r="I114" s="8" t="inlineStr">
         <is>
           <t>Cornell Feline Health Center / Wikipedia — Cat Vocalization: https://en.wikipedia.org/wiki/Cat_communication</t>
         </is>
       </c>
-      <c r="J114" s="5" t="n"/>
-      <c r="K114" s="5" t="n"/>
-      <c r="L114" s="5" t="n"/>
-      <c r="M114" s="5" t="n"/>
+      <c r="J114" s="8" t="n"/>
+      <c r="K114" s="8" t="n"/>
+      <c r="L114" s="8" t="n"/>
+      <c r="M114" s="8" t="n"/>
     </row>
     <row r="115" ht="42" customHeight="1">
-      <c r="A115" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="inlineStr">
+      <c r="A115" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
         <is>
           <t>video_95.mp4</t>
         </is>
       </c>
-      <c r="C115" s="5" t="inlineStr">
+      <c r="C115" s="8" t="inlineStr">
         <is>
           <t>Dünya Uzayda Saniyede 30 Kilometre Hızla Uçuyor! 🌍⚡ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D115" s="5" t="inlineStr">
+      <c r="D115" s="8" t="inlineStr">
         <is>
           <t>Dünya Güneş etrafındaki yörüngesinde saniyede 30 km, yani saatte 108 bin km hızla ilerler.
 Dünya'nın uzayda saniyede otuz kilometre hızla uçtuğunu bilmek başınızı döndürdü mü? Yorumlara yazın! 👇
@@ -7025,53 +7040,53 @@
 #bilgidozu #shorts #dünya #uzay #bilim</t>
         </is>
       </c>
-      <c r="E115" s="5" t="inlineStr">
+      <c r="E115" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #dünya #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F115" s="5" t="inlineStr">
+      <c r="F115" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, dünya, uzay, güneş sistemi, hız, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G115" s="5" t="inlineStr">
+      <c r="G115" s="8" t="inlineStr">
         <is>
           <t>Dünya'nın uzayda saniyede otuz kilometre hızla uçtuğunu bilmek başınızı döndürdü mü? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H115" s="5" t="inlineStr">
+      <c r="H115" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Evren</t>
         </is>
       </c>
-      <c r="I115" s="5" t="inlineStr">
+      <c r="I115" s="8" t="inlineStr">
         <is>
           <t>NASA Earth Fact Sheet — Orbital Velocity: https://science.nasa.gov/earth/facts/</t>
         </is>
       </c>
-      <c r="J115" s="5" t="n"/>
-      <c r="K115" s="5" t="n"/>
-      <c r="L115" s="5" t="n"/>
-      <c r="M115" s="5" t="n"/>
+      <c r="J115" s="8" t="n"/>
+      <c r="K115" s="8" t="n"/>
+      <c r="L115" s="8" t="n"/>
+      <c r="M115" s="8" t="n"/>
     </row>
     <row r="116" ht="42" customHeight="1">
-      <c r="A116" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B116" s="4" t="inlineStr">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B116" s="7" t="inlineStr">
         <is>
           <t>video_96.mp4</t>
         </is>
       </c>
-      <c r="C116" s="5" t="inlineStr">
+      <c r="C116" s="8" t="inlineStr">
         <is>
           <t>Mısır Piramitlerinden Çıkan 3000 Yıllık Yenebilir Bal! 🍯🏺 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D116" s="5" t="inlineStr">
+      <c r="D116" s="8" t="inlineStr">
         <is>
           <t>Mısır firavun mezarlarında bulunan 3000 yıllık mühürlü bal küpleri, düşük nem ve asidik yapı sayesinde bozulmadan kalmıştır.
 Peki üç bin yıllık bir mezardan çıkan balı tatmaya cesaret eder miydiniz? Yorumlara yazın! 👇
@@ -7080,53 +7095,53 @@
 #bilgidozu #shorts #tarih #mısır #bilim</t>
         </is>
       </c>
-      <c r="E116" s="5" t="inlineStr">
+      <c r="E116" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #mısır #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F116" s="5" t="inlineStr">
+      <c r="F116" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, mısır piramitleri, bal, tarih, arkeoloji, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G116" s="5" t="inlineStr">
+      <c r="G116" s="8" t="inlineStr">
         <is>
           <t>Peki üç bin yıllık bir mezardan çıkan balı tatmaya cesaret eder miydiniz? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H116" s="5" t="inlineStr">
+      <c r="H116" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Arkeoloji</t>
         </is>
       </c>
-      <c r="I116" s="5" t="inlineStr">
+      <c r="I116" s="8" t="inlineStr">
         <is>
           <t>Smithsonian Magazine — The Science Behind Honey's Eternal Shelf Life: https://en.wikipedia.org/wiki/Honey</t>
         </is>
       </c>
-      <c r="J116" s="5" t="n"/>
-      <c r="K116" s="5" t="n"/>
-      <c r="L116" s="5" t="n"/>
-      <c r="M116" s="5" t="n"/>
+      <c r="J116" s="8" t="n"/>
+      <c r="K116" s="8" t="n"/>
+      <c r="L116" s="8" t="n"/>
+      <c r="M116" s="8" t="n"/>
     </row>
     <row r="117" ht="42" customHeight="1">
-      <c r="A117" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B117" s="4" t="inlineStr">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B117" s="7" t="inlineStr">
         <is>
           <t>video_97.mp4</t>
         </is>
       </c>
-      <c r="C117" s="5" t="inlineStr">
+      <c r="C117" s="8" t="inlineStr">
         <is>
           <t>Dünya'nın Çekirdeği Güneş Yüzeyi Kadar Sıcak: 5400 Derece! 🌋🔥 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D117" s="5" t="inlineStr">
+      <c r="D117" s="8" t="inlineStr">
         <is>
           <t>Dünya'nın iç çekirdeği yaklaşık 5400 santigrat derece sıcaklığıyla Güneş'in yüzeyi kadar sıcaktır ancak dev basınç nedeniyle katıdır.
 Ayaklarımızın altında Güneş kadar sıcak bir çekirdek olması sizi de şaşırttı mı? Yorumlarda buluşalım! 👇
@@ -7135,53 +7150,53 @@
 #bilgidozu #shorts #dünya #bilim #jeoloji</t>
         </is>
       </c>
-      <c r="E117" s="5" t="inlineStr">
+      <c r="E117" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #dünya #bilim #jeoloji #dozdışı</t>
         </is>
       </c>
-      <c r="F117" s="5" t="inlineStr">
+      <c r="F117" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, dünya çekirdeği, güneş, jeoloji, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G117" s="5" t="inlineStr">
+      <c r="G117" s="8" t="inlineStr">
         <is>
           <t>Ayaklarımızın altında Güneş kadar sıcak bir çekirdek olması sizi de şaşırttı mı? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H117" s="5" t="inlineStr">
+      <c r="H117" s="8" t="inlineStr">
         <is>
           <t>Fizik ve Mühendislik</t>
         </is>
       </c>
-      <c r="I117" s="5" t="inlineStr">
+      <c r="I117" s="8" t="inlineStr">
         <is>
           <t>Science / Wikipedia — Earth's Inner Core Temperature: https://en.wikipedia.org/wiki/Earth%27s_inner_core</t>
         </is>
       </c>
-      <c r="J117" s="5" t="n"/>
-      <c r="K117" s="5" t="n"/>
-      <c r="L117" s="5" t="n"/>
-      <c r="M117" s="5" t="n"/>
+      <c r="J117" s="8" t="n"/>
+      <c r="K117" s="8" t="n"/>
+      <c r="L117" s="8" t="n"/>
+      <c r="M117" s="8" t="n"/>
     </row>
     <row r="118" ht="42" customHeight="1">
-      <c r="A118" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B118" s="4" t="inlineStr">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B118" s="7" t="inlineStr">
         <is>
           <t>video_98.mp4</t>
         </is>
       </c>
-      <c r="C118" s="5" t="inlineStr">
+      <c r="C118" s="8" t="inlineStr">
         <is>
           <t>Filler Kilometrelerce Uzaktaki Sesi Ayak Tabanıyla Duyar! 🐘🌍 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D118" s="5" t="inlineStr">
+      <c r="D118" s="8" t="inlineStr">
         <is>
           <t>Filler çıkardıkları düşük frekanslı seslerin topraktaki sismik titreşimlerini hassas ayak tabanlarıyla kilometrelerce uzaktan algılar.
 Fillerin ayak tabanlarıyla yeri dinleyerek anlaşması hakkında ne düşünüyorsunuz? Yorumlara yazın! 👇
@@ -7190,53 +7205,53 @@
 #bilgidozu #shorts #filler #doğa #bilim</t>
         </is>
       </c>
-      <c r="E118" s="5" t="inlineStr">
+      <c r="E118" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #filler #doğa #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F118" s="5" t="inlineStr">
+      <c r="F118" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, filler, doğa, hayvanlar, sismik ses, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G118" s="5" t="inlineStr">
+      <c r="G118" s="8" t="inlineStr">
         <is>
           <t>Fillerin ayak tabanlarıyla yeri dinleyerek anlaşması hakkında ne düşünüyorsunuz? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H118" s="5" t="inlineStr">
+      <c r="H118" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Canlılar</t>
         </is>
       </c>
-      <c r="I118" s="5" t="inlineStr">
+      <c r="I118" s="8" t="inlineStr">
         <is>
           <t>Stanford University / Wikipedia — Elephant Seismic Communication: https://en.wikipedia.org/wiki/Elephant_cognition</t>
         </is>
       </c>
-      <c r="J118" s="5" t="n"/>
-      <c r="K118" s="5" t="n"/>
-      <c r="L118" s="5" t="n"/>
-      <c r="M118" s="5" t="n"/>
+      <c r="J118" s="8" t="n"/>
+      <c r="K118" s="8" t="n"/>
+      <c r="L118" s="8" t="n"/>
+      <c r="M118" s="8" t="n"/>
     </row>
     <row r="119" ht="42" customHeight="1">
-      <c r="A119" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B119" s="4" t="inlineStr">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B119" s="7" t="inlineStr">
         <is>
           <t>video_99.mp4</t>
         </is>
       </c>
-      <c r="C119" s="5" t="inlineStr">
+      <c r="C119" s="8" t="inlineStr">
         <is>
           <t>Yan Yatarak Dönen Gezegen Uranüs'te 1 Gece 42 Yıl Sürüyor! 🪐❄️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D119" s="5" t="inlineStr">
+      <c r="D119" s="8" t="inlineStr">
         <is>
           <t>Yörüngesinde 98 derece yan yatmış olan Uranüs'ün kutuplarında bir gündüz ve bir gece aralıksız 42 Dünya yılı sürer.
 Kırk iki yıl süren bir gecede mi yoksa kırk iki yıl süren gündüzde mi yaşamak isterdiniz? Yorumlara yazın! 👇
@@ -7245,53 +7260,53 @@
 #bilgidozu #shorts #uranüs #uzay #bilim</t>
         </is>
       </c>
-      <c r="E119" s="5" t="inlineStr">
+      <c r="E119" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uranüs #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F119" s="5" t="inlineStr">
+      <c r="F119" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, uranüs, uzay, gezegenler, astronomi, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G119" s="5" t="inlineStr">
+      <c r="G119" s="8" t="inlineStr">
         <is>
           <t>Kırk iki yıl süren bir gecede mi yoksa kırk iki yıl süren gündüzde mi yaşamak isterdiniz? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H119" s="5" t="inlineStr">
+      <c r="H119" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Evren</t>
         </is>
       </c>
-      <c r="I119" s="5" t="inlineStr">
+      <c r="I119" s="8" t="inlineStr">
         <is>
           <t>NASA — Uranus Planetary Fact Sheet: https://science.nasa.gov/uranus/facts/</t>
         </is>
       </c>
-      <c r="J119" s="5" t="n"/>
-      <c r="K119" s="5" t="n"/>
-      <c r="L119" s="5" t="n"/>
-      <c r="M119" s="5" t="n"/>
+      <c r="J119" s="8" t="n"/>
+      <c r="K119" s="8" t="n"/>
+      <c r="L119" s="8" t="n"/>
+      <c r="M119" s="8" t="n"/>
     </row>
     <row r="120" ht="42" customHeight="1">
-      <c r="A120" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B120" s="4" t="inlineStr">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B120" s="7" t="inlineStr">
         <is>
           <t>video_101.mp4</t>
         </is>
       </c>
-      <c r="C120" s="5" t="inlineStr">
+      <c r="C120" s="8" t="inlineStr">
         <is>
           <t>Güneş Bir Saniyeliğine Sönseydi Ne Olurdu? ☀️🌑 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D120" s="5" t="inlineStr">
+      <c r="D120" s="8" t="inlineStr">
         <is>
           <t>Şu an başını kaldırıp gökyüzüne baktığında, Güneş'in hâlâ orada olduğundan gerçekten emin misin? Ya tam şu saniye sessizce söndüyse? İşin en ürpertici kısmı ne biliyor musun? Bunu tam sekiz dakika yirmi saniye boyunca ruhun bile duymayacak. Çünkü Güneş'ten çıkan son ışık gözüne ulaşana kadar gökyüzü masmavi kalır. Ama sekizinci dakikanın sonunda gökyüzü bir anda zifiri karanlığa gömülür ve Dünya yörüngeden kopup buzlu boşluğa savrulur. Peki sen o son sekiz dakikayı dışarıda gökyüzünü izleyerek mi geçirirdin, yoksa yeraltı sığınaklarına inerek mi? Yorumlarda buluşalım.
 💬 Peki böyle bir kırılma anında sen sekiz dakikalık son gün ışığını dışarıda izlemeyi mi seçerdin, yoksa doğrudan yeraltı sığınaklarına inmeyi mi? Yorumlarda buluşalım! 👇
@@ -7300,53 +7315,53 @@
 #bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
-      <c r="E120" s="5" t="inlineStr">
+      <c r="E120" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F120" s="5" t="inlineStr">
+      <c r="F120" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, güneş, uzay, kozmik felaket, astronomi, bilim, dünya, ışık hızı, ilginç bilgiler, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G120" s="5" t="inlineStr">
+      <c r="G120" s="8" t="inlineStr">
         <is>
           <t>Peki böyle bir kırılma anında sen sekiz dakikalık son gün ışığını dışarıda izlemeyi mi seçerdin, yoksa doğrudan yeraltı sığınaklarına inmeyi mi? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H120" s="5" t="inlineStr">
+      <c r="H120" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I120" s="5" t="inlineStr">
+      <c r="I120" s="8" t="inlineStr">
         <is>
           <t>NASA / Wikipedia — Sunlight (Işık Hızı ve Güneş Işığı Süresi): https://en.wikipedia.org/wiki/Sunlight</t>
         </is>
       </c>
-      <c r="J120" s="5" t="n"/>
-      <c r="K120" s="5" t="n"/>
-      <c r="L120" s="5" t="n"/>
-      <c r="M120" s="5" t="n"/>
+      <c r="J120" s="8" t="n"/>
+      <c r="K120" s="8" t="n"/>
+      <c r="L120" s="8" t="n"/>
+      <c r="M120" s="8" t="n"/>
     </row>
     <row r="121" ht="42" customHeight="1">
-      <c r="A121" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B121" s="4" t="inlineStr">
+      <c r="A121" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B121" s="7" t="inlineStr">
         <is>
           <t>video_102.mp4</t>
         </is>
       </c>
-      <c r="C121" s="5" t="inlineStr">
+      <c r="C121" s="8" t="inlineStr">
         <is>
           <t>Ay Dünya'ya Yaklaşsaydı Okyanuslara Ne Olurdu? 🌕🌊 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D121" s="5" t="inlineStr">
+      <c r="D121" s="8" t="inlineStr">
         <is>
           <t>Gece gökyüzüne baktığında, Ay'ın hep aynı yerde durduğunu sanıyorsun değil mi? Peki ya Ay Dünya'ya doğru yaklaşmaya başlasaydı ne olurdu? İlk başta gökyüzünde devasa görünürdü ama hemen ardından kütle çekim kabusu başlardı. Okyanuslar yüzlerce metre yükselip kıyı şehirlerini yutardı. Dünya'ya on sekiz bin kilometre mesafedeki Roche sınırına girdiği anda ise Ay gökyüzünde paramparça olur ve Dünya'nın etrafında tıpkı Satürn gibi parlak bir halka oluştururdu. Peki sen gökyüzünde Satürn gibi dev bir halka görmeyi mi isterdin, yoksa Ay'ın olduğu yerde kalmasını mı? Yorumlarda buluşalım.
 💬 Peki sen gökyüzünde dev bir Ay yerine Satürn gibi muazzam bir halka görmeyi mi isterdin, yoksa Ay'ın olduğu yerde kalmasını mı? Yorumlarda buluşalım! 👇
@@ -7355,53 +7370,53 @@
 #bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
-      <c r="E121" s="5" t="inlineStr">
+      <c r="E121" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F121" s="5" t="inlineStr">
+      <c r="F121" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, ay, dünya, roche sınırı, satürn, uzay, astronomi, bilim, kozmik felaket, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G121" s="5" t="inlineStr">
+      <c r="G121" s="8" t="inlineStr">
         <is>
           <t>Peki sen gökyüzünde dev bir Ay yerine Satürn gibi muazzam bir halka görmeyi mi isterdin, yoksa Ay'ın olduğu yerde kalmasını mı? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H121" s="5" t="inlineStr">
+      <c r="H121" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I121" s="5" t="inlineStr">
+      <c r="I121" s="8" t="inlineStr">
         <is>
           <t>NASA / Wikipedia — Roche Limit (Gelgit Parçalanma Sınırı): https://en.wikipedia.org/wiki/Roche_limit</t>
         </is>
       </c>
-      <c r="J121" s="5" t="n"/>
-      <c r="K121" s="5" t="n"/>
-      <c r="L121" s="5" t="n"/>
-      <c r="M121" s="5" t="n"/>
+      <c r="J121" s="8" t="n"/>
+      <c r="K121" s="8" t="n"/>
+      <c r="L121" s="8" t="n"/>
+      <c r="M121" s="8" t="n"/>
     </row>
     <row r="122" ht="42" customHeight="1">
-      <c r="A122" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B122" s="4" t="inlineStr">
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B122" s="7" t="inlineStr">
         <is>
           <t>video_103.mp4</t>
         </is>
       </c>
-      <c r="C122" s="5" t="inlineStr">
+      <c r="C122" s="8" t="inlineStr">
         <is>
           <t>Uzayda Ağlarsan Gözyaşların Neden Yanağından Akmaz? 🧑‍🚀💧 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D122" s="5" t="inlineStr">
+      <c r="D122" s="8" t="inlineStr">
         <is>
           <t>Uzayda tek başına süzülürken bir anda ağlamaya başlasan gözyaşlarının yanağından aşağı süzüleceğini mi sanıyorsun? Hiç de öyle olmaz. Dünya'da gözyaşını aşağı çeken şey yerçekimidir. Ama uzayın ağırlıksız boşluğunda, su moleküllerini birbirine kenetleyen yüzey gerilimi tek patron haline gelir. Gözünden çıkan her damla, akmak yerine göz pınarının tam üzerinde şeffaf, titreyen bir su küresine dönüşür ve sen bir bezle silene kadar yüzünden asla ayrılmaz. Peki sen yerçekimsiz ortamda yaşamayı deneyimlemek mi isterdin, yoksa ayağının yere bastığı Dünya'da kalmayı mı? Yorumlarda buluşalım.
 💬 Peki sen yerçekimsiz ortamda haftalarca yaşamayı deneyimlemek mi isterdin, yoksa ayağının sağlamca yere bastığı Dünya'da kalmayı mı? Yorumlarda buluşalım! 👇
@@ -7410,53 +7425,53 @@
 #bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
-      <c r="E122" s="5" t="inlineStr">
+      <c r="E122" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F122" s="5" t="inlineStr">
+      <c r="F122" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, uzay, astronot, yerçekimi, yüzey gerilimi, bilim, fizik, uzay istasyonu, ilginç bilgiler, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G122" s="5" t="inlineStr">
+      <c r="G122" s="8" t="inlineStr">
         <is>
           <t>Peki sen yerçekimsiz ortamda haftalarca yaşamayı deneyimlemek mi isterdin, yoksa ayağının sağlamca yere bastığı Dünya'da kalmayı mı? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H122" s="5" t="inlineStr">
+      <c r="H122" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I122" s="5" t="inlineStr">
+      <c r="I122" s="8" t="inlineStr">
         <is>
           <t>CSA / Wikipedia — Surface Tension in Microgravity (Uzayda Yüzey Gerilimi): https://en.wikipedia.org/wiki/Surface_tension</t>
         </is>
       </c>
-      <c r="J122" s="5" t="n"/>
-      <c r="K122" s="5" t="n"/>
-      <c r="L122" s="5" t="n"/>
-      <c r="M122" s="5" t="n"/>
+      <c r="J122" s="8" t="n"/>
+      <c r="K122" s="8" t="n"/>
+      <c r="L122" s="8" t="n"/>
+      <c r="M122" s="8" t="n"/>
     </row>
     <row r="123" ht="42" customHeight="1">
-      <c r="A123" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B123" s="4" t="inlineStr">
+      <c r="A123" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B123" s="7" t="inlineStr">
         <is>
           <t>video_104.mp4</t>
         </is>
       </c>
-      <c r="C123" s="5" t="inlineStr">
+      <c r="C123" s="8" t="inlineStr">
         <is>
           <t>Dünya'ya 50 Işık Yılı Mesafede Süpernova Patlasa Ne Olur? 💥🌟 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D123" s="5" t="inlineStr">
+      <c r="D123" s="8" t="inlineStr">
         <is>
           <t>Gündüz vakti masmavi gökyüzünde bir anda ikinci bir Güneş'in parladığını hayal et. Dünya'ya elli ışık yılı mesafede dev bir yıldız süpernova olarak patlasaydı tam olarak bunu yaşardık. Haftalarca geceleri bile gökyüzü hiç kararmazdı. Ama asıl tehlike o parlak ışık değil, görünmez gama ışınları olurdu. Üst atmosferdeki ozon tabakası hızla erir ve yüzeye inen radyasyon okyanuslardaki besin zincirini altüst ederdi. Peki böyle bir kozmik patlama görsen, önce teleskopla izlemeye mi koşardın yoksa radyasyondan korunacak bir yer mi arardın? Yorumlarda buluşalım.
 💬 Peki böyle bir kozmik patlama görsen önce teleskopla izlemeye mi koşardın, yoksa radyasyondan korunacak bir yer mi arardın? Yorumlarda buluşalım! 👇
@@ -7465,53 +7480,53 @@
 #bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
-      <c r="E123" s="5" t="inlineStr">
+      <c r="E123" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F123" s="5" t="inlineStr">
+      <c r="F123" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, süpernova, uzay, gama ışınları, kozmik felaket, yıldız, astronomi, bilim, dünya, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G123" s="5" t="inlineStr">
+      <c r="G123" s="8" t="inlineStr">
         <is>
           <t>Peki böyle bir kozmik patlama görsen önce teleskopla izlemeye mi koşardın, yoksa radyasyondan korunacak bir yer mi arardın? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H123" s="5" t="inlineStr">
+      <c r="H123" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I123" s="5" t="inlineStr">
+      <c r="I123" s="8" t="inlineStr">
         <is>
           <t>NASA / Wikipedia — Near-Earth Supernova (Yakın Süpernova Etkileri): https://en.wikipedia.org/wiki/Near-Earth_supernova</t>
         </is>
       </c>
-      <c r="J123" s="5" t="n"/>
-      <c r="K123" s="5" t="n"/>
-      <c r="L123" s="5" t="n"/>
-      <c r="M123" s="5" t="n"/>
+      <c r="J123" s="8" t="n"/>
+      <c r="K123" s="8" t="n"/>
+      <c r="L123" s="8" t="n"/>
+      <c r="M123" s="8" t="n"/>
     </row>
     <row r="124" ht="42" customHeight="1">
-      <c r="A124" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B124" s="4" t="inlineStr">
+      <c r="A124" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B124" s="7" t="inlineStr">
         <is>
           <t>video_105.mp4</t>
         </is>
       </c>
-      <c r="C124" s="5" t="inlineStr">
+      <c r="C124" s="8" t="inlineStr">
         <is>
           <t>Bir Çay Kaşığı Nötron Yıldızı Dünya'ya Düşse Ne Olur? 🥄🌌 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D124" s="5" t="inlineStr">
+      <c r="D124" s="8" t="inlineStr">
         <is>
           <t>Elindeki küçücük bir çay kaşığının Everest Dağı kadar ağır olabileceğini hayal edebilir misin? Evrenin en ekstrem canavarı olan nötron yıldızlarıyla tanış. Dev bir yıldız çöktüğünde çekirdeği o kadar korkunç sıkışır ki, koca bir Güneş sadece yirmi kilometre çapında bir küreye hapsolur. Bu yıldızdan alacağın tek bir çay kaşığı madde tam bir milyar ton ağırlığındadır. Onu Dünya'da elinden bıraksan toprağı ve kayaları delip doğrudan gezegenin çekirdeğine kadar batardı. Peki seni uzayda en çok büyüleyen şey, kara delikler mi yoksa nötron yıldızları mı? Yorumlarda buluşalım.
 💬 Peki seni uzayda en çok büyüleyen şey her şeyi yutan kara delikler mi, yoksa bu inanılmaz yoğunluktaki nötron yıldızları mı? Yorumlarda buluşalım! 👇
@@ -7520,53 +7535,53 @@
 #bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
-      <c r="E124" s="5" t="inlineStr">
+      <c r="E124" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F124" s="5" t="inlineStr">
+      <c r="F124" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, nötron yıldızı, kara delik, uzay, astronomi, fizik, bilim, evren, ilginç bilgiler, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G124" s="5" t="inlineStr">
+      <c r="G124" s="8" t="inlineStr">
         <is>
           <t>Peki seni uzayda en çok büyüleyen şey her şeyi yutan kara delikler mi, yoksa bu inanılmaz yoğunluktaki nötron yıldızları mı? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H124" s="5" t="inlineStr">
+      <c r="H124" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I124" s="5" t="inlineStr">
+      <c r="I124" s="8" t="inlineStr">
         <is>
           <t>NASA / Wikipedia — Neutron Star (Nötron Yıldızı Yoğunluğu): https://en.wikipedia.org/wiki/Neutron_star</t>
         </is>
       </c>
-      <c r="J124" s="5" t="n"/>
-      <c r="K124" s="5" t="n"/>
-      <c r="L124" s="5" t="n"/>
-      <c r="M124" s="5" t="n"/>
+      <c r="J124" s="8" t="n"/>
+      <c r="K124" s="8" t="n"/>
+      <c r="L124" s="8" t="n"/>
+      <c r="M124" s="8" t="n"/>
     </row>
     <row r="125" ht="42" customHeight="1">
-      <c r="A125" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B125" s="4" t="inlineStr">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B125" s="7" t="inlineStr">
         <is>
           <t>video_111.mp4</t>
         </is>
       </c>
-      <c r="C125" s="5" t="inlineStr">
+      <c r="C125" s="8" t="inlineStr">
         <is>
           <t>Dünya'nın En Issız Noktası Point Nemo: En Yakın İnsanlar Uzayda! 🌊🛰️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D125" s="5" t="inlineStr">
+      <c r="D125" s="8" t="inlineStr">
         <is>
           <t>Dünya üzerinde öyle ıssız bir nokta var ki, orada bir tekneyle mahsur kalsan sana en yakın insanlar Dünya'da değil, uzayda olurdu. Güney Pasifik Okyanusu'nun ortasındaki Point Nemo ile tanış. Burası en yakın kara parçasına tam 2.688 kilometre uzaklıktadır. Buna karşılık, Uluslararası Uzay İstasyonu başının sadece 400 kilometre üzerinden geçer. Yani gökyüzündeki astronotlar, sana karadaki insanlardan tam 6 kat daha yakındır. Uzay ajansları da ömrü biten uyduları bu dev su mezarlığına düşürür. Peki sen böyle mutlak bir sessizliğin ortasında tek başına bir gece geçirmeye cesaret edebilir miydin, yoksa kıyıdan asla ayrılmaz mıydın? Yorumlarda buluşalım!
 💬 Peki sen böyle mutlak bir sessizliğin ortasında tek başına bir gece geçirmeye cesaret edebilir miydin, yoksa kıyıdan asla ayrılmaz mıydın? Yorumlarda buluşalım! 👇
@@ -7575,53 +7590,53 @@
 #bilgidozu #shorts #doğa #okyanus #coğrafya #bilim</t>
         </is>
       </c>
-      <c r="E125" s="5" t="inlineStr">
+      <c r="E125" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #okyanus #coğrafya #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F125" s="5" t="inlineStr">
+      <c r="F125" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, point nemo, güney pasifik, dünyanın en ıssız noktası, uydu mezarlığı, uluslararası uzay istasyonu, coğrafya, doğa, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G125" s="5" t="inlineStr">
+      <c r="G125" s="8" t="inlineStr">
         <is>
           <t>Peki sen böyle mutlak bir sessizliğin ortasında tek başına bir gece geçirmeye cesaret edebilir miydin, yoksa kıyıdan asla ayrılmaz mıydın? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H125" s="5" t="inlineStr">
+      <c r="H125" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I125" s="5" t="inlineStr">
+      <c r="I125" s="8" t="inlineStr">
         <is>
           <t>NOAA / Wikipedia — Oceanic Pole of Inaccessibility (Point Nemo): https://en.wikipedia.org/wiki/Pole_of_inaccessibility</t>
         </is>
       </c>
-      <c r="J125" s="5" t="n"/>
-      <c r="K125" s="5" t="n"/>
-      <c r="L125" s="5" t="n"/>
-      <c r="M125" s="5" t="n"/>
+      <c r="J125" s="8" t="n"/>
+      <c r="K125" s="8" t="n"/>
+      <c r="L125" s="8" t="n"/>
+      <c r="M125" s="8" t="n"/>
     </row>
     <row r="126" ht="42" customHeight="1">
-      <c r="A126" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B126" s="4" t="inlineStr">
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B126" s="7" t="inlineStr">
         <is>
           <t>video_112.mp4</t>
         </is>
       </c>
-      <c r="C126" s="5" t="inlineStr">
+      <c r="C126" s="8" t="inlineStr">
         <is>
           <t>Antarktika'daki Buzuldan Neden Kan Kırmızısı Şelale Akıyor? 🧊🩸 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D126" s="5" t="inlineStr">
+      <c r="D126" s="8" t="inlineStr">
         <is>
           <t>Antarktika'nın bembeyaz, dondurucu buzullarının arasından bir anda kıpkırmızı, kan renginde bir şelalenin aktığını görsen ne düşünürdün? Taylor Buzulu'ndaki bu ürpertici manzaranın sebebi kan ya da yosun değil, tam 5 milyon yıl önce buzulun 400 metre altına hapsolmuş antik bir yeraltı gölü. Bu gizli gölün suyu okyanuslardan 3 kat daha tuzlu olduğu için dondurucu soğukta bile asla donmuyor. İçindeki yoğun demir, buzulun çatlaklarından sızıp milyonlarca yıl sonra ilk kez havadaki oksijenle temas ettiği anda saniyeler içinde paslanarak kıpkırmızı bir şelaleye dönüşüyor. Peki sen Antarktika'daki bu gizemli buzulun yanına gitmeyi mi seçerdin, yoksa sıcak bir tropik adada kalmayı mı? Yorumlarda buluşalım!
 💬 Peki sen Antarktika'daki bu gizemli buzulun yanına gitmeyi mi seçerdin, yoksa sıcak bir tropik adada kalmayı mı? Yorumlarda buluşalım! 👇
@@ -7630,53 +7645,53 @@
 #bilgidozu #shorts #antarktika #doğa #coğrafya #bilim</t>
         </is>
       </c>
-      <c r="E126" s="5" t="inlineStr">
+      <c r="E126" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #antarktika #doğa #coğrafya #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F126" s="5" t="inlineStr">
+      <c r="F126" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, kan şelalesi, blood falls, antarktika, taylor buzulu, doğa olayları, coğrafya, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G126" s="5" t="inlineStr">
+      <c r="G126" s="8" t="inlineStr">
         <is>
           <t>Peki sen Antarktika'daki bu gizemli buzulun yanına gitmeyi mi seçerdin, yoksa sıcak bir tropik adada kalmayı mı? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H126" s="5" t="inlineStr">
+      <c r="H126" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I126" s="5" t="inlineStr">
+      <c r="I126" s="8" t="inlineStr">
         <is>
           <t>NSF / Wikipedia — Blood Falls, Taylor Glacier Antarctica (Kan Şelalesi): https://en.wikipedia.org/wiki/Blood_Falls</t>
         </is>
       </c>
-      <c r="J126" s="5" t="n"/>
-      <c r="K126" s="5" t="n"/>
-      <c r="L126" s="5" t="n"/>
-      <c r="M126" s="5" t="n"/>
+      <c r="J126" s="8" t="n"/>
+      <c r="K126" s="8" t="n"/>
+      <c r="L126" s="8" t="n"/>
+      <c r="M126" s="8" t="n"/>
     </row>
     <row r="127" ht="42" customHeight="1">
-      <c r="A127" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B127" s="4" t="inlineStr">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B127" s="7" t="inlineStr">
         <is>
           <t>video_113.mp4</t>
         </is>
       </c>
-      <c r="C127" s="5" t="inlineStr">
+      <c r="C127" s="8" t="inlineStr">
         <is>
           <t>5,5 Milyon Yıldır Güneş Görmeyen Mühürlü Mağara: Movile! 🕳️🕷️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D127" s="5" t="inlineStr">
+      <c r="D127" s="8" t="inlineStr">
         <is>
           <t>Tam 5,5 milyon yıl boyunca güneş ışığının tek bir zerresini bile görmemiş, mühürlü bir yeraltı dünyasının kapısını açtığını hayal et. Romanya'da tesadüfen keşfedilen Movile Mağarası, dış dünyadan tamamen kopuk bambaşka bir gezegen gibi. İçerideki havada oksijen normalin yarısından bile az, atmosferi ise zehirli hidrojen sülfür ve karbondioksitle dolu. Güneş ışığı olmadığı için buradaki yaşam tamamen kimyasal enerjiyle ayakta kalıyor ve içeride gözleri yok olmuş, sadece buraya özgü 30'dan fazla gizemli canlı türü yaşıyor. Peki özel bir oksijen tüpüyle bu karanlık mağaraya inme şansın olsa içeri adım atar mıydın, yoksa kapısını mühürlü mü bırakırdın? Yorumlarda buluşalım!
 💬 Peki özel bir oksijen tüpüyle bu karanlık mağaraya inme şansın olsa içeri adım atar mıydın, yoksa kapısını mühürlü mü bırakırdın? Yorumlarda buluşalım! 👇
@@ -7685,53 +7700,53 @@
 #bilgidozu #shorts #mağara #doğa #biyoloji #bilim</t>
         </is>
       </c>
-      <c r="E127" s="5" t="inlineStr">
+      <c r="E127" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #mağara #doğa #biyoloji #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F127" s="5" t="inlineStr">
+      <c r="F127" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, movile mağarası, mühürlü mağara, romanya, kemosentez, gizemli yerler, doğa, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G127" s="5" t="inlineStr">
+      <c r="G127" s="8" t="inlineStr">
         <is>
           <t>Peki özel bir oksijen tüpüyle bu karanlık mağaraya inme şansın olsa içeri adım atar mıydın, yoksa kapısını mühürlü mü bırakırdın? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H127" s="5" t="inlineStr">
+      <c r="H127" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I127" s="5" t="inlineStr">
+      <c r="I127" s="8" t="inlineStr">
         <is>
           <t>BBC / Wikipedia — Movile Cave Chemosynthesis Ecosystem (Movile Mağarası): https://en.wikipedia.org/wiki/Movile_Cave</t>
         </is>
       </c>
-      <c r="J127" s="5" t="n"/>
-      <c r="K127" s="5" t="n"/>
-      <c r="L127" s="5" t="n"/>
-      <c r="M127" s="5" t="n"/>
+      <c r="J127" s="8" t="n"/>
+      <c r="K127" s="8" t="n"/>
+      <c r="L127" s="8" t="n"/>
+      <c r="M127" s="8" t="n"/>
     </row>
     <row r="128" ht="42" customHeight="1">
-      <c r="A128" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B128" s="4" t="inlineStr">
+      <c r="A128" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B128" s="7" t="inlineStr">
         <is>
           <t>video_114.mp4</t>
         </is>
       </c>
-      <c r="C128" s="5" t="inlineStr">
+      <c r="C128" s="8" t="inlineStr">
         <is>
           <t>Dallol Volkanı: Dünya Üzerindeki En Asidik ve Renkli Cehennem! 🌋🧪 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D128" s="5" t="inlineStr">
+      <c r="D128" s="8" t="inlineStr">
         <is>
           <t>Şu gördüğün neon sarısı ve zümrüt yeşili göller başka bir gezegene değil, Dünya üzerindeki en tehlikeli cehenneme ait. Etiyopya'daki Danakil Çöküntüsü'nde yer alan Dallol Volkanı, deniz seviyesinin 48 metre altında kaynayan dev bir kimya laboratuvarı gibidir. Yerin altındaki kızgın magma, kalın tuz ve kükürt yataklarıyla buluştuğunda, yüzeye akü asidinden bile daha yakıcı kaynar sular ve zehirli klor gazları fışkırır. Burada maskesiz uzun süre nefes almak bile imkânsızdır. Peki sen uzaylı bir gezegeni andıran bu yeri uzaktan dronelarla izlemeyi mi seçerdin, yoksa özel koruyucu kıyafetle yanına kadar yürümeyi mi? Yorumlarda buluşalım!
 💬 Peki sen uzaylı bir gezegeni andıran bu yeri uzaktan dronelarla izlemeyi mi seçerdin, yoksa özel koruyucu kıyafetle yanına kadar yürümeyi mi? Yorumlarda buluşalım! 👇
@@ -7740,53 +7755,53 @@
 #bilgidozu #shorts #volkan #doğa #coğrafya #bilim</t>
         </is>
       </c>
-      <c r="E128" s="5" t="inlineStr">
+      <c r="E128" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #volkan #doğa #coğrafya #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F128" s="5" t="inlineStr">
+      <c r="F128" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, dallol volkanı, danakil çöküntüsü, etiyopya, asit gölleri, ekstrem doğa, coğrafya, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G128" s="5" t="inlineStr">
+      <c r="G128" s="8" t="inlineStr">
         <is>
           <t>Peki sen uzaylı bir gezegeni andıran bu yeri uzaktan dronelarla izlemeyi mi seçerdin, yoksa özel koruyucu kıyafetle yanına kadar yürümeyi mi? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H128" s="5" t="inlineStr">
+      <c r="H128" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I128" s="5" t="inlineStr">
+      <c r="I128" s="8" t="inlineStr">
         <is>
           <t>Nature Ecology &amp; Evolution / Wikipedia — Dallol Hydrothermal System: https://en.wikipedia.org/wiki/Dallol_(hydrothermal_system)</t>
         </is>
       </c>
-      <c r="J128" s="5" t="n"/>
-      <c r="K128" s="5" t="n"/>
-      <c r="L128" s="5" t="n"/>
-      <c r="M128" s="5" t="n"/>
+      <c r="J128" s="8" t="n"/>
+      <c r="K128" s="8" t="n"/>
+      <c r="L128" s="8" t="n"/>
+      <c r="M128" s="8" t="n"/>
     </row>
     <row r="129" ht="42" customHeight="1">
-      <c r="A129" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B129" s="4" t="inlineStr">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B129" s="7" t="inlineStr">
         <is>
           <t>video_115.mp4</t>
         </is>
       </c>
-      <c r="C129" s="5" t="inlineStr">
+      <c r="C129" s="8" t="inlineStr">
         <is>
           <t>Yerin 2.224 Metre Altında Ne Var? Dünya'nın En Derin Mağarası! 🧗‍♂️🌑 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D129" s="5" t="inlineStr">
+      <c r="D129" s="8" t="inlineStr">
         <is>
           <t>Yerin tam 2.224 metre altına, yani üst üste dizilmiş 7 Eyfel Kulesi derinliğine karanlık bir kuyudan indiğini hayal et. Kafkas Dağları'ndaki Krubera Mağarası, Dünya'nın bilinen en derin uçurumlarından biridir. Buraya inen mağaracıların en dibe ulaşması haftalar sürer ve içeride yeraltı şelaleleriyle buz gibi su tünelleri vardır. En şaşırtıcı olanı ise, 2.000 metre derinlikteki o dondurucu ve ışıksız sularda bile dış dünyayı hiç görmemiş şeffaf canlıların yaşamaya devam etmesidir. Peki sana sınırsız ekipman verilse okyanusun en derin çukuruna dalmayı mı seçerdin, yoksa Dünya'nın en derin mağarasına inmeyi mi? Yorumlarda buluşalım!
 💬 Peki sana sınırsız ekipman verilse okyanusun en derin çukuruna dalmayı mı seçerdin, yoksa Dünya'nın en derin mağarasına inmeyi mi? Yorumlarda buluşalım! 👇
@@ -7795,53 +7810,53 @@
 #bilgidozu #shorts #mağara #doğa #keşif #bilim</t>
         </is>
       </c>
-      <c r="E129" s="5" t="inlineStr">
+      <c r="E129" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #mağara #doğa #keşif #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F129" s="5" t="inlineStr">
+      <c r="F129" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, krubera mağarası, dünyanın en derin mağarası, kafkas dağları, mağaracılık, doğa, coğrafya, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G129" s="5" t="inlineStr">
+      <c r="G129" s="8" t="inlineStr">
         <is>
           <t>Peki sana sınırsız ekipman verilse okyanusun en derin çukuruna dalmayı mı seçerdin, yoksa Dünya'nın en derin mağarasına inmeyi mi? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H129" s="5" t="inlineStr">
+      <c r="H129" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I129" s="5" t="inlineStr">
+      <c r="I129" s="8" t="inlineStr">
         <is>
           <t>National Geographic / Wikipedia — Krubera Cave (Dünya'nın En Derin Mağaraları): https://en.wikipedia.org/wiki/Krubera_Cave</t>
         </is>
       </c>
-      <c r="J129" s="5" t="n"/>
-      <c r="K129" s="5" t="n"/>
-      <c r="L129" s="5" t="n"/>
-      <c r="M129" s="5" t="n"/>
+      <c r="J129" s="8" t="n"/>
+      <c r="K129" s="8" t="n"/>
+      <c r="L129" s="8" t="n"/>
+      <c r="M129" s="8" t="n"/>
     </row>
     <row r="130" ht="42" customHeight="1">
-      <c r="A130" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B130" s="4" t="inlineStr">
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B130" s="7" t="inlineStr">
         <is>
           <t>video_116.mp4</t>
         </is>
       </c>
-      <c r="C130" s="5" t="inlineStr">
+      <c r="C130" s="8" t="inlineStr">
         <is>
           <t>2.100 Yıllık Batıktan Çıkan İlk Analog Bilgisayar: Antikythera! ⚙️🏛️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D130" s="5" t="inlineStr">
+      <c r="D130" s="8" t="inlineStr">
         <is>
           <t>Denizin dibinde iki bin yıl boyunca paslanmış bir Yunan batığından, modern saatler kadar karmaşık dişlilere sahip antik bir bilgisayar çıktığını biliyor muydun?
 💬 Peki sence antik dünyada bunun gibi henüz keşfedemediğimiz başka yüksek teknolojiler de var mıdır, yoksa bu tek bir dahinin eseri miydi? Yorumlarda buluşalım! 👇
@@ -7850,53 +7865,53 @@
 #bilgidozu #shorts #tarih #arkeoloji #bilim</t>
         </is>
       </c>
-      <c r="E130" s="5" t="inlineStr">
+      <c r="E130" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #arkeoloji #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F130" s="5" t="inlineStr">
+      <c r="F130" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, antik mühendislik, tarih, arkeoloji, gizemli yapılar, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G130" s="5" t="inlineStr">
+      <c r="G130" s="8" t="inlineStr">
         <is>
           <t>Peki sence antik dünyada bunun gibi henüz keşfedemediğimiz başka yüksek teknolojiler de var mıdır, yoksa bu tek bir dahinin eseri miydi? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H130" s="5" t="inlineStr">
+      <c r="H130" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Antik Mühendislik</t>
         </is>
       </c>
-      <c r="I130" s="5" t="inlineStr">
+      <c r="I130" s="8" t="inlineStr">
         <is>
           <t>Nature / Wikipedia — Antikythera Mechanism (2.100 Yıllık Antik Analog Bilgisayar): https://en.wikipedia.org/wiki/Antikythera_mechanism</t>
         </is>
       </c>
-      <c r="J130" s="5" t="n"/>
-      <c r="K130" s="5" t="n"/>
-      <c r="L130" s="5" t="n"/>
-      <c r="M130" s="5" t="n"/>
+      <c r="J130" s="8" t="n"/>
+      <c r="K130" s="8" t="n"/>
+      <c r="L130" s="8" t="n"/>
+      <c r="M130" s="8" t="n"/>
     </row>
     <row r="131" ht="42" customHeight="1">
-      <c r="A131" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B131" s="4" t="inlineStr">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B131" s="7" t="inlineStr">
         <is>
           <t>video_117.mp4</t>
         </is>
       </c>
-      <c r="C131" s="5" t="inlineStr">
+      <c r="C131" s="8" t="inlineStr">
         <is>
           <t>Derinkuyu Yeraltı Şehri: 20 Bin Kişi Yerin Altında Nasıl Nefes Aldı? 🏺🕯️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D131" s="5" t="inlineStr">
+      <c r="D131" s="8" t="inlineStr">
         <is>
           <t>Kapadokya'nın altında, yirmi bin insanın hayvanları ve erzaklarıyla birlikte haftalarca hiç yeryüzüne çıkmadan yaşayabildiği sekiz katlı dev bir yeraltı şehri var: Derinkuyu.
 💬 Peki sen tehlike anında haftalarca böyle bir yeraltı şehrinde yaşayabilir miydin, yoksa kapalı alanda daralır mıydın? Yorumlarda buluşalım! 👇
@@ -7905,53 +7920,53 @@
 #bilgidozu #shorts #tarih #arkeoloji #bilim</t>
         </is>
       </c>
-      <c r="E131" s="5" t="inlineStr">
+      <c r="E131" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #arkeoloji #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F131" s="5" t="inlineStr">
+      <c r="F131" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, antik mühendislik, tarih, arkeoloji, gizemli yapılar, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G131" s="5" t="inlineStr">
+      <c r="G131" s="8" t="inlineStr">
         <is>
           <t>Peki sen tehlike anında haftalarca böyle bir yeraltı şehrinde yaşayabilir miydin, yoksa kapalı alanda daralır mıydın? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H131" s="5" t="inlineStr">
+      <c r="H131" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Antik Mühendislik</t>
         </is>
       </c>
-      <c r="I131" s="5" t="inlineStr">
+      <c r="I131" s="8" t="inlineStr">
         <is>
           <t>UNESCO / Wikipedia — Derinkuyu Underground City (Derinkuyu Yeraltı Şehri): https://en.wikipedia.org/wiki/Derinkuyu_underground_city</t>
         </is>
       </c>
-      <c r="J131" s="5" t="n"/>
-      <c r="K131" s="5" t="n"/>
-      <c r="L131" s="5" t="n"/>
-      <c r="M131" s="5" t="n"/>
+      <c r="J131" s="8" t="n"/>
+      <c r="K131" s="8" t="n"/>
+      <c r="L131" s="8" t="n"/>
+      <c r="M131" s="8" t="n"/>
     </row>
     <row r="132" ht="42" customHeight="1">
-      <c r="A132" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B132" s="4" t="inlineStr">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B132" s="7" t="inlineStr">
         <is>
           <t>video_118.mp4</t>
         </is>
       </c>
-      <c r="C132" s="5" t="inlineStr">
+      <c r="C132" s="8" t="inlineStr">
         <is>
           <t>Voynich El Yazması: 600 Yıldır Kimsenin Okuyamadığı Şifreli Kitap! 📜🔍 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D132" s="5" t="inlineStr">
+      <c r="D132" s="8" t="inlineStr">
         <is>
           <t>Dünyanın en iyi şifre çözücüleri, dilbilimcileri ve yapay zekâları bir araya geldi ama altı yüz yıllık bu kitabın tek bir cümlesini bile okuyamadı: Voynich El Yazması.
 💬 Peki sence bu kitap unutulmuş gizli bir bilimin şifreli kaydı mı, yoksa tarihin en zekice kurgulanmış bilmecesi mi? Yorumlarda buluşalım! 👇
@@ -7960,53 +7975,53 @@
 #bilgidozu #shorts #tarih #arkeoloji #bilim</t>
         </is>
       </c>
-      <c r="E132" s="5" t="inlineStr">
+      <c r="E132" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #arkeoloji #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F132" s="5" t="inlineStr">
+      <c r="F132" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, antik mühendislik, tarih, arkeoloji, gizemli yapılar, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G132" s="5" t="inlineStr">
+      <c r="G132" s="8" t="inlineStr">
         <is>
           <t>Peki sence bu kitap unutulmuş gizli bir bilimin şifreli kaydı mı, yoksa tarihin en zekice kurgulanmış bilmecesi mi? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H132" s="5" t="inlineStr">
+      <c r="H132" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Antik Mühendislik</t>
         </is>
       </c>
-      <c r="I132" s="5" t="inlineStr">
+      <c r="I132" s="8" t="inlineStr">
         <is>
           <t>Yale Beinecke Library / Wikipedia — Voynich Manuscript (Voynich El Yazması): https://en.wikipedia.org/wiki/Voynich_manuscript</t>
         </is>
       </c>
-      <c r="J132" s="5" t="n"/>
-      <c r="K132" s="5" t="n"/>
-      <c r="L132" s="5" t="n"/>
-      <c r="M132" s="5" t="n"/>
+      <c r="J132" s="8" t="n"/>
+      <c r="K132" s="8" t="n"/>
+      <c r="L132" s="8" t="n"/>
+      <c r="M132" s="8" t="n"/>
     </row>
     <row r="133" ht="42" customHeight="1">
-      <c r="A133" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B133" s="4" t="inlineStr">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B133" s="7" t="inlineStr">
         <is>
           <t>video_119.mp4</t>
         </is>
       </c>
-      <c r="C133" s="5" t="inlineStr">
+      <c r="C133" s="8" t="inlineStr">
         <is>
           <t>Puma Punku H-Blokları: Jilet Bile Girmeyen Antik Taşların Sırrı! 🪨📐 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D133" s="5" t="inlineStr">
+      <c r="D133" s="8" t="inlineStr">
         <is>
           <t>Deniz seviyesinden üç bin sekiz yüz metre yüksekte, aralarına jilet bile girmeyecek kadar kusursuz kesilmiş yüz tonluk taş bloklar düşün: Puma Punku.
 💬 Peki sence antik ustalar bu kusursuz taş işçiliğini sabırlı el aletleriyle mi başardı, yoksa bugün unuttuğumuz özel bir teknikleri mi vardı? Yorumlarda buluşalım! 👇
@@ -8015,53 +8030,53 @@
 #bilgidozu #shorts #tarih #arkeoloji #bilim</t>
         </is>
       </c>
-      <c r="E133" s="5" t="inlineStr">
+      <c r="E133" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #arkeoloji #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F133" s="5" t="inlineStr">
+      <c r="F133" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, antik mühendislik, tarih, arkeoloji, gizemli yapılar, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G133" s="5" t="inlineStr">
+      <c r="G133" s="8" t="inlineStr">
         <is>
           <t>Peki sence antik ustalar bu kusursuz taş işçiliğini sabırlı el aletleriyle mi başardı, yoksa bugün unuttuğumuz özel bir teknikleri mi vardı? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H133" s="5" t="inlineStr">
+      <c r="H133" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Antik Mühendislik</t>
         </is>
       </c>
-      <c r="I133" s="5" t="inlineStr">
+      <c r="I133" s="8" t="inlineStr">
         <is>
           <t>UNESCO / Wikipedia — Pumapunku Andesite Megaliths (Puma Punku H-Blokları): https://en.wikipedia.org/wiki/Pumapunku</t>
         </is>
       </c>
-      <c r="J133" s="5" t="n"/>
-      <c r="K133" s="5" t="n"/>
-      <c r="L133" s="5" t="n"/>
-      <c r="M133" s="5" t="n"/>
+      <c r="J133" s="8" t="n"/>
+      <c r="K133" s="8" t="n"/>
+      <c r="L133" s="8" t="n"/>
+      <c r="M133" s="8" t="n"/>
     </row>
     <row r="134" ht="42" customHeight="1">
-      <c r="A134" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B134" s="4" t="inlineStr">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B134" s="7" t="inlineStr">
         <is>
           <t>video_120.mp4</t>
         </is>
       </c>
-      <c r="C134" s="5" t="inlineStr">
+      <c r="C134" s="8" t="inlineStr">
         <is>
           <t>Babil'in Asma Bahçeleri Gerçekte Babil'de Değil Miydi? 🌿🏛️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D134" s="5" t="inlineStr">
+      <c r="D134" s="8" t="inlineStr">
         <is>
           <t>Dünyanın Yedi Harikası'ndan biri sayılan Babil'in Asma Bahçeleri'nin aslında hiçbir zaman Babil'de olmadığını duysan ne derdin?
 💬 Peki sen geçmişe gidebilsen önce bu efsanevi Asma Bahçeleri'ni mi görmek isterdin, yoksa İskenderiye Kütüphanesi'ni mi? Yorumlarda buluşalım! 👇
@@ -8070,85 +8085,200 @@
 #bilgidozu #shorts #tarih #arkeoloji #bilim</t>
         </is>
       </c>
-      <c r="E134" s="5" t="inlineStr">
+      <c r="E134" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #arkeoloji #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F134" s="5" t="inlineStr">
+      <c r="F134" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, antik mühendislik, tarih, arkeoloji, gizemli yapılar, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G134" s="5" t="inlineStr">
+      <c r="G134" s="8" t="inlineStr">
         <is>
           <t>Peki sen geçmişe gidebilsen önce bu efsanevi Asma Bahçeleri'ni mi görmek isterdin, yoksa İskenderiye Kütüphanesi'ni mi? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H134" s="5" t="inlineStr">
+      <c r="H134" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Antik Mühendislik</t>
         </is>
       </c>
-      <c r="I134" s="5" t="inlineStr">
+      <c r="I134" s="8" t="inlineStr">
         <is>
           <t>Oxford University (Stephanie Dalley) / Wikipedia — Hanging Gardens of Babylon: https://en.wikipedia.org/wiki/Hanging_Gardens_of_Babylon</t>
         </is>
       </c>
-      <c r="J134" s="5" t="n"/>
-      <c r="K134" s="5" t="n"/>
-      <c r="L134" s="5" t="n"/>
-      <c r="M134" s="5" t="n"/>
+      <c r="J134" s="8" t="n"/>
+      <c r="K134" s="8" t="n"/>
+      <c r="L134" s="8" t="n"/>
+      <c r="M134" s="8" t="n"/>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
+      <c r="A135" s="9" t="inlineStr">
         <is>
           <t>BEKLEMEDE</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B135" s="9" t="inlineStr">
         <is>
           <t>video_131.mp4</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Kâğıt Kesiği Neden Bu Kadar Acıtır? 🩹 #bilgidozu #shorts</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
+      <c r="C135" s="9" t="inlineStr">
+        <is>
+          <t>Kâğıt Kesiği Neden Bu Kadar Acıtır? 🩹</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="inlineStr">
         <is>
           <t>Küçücük bir kâğıt kesiği neden beklediğinden çok daha fazla can yakar? Parmak uçlarımız dokunma ve ağrıyı algılayan yoğun duyu sinirleriyle donatılmıştır. Üstelik çıplak gözle düz görünen kâğıt kenarı, mikroskobik ölçekte lifli ve düzensiz bir yapıya sahiptir; gün boyu ellerimizi kullanmaya devam etmemiz de hassaslaşan dokuyu tekrar tekrar uyarır.
-Senin de başına geldi mi? Yorumlarda buluşalım! 👇
+💬 Senin de başına geldi mi? En son ne zaman kâğıt kesiği yaşadın, yorumlara yaz! 👇
 📚 Kaynak: Dr. Hayley Goldbach (UCLA Dermatology) / BBC Future &amp; StatPearls
-🎨 Görseller temsilîdir (AI bilimsel canlandırma).</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
+🎨 Görseller temsilîdir (AI bilimsel canlandırma).
+#bilgidozu #shorts #insanvücudu #beyin #bilim</t>
+        </is>
+      </c>
+      <c r="E135" s="9" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #insanvücudu #beyin #bilim</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
+      <c r="F135" s="9" t="inlineStr">
         <is>
           <t>bilgi dozu, kağıt kesiği, insan vücudu, duyu sinirleri, bilim, ilginç bilgiler, shorts</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
+      <c r="G135" s="9" t="inlineStr">
         <is>
           <t>Senin de başına geldi mi? En son ne zaman kâğıt kesiği yaşadın, yorumlara yaz! 👇</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
+      <c r="H135" s="9" t="inlineStr">
         <is>
           <t>İnsan Vücudu ve Beyin</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
+      <c r="I135" s="9" t="inlineStr">
         <is>
           <t>BBC Future (Dr. H. Goldbach, UCLA, 2016) &amp; StatPearls</t>
         </is>
       </c>
+      <c r="J135" s="9" t="n"/>
+      <c r="K135" s="9" t="n"/>
+      <c r="L135" s="9" t="n"/>
+      <c r="M135" s="9" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="9" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B136" s="9" t="inlineStr">
+        <is>
+          <t>video_132.mp4</t>
+        </is>
+      </c>
+      <c r="C136" s="9" t="inlineStr">
+        <is>
+          <t>Baldırın İkinci Kalbin: Kanı Kalbe O Taşıyor! 🦵</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="inlineStr">
+        <is>
+          <t>Kalp kanı bacaklara kolayca gönderir; peki düşük basınçlı toplardamarlardaki kan yerçekimine karşı kalbe nasıl geri çıkar? Baldırımızdaki soleus ve gastroknemius kasları her adımda derin toplardamarları sıkıştırarak tek yönlü kapakçıklar yardımıyla kanı yukarı iter.
+💬 Bacaklarında akşamları ağırlık hissedenler 1 yazsın, hissetmeyenler 2! 👇
+📚 Kaynak: NCBI StatPearls (NBK430975, NBK534256) &amp; Cleveland Clinic (Dr. Teresa Wu)
+🎨 Görseller temsilîdir (AI bilimsel canlandırma).
+#bilgidozu #shorts #insanvücudu #biyoloji #bilim</t>
+        </is>
+      </c>
+      <c r="E136" s="9" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #insanvücudu #biyoloji #bilim</t>
+        </is>
+      </c>
+      <c r="F136" s="9" t="inlineStr">
+        <is>
+          <t>bilgi dozu, ikinci kalp, baldır kasları, kan dolaşımı, insan vücudu, bilim, shorts</t>
+        </is>
+      </c>
+      <c r="G136" s="9" t="inlineStr">
+        <is>
+          <t>Bacaklarında akşamları ağırlık hissedenler 1 yazsın, hissetmeyenler 2! 👇</t>
+        </is>
+      </c>
+      <c r="H136" s="9" t="inlineStr">
+        <is>
+          <t>Biyoloji ve Vücut</t>
+        </is>
+      </c>
+      <c r="I136" s="9" t="inlineStr">
+        <is>
+          <t>NCBI StatPearls (NBK430975, NBK534256) &amp; Cleveland Clinic (Dr. Teresa Wu)</t>
+        </is>
+      </c>
+      <c r="J136" s="9" t="n"/>
+      <c r="K136" s="9" t="n"/>
+      <c r="L136" s="9" t="n"/>
+      <c r="M136" s="9" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="9" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B137" s="9" t="inlineStr">
+        <is>
+          <t>video_133.mp4</t>
+        </is>
+      </c>
+      <c r="C137" s="9" t="inlineStr">
+        <is>
+          <t>Göz Kapağın Seğirirse Vücut Ne Anlatıyor? 👁</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="inlineStr">
+        <is>
+          <t>Gözünün altında başlayan istemsiz seğirme (oküler miyokimi) çoğu zaman korkutucu gelse de genellikle beynin değil, uykusuzluk, yoğun stres, fazla kafein ve ekran yorgunluğuyla geçici olarak aşırı uyarılan küçük sinir uçlarının eseridir.
+💬 Göz kapağı seğirmesi daha önce yaşayanlar 1, ilk kez duyanlar 2 yazsın! 👇
+📚 Kaynak: Mayo Clinic &amp; Cleveland Clinic — Eyelid Myokymia
+🎨 Görseller temsilîdir (AI bilimsel canlandırma).
+#bilgidozu #shorts #beyin #insanvücudu #bilim</t>
+        </is>
+      </c>
+      <c r="E137" s="9" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #beyin #insanvücudu #bilim</t>
+        </is>
+      </c>
+      <c r="F137" s="9" t="inlineStr">
+        <is>
+          <t>bilgi dozu, göz seğirmesi, miyokimi, beyin ve psikoloji, insan vücudu, bilim, shorts</t>
+        </is>
+      </c>
+      <c r="G137" s="9" t="inlineStr">
+        <is>
+          <t>Göz kapağı seğirmesi daha önce yaşayanlar 1, ilk kez duyanlar 2 yazsın! 👇</t>
+        </is>
+      </c>
+      <c r="H137" s="9" t="inlineStr">
+        <is>
+          <t>Beyin ve Psikoloji</t>
+        </is>
+      </c>
+      <c r="I137" s="9" t="inlineStr">
+        <is>
+          <t>Mayo Clinic &amp; Cleveland Clinic — Eyelid Myokymia</t>
+        </is>
+      </c>
+      <c r="J137" s="9" t="n"/>
+      <c r="K137" s="9" t="n"/>
+      <c r="L137" s="9" t="n"/>
+      <c r="M137" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/bilgidozu_yukleme_tablosu.xlsx
+++ b/bilgidozu_yukleme_tablosu.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,8 +61,19 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="007F6000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00222222"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -93,6 +104,12 @@
         <bgColor rgb="00E0E0E0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF9C4"/>
+        <bgColor rgb="00FFF9C4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -107,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -134,6 +151,12 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -501,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M137"/>
+  <dimension ref="A1:M138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8128,7 +8151,7 @@
       </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>Kâğıt Kesiği Neden Bu Kadar Acıtır? 🩹</t>
+          <t>Küçücük Kâğıt Kesiği Neden Bu Kadar Çok Acıtır? 🩹⚡ #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
@@ -8171,114 +8194,202 @@
       <c r="M135" s="9" t="n"/>
     </row>
     <row r="136">
-      <c r="A136" s="9" t="inlineStr">
+      <c r="A136" s="10" t="inlineStr">
         <is>
           <t>BEKLEMEDE</t>
         </is>
       </c>
-      <c r="B136" s="9" t="inlineStr">
+      <c r="B136" s="10" t="inlineStr">
         <is>
           <t>video_132.mp4</t>
         </is>
       </c>
-      <c r="C136" s="9" t="inlineStr">
-        <is>
-          <t>Baldırın İkinci Kalbin: Kanı Kalbe O Taşıyor! 🦵</t>
-        </is>
-      </c>
-      <c r="D136" s="9" t="inlineStr">
-        <is>
-          <t>Kalp kanı bacaklara kolayca gönderir; peki düşük basınçlı toplardamarlardaki kan yerçekimine karşı kalbe nasıl geri çıkar? Baldırımızdaki soleus ve gastroknemius kasları her adımda derin toplardamarları sıkıştırarak tek yönlü kapakçıklar yardımıyla kanı yukarı iter.
-💬 Bacaklarında akşamları ağırlık hissedenler 1 yazsın, hissetmeyenler 2! 👇
-📚 Kaynak: NCBI StatPearls (NBK430975, NBK534256) &amp; Cleveland Clinic (Dr. Teresa Wu)
-🎨 Görseller temsilîdir (AI bilimsel canlandırma).
-#bilgidozu #shorts #insanvücudu #biyoloji #bilim</t>
-        </is>
-      </c>
-      <c r="E136" s="9" t="inlineStr">
-        <is>
-          <t>#bilgidozu #shorts #insanvücudu #biyoloji #bilim</t>
-        </is>
-      </c>
-      <c r="F136" s="9" t="inlineStr">
-        <is>
-          <t>bilgi dozu, ikinci kalp, baldır kasları, kan dolaşımı, insan vücudu, bilim, shorts</t>
-        </is>
-      </c>
-      <c r="G136" s="9" t="inlineStr">
+      <c r="C136" s="11" t="inlineStr">
+        <is>
+          <t>Baldır Kasların Aslında İkinci Kalbin! Kanı Kalbe Nasıl Taşıyor? 🦵💪 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D136" s="11" t="inlineStr">
+        <is>
+          <t>Kalp kanı bacaklara gönderir; peki kan, yerçekimine karşı nasıl kalbe geri çıkar? Bu işi aslında baldırındaki kaslar yapıyor — "İkinci Kalp".
+📍 BÖLÜMLER
+00:00 Kan neden geri bu kadar zor çıkar?
+00:09 Toplardamarlarda basınç neden düşük?
+00:15 Baldır kasları: soleus ve gastroknemius
+00:24 Tek yönlü kapakçıklar nasıl çalışır?
+00:31 Hareketsizlik şişliği neden artırır?
+00:41 "İkinci kalp" gerçekten ne demek?
+📊 Kaynaklar:
+• StatPearls — Venous Insufficiency: https://www.ncbi.nlm.nih.gov/books/NBK430975/
+• NCBI Bookshelf — Varicose Veins (kas pompası fizyolojisi): https://www.ncbi.nlm.nih.gov/books/NBK534256/
+• StatPearls — Leg Posterior Compartment: https://www.ncbi.nlm.nih.gov/sites/books/NBK537340/
+• Cleveland Clinic (TODAY röportajı): https://www.today.com/health/diet-fitness/what-is-second-heart-rcna117576
+🩺 Uyarı: Genel bilgi amaçlıdır, tıbbi tavsiye değildir.
+🖼️ Görseller temsili (AI bilimsel canlandırma).
+Bir doz bilgi, her gün: 💊 ABONE OL!
+#bilgidozu #shorts #ikincikalp #baldır #kandolaşımı</t>
+        </is>
+      </c>
+      <c r="E136" s="11" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #ikincikalp #baldır #kandolaşımı</t>
+        </is>
+      </c>
+      <c r="F136" s="11" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, ikinci kalp, baldır kasları, venöz pompa, kas pompası, toplardamar, kan kalbe nasıl döner, dolaşım sistemi, insan vücudu, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G136" s="11" t="inlineStr">
         <is>
           <t>Bacaklarında akşamları ağırlık hissedenler 1 yazsın, hissetmeyenler 2! 👇</t>
         </is>
       </c>
-      <c r="H136" s="9" t="inlineStr">
-        <is>
-          <t>Biyoloji ve Vücut</t>
-        </is>
-      </c>
-      <c r="I136" s="9" t="inlineStr">
-        <is>
-          <t>NCBI StatPearls (NBK430975, NBK534256) &amp; Cleveland Clinic (Dr. Teresa Wu)</t>
-        </is>
-      </c>
-      <c r="J136" s="9" t="n"/>
-      <c r="K136" s="9" t="n"/>
-      <c r="L136" s="9" t="n"/>
-      <c r="M136" s="9" t="n"/>
+      <c r="H136" s="11" t="inlineStr">
+        <is>
+          <t>İnsan Vücudu ve Beyin</t>
+        </is>
+      </c>
+      <c r="I136" s="11" t="inlineStr">
+        <is>
+          <t>StatPearls (NBK430975, NBK534256, NBK537340) &amp; Cleveland Clinic</t>
+        </is>
+      </c>
+      <c r="J136" s="11" t="n"/>
+      <c r="K136" s="11" t="n"/>
+      <c r="L136" s="11" t="n"/>
+      <c r="M136" s="11" t="n"/>
     </row>
     <row r="137">
-      <c r="A137" s="9" t="inlineStr">
+      <c r="A137" s="10" t="inlineStr">
         <is>
           <t>BEKLEMEDE</t>
         </is>
       </c>
-      <c r="B137" s="9" t="inlineStr">
+      <c r="B137" s="10" t="inlineStr">
         <is>
           <t>video_133.mp4</t>
         </is>
       </c>
-      <c r="C137" s="9" t="inlineStr">
-        <is>
-          <t>Göz Kapağın Seğirirse Vücut Ne Anlatıyor? 👁</t>
-        </is>
-      </c>
-      <c r="D137" s="9" t="inlineStr">
-        <is>
-          <t>Gözünün altında başlayan istemsiz seğirme (oküler miyokimi) çoğu zaman korkutucu gelse de genellikle beynin değil, uykusuzluk, yoğun stres, fazla kafein ve ekran yorgunluğuyla geçici olarak aşırı uyarılan küçük sinir uçlarının eseridir.
-💬 Göz kapağı seğirmesi daha önce yaşayanlar 1, ilk kez duyanlar 2 yazsın! 👇
-📚 Kaynak: Mayo Clinic &amp; Cleveland Clinic — Eyelid Myokymia
-🎨 Görseller temsilîdir (AI bilimsel canlandırma).
-#bilgidozu #shorts #beyin #insanvücudu #bilim</t>
-        </is>
-      </c>
-      <c r="E137" s="9" t="inlineStr">
-        <is>
-          <t>#bilgidozu #shorts #beyin #insanvücudu #bilim</t>
-        </is>
-      </c>
-      <c r="F137" s="9" t="inlineStr">
-        <is>
-          <t>bilgi dozu, göz seğirmesi, miyokimi, beyin ve psikoloji, insan vücudu, bilim, shorts</t>
-        </is>
-      </c>
-      <c r="G137" s="9" t="inlineStr">
+      <c r="C137" s="11" t="inlineStr">
+        <is>
+          <t>Göz Kapağın Neden Kendi Kendine Seğirir? Anlamı Bu! 👁🧠 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>Gözünün altındaki o minik seğirme ne anlama geliyor? Tıbbi adı miyokimi; çoğu zaman zararsız ve kendiliğinden geçiyor.
+📍 BÖLÜMLER
+00:00 Göz kapağı seğirmesi (miyokimi) nedir?
+00:09 Orbicularis oculi kas lifleri
+00:18 Kaynağı beynin değil, sinir uçlarının
+00:26 Tetikleyiciler: uykusuzluk, stres, kafein, ekran
+00:35 Magnezyum efsanesi ve ne zaman doktora gitmeli?
+00:43 Sıradaki bölüm: bulaşıcı esneme
+📊 Kaynaklar:
+• Mayo Clinic — Eye twitching: https://www.mayoclinic.org/symptoms/eye-twitching/basics/causes/sym-20050838
+• Cleveland Clinic — Myokymia: https://my.clevelandclinic.org/health/diseases/myokymia
+• UCLA Health — Twitching Eyelid: https://www.uclahealth.org/medical-services/ophthalmology/eye-signs-and-symptoms/twitching-eyelid
+🩺 Uyarı: Genel bilgi amaçlıdır, tıbbi tavsiye değildir.
+🖼️ Görseller temsili (AI bilimsel canlandırma).
+Bir doz bilgi, her gün: 💊 ABONE OL!
+#bilgidozu #shorts #gözkapağı #miyokimi #beyinsağlığı</t>
+        </is>
+      </c>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #gözkapağı #miyokimi #beyinsağlığı</t>
+        </is>
+      </c>
+      <c r="F137" s="11" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, göz kapağı seğirmesi, miyokimi, göz seğirmesi, göz tiki, stres, kafein, uykusuzluk, insan vücudu, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G137" s="11" t="inlineStr">
         <is>
           <t>Göz kapağı seğirmesi daha önce yaşayanlar 1, ilk kez duyanlar 2 yazsın! 👇</t>
         </is>
       </c>
-      <c r="H137" s="9" t="inlineStr">
-        <is>
-          <t>Beyin ve Psikoloji</t>
-        </is>
-      </c>
-      <c r="I137" s="9" t="inlineStr">
-        <is>
-          <t>Mayo Clinic &amp; Cleveland Clinic — Eyelid Myokymia</t>
-        </is>
-      </c>
-      <c r="J137" s="9" t="n"/>
-      <c r="K137" s="9" t="n"/>
-      <c r="L137" s="9" t="n"/>
-      <c r="M137" s="9" t="n"/>
+      <c r="H137" s="11" t="inlineStr">
+        <is>
+          <t>İnsan Vücudu ve Beyin</t>
+        </is>
+      </c>
+      <c r="I137" s="11" t="inlineStr">
+        <is>
+          <t>Mayo Clinic, Cleveland Clinic &amp; UCLA Health — Eyelid Myokymia</t>
+        </is>
+      </c>
+      <c r="J137" s="11" t="n"/>
+      <c r="K137" s="11" t="n"/>
+      <c r="L137" s="11" t="n"/>
+      <c r="M137" s="11" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="10" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B138" s="10" t="inlineStr">
+        <is>
+          <t>video_134.mp4</t>
+        </is>
+      </c>
+      <c r="C138" s="11" t="inlineStr">
+        <is>
+          <t>Bir Esnedin, Etraf da Esnedi! Esnemenin Bulaşma Sırrı 😮🧠 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D138" s="11" t="inlineStr">
+        <is>
+          <t>Esneme neden bu kadar kolay bulaşıyor — ve neden bazı insanlara hiç bulaşmıyor? Cevap, yakınlık sırasına gizlenmiş.
+📍 BÖLÜMLER
+00:00 Neden herkesten aynı oranda bulaşmaz?
+00:10 Normal esneme ile bulaşıcı esneme farkı
+00:21 Pisa araştırması: akraba &gt; arkadaş &gt; yabancı
+00:35 Şempanzelerde de aynı desen
+00:40 Çocuklarda 4 yaş sonrası belirginleşme
+00:46 Sıradaki bölüm: güneşte hapşırma (ACHOO)
+📊 Kaynaklar:
+• Norscia &amp; Palagi (2011) PLoS ONE: https://journals.plos.org/plosone/article?id=10.1371/journal.pone.0028472
+• Campbell &amp; de Waal (2011) PLoS ONE: https://journals.plos.org/plosone/article?id=10.1371/journal.pone.0018283
+• Yavru şempanzelerde yaşla artan bulaşma (2013): https://journals.plos.org/plosone/article?id=10.1371/journal.pone.0076266
+🖼️ Görseller temsili (AI bilimsel canlandırma).
+Bir doz bilgi, her gün: 💊 ABONE OL!
+#bilgidozu #shorts #esneme #empati #beyin</t>
+        </is>
+      </c>
+      <c r="E138" s="11" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #esneme #empati #beyin</t>
+        </is>
+      </c>
+      <c r="F138" s="11" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, bulaşıcı esneme, esneme neden bulaşır, empati, şempanze, sosyal davranış, beyin, psikoloji, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G138" s="11" t="inlineStr">
+        <is>
+          <t>Sana en çok kim esneme bulaştırır? Akraba 1, arkadaş 2, yabancı 3 yazsın! 👇</t>
+        </is>
+      </c>
+      <c r="H138" s="11" t="inlineStr">
+        <is>
+          <t>İnsan Vücudu ve Beyin</t>
+        </is>
+      </c>
+      <c r="I138" s="11" t="inlineStr">
+        <is>
+          <t>Norscia &amp; Palagi (2011) PLoS ONE &amp; Campbell &amp; de Waal (2011)</t>
+        </is>
+      </c>
+      <c r="J138" s="11" t="n"/>
+      <c r="K138" s="11" t="n"/>
+      <c r="L138" s="11" t="n"/>
+      <c r="M138" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/bilgidozu_yukleme_tablosu.xlsx
+++ b/bilgidozu_yukleme_tablosu.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M138"/>
+  <dimension ref="A1:M140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8391,6 +8391,137 @@
       <c r="L138" s="11" t="n"/>
       <c r="M138" s="11" t="n"/>
     </row>
+    <row r="139">
+      <c r="A139" s="10" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B139" s="10" t="inlineStr">
+        <is>
+          <t>video_135.mp4</t>
+        </is>
+      </c>
+      <c r="C139" s="11" t="inlineStr">
+        <is>
+          <t>Güneşe Dönünce Hapşırıyor musun? Bu Bir Refleks: ACHOO! ☀️🤧 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>Güneşli havada hapşırıyorsan bu bir alerji değil: fotik hapşırma refleksi, yani ACHOO. Toplumun yaklaşık %18–%35'inde var.
+📍 BÖLÜMLER
+00:00 Fotik hapşırma refleksi (ACHOO) nedir?
+00:06 Otozomal baskın kalıtsallık: ebeveynden biri yeter
+00:12 Toplumda %18–%35 görülme sıklığı
+00:24 Mekanizma: görme ve trigeminal sinir komşuluğu
+00:36 Çoklu kromozom genetik işaretleri
+00:42 Sıradaki bölüm: dondurma sızısı (brain freeze)
+📊 Kaynaklar:
+• Nature Scientific Reports (2019 GWAS): https://www.nature.com/articles/s41598-019-41551-0
+• Cleveland Clinic Journal of Medicine: https://www.ccjm.org/content/ccjom/54/5/431.full.pdf
+• Derleme: https://en.wikipedia.org/wiki/Photic_sneeze_reflex
+🖼️ Görseller temsili (AI bilimsel canlandırma).
+Bir doz bilgi, her gün: 💊 ABONE OL!
+#bilgidozu #shorts #ACHOO #hapşırma #genetik</t>
+        </is>
+      </c>
+      <c r="E139" s="11" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #ACHOO #hapşırma #genetik</t>
+        </is>
+      </c>
+      <c r="F139" s="11" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, ACHOO, fotik hapşırma, güneş hapşırması, hapşırma refleksi, genetik, otozomal dominant, insan vücudu, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G139" s="11" t="inlineStr">
+        <is>
+          <t>Güneşte hapşırıyorsan 1 yaz, hiç tepki vermeyen 2 yazsın! 👇</t>
+        </is>
+      </c>
+      <c r="H139" s="11" t="inlineStr">
+        <is>
+          <t>İnsan Vücudu ve Beyin</t>
+        </is>
+      </c>
+      <c r="I139" s="11" t="inlineStr">
+        <is>
+          <t>Nature Scientific Reports (2019) &amp; Cleveland Clinic JM</t>
+        </is>
+      </c>
+      <c r="J139" s="11" t="n"/>
+      <c r="K139" s="11" t="n"/>
+      <c r="L139" s="11" t="n"/>
+      <c r="M139" s="11" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="10" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B140" s="10" t="inlineStr">
+        <is>
+          <t>video_136.mp4</t>
+        </is>
+      </c>
+      <c r="C140" s="11" t="inlineStr">
+        <is>
+          <t>Dondurma Damağına Değer Ama Neden Alnın Sızlar? 🧊🧠 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D140" s="11" t="inlineStr">
+        <is>
+          <t>Soğuk bir dondurma ya da buzlu su üst damağına değdiği halde sızı neden bir anda alnının ortasına vurur? Cevap beynin acil ısınma savunmasında gizli.
+📍 BÖLÜMLER
+00:00 Ağızdaki soğuk neden alında sızlar?
+00:13 Harvard beyin ultrasonu araştırması
+00:18 Ön beyin atardamarının ani genişlemesi
+00:29 Trigeminal sinir ve alına yansıyan ağrı
+00:39 Damarın daralması ve dil-damak çözümü
+00:47 Sıradaki bölüm: müzik ürpertisi (frisson)
+📊 Kaynaklar:
+• Serrador ve ark. (2012) Harvard Medical School / The FASEB Journal, 26(1): 685.4
+• ScienceDaily (American Physiological Society): https://www.sciencedaily.com/releases/2012/04/120422231742.htm
+• Cleveland Clinic — Brain Freeze: https://health.clevelandclinic.org/what-causes-brain-freeze
+🩺 Uyarı: Genel bilgi amaçlıdır, tıbbi tavsiye değildir.
+🖼️ Görseller temsili (AI bilimsel canlandırma).
+Bir doz bilgi, her gün: 💊 ABONE OL!
+#bilgidozu #shorts #beyin #dondurma #insanvücudu</t>
+        </is>
+      </c>
+      <c r="E140" s="11" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #beyin #dondurma #insanvücudu</t>
+        </is>
+      </c>
+      <c r="F140" s="11" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, dondurma baş ağrısı, brain freeze, ön beyin atardamarı, trigeminal sinir, yansıyan ağrı, beyin, insan vücudu, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G140" s="11" t="inlineStr">
+        <is>
+          <t>Dondurma ya da buzlu suda alnı sızlayanlar 1, hiç yaşamayanlar 2 yazsın! 👇</t>
+        </is>
+      </c>
+      <c r="H140" s="11" t="inlineStr">
+        <is>
+          <t>İnsan Vücudu ve Beyin</t>
+        </is>
+      </c>
+      <c r="I140" s="11" t="inlineStr">
+        <is>
+          <t>Harvard Medical School — Jorge Serrador et al. (2012) FASEB Journal</t>
+        </is>
+      </c>
+      <c r="J140" s="11" t="n"/>
+      <c r="K140" s="11" t="n"/>
+      <c r="L140" s="11" t="n"/>
+      <c r="M140" s="11" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilgidozu_yukleme_tablosu.xlsx
+++ b/bilgidozu_yukleme_tablosu.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M140"/>
+  <dimension ref="A1:M130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>video_106.mp4</t>
+          <t>video_96.mp4</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>video_107.mp4</t>
+          <t>video_97.mp4</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>video_108.mp4</t>
+          <t>video_98.mp4</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>video_109.mp4</t>
+          <t>video_99.mp4</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>video_110.mp4</t>
+          <t>video_100.mp4</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>video_91.mp4</t>
+          <t>video_86.mp4</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
@@ -4133,70 +4133,15 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>video_100.mp4</t>
+          <t>video_111.mp4</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Beynimizin Sadece Yüzde 10'unu Kullandığımız Efsanesi Yalan! 🧠⚡ #bilgidozu #shorts</t>
+          <t>Rüyanda Neden Koşamazsın? Beynin Gece Seni Kilitler! 🧠</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
-        <is>
-          <t>Modern beyin görüntüleme cihazları gün içinde konuşurken, yürürken ve uyurken beynimizin neredeyse tamamının aktif çalıştığını kanıtlamıştır.
-Siz de yıllarca beynimizin sadece yüzde onunu kullandığımız efsanesine inanmış mıydınız? Yorumlara yazın! 👇
-📚 Kaynak: Nature Reviews Neuroscience — The 10% Brain Myth
-🎨 Görseller temsilîdir (AI üretimi).
-#bilgidozu #shorts #beyin #psikoloji #bilim</t>
-        </is>
-      </c>
-      <c r="E62" s="8" t="inlineStr">
-        <is>
-          <t>#bilgidozu #shorts #beyin #psikoloji #bilim</t>
-        </is>
-      </c>
-      <c r="F62" s="8" t="inlineStr">
-        <is>
-          <t>bilgi dozu, beyin, yüzde 10 efsanesi, psikoloji, nörobilim, shorts</t>
-        </is>
-      </c>
-      <c r="G62" s="8" t="inlineStr">
-        <is>
-          <t>Siz de yıllarca beynimizin sadece yüzde onunu kullandığımız efsanesine inanmış mıydınız? Yorumlara yazın! 👇</t>
-        </is>
-      </c>
-      <c r="H62" s="8" t="inlineStr">
-        <is>
-          <t>İnsan Vücudu ve Psikoloji</t>
-        </is>
-      </c>
-      <c r="I62" s="8" t="inlineStr">
-        <is>
-          <t>Nature Reviews Neuroscience — The 10% Brain Myth: https://en.wikipedia.org/wiki/Ten_percent_of_brain_myth</t>
-        </is>
-      </c>
-      <c r="J62" s="8" t="n"/>
-      <c r="K62" s="8" t="n"/>
-      <c r="L62" s="8" t="n"/>
-      <c r="M62" s="8" t="n"/>
-    </row>
-    <row r="63" ht="42" customHeight="1">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t>ESKİ_STOK_ASKIDA</t>
-        </is>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>video_121.mp4</t>
-        </is>
-      </c>
-      <c r="C63" s="8" t="inlineStr">
-        <is>
-          <t>Rüyanda Neden Koşamazsın? Beynin Gece Seni Kilitler! 🧠</t>
-        </is>
-      </c>
-      <c r="D63" s="8" t="inlineStr">
         <is>
           <t>Rüyanda tehlikeden kaçmaya çalışırken bacaklarının kurşun gibi ağırlaştığını hiç hissettin mi? REM uykusu sırasında beynin uyanıkmış gibi aktif çalışır ancak beyin sapındaki devreler GABA ve glisin aracılığıyla iskelet kaslarına giden motor nöronları geçici olarak kilitler. REM atonisi denilen bu koruyucu mekanizma sayesinde rüyalarını yatakta fiziksel olarak oynamaz ve kendine zarar vermezsin.
 Peki sen rüyanda daha çok koşamadığın mı yoksa bağıramadığın anları mı yaşıyorsun? Yorumlarda buluşalım! 👇
@@ -4205,53 +4150,53 @@
 #bilgidozu #shorts #beyin #uyku #psikoloji #nörobilim #bilim</t>
         </is>
       </c>
-      <c r="E63" s="8" t="inlineStr">
+      <c r="E62" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #beyin #uyku #psikoloji #nörobilim #bilim</t>
         </is>
       </c>
-      <c r="F63" s="8" t="inlineStr">
+      <c r="F62" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, rüyanda neden koşamazsın, rem uykusu, uyku atonisi, beyin, nörobilim, psikoloji, uyku bilimi, ilginç bilgiler, şaşırtıcı gerçekler, bilim, shorts</t>
         </is>
       </c>
-      <c r="G63" s="8" t="inlineStr">
+      <c r="G62" s="8" t="inlineStr">
         <is>
           <t>Peki sen rüyanda daha çok koşamadığın mı yoksa bağıramadığın anları mı yaşıyorsun? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H63" s="8" t="inlineStr">
+      <c r="H62" s="8" t="inlineStr">
         <is>
           <t>Beyin ve Psikoloji</t>
         </is>
       </c>
-      <c r="I63" s="8" t="inlineStr">
+      <c r="I62" s="8" t="inlineStr">
         <is>
           <t>https://www.jneurosci.org/content/32/29/9785</t>
         </is>
       </c>
-      <c r="J63" s="8" t="n"/>
-      <c r="K63" s="8" t="n"/>
-      <c r="L63" s="8" t="n"/>
-      <c r="M63" s="8" t="n"/>
-    </row>
-    <row r="64" ht="42" customHeight="1">
-      <c r="A64" s="7" t="inlineStr">
+      <c r="J62" s="8" t="n"/>
+      <c r="K62" s="8" t="n"/>
+      <c r="L62" s="8" t="n"/>
+      <c r="M62" s="8" t="n"/>
+    </row>
+    <row r="63" ht="42" customHeight="1">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>video_83.mp4</t>
         </is>
       </c>
-      <c r="C64" s="8" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>Sevdiğin Birine Bakınca Göz Bebeğin Neden Otomatik Büyür? 👀❤️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D64" s="8" t="inlineStr">
+      <c r="D63" s="8" t="inlineStr">
         <is>
           <t>Hoşlandığımız birine baktığımızda dopamin ve oksitosin etkisiyle sempatik sinir sistemi göz bebeklerimizi istemsizce büyütür.
 Siz konuşurken karşınızdakinin göz bebeklerine dikkat eder misiniz? Yorumlara yazın! 👇
@@ -4260,53 +4205,53 @@
 #bilgidozu #shorts #psikoloji #insanvücudu #bilim</t>
         </is>
       </c>
-      <c r="E64" s="8" t="inlineStr">
+      <c r="E63" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #psikoloji #insanvücudu #bilim</t>
         </is>
       </c>
-      <c r="F64" s="8" t="inlineStr">
+      <c r="F63" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, psikoloji, göz bebeği, insan vücudu, bilim, shorts</t>
         </is>
       </c>
-      <c r="G64" s="8" t="inlineStr">
+      <c r="G63" s="8" t="inlineStr">
         <is>
           <t>Siz konuşurken karşınızdakinin göz bebeklerine dikkat eder misiniz? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H64" s="8" t="inlineStr">
+      <c r="H63" s="8" t="inlineStr">
         <is>
           <t>İnsan Vücudu ve Psikoloji</t>
         </is>
       </c>
-      <c r="I64" s="8" t="inlineStr">
+      <c r="I63" s="8" t="inlineStr">
         <is>
           <t>Hess &amp; Polt (1960) / Wikipedia — Pupillometry Research: https://en.wikipedia.org/wiki/Pupillometry</t>
         </is>
       </c>
-      <c r="J64" s="8" t="n"/>
-      <c r="K64" s="8" t="n"/>
-      <c r="L64" s="8" t="n"/>
-      <c r="M64" s="8" t="n"/>
-    </row>
-    <row r="65" ht="42" customHeight="1">
-      <c r="A65" s="7" t="inlineStr">
+      <c r="J63" s="8" t="n"/>
+      <c r="K63" s="8" t="n"/>
+      <c r="L63" s="8" t="n"/>
+      <c r="M63" s="8" t="n"/>
+    </row>
+    <row r="64" ht="42" customHeight="1">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>uzun_video_8.mp4</t>
         </is>
       </c>
-      <c r="C65" s="8" t="inlineStr">
+      <c r="C64" s="8" t="inlineStr">
         <is>
           <t>Okyanusta Kendi Işığını Üreten Canlılar: Soğuk Işık, Av Tuzağı ve Karşı Aydınlatma! 🌊✨ #bilgidozu</t>
         </is>
       </c>
-      <c r="D65" s="8" t="inlineStr">
+      <c r="D64" s="8" t="inlineStr">
         <is>
           <t>Güneş ışığının ulaşamadığı derin okyanus sularında kendi ışığını üreten canlıların kimyasal sırrı ne? Denizlerin alacakaranlık kuşağında parlayan biyolüminesans dünyasını inceliyoruz! 🌊✨
 BÖLÜMLER:
@@ -4318,53 +4263,53 @@
 #bilgidozu #okyanus #bilim #biyolüminesans #doğa #denizcanlıları</t>
         </is>
       </c>
-      <c r="E65" s="8" t="inlineStr">
+      <c r="E64" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #bilim</t>
         </is>
       </c>
-      <c r="F65" s="8" t="inlineStr">
+      <c r="F64" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, okyanus, biyolüminesans, derin deniz, fenerbalığı, doğa, biyoloji, bilim, ilginç bilgiler</t>
         </is>
       </c>
-      <c r="G65" s="8" t="inlineStr">
+      <c r="G64" s="8" t="inlineStr">
         <is>
           <t>Derin okyanustaki hangi ışık stratejisi seni en çok şaşırttı? 🌊 1-Soğuk Işık 2-Fener Tuzağı 3-Görünmezlik — Yorumlara yaz! 👇</t>
         </is>
       </c>
-      <c r="H65" s="8" t="inlineStr">
+      <c r="H64" s="8" t="inlineStr">
         <is>
           <t>Uzun — Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I65" s="8" t="inlineStr">
+      <c r="I64" s="8" t="inlineStr">
         <is>
           <t>NOAA Ocean Exploration — Bioluminescence: https://oceanexplorer.noaa.gov/facts/bioluminescence.html Smithsonian Ocean — Bioluminescence: https://ocean.si.edu/ocean-life/fish/bioluminescence</t>
         </is>
       </c>
-      <c r="J65" s="8" t="n"/>
-      <c r="K65" s="8" t="n"/>
-      <c r="L65" s="8" t="n"/>
-      <c r="M65" s="8" t="n"/>
-    </row>
-    <row r="66" ht="42" customHeight="1">
-      <c r="A66" s="7" t="inlineStr">
+      <c r="J64" s="8" t="n"/>
+      <c r="K64" s="8" t="n"/>
+      <c r="L64" s="8" t="n"/>
+      <c r="M64" s="8" t="n"/>
+    </row>
+    <row r="65" ht="42" customHeight="1">
+      <c r="A65" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>uzun_video_9.mp4</t>
         </is>
       </c>
-      <c r="C66" s="8" t="inlineStr">
+      <c r="C65" s="8" t="inlineStr">
         <is>
           <t>Beynin Seni Ayakta Tutan 3 Gizli Sensörü: İç Kulak Pusulası, Kristaller ve Algı Çatışması! 🧠⚡ #bilgidozu</t>
         </is>
       </c>
-      <c r="D66" s="8" t="inlineStr">
+      <c r="D65" s="8" t="inlineStr">
         <is>
           <t>Yürürken başını çevirdiğinde görüntü neden titremiyor? Araçta telefon okurken neden miden bulanıyor? Vücudumuzun görünmez denge merkezi olan vestibüler sistemi inceliyoruz! 🧠⚡
 BÖLÜMLER:
@@ -4376,53 +4321,53 @@
 #bilgidozu #beyin #nörobilim #denge #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="E66" s="8" t="inlineStr">
+      <c r="E65" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #bilim</t>
         </is>
       </c>
-      <c r="F66" s="8" t="inlineStr">
+      <c r="F65" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, beyin, nörobilim, denge, içkulak, vestibülersistem, algı, psikoloji, bilim</t>
         </is>
       </c>
-      <c r="G66" s="8" t="inlineStr">
+      <c r="G65" s="8" t="inlineStr">
         <is>
           <t>Arabada veya gemide giderken telefon okuyabiliyor musun, yoksa hemen miden mi bulanıyor? 🚗🧠 Yorumlara yaz! 👇</t>
         </is>
       </c>
-      <c r="H66" s="8" t="inlineStr">
+      <c r="H65" s="8" t="inlineStr">
         <is>
           <t>Uzun — Beyin ve Psikoloji</t>
         </is>
       </c>
-      <c r="I66" s="8" t="inlineStr">
+      <c r="I65" s="8" t="inlineStr">
         <is>
           <t>NIH / NIDCD — Balance Disorders: https://www.nidcd.nih.gov/health/balance-disorders</t>
         </is>
       </c>
-      <c r="J66" s="8" t="n"/>
-      <c r="K66" s="8" t="n"/>
-      <c r="L66" s="8" t="n"/>
-      <c r="M66" s="8" t="n"/>
-    </row>
-    <row r="67" ht="42" customHeight="1">
-      <c r="A67" s="7" t="inlineStr">
+      <c r="J65" s="8" t="n"/>
+      <c r="K65" s="8" t="n"/>
+      <c r="L65" s="8" t="n"/>
+      <c r="M65" s="8" t="n"/>
+    </row>
+    <row r="66" ht="42" customHeight="1">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B66" s="7" t="inlineStr">
         <is>
           <t>uzun_video_10.mp4</t>
         </is>
       </c>
-      <c r="C67" s="8" t="inlineStr">
+      <c r="C66" s="8" t="inlineStr">
         <is>
           <t>Uzay Sessizse NASA'nın Kaydettiği Bu Sesler Ne? Kara Delik Seslerinin Gerçek Sırrı! 🪐🔊 #bilgidozu</t>
         </is>
       </c>
-      <c r="D67" s="8" t="inlineStr">
+      <c r="D66" s="8" t="inlineStr">
         <is>
           <t>Uzay boşluğunda ses yayılmıyorsa NASA'nın paylaştığı kara delik ve galaksi sesleri gerçekte ne? Perseus galaksi kümesindeki gerçek basınç dalgaları ile M87 veri sonifikasyonunun farkını inceliyoruz! 🪐🔊
 BÖLÜMLER:
@@ -4434,53 +4379,53 @@
 #bilgidozu #uzay #nasa #karadelik #astronomi #bilim</t>
         </is>
       </c>
-      <c r="E67" s="8" t="inlineStr">
+      <c r="E66" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #bilim</t>
         </is>
       </c>
-      <c r="F67" s="8" t="inlineStr">
+      <c r="F66" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, uzay, nasa, karadelik, perseus, m87, chandra, astronomi, astrofizik, bilim</t>
         </is>
       </c>
-      <c r="G67" s="8" t="inlineStr">
+      <c r="G66" s="8" t="inlineStr">
         <is>
           <t>Perseus kara deliğinin 57 oktav yükseltilmiş gerçek basınç sesini duymuş muydun? 🕳️🔊 Duyanlar 1, yeni öğrenenler 2 yazsın! 👇</t>
         </is>
       </c>
-      <c r="H67" s="8" t="inlineStr">
+      <c r="H66" s="8" t="inlineStr">
         <is>
           <t>Uzun — Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I67" s="8" t="inlineStr">
+      <c r="I66" s="8" t="inlineStr">
         <is>
           <t>NASA — New NASA Black Hole Sonifications: https://www.nasa.gov/universe/new-nasa-black-hole-sonifications-with-a-remix/</t>
         </is>
       </c>
-      <c r="J67" s="8" t="n"/>
-      <c r="K67" s="8" t="n"/>
-      <c r="L67" s="8" t="n"/>
-      <c r="M67" s="8" t="n"/>
-    </row>
-    <row r="68" ht="42" customHeight="1">
-      <c r="A68" s="7" t="inlineStr">
+      <c r="J66" s="8" t="n"/>
+      <c r="K66" s="8" t="n"/>
+      <c r="L66" s="8" t="n"/>
+      <c r="M66" s="8" t="n"/>
+    </row>
+    <row r="67" ht="42" customHeight="1">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t>uzun_video_11.mp4</t>
         </is>
       </c>
-      <c r="C68" s="8" t="inlineStr">
+      <c r="C67" s="8" t="inlineStr">
         <is>
           <t>Zaman Yukarıda Daha Hızlı Akıyor! Telefonundaki Konum İçin Einstein Neden Gerekli? ⏱️🛰️ #bilgidozu</t>
         </is>
       </c>
-      <c r="D68" s="8" t="inlineStr">
+      <c r="D67" s="8" t="inlineStr">
         <is>
           <t>Telefonundaki mavi konum noktasının doğru çalışması için Einstein'ın özel ve genel görelilik kuramlarının her saniye hesaba katıldığını biliyor muydun? ⏱️🛰️
 BÖLÜMLER:
@@ -4492,53 +4437,53 @@
 #bilgidozu #uzay #zaman #einstein #görelilik #bilim</t>
         </is>
       </c>
-      <c r="E68" s="8" t="inlineStr">
+      <c r="E67" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #bilim</t>
         </is>
       </c>
-      <c r="F68" s="8" t="inlineStr">
+      <c r="F67" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, uzay, zaman, einstein, görelilik, atomsaati, gps, fizik, bilim</t>
         </is>
       </c>
-      <c r="G68" s="8" t="inlineStr">
+      <c r="G67" s="8" t="inlineStr">
         <is>
           <t>Einstein'ın görelilik hesabı olmasa GPS konumunun günde 10 kilometre sapacağını biliyor muydun? ⏱️🛰️ 1 veya 2 yaz! 👇</t>
         </is>
       </c>
-      <c r="H68" s="8" t="inlineStr">
+      <c r="H67" s="8" t="inlineStr">
         <is>
           <t>Uzun — Fizik ve Uzay</t>
         </is>
       </c>
-      <c r="I68" s="8" t="inlineStr">
+      <c r="I67" s="8" t="inlineStr">
         <is>
           <t>NIST — Putting Einstein to the Test: https://www.nist.gov/atomic-clocks/a-powerful-tool-for-science/putting-einstein-test</t>
         </is>
       </c>
-      <c r="J68" s="8" t="n"/>
-      <c r="K68" s="8" t="n"/>
-      <c r="L68" s="8" t="n"/>
-      <c r="M68" s="8" t="n"/>
-    </row>
-    <row r="69" ht="42" customHeight="1">
-      <c r="A69" s="7" t="inlineStr">
+      <c r="J67" s="8" t="n"/>
+      <c r="K67" s="8" t="n"/>
+      <c r="L67" s="8" t="n"/>
+      <c r="M67" s="8" t="n"/>
+    </row>
+    <row r="68" ht="42" customHeight="1">
+      <c r="A68" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
+      <c r="B68" s="7" t="inlineStr">
         <is>
           <t>uzun_video_12.mp4</t>
         </is>
       </c>
-      <c r="C69" s="8" t="inlineStr">
+      <c r="C68" s="8" t="inlineStr">
         <is>
           <t>Sizin Beğendikleriniz · Bölüm 1: Kargalar, Ahtapotlar, Tardigradlar! 🐙🔬 #bilgidozu</t>
         </is>
       </c>
-      <c r="D69" s="8" t="inlineStr">
+      <c r="D68" s="8" t="inlineStr">
         <is>
           <t>Sizin Beğendikleriniz serisinin ilk bölümünde üç efsane canlının sıra dışı biyolojisini inceliyoruz: kargaların yüz hafızası ve sosyal öğrenmesi, ahtapotların kollara dağılmış sinir sistemi ile üç kalbi ve tardigradların kriptobiyoz dayanıklılığı.
 BÖLÜMLER:
@@ -4556,27 +4501,27 @@
 #bilgidozu #bilim #doğa #hayvanlar #biyoloji</t>
         </is>
       </c>
-      <c r="E69" s="8" t="inlineStr">
+      <c r="E68" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #bilim #doğa #hayvanlar #biyoloji</t>
         </is>
       </c>
-      <c r="F69" s="8" t="inlineStr">
+      <c r="F68" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, kargalar, ahtapot, tardigrad, su ayısı, hayvanlar, doğa, bilim, biyoloji, ilginç bilgiler</t>
         </is>
       </c>
-      <c r="G69" s="8" t="inlineStr">
+      <c r="G68" s="8" t="inlineStr">
         <is>
           <t>Bu 3 olaydan sizi en çok hangisi şaşırttı: 1 mi, 2 mi, 3 mü? Yorumlara yazın! (1 Kargalar, 2 Ahtapotlar, 3 Tardigradlar)</t>
         </is>
       </c>
-      <c r="H69" s="8" t="inlineStr">
+      <c r="H68" s="8" t="inlineStr">
         <is>
           <t>Uzun — Bilim ve Doğa</t>
         </is>
       </c>
-      <c r="I69" s="8" t="inlineStr">
+      <c r="I68" s="8" t="inlineStr">
         <is>
           <t>Kargalar — Marzluff et al. (2012), PNAS: https://www.pnas.org/doi/10.1073/pnas.1206109109
 Kargalar sosyal öğrenme — Cornell et al. (2011), Proc. R. Soc. B: https://doi.org/10.1098/rspb.2011.0957
@@ -4586,28 +4531,28 @@
 Tardigrad Dsup — Hashimoto et al. (2016), Nature Communications: https://www.nature.com/articles/ncomms12808</t>
         </is>
       </c>
-      <c r="J69" s="8" t="n"/>
-      <c r="K69" s="8" t="n"/>
-      <c r="L69" s="8" t="n"/>
-      <c r="M69" s="8" t="n"/>
-    </row>
-    <row r="70" ht="42" customHeight="1">
-      <c r="A70" s="7" t="inlineStr">
+      <c r="J68" s="8" t="n"/>
+      <c r="K68" s="8" t="n"/>
+      <c r="L68" s="8" t="n"/>
+      <c r="M68" s="8" t="n"/>
+    </row>
+    <row r="69" ht="42" customHeight="1">
+      <c r="A69" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t>uzun_video_13.mp4</t>
         </is>
       </c>
-      <c r="C70" s="8" t="inlineStr">
+      <c r="C69" s="8" t="inlineStr">
         <is>
           <t>Beyninin Senden Gizlediği 3 Otomatik Hile (Kendi Sesin, Boşluğun Çağrısı ve Sahte Acı) 🧠🔒 #bilgidozu</t>
         </is>
       </c>
-      <c r="D70" s="8" t="inlineStr">
+      <c r="D69" s="8" t="inlineStr">
         <is>
           <t>Beyninin senden gizlediği 3 otomatik hileyi tek bir merak yolculuğunda inceliyoruz:
 1 · Kendi Sesin Neden Kayıtta Yabancı Gelir? (Kafatası Kemik İletimi)
@@ -4622,97 +4567,149 @@
 #bilgidozu #bilim #psikoloji #nörobilim #insanbedeni</t>
         </is>
       </c>
-      <c r="E70" s="8" t="inlineStr">
+      <c r="E69" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #bilim #psikoloji #nörobilim #insanbedeni</t>
         </is>
       </c>
-      <c r="F70" s="8" t="inlineStr">
+      <c r="F69" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, nörobilim, psikoloji, insan beyni, kemik iletimi, kapsaisin, bilim, belgesel</t>
         </is>
       </c>
-      <c r="G70" s="8" t="inlineStr">
+      <c r="G69" s="8" t="inlineStr">
         <is>
           <t>Bu 3 beyin hilesinden seni en çok şaşırtan hangisi oldu: Kendi sesinin kemik iletimi mi, yüksek yerdeki Boşluğun Çağrısı mı, yoksa acı biberin sahte yanık alarmı mı? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H70" s="8" t="inlineStr">
+      <c r="H69" s="8" t="inlineStr">
         <is>
           <t>Uzun — Nörobilim ve Psikoloji</t>
         </is>
       </c>
-      <c r="I70" s="8" t="inlineStr">
+      <c r="I69" s="8" t="inlineStr">
         <is>
           <t>1) Kemik İletimi — Wikipedia: https://en.wikipedia.org/wiki/Bone_conduction
 2) Boşluğun Çağrısı — Wikipedia: https://en.wikipedia.org/wiki/The_imp_of_the_perverse
 3) Kapsaisin &amp; TRPV1 — Wikipedia: https://en.wikipedia.org/wiki/Capsaicin</t>
         </is>
       </c>
-      <c r="J70" s="8" t="n"/>
-      <c r="K70" s="8" t="n"/>
-      <c r="L70" s="8" t="n"/>
-      <c r="M70" s="8" t="n"/>
-    </row>
-    <row r="71" ht="42" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="J69" s="8" t="n"/>
+      <c r="K69" s="8" t="n"/>
+      <c r="L69" s="8" t="n"/>
+      <c r="M69" s="8" t="n"/>
+    </row>
+    <row r="70" ht="42" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>YÜKLENDİ</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>video_40.mp4</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>Kışın Kalbi Durup Buz Tutan, Baharda Çözülüp Canlanan Kurbağa! 🐸❄️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>Kuzey Amerika orman kurbağası kış geldiğinde donarak hayatta kalan mucizevi bir canlıdır! Vücudundaki suyun büyük kısmı buz tutarken karaciğeri hücrelerin içine yoğun glikoz pompalar; bu doğal antifriz hücrelerin parçalanmasını önler ve bahar geldiğinde kurbağa çözülüp yaşamına devam eder.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr">
+      <c r="F70" s="3" t="inlineStr">
         <is>
           <t>bilgidozu, ormankurbağası, doğa, biyoloji, hayvanlaralemi, kışuykusu, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G71" s="3" t="inlineStr">
+      <c r="G70" s="3" t="inlineStr">
         <is>
           <t>Donup baharda yeniden canlanan bu kurbağayı daha önce duymuş muydun? 🐸❄️ Duyanlar '1', ilk kez öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H71" s="3" t="inlineStr">
+      <c r="H70" s="3" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I71" s="3" t="inlineStr">
+      <c r="I70" s="3" t="inlineStr">
         <is>
           <t>Wikipedia — Wood frog (Cold tolerance): https://en.wikipedia.org/wiki/Wood_frog</t>
         </is>
       </c>
-      <c r="J71" s="3" t="inlineStr">
+      <c r="J70" s="3" t="inlineStr">
         <is>
           <t>https://youtu.be/jrySNivbPcQ</t>
         </is>
       </c>
-      <c r="K71" s="3" t="inlineStr">
+      <c r="K70" s="3" t="inlineStr">
         <is>
           <t>2026-10-26 11:39</t>
         </is>
       </c>
-      <c r="L71" s="3" t="n"/>
-      <c r="M71" s="3" t="n"/>
+      <c r="L70" s="3" t="n"/>
+      <c r="M70" s="3" t="n"/>
+    </row>
+    <row r="71" ht="42" customHeight="1">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>video_41.mp4</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>Eşini Etkilemek İçin Renkli Karnını Açıp Dans Eden Minik Örümcek! 🕷️💃 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>Avustralya'da yaşayan ve pirinç tanesi kadar küçük olan tavuskuşu örümceği, doğanın en renkli dansçılarından biridir! Erkek örümcekler gökkuşağı renklerindeki karın kanatlarını yelpaze gibi açar, üçüncü bacaklarını havaya kaldırır ve çıkardıkları titreşimlerle kusursuz bir ritim sergiler.
+Daha fazla bilgi dozu için takip etmeyi unutma!</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #doğa #bilim #dozdışı</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>bilgidozu, tavuskuşuörümceği, doğa, hayvanlaralemi, biyoloji, avustralya, ilginçbilgiler, bilim, shorts, doz dışı</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t>Örümceklerden korkanları bile gülümsetecek bir dans değil mi? 🕷️💃 Beğenenler '1' yazsın! 👇</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>Doğa ve Hayvanlar</t>
+        </is>
+      </c>
+      <c r="I71" s="8" t="inlineStr">
+        <is>
+          <t>Western Australian Museum — Peacock Spider: https://museum.wa.gov.au/explore/articles/peacock-spiders</t>
+        </is>
+      </c>
+      <c r="J71" s="8" t="n"/>
+      <c r="K71" s="8" t="n"/>
+      <c r="L71" s="8" t="n"/>
+      <c r="M71" s="8" t="n"/>
     </row>
     <row r="72" ht="42" customHeight="1">
       <c r="A72" s="7" t="inlineStr">
@@ -4722,17 +4719,17 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>video_41.mp4</t>
+          <t>video_42.mp4</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Eşini Etkilemek İçin Renkli Karnını Açıp Dans Eden Minik Örümcek! 🕷️💃 #bilgidozu #shorts</t>
+          <t>Doğada Havada Asılı Kalıp Geriye Doğru Uçabilen Tek Kuş! 🐦🔄 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Avustralya'da yaşayan ve pirinç tanesi kadar küçük olan tavuskuşu örümceği, doğanın en renkli dansçılarından biridir! Erkek örümcekler gökkuşağı renklerindeki karın kanatlarını yelpaze gibi açar, üçüncü bacaklarını havaya kaldırır ve çıkardıkları titreşimlerle kusursuz bir ritim sergiler.
+          <t>Sinek kuşları, kuşlar dünyasında uzun süreli olarak geriye doğru uçabilen tek türdür! Kanatlarını sadece aşağı-yukarı değil, omuz eklemlerinden sekiz çizecek şekilde döndürerek saniyede 50 ila 80 kez çırparlar; böylece helikopter gibi havada sabit kalıp geri vitese takabilirler.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
@@ -4743,12 +4740,12 @@
       </c>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>bilgidozu, tavuskuşuörümceği, doğa, hayvanlaralemi, biyoloji, avustralya, ilginçbilgiler, bilim, shorts, doz dışı</t>
+          <t>bilgidozu, sinekkuşu, kuşlar, doğa, biyoloji, hayvanlaralemi, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>Örümceklerden korkanları bile gülümsetecek bir dans değil mi? 🕷️💃 Beğenenler '1' yazsın! 👇</t>
+          <t>Sinek kuşunun saniyede 80 kez kanat çırptığını biliyor muydun? 🐦🔄 Bilenler '1', yeni öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
@@ -4758,7 +4755,7 @@
       </c>
       <c r="I72" s="8" t="inlineStr">
         <is>
-          <t>Western Australian Museum — Peacock Spider: https://museum.wa.gov.au/explore/articles/peacock-spiders</t>
+          <t>UC Davis — Hummingbird Facts: https://www.ucdavis.edu/</t>
         </is>
       </c>
       <c r="J72" s="8" t="n"/>
@@ -4774,17 +4771,17 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>video_42.mp4</t>
+          <t>video_43.mp4</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>Doğada Havada Asılı Kalıp Geriye Doğru Uçabilen Tek Kuş! 🐦🔄 #bilgidozu #shorts</t>
+          <t>Suyun Altından Ağaçtaki Böceği Su Tabancası Gibi Vuran Balık! 🐟🎯 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>Sinek kuşları, kuşlar dünyasında uzun süreli olarak geriye doğru uçabilen tek türdür! Kanatlarını sadece aşağı-yukarı değil, omuz eklemlerinden sekiz çizecek şekilde döndürerek saniyede 50 ila 80 kez çırparlar; böylece helikopter gibi havada sabit kalıp geri vitese takabilirler.
+          <t>Okçu balığı, suyun dışındaki dallarda duran böcekleri ağzından fırlattığı keskin bir su jetiyle vurarak avlar! Üstelik ışığın sudan havaya geçerken kırılmasını (optik kırılmayı) doğuştan hesaba katar ve hedefine neredeyse sıfır hatayla nişan alır.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
@@ -4795,12 +4792,12 @@
       </c>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>bilgidozu, sinekkuşu, kuşlar, doğa, biyoloji, hayvanlaralemi, ilginçbilgiler, bilim, shorts, doz dışı</t>
+          <t>bilgidozu, okçubalığı, balıklar, doğa, fizik, hayvanlaralemi, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>Sinek kuşunun saniyede 80 kez kanat çırptığını biliyor muydun? 🐦🔄 Bilenler '1', yeni öğrenenler '2' yazsın! 👇</t>
+          <t>Işığın kırılmasını hesaplayıp suyla ateş eden bu keskin nişancı balığı duymuş muydun? 🐟🎯 '1' veya '2' yaz! 👇</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
@@ -4810,7 +4807,7 @@
       </c>
       <c r="I73" s="8" t="inlineStr">
         <is>
-          <t>UC Davis — Hummingbird Facts: https://www.ucdavis.edu/</t>
+          <t>PLOS ONE (Vailati et al., 2012 — Archerfish water jet): https://journals.plos.org/plosone/article?id=10.1371/journal.pone.0047867</t>
         </is>
       </c>
       <c r="J73" s="8" t="n"/>
@@ -4826,17 +4823,17 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>video_43.mp4</t>
+          <t>video_44.mp4</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Suyun Altından Ağaçtaki Böceği Su Tabancası Gibi Vuran Balık! 🐟🎯 #bilgidozu #shorts</t>
+          <t>Sadece Rengini Değil, Derisinin Dokusunu da Anında Değiştiren Canlı! 🦑🎭 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Okçu balığı, suyun dışındaki dallarda duran böcekleri ağzından fırlattığı keskin bir su jetiyle vurarak avlar! Üstelik ışığın sudan havaya geçerken kırılmasını (optik kırılmayı) doğuştan hesaba katar ve hedefine neredeyse sıfır hatayla nişan alır.
+          <t>Mürekkep balığı, okyanusun en üstün kamuflaj ustalarından biridir! Derisindeki milyonlarca renk hücresiyle saniyede renk ve desen değiştirirken, özel kas kabarcıkları (papilla) sayesinde pürüzsüz derisini anında dikenli bir mercan ya da pütürlü bir kaya dokusuna dönüştürebilir.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
@@ -4847,12 +4844,12 @@
       </c>
       <c r="F74" s="8" t="inlineStr">
         <is>
-          <t>bilgidozu, okçubalığı, balıklar, doğa, fizik, hayvanlaralemi, ilginçbilgiler, bilim, shorts, doz dışı</t>
+          <t>bilgidozu, mürekkepbalığı, okyanus, kamuflaj, doğa, biyoloji, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>Işığın kırılmasını hesaplayıp suyla ateş eden bu keskin nişancı balığı duymuş muydun? 🐟🎯 '1' veya '2' yaz! 👇</t>
+          <t>Mürekkep balığının derisini 3 boyutlu olarak kabartıp kaya şekline sokabildiğini biliyor muydun? 🦑🎭 '1' / '2' yaz! 👇</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
@@ -4862,7 +4859,7 @@
       </c>
       <c r="I74" s="8" t="inlineStr">
         <is>
-          <t>PLOS ONE (Vailati et al., 2012 — Archerfish water jet): https://journals.plos.org/plosone/article?id=10.1371/journal.pone.0047867</t>
+          <t>Marine Biological Laboratory — Cuttlefish Camouflage: https://www.mbl.edu/</t>
         </is>
       </c>
       <c r="J74" s="8" t="n"/>
@@ -4878,17 +4875,17 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>video_44.mp4</t>
+          <t>video_45.mp4</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>Sadece Rengini Değil, Derisinin Dokusunu da Anında Değiştiren Canlı! 🦑🎭 #bilgidozu #shorts</t>
+          <t>Flamingolar Aslında Gri Doğar! Peki Tüyleri Neden Pembeleşir? 🦩🦐 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>Mürekkep balığı, okyanusun en üstün kamuflaj ustalarından biridir! Derisindeki milyonlarca renk hücresiyle saniyede renk ve desen değiştirirken, özel kas kabarcıkları (papilla) sayesinde pürüzsüz derisini anında dikenli bir mercan ya da pütürlü bir kaya dokusuna dönüştürebilir.
+          <t>Flamingolar dünyaya geldiklerinde pembe değil, gri ve beyaz tüylere sahiptir! İkonik pembe ve mercan renklerini, sulak alanlarda tükettikleri mikroskobik algler ve tuzlu su karideslerinin içindeki 'karotenoid' pigmentlerinin karaciğerde işlenip yeni çıkan tüylere yerleşmesiyle kazanırlar.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
@@ -4899,12 +4896,12 @@
       </c>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>bilgidozu, mürekkepbalığı, okyanus, kamuflaj, doğa, biyoloji, ilginçbilgiler, bilim, shorts, doz dışı</t>
+          <t>bilgidozu, flamingo, kuşlar, doğa, biyoloji, hayvanlaralemi, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>Mürekkep balığının derisini 3 boyutlu olarak kabartıp kaya şekline sokabildiğini biliyor muydun? 🦑🎭 '1' / '2' yaz! 👇</t>
+          <t>Flamingoların gri doğduğunu ve yedikleriyle pembeleştiğini biliyor muydun? 🦩🦐 Bilenler '1', yeni öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
@@ -4914,7 +4911,7 @@
       </c>
       <c r="I75" s="8" t="inlineStr">
         <is>
-          <t>Marine Biological Laboratory — Cuttlefish Camouflage: https://www.mbl.edu/</t>
+          <t>San Diego Zoo — Flamingo Facts: https://animals.sandiegozoo.org/animals/flamingo</t>
         </is>
       </c>
       <c r="J75" s="8" t="n"/>
@@ -4930,17 +4927,17 @@
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>video_45.mp4</t>
+          <t>video_49.mp4</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>Flamingolar Aslında Gri Doğar! Peki Tüyleri Neden Pembeleşir? 🦩🦐 #bilgidozu #shorts</t>
+          <t>Bu Hayvanın Parmak İzi İnsanla O Kadar Aynı ki Mikroskopta Bile Karışıyor! 🐨🔍 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>Flamingolar dünyaya geldiklerinde pembe değil, gri ve beyaz tüylere sahiptir! İkonik pembe ve mercan renklerini, sulak alanlarda tükettikleri mikroskobik algler ve tuzlu su karideslerinin içindeki 'karotenoid' pigmentlerinin karaciğerde işlenip yeni çıkan tüylere yerleşmesiyle kazanırlar.
+          <t>Bir koalanın parmak izi insanınkine o kadar kusursuz benzer ki taramalı elektron mikroskobu altında bile ayırt etmek oldukça zordur! Evrimsel olarak bizden milyonlarca yıl önce ayrılmış olsalar da okaliptüs dallarını sıkıca kavrama ihtiyacı, koalalarda insanla neredeyse birebir aynı parmak izi kıvrımlarını oluşturmuştur.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
@@ -4951,12 +4948,12 @@
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>bilgidozu, flamingo, kuşlar, doğa, biyoloji, hayvanlaralemi, ilginçbilgiler, bilim, shorts, doz dışı</t>
+          <t>bilgidozu, koala, parmakizi, doğa, hayvanlaralemi, biyoloji, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>Flamingoların gri doğduğunu ve yedikleriyle pembeleştiğini biliyor muydun? 🦩🦐 Bilenler '1', yeni öğrenenler '2' yazsın! 👇</t>
+          <t>Koalaların parmak izinin insanla neredeyse birebir aynı olduğunu biliyor muydun? 🐨🔍 Duyanlar '1', ilk kez öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -4966,7 +4963,7 @@
       </c>
       <c r="I76" s="8" t="inlineStr">
         <is>
-          <t>San Diego Zoo — Flamingo Facts: https://animals.sandiegozoo.org/animals/flamingo</t>
+          <t>Wikipedia — Koala (Fingerprints): https://en.wikipedia.org/wiki/Koala</t>
         </is>
       </c>
       <c r="J76" s="8" t="n"/>
@@ -4982,43 +4979,43 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>video_49.mp4</t>
+          <t>video_50.mp4</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>Bu Hayvanın Parmak İzi İnsanla O Kadar Aynı ki Mikroskopta Bile Karışıyor! 🐨🔍 #bilgidozu #shorts</t>
+          <t>Mikrodalga Fırın Yemeği İçeriden Dışarıya Doğru Pişirmez! İşte Gerçek! ⚡🔬 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>Bir koalanın parmak izi insanınkine o kadar kusursuz benzer ki taramalı elektron mikroskobu altında bile ayırt etmek oldukça zordur! Evrimsel olarak bizden milyonlarca yıl önce ayrılmış olsalar da okaliptüs dallarını sıkıca kavrama ihtiyacı, koalalarda insanla neredeyse birebir aynı parmak izi kıvrımlarını oluşturmuştur.
+          <t>Mikrodalga fırının yemeği içeriden dışarıya doğru pişirdiği bilgisi tamamen bir şehir efsanesidir! Mikrodalgalar besinin dış yüzeyinden içeriye yalnızca birkaç santimetre nüfuz ederek su moleküllerini titreştirir; kalın yiyeceklerin en iç kısmı ise dış katmandan içeriye yayılan normal ısı iletimiyle ısınır.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>#bilgidozu #shorts #doğa #bilim #dozdışı</t>
+          <t>#bilgidozu #shorts #fizik #bilim #dozdışı</t>
         </is>
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>bilgidozu, koala, parmakizi, doğa, hayvanlaralemi, biyoloji, ilginçbilgiler, bilim, shorts, doz dışı</t>
+          <t>bilgidozu, mikrodalga, fizik, teknoloji, günlükhayat, efsaneavrı, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>Koalaların parmak izinin insanla neredeyse birebir aynı olduğunu biliyor muydun? 🐨🔍 Duyanlar '1', ilk kez öğrenenler '2' yazsın! 👇</t>
+          <t>Mikrodalganın yemeği içeriden dışarıya pişirdiğini sananlardan mıydın? ⚡🔬 Evet diyenler '1', gerçeği bilenler '2' yazsın! 👇</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>Doğa ve Hayvanlar</t>
+          <t>Fizik ve Bilim</t>
         </is>
       </c>
       <c r="I77" s="8" t="inlineStr">
         <is>
-          <t>Wikipedia — Koala (Fingerprints): https://en.wikipedia.org/wiki/Koala</t>
+          <t>FDA — Microwave Oven Radiation: https://www.fda.gov/radiation-emitting-products/resources-you-radiation-emitting-products/microwave-oven-radiation</t>
         </is>
       </c>
       <c r="J77" s="8" t="n"/>
@@ -5034,43 +5031,43 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>video_50.mp4</t>
+          <t>video_51.mp4</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>Mikrodalga Fırın Yemeği İçeriden Dışarıya Doğru Pişirmez! İşte Gerçek! ⚡🔬 #bilgidozu #shorts</t>
+          <t>Uzay Boşluk Olmasaydı Güneş'in Devasa Uğultusunu Dünya'dan Duyardık! ☀️🔊 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>Mikrodalga fırının yemeği içeriden dışarıya doğru pişirdiği bilgisi tamamen bir şehir efsanesidir! Mikrodalgalar besinin dış yüzeyinden içeriye yalnızca birkaç santimetre nüfuz ederek su moleküllerini titreştirir; kalın yiyeceklerin en iç kısmı ise dış katmandan içeriye yayılan normal ısı iletimiyle ısınır.
+          <t>Uzay boşluk olmasaydı, Güneş'in devasa uğultusunu Dünya'dan sürekli duyardık! Güneş yüzeyinin altındaki kaynayan dev plazma hücreleri sürekli yükselip çökerken muazzam ses dalgaları üretir; aradaki 150 milyon kilometrelik vakum sesi iletmediği için Dünya sessizdir, aksi halde gökyüzü kesintisiz bir motor gürültüsüyle çınlardı.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>#bilgidozu #shorts #fizik #bilim #dozdışı</t>
+          <t>#bilgidozu #shorts #uzay #bilim #dozdışı</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>bilgidozu, mikrodalga, fizik, teknoloji, günlükhayat, efsaneavrı, ilginçbilgiler, bilim, shorts, doz dışı</t>
+          <t>bilgidozu, güneş, uzay, ses, astronomi, fizik, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>Mikrodalganın yemeği içeriden dışarıya pişirdiğini sananlardan mıydın? ⚡🔬 Evet diyenler '1', gerçeği bilenler '2' yazsın! 👇</t>
+          <t>Uzayda hava olsaydı Güneş'in uğultusunu 150 milyon km öteden duyacağımızı biliyor muydun? ☀️🔊 Duyanlar '1', yeni öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>Fizik ve Bilim</t>
+          <t>Uzay ve Astronomi</t>
         </is>
       </c>
       <c r="I78" s="8" t="inlineStr">
         <is>
-          <t>FDA — Microwave Oven Radiation: https://www.fda.gov/radiation-emitting-products/resources-you-radiation-emitting-products/microwave-oven-radiation</t>
+          <t>ESA SOHO — Solar Interior Helioseismology: https://sci.esa.int/web/soho/-/30851-solar-interior</t>
         </is>
       </c>
       <c r="J78" s="8" t="n"/>
@@ -5086,43 +5083,43 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>video_51.mp4</t>
+          <t>video_53.mp4</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>Uzay Boşluk Olmasaydı Güneş'in Devasa Uğultusunu Dünya'dan Duyardık! ☀️🔊 #bilgidozu #shorts</t>
+          <t>Tutankhamun'un Mezarındaki Hançer Uzaydan Gelen Göktaşından Yapılmış! 🗡️☄️ #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>Uzay boşluk olmasaydı, Güneş'in devasa uğultusunu Dünya'dan sürekli duyardık! Güneş yüzeyinin altındaki kaynayan dev plazma hücreleri sürekli yükselip çökerken muazzam ses dalgaları üretir; aradaki 150 milyon kilometrelik vakum sesi iletmediği için Dünya sessizdir, aksi halde gökyüzü kesintisiz bir motor gürültüsüyle çınlardı.
+          <t>Mısır Firavunu Tutankhamun'un mezarında bulunan ünlü demir hançerin Dünya dışından gelen bir göktaşından dövüldüğü kanıtlandı! X-ışını analizleri, demir çağı başlamadan asırlar önce yapılan bu bıçakta yüksek oranda nikel ve kobalt bulunduğunu, yani firavunun hançerinin gerçekten uzaydan düşen bir meteoritten üretildiğini ortaya koydu.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>#bilgidozu #shorts #uzay #bilim #dozdışı</t>
+          <t>#bilgidozu #shorts #tarih #bilim #dozdışı</t>
         </is>
       </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>bilgidozu, güneş, uzay, ses, astronomi, fizik, ilginçbilgiler, bilim, shorts, doz dışı</t>
+          <t>bilgidozu, tutankhamun, mısır, göktaşı, tarih, arkeoloji, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>Uzayda hava olsaydı Güneş'in uğultusunu 150 milyon km öteden duyacağımızı biliyor muydun? ☀️🔊 Duyanlar '1', yeni öğrenenler '2' yazsın! 👇</t>
+          <t>Tutankhamun'un hançerinin uzaydan düşen bir göktaşından yapıldığını biliyor muydun? 🗡️☄️ Duyanlar '1', ilk kez öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
         <is>
-          <t>Uzay ve Astronomi</t>
+          <t>Tarih ve Arkeoloji</t>
         </is>
       </c>
       <c r="I79" s="8" t="inlineStr">
         <is>
-          <t>ESA SOHO — Solar Interior Helioseismology: https://sci.esa.int/web/soho/-/30851-solar-interior</t>
+          <t>Wikipedia — Tutankhamun's meteoric iron dagger: https://en.wikipedia.org/wiki/Tutankhamun%27s_meteoric_iron_dagger</t>
         </is>
       </c>
       <c r="J79" s="8" t="n"/>
@@ -5138,67 +5135,15 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>video_53.mp4</t>
+          <t>video_54.mp4</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>Tutankhamun'un Mezarındaki Hançer Uzaydan Gelen Göktaşından Yapılmış! 🗡️☄️ #bilgidozu #shorts</t>
+          <t>Koltuk Altındaki Gizli Cebinde Kendi Çekiç Taşını Taşıyan Hayvan! 🦦🪨 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
-        <is>
-          <t>Mısır Firavunu Tutankhamun'un mezarında bulunan ünlü demir hançerin Dünya dışından gelen bir göktaşından dövüldüğü kanıtlandı! X-ışını analizleri, demir çağı başlamadan asırlar önce yapılan bu bıçakta yüksek oranda nikel ve kobalt bulunduğunu, yani firavunun hançerinin gerçekten uzaydan düşen bir meteoritten üretildiğini ortaya koydu.
-Daha fazla bilgi dozu için takip etmeyi unutma!</t>
-        </is>
-      </c>
-      <c r="E80" s="8" t="inlineStr">
-        <is>
-          <t>#bilgidozu #shorts #tarih #bilim #dozdışı</t>
-        </is>
-      </c>
-      <c r="F80" s="8" t="inlineStr">
-        <is>
-          <t>bilgidozu, tutankhamun, mısır, göktaşı, tarih, arkeoloji, ilginçbilgiler, bilim, shorts, doz dışı</t>
-        </is>
-      </c>
-      <c r="G80" s="8" t="inlineStr">
-        <is>
-          <t>Tutankhamun'un hançerinin uzaydan düşen bir göktaşından yapıldığını biliyor muydun? 🗡️☄️ Duyanlar '1', ilk kez öğrenenler '2' yazsın! 👇</t>
-        </is>
-      </c>
-      <c r="H80" s="8" t="inlineStr">
-        <is>
-          <t>Tarih ve Arkeoloji</t>
-        </is>
-      </c>
-      <c r="I80" s="8" t="inlineStr">
-        <is>
-          <t>Wikipedia — Tutankhamun's meteoric iron dagger: https://en.wikipedia.org/wiki/Tutankhamun%27s_meteoric_iron_dagger</t>
-        </is>
-      </c>
-      <c r="J80" s="8" t="n"/>
-      <c r="K80" s="8" t="n"/>
-      <c r="L80" s="8" t="n"/>
-      <c r="M80" s="8" t="n"/>
-    </row>
-    <row r="81" ht="42" customHeight="1">
-      <c r="A81" s="7" t="inlineStr">
-        <is>
-          <t>ESKİ_STOK_ASKIDA</t>
-        </is>
-      </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>video_54.mp4</t>
-        </is>
-      </c>
-      <c r="C81" s="8" t="inlineStr">
-        <is>
-          <t>Koltuk Altındaki Gizli Cebinde Kendi Çekiç Taşını Taşıyan Hayvan! 🦦🪨 #bilgidozu #shorts</t>
-        </is>
-      </c>
-      <c r="D81" s="8" t="inlineStr">
         <is>
           <t>Deniz samurlarının koltuk altlarında gizli bir deri cebi olduğunu ve burada en sevdikleri taşı sakladıklarını biliyor muydun? Çoğu deniz memelisinin aksine kalın bir yağ tabakası olmayan bu canlılar, santimetrekarede 150.000 teli bulan dünyanın en yoğun kürküyle ısınır. Sol koltuk altlarındaki gevşek deri kesesini ise avladıkları kabukluları ve kendi çekiç taşlarını taşımak için kullanırlar.
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 👇
@@ -5208,29 +5153,81 @@
 #bilgidozu #shorts #doğa #hayvanlar #denizsamuru #bilim #ilginçbilgiler</t>
         </is>
       </c>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>bilgi dozu, shorts, deniz samuru, su samuru, koltuk altı cebi, alet kullanan hayvanlar, doğa ve hayvanlar, ilginç bilgiler, bilim #dozdışı</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #doğa, doz dışı</t>
+        </is>
+      </c>
+      <c r="G80" s="8" t="inlineStr">
+        <is>
+          <t>Deniz samurlarının koltuk altında kendi çekiç taşını taşıdığını daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🦦🪨👇</t>
+        </is>
+      </c>
+      <c r="H80" s="8" t="inlineStr">
+        <is>
+          <t>Doğa ve Hayvanlar</t>
+        </is>
+      </c>
+      <c r="I80" s="8" t="inlineStr">
+        <is>
+          <t>Wikipedia / MarineBio — Sea Otter Tool Use &amp; Fur Density: https://en.wikipedia.org/wiki/Sea_otter</t>
+        </is>
+      </c>
+      <c r="J80" s="8" t="n"/>
+      <c r="K80" s="8" t="n"/>
+      <c r="L80" s="8" t="n"/>
+      <c r="M80" s="8" t="n"/>
+    </row>
+    <row r="81" ht="42" customHeight="1">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>video_55.mp4</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>Uçak Pencerelerinin Altındaki O Minik Delik Neden Var? ✈️🪟 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>Uçak pencerelerinin alt kısmındaki o minik delik bir üretim hatası değil, hayat kurtaran bir mühendislik detayıdır! Üç ayrı akrilik katmandan oluşan uçak pencerelerinin ortadaki camında yer alan bu nefes deliği, yüksek irtifadaki dev basınç yükünü en dıştaki kalın cama aktarır ve camların buğulanıp buz tutmasını önler.
+Daha fazla bilgi dozu için takip etmeyi unutma!</t>
+        </is>
+      </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>bilgi dozu, shorts, deniz samuru, su samuru, koltuk altı cebi, alet kullanan hayvanlar, doğa ve hayvanlar, ilginç bilgiler, bilim #dozdışı</t>
+          <t>#bilgidozu #shorts #fizik #bilim #dozdışı</t>
         </is>
       </c>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>#bilgidozu #shorts #doğa, doz dışı</t>
+          <t>bilgidozu, uçak, havacılık, mühendislik, fizik, günlükhayat, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>Deniz samurlarının koltuk altında kendi çekiç taşını taşıdığını daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🦦🪨👇</t>
+          <t>Uçak camındaki o minik deliğin ne işe yaradığını daha önce merak etmiş miydin? ✈️🪟 Bilenler '1', yeni öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>Doğa ve Hayvanlar</t>
+          <t>Fizik ve Mühendislik</t>
         </is>
       </c>
       <c r="I81" s="8" t="inlineStr">
         <is>
-          <t>Wikipedia / MarineBio — Sea Otter Tool Use &amp; Fur Density: https://en.wikipedia.org/wiki/Sea_otter</t>
+          <t>Business Insider / FAA — Airplane Window Bleed Hole: https://www.businessinsider.com/airplane-windows-tiny-holes-2016-3</t>
         </is>
       </c>
       <c r="J81" s="8" t="n"/>
@@ -5246,43 +5243,43 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>video_55.mp4</t>
+          <t>video_56.mp4</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>Uçak Pencerelerinin Altındaki O Minik Delik Neden Var? ✈️🪟 #bilgidozu #shorts</t>
+          <t>Bir Kibrit Kutusu Kadar Parçası 3 Milyar Ton Çeken Yıldız! 🪐⚡ #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Uçak pencerelerinin alt kısmındaki o minik delik bir üretim hatası değil, hayat kurtaran bir mühendislik detayıdır! Üç ayrı akrilik katmandan oluşan uçak pencerelerinin ortadaki camında yer alan bu nefes deliği, yüksek irtifadaki dev basınç yükünü en dıştaki kalın cama aktarır ve camların buğulanıp buz tutmasını önler.
+          <t>Uzayda yalnızca bir kibrit kutusu büyüklüğündeki parçası Dünya'da tam 3 milyar ton ağırlığında çeken nötron yıldızları vardır! Dev bir yıldız süpernova olarak çöküp patladığında Güneş'ten fazla kütle 20 kilometre çapındaki bir küreye sıkışır ve atomların içindeki boşluk yok olarak bir kibrit kutusu madde 800 metrelik bir kaya dağı kadar ağırlaşır.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>#bilgidozu #shorts #fizik #bilim #dozdışı</t>
+          <t>#bilgidozu #shorts #uzay #bilim #dozdışı</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>bilgidozu, uçak, havacılık, mühendislik, fizik, günlükhayat, ilginçbilgiler, bilim, shorts, doz dışı</t>
+          <t>bilgidozu, nötronyıldızı, uzay, astronomi, astrofizik, evren, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>Uçak camındaki o minik deliğin ne işe yaradığını daha önce merak etmiş miydin? ✈️🪟 Bilenler '1', yeni öğrenenler '2' yazsın! 👇</t>
+          <t>Bir kibrit kutusu nötron yıldızı maddesinin Dünya'da 3 milyar ton çektiğini biliyor muydun? 🪐⚡ Duyanlar '1', ilk kez öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
       <c r="H82" s="8" t="inlineStr">
         <is>
-          <t>Fizik ve Mühendislik</t>
+          <t>Uzay ve Astronomi</t>
         </is>
       </c>
       <c r="I82" s="8" t="inlineStr">
         <is>
-          <t>Business Insider / FAA — Airplane Window Bleed Hole: https://www.businessinsider.com/airplane-windows-tiny-holes-2016-3</t>
+          <t>NASA / Wikipedia — Neutron Star: https://en.wikipedia.org/wiki/Neutron_star</t>
         </is>
       </c>
       <c r="J82" s="8" t="n"/>
@@ -5298,43 +5295,43 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>video_56.mp4</t>
+          <t>video_58.mp4</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>Bir Kibrit Kutusu Kadar Parçası 3 Milyar Ton Çeken Yıldız! 🪐⚡ #bilgidozu #shorts</t>
+          <t>Vezüv Patlamasında Beyni Gerçek Siyah Cama Dönüşen Romalı! 🌋🖤 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Uzayda yalnızca bir kibrit kutusu büyüklüğündeki parçası Dünya'da tam 3 milyar ton ağırlığında çeken nötron yıldızları vardır! Dev bir yıldız süpernova olarak çöküp patladığında Güneş'ten fazla kütle 20 kilometre çapındaki bir küreye sıkışır ve atomların içindeki boşluk yok olarak bir kibrit kutusu madde 800 metrelik bir kaya dağı kadar ağırlaşır.
+          <t>MS 79 yılındaki Vezüv Yanardağı patlamasında Herculaneum kentinde hayatını kaybeden genç bir Romalının beyninin aşırı sıcaklıktan gerçek siyah cama dönüştüğü kanıtlandı! 510 derecelik kavurucu kül bulutuyla saniyeler içinde ısınan ve hemen ardından hızla soğuyan beyin dokusu, nöron yapılarını bile koruyarak obsidyen benzeri cama dönüştü.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>#bilgidozu #shorts #uzay #bilim #dozdışı</t>
+          <t>#bilgidozu #shorts #tarih #bilim #dozdışı</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>bilgidozu, nötronyıldızı, uzay, astronomi, astrofizik, evren, ilginçbilgiler, bilim, shorts, doz dışı</t>
+          <t>bilgidozu, vezüv, herculaneum, pompeii, tarih, arkeoloji, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>Bir kibrit kutusu nötron yıldızı maddesinin Dünya'da 3 milyar ton çektiğini biliyor muydun? 🪐⚡ Duyanlar '1', ilk kez öğrenenler '2' yazsın! 👇</t>
+          <t>Vezüv patlamasında 510 derecelik kül bulutuyla bir insanın beyninin siyah cama dönüştüğünü biliyor muydun? 🌋🖤 Duyanlar '1', şaşıranlar '2' yazsın! 👇</t>
         </is>
       </c>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>Uzay ve Astronomi</t>
+          <t>Tarih ve Arkeoloji</t>
         </is>
       </c>
       <c r="I83" s="8" t="inlineStr">
         <is>
-          <t>NASA / Wikipedia — Neutron Star: https://en.wikipedia.org/wiki/Neutron_star</t>
+          <t>BBC / Scientific Reports — Herculaneum Glass Brain: https://www.bbc.com/news/articles/cgr2n8xx5gyo</t>
         </is>
       </c>
       <c r="J83" s="8" t="n"/>
@@ -5350,43 +5347,43 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>video_58.mp4</t>
+          <t>video_59.mp4</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>Vezüv Patlamasında Beyni Gerçek Siyah Cama Dönüşen Romalı! 🌋🖤 #bilgidozu #shorts</t>
+          <t>Bu Hayvan Su Altında Nefesini Yunuslardan 4 Kat Uzun Tutuyor! 🦥🌊 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>MS 79 yılındaki Vezüv Yanardağı patlamasında Herculaneum kentinde hayatını kaybeden genç bir Romalının beyninin aşırı sıcaklıktan gerçek siyah cama dönüştüğü kanıtlandı! 510 derecelik kavurucu kül bulutuyla saniyeler içinde ısınan ve hemen ardından hızla soğuyan beyin dokusu, nöron yapılarını bile koruyarak obsidyen benzeri cama dönüştü.
+          <t>Karada dünyanın en yavaş memelisi olan tembel hayvanlar, su altında nefesini yunuslardan bile 4 kat daha uzun tutabilir! Yunuslar yaklaşık 10 dakikada bir yüzeye çıkarken, tembel hayvanlar suya girdiklerinde kalp atış hızlarını normalin üçte birine düşürüp metabolizmalarını yavaşlatarak tam 40 dakika boyunca nefes almadan kalabilir.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>#bilgidozu #shorts #tarih #bilim #dozdışı</t>
+          <t>#bilgidozu #shorts #doğa #bilim #dozdışı</t>
         </is>
       </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t>bilgidozu, vezüv, herculaneum, pompeii, tarih, arkeoloji, ilginçbilgiler, bilim, shorts, doz dışı</t>
+          <t>bilgidozu, tembelhayvan, yunus, doğa, hayvanlaralemi, biyoloji, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>Vezüv patlamasında 510 derecelik kül bulutuyla bir insanın beyninin siyah cama dönüştüğünü biliyor muydun? 🌋🖤 Duyanlar '1', şaşıranlar '2' yazsın! 👇</t>
+          <t>Tembel hayvanların su altında nefesini 40 dakika tutarak yunusları bile geçtiğini biliyor muydun? 🦥🌊 Duyanlar '1', ilk kez öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>Tarih ve Arkeoloji</t>
+          <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
       <c r="I84" s="8" t="inlineStr">
         <is>
-          <t>BBC / Scientific Reports — Herculaneum Glass Brain: https://www.bbc.com/news/articles/cgr2n8xx5gyo</t>
+          <t>BBC Bitesize — Sloths Hold Breath 40 Minutes: https://www.bbc.co.uk/bitesize/articles/zqk4qyc</t>
         </is>
       </c>
       <c r="J84" s="8" t="n"/>
@@ -5402,43 +5399,43 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>video_59.mp4</t>
+          <t>video_60.mp4</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>Bu Hayvan Su Altında Nefesini Yunuslardan 4 Kat Uzun Tutuyor! 🦥🌊 #bilgidozu #shorts</t>
+          <t>Araba Ön Camlarındaki Siyah Noktalar Neden Var? Süs Değilmiş! 🚗⚫ #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>Karada dünyanın en yavaş memelisi olan tembel hayvanlar, su altında nefesini yunuslardan bile 4 kat daha uzun tutabilir! Yunuslar yaklaşık 10 dakikada bir yüzeye çıkarken, tembel hayvanlar suya girdiklerinde kalp atış hızlarını normalin üçte birine düşürüp metabolizmalarını yavaşlatarak tam 40 dakika boyunca nefes almadan kalabilir.
+          <t>Araba ön camlarının kenarındaki siyah şerit (frit bandı) ve küçülerek dağılan siyah noktalar süs değil, kritik bir mühendislik kalkanıdır! Cama fırınlanan bu seramik katman, camı gövdeye bağlayan yapıştırıcıyı güneşin morötesi ışınlarından korurken, siyah noktalar cam yüksek ısıda bükülürken sıcaklığı eşit dağıtarak optik bozulmayı önler.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>#bilgidozu #shorts #doğa #bilim #dozdışı</t>
+          <t>#bilgidozu #shorts #fizik #bilim #dozdışı</t>
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>bilgidozu, tembelhayvan, yunus, doğa, hayvanlaralemi, biyoloji, ilginçbilgiler, bilim, shorts, doz dışı</t>
+          <t>bilgidozu, araba, otomobil, mühendislik, fizik, günlükhayat, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t>Tembel hayvanların su altında nefesini 40 dakika tutarak yunusları bile geçtiğini biliyor muydun? 🦥🌊 Duyanlar '1', ilk kez öğrenenler '2' yazsın! 👇</t>
+          <t>Araba camlarının kenarındaki siyah noktaların yapıştırıcıyı güneşten koruduğunu biliyor muydun? 🚗⚫ Duyanlar '1', yeni öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
       <c r="H85" s="8" t="inlineStr">
         <is>
-          <t>Doğa ve Hayvanlar</t>
+          <t>Fizik ve Mühendislik</t>
         </is>
       </c>
       <c r="I85" s="8" t="inlineStr">
         <is>
-          <t>BBC Bitesize — Sloths Hold Breath 40 Minutes: https://www.bbc.co.uk/bitesize/articles/zqk4qyc</t>
+          <t>Jalopnik / Pilkington — Windshield Frit Dots: https://www.jalopnik.com/heres-what-those-little-dots-are-on-the-edges-of-your-c-1791075995/</t>
         </is>
       </c>
       <c r="J85" s="8" t="n"/>
@@ -5454,67 +5451,15 @@
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>video_60.mp4</t>
+          <t>video_61.mp4</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>Araba Ön Camlarındaki Siyah Noktalar Neden Var? Süs Değilmiş! 🚗⚫ #bilgidozu #shorts</t>
+          <t>Tepesinden Atlayınca Dibe Düşmenin 12 Dakika Sürdüğü 20 Km'lik Uçurum! 🪐🧗 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
-        <is>
-          <t>Araba ön camlarının kenarındaki siyah şerit (frit bandı) ve küçülerek dağılan siyah noktalar süs değil, kritik bir mühendislik kalkanıdır! Cama fırınlanan bu seramik katman, camı gövdeye bağlayan yapıştırıcıyı güneşin morötesi ışınlarından korurken, siyah noktalar cam yüksek ısıda bükülürken sıcaklığı eşit dağıtarak optik bozulmayı önler.
-Daha fazla bilgi dozu için takip etmeyi unutma!</t>
-        </is>
-      </c>
-      <c r="E86" s="8" t="inlineStr">
-        <is>
-          <t>#bilgidozu #shorts #fizik #bilim #dozdışı</t>
-        </is>
-      </c>
-      <c r="F86" s="8" t="inlineStr">
-        <is>
-          <t>bilgidozu, araba, otomobil, mühendislik, fizik, günlükhayat, ilginçbilgiler, bilim, shorts, doz dışı</t>
-        </is>
-      </c>
-      <c r="G86" s="8" t="inlineStr">
-        <is>
-          <t>Araba camlarının kenarındaki siyah noktaların yapıştırıcıyı güneşten koruduğunu biliyor muydun? 🚗⚫ Duyanlar '1', yeni öğrenenler '2' yazsın! 👇</t>
-        </is>
-      </c>
-      <c r="H86" s="8" t="inlineStr">
-        <is>
-          <t>Fizik ve Mühendislik</t>
-        </is>
-      </c>
-      <c r="I86" s="8" t="inlineStr">
-        <is>
-          <t>Jalopnik / Pilkington — Windshield Frit Dots: https://www.jalopnik.com/heres-what-those-little-dots-are-on-the-edges-of-your-c-1791075995/</t>
-        </is>
-      </c>
-      <c r="J86" s="8" t="n"/>
-      <c r="K86" s="8" t="n"/>
-      <c r="L86" s="8" t="n"/>
-      <c r="M86" s="8" t="n"/>
-    </row>
-    <row r="87" ht="42" customHeight="1">
-      <c r="A87" s="7" t="inlineStr">
-        <is>
-          <t>ESKİ_STOK_ASKIDA</t>
-        </is>
-      </c>
-      <c r="B87" s="7" t="inlineStr">
-        <is>
-          <t>video_61.mp4</t>
-        </is>
-      </c>
-      <c r="C87" s="8" t="inlineStr">
-        <is>
-          <t>Tepesinden Atlayınca Dibe Düşmenin 12 Dakika Sürdüğü 20 Km'lik Uçurum! 🪐🧗 #bilgidozu #shorts</t>
-        </is>
-      </c>
-      <c r="D87" s="8" t="inlineStr">
         <is>
           <t>Tepesinden atladığında yere çarpmanın tam 12 dakika sürdüğü devasa bir uçurum olduğunu biliyor muydun? Uranüs'ün uydusu Miranda üzerindeki 20 km'lik Verona Rupes uçurumunu inceliyoruz.
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -5523,53 +5468,53 @@
 #bilgidozu #shorts #uzay #miranda #bilim</t>
         </is>
       </c>
-      <c r="E87" s="8" t="inlineStr">
+      <c r="E86" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #miranda #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F87" s="8" t="inlineStr">
+      <c r="F86" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, verona rupes, miranda, uranüs, uzay, astronomi, uçurum, nasa, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G87" s="8" t="inlineStr">
+      <c r="G86" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🪐🧗</t>
         </is>
       </c>
-      <c r="H87" s="8" t="inlineStr">
+      <c r="H86" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I87" s="8" t="inlineStr">
+      <c r="I86" s="8" t="inlineStr">
         <is>
           <t>NASA Voyager 2 / USGS Astrogeology — Verona Rupes: https://en.wikipedia.org/wiki/Verona_Rupes</t>
         </is>
       </c>
-      <c r="J87" s="8" t="n"/>
-      <c r="K87" s="8" t="n"/>
-      <c r="L87" s="8" t="n"/>
-      <c r="M87" s="8" t="n"/>
-    </row>
-    <row r="88" ht="42" customHeight="1">
-      <c r="A88" s="7" t="inlineStr">
+      <c r="J86" s="8" t="n"/>
+      <c r="K86" s="8" t="n"/>
+      <c r="L86" s="8" t="n"/>
+      <c r="M86" s="8" t="n"/>
+    </row>
+    <row r="87" ht="42" customHeight="1">
+      <c r="A87" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B88" s="7" t="inlineStr">
+      <c r="B87" s="7" t="inlineStr">
         <is>
           <t>video_63.mp4</t>
         </is>
       </c>
-      <c r="C88" s="8" t="inlineStr">
+      <c r="C87" s="8" t="inlineStr">
         <is>
           <t>Harç ve Çimento Olmadan Depremde Yıkılmayan 500 Yıllık İnka Duvarları! 🏛️🪨 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D88" s="8" t="inlineStr">
+      <c r="D87" s="8" t="inlineStr">
         <is>
           <t>İnkaların 500 yıl önce tek damla harç veya çimento kullanmadan yaptığı taş duvarların büyük depremlerde bile neden yıkılmadığını biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -5578,53 +5523,53 @@
 #bilgidozu #shorts #tarih #inka #arkeoloji</t>
         </is>
       </c>
-      <c r="E88" s="8" t="inlineStr">
+      <c r="E87" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #inka #arkeoloji #dozdışı</t>
         </is>
       </c>
-      <c r="F88" s="8" t="inlineStr">
+      <c r="F87" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, inka duvarları, deprem, cusco, tarih, arkeoloji, mühendislik, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G88" s="8" t="inlineStr">
+      <c r="G87" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🏛️🪨</t>
         </is>
       </c>
-      <c r="H88" s="8" t="inlineStr">
+      <c r="H87" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Arkeoloji</t>
         </is>
       </c>
-      <c r="I88" s="8" t="inlineStr">
+      <c r="I87" s="8" t="inlineStr">
         <is>
           <t>UNESCO World Heritage Cusco / Inca Architecture: https://en.wikipedia.org/wiki/Inca_architecture</t>
         </is>
       </c>
-      <c r="J88" s="8" t="n"/>
-      <c r="K88" s="8" t="n"/>
-      <c r="L88" s="8" t="n"/>
-      <c r="M88" s="8" t="n"/>
-    </row>
-    <row r="89" ht="42" customHeight="1">
-      <c r="A89" s="7" t="inlineStr">
+      <c r="J87" s="8" t="n"/>
+      <c r="K87" s="8" t="n"/>
+      <c r="L87" s="8" t="n"/>
+      <c r="M87" s="8" t="n"/>
+    </row>
+    <row r="88" ht="42" customHeight="1">
+      <c r="A88" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B89" s="7" t="inlineStr">
+      <c r="B88" s="7" t="inlineStr">
         <is>
           <t>video_64.mp4</t>
         </is>
       </c>
-      <c r="C89" s="8" t="inlineStr">
+      <c r="C88" s="8" t="inlineStr">
         <is>
           <t>Baykuşlar Karanlıkta Uçarken Nasıl Sıfır Ses Çıkarır? Hayalet Kanat Sırrı! 🦉🌙 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D89" s="8" t="inlineStr">
+      <c r="D88" s="8" t="inlineStr">
         <is>
           <t>Diğer bütün kuşlar kanat çırparken hışırtı çıkarırken baykuşların zifiri karanlıkta tamamen sessiz uçabildiğini biliyor muydun? Üçlü akustik susturucu kanat yapısını inceliyoruz.
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -5633,53 +5578,53 @@
 #bilgidozu #shorts #baykuş #doğa #hayvanlar</t>
         </is>
       </c>
-      <c r="E89" s="8" t="inlineStr">
+      <c r="E88" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #baykuş #doğa #hayvanlar #dozdışı</t>
         </is>
       </c>
-      <c r="F89" s="8" t="inlineStr">
+      <c r="F88" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, baykuş, sessiz uçuş, doğa, hayvanlar, aerodinamik, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G89" s="8" t="inlineStr">
+      <c r="G88" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🦉🌙</t>
         </is>
       </c>
-      <c r="H89" s="8" t="inlineStr">
+      <c r="H88" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I89" s="8" t="inlineStr">
+      <c r="I88" s="8" t="inlineStr">
         <is>
           <t>Royal Society Interface / Owl Silent Flight: https://en.wikipedia.org/wiki/Owl</t>
         </is>
       </c>
-      <c r="J89" s="8" t="n"/>
-      <c r="K89" s="8" t="n"/>
-      <c r="L89" s="8" t="n"/>
-      <c r="M89" s="8" t="n"/>
-    </row>
-    <row r="90" ht="42" customHeight="1">
-      <c r="A90" s="7" t="inlineStr">
+      <c r="J88" s="8" t="n"/>
+      <c r="K88" s="8" t="n"/>
+      <c r="L88" s="8" t="n"/>
+      <c r="M88" s="8" t="n"/>
+    </row>
+    <row r="89" ht="42" customHeight="1">
+      <c r="A89" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B90" s="7" t="inlineStr">
+      <c r="B89" s="7" t="inlineStr">
         <is>
           <t>video_65.mp4</t>
         </is>
       </c>
-      <c r="C90" s="8" t="inlineStr">
+      <c r="C89" s="8" t="inlineStr">
         <is>
           <t>Tükenmez Kalem Kapağındaki O Küçük Delik Neden Hayat Kurtarır? 🖊️⚡ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D90" s="8" t="inlineStr">
+      <c r="D89" s="8" t="inlineStr">
         <is>
           <t>Tükenmez kalemlerin kapağındaki o küçük deliğin mürekkep kurumasın diye değil, hayat kurtarmak için açıldığını biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -5688,53 +5633,53 @@
 #bilgidozu #shorts #ilginçbilgiler #tasarım #bilim</t>
         </is>
       </c>
-      <c r="E90" s="8" t="inlineStr">
+      <c r="E89" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #ilginçbilgiler #tasarım #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F90" s="8" t="inlineStr">
+      <c r="F89" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, tükenmez kalem kapağı, bic cristal, güvenlik deliği, günlük bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G90" s="8" t="inlineStr">
+      <c r="G89" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🖊️⚡</t>
         </is>
       </c>
-      <c r="H90" s="8" t="inlineStr">
+      <c r="H89" s="8" t="inlineStr">
         <is>
           <t>Fizik ve Mühendislik</t>
         </is>
       </c>
-      <c r="I90" s="8" t="inlineStr">
+      <c r="I89" s="8" t="inlineStr">
         <is>
           <t>ISO 11540 / BIC Cristal Safety Design: https://en.wikipedia.org/wiki/Bic_Cristal</t>
         </is>
       </c>
-      <c r="J90" s="8" t="n"/>
-      <c r="K90" s="8" t="n"/>
-      <c r="L90" s="8" t="n"/>
-      <c r="M90" s="8" t="n"/>
-    </row>
-    <row r="91" ht="42" customHeight="1">
-      <c r="A91" s="7" t="inlineStr">
+      <c r="J89" s="8" t="n"/>
+      <c r="K89" s="8" t="n"/>
+      <c r="L89" s="8" t="n"/>
+      <c r="M89" s="8" t="n"/>
+    </row>
+    <row r="90" ht="42" customHeight="1">
+      <c r="A90" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B91" s="7" t="inlineStr">
+      <c r="B90" s="7" t="inlineStr">
         <is>
           <t>video_66.mp4</t>
         </is>
       </c>
-      <c r="C91" s="8" t="inlineStr">
+      <c r="C90" s="8" t="inlineStr">
         <is>
           <t>Su Değil Sert Kaya Zemini Her Gün 100 Metre Yükselip Alçalan Uydu! 🪐🌋 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D91" s="8" t="inlineStr">
+      <c r="D90" s="8" t="inlineStr">
         <is>
           <t>Dünya'da okyanus suları yükselip alçalırken, Jüpiter'in uydusu İo'da suyun değil doğrudan sert kaya zeminin her gün 100 metre yükselip alçaldığını biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -5743,53 +5688,53 @@
 #bilgidozu #shorts #uzay #jüpiter #bilim</t>
         </is>
       </c>
-      <c r="E91" s="8" t="inlineStr">
+      <c r="E90" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #jüpiter #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F91" s="8" t="inlineStr">
+      <c r="F90" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, io uydusu, jüpiter, kaya gelgiti, yanardağ, uzay, astronomi, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G91" s="8" t="inlineStr">
+      <c r="G90" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🪐🌋</t>
         </is>
       </c>
-      <c r="H91" s="8" t="inlineStr">
+      <c r="H90" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I91" s="8" t="inlineStr">
+      <c r="I90" s="8" t="inlineStr">
         <is>
           <t>NASA Juno &amp; Galileo Mission / Io Facts: https://science.nasa.gov/jupiter/moons/io/</t>
         </is>
       </c>
-      <c r="J91" s="8" t="n"/>
-      <c r="K91" s="8" t="n"/>
-      <c r="L91" s="8" t="n"/>
-      <c r="M91" s="8" t="n"/>
-    </row>
-    <row r="92" ht="42" customHeight="1">
-      <c r="A92" s="7" t="inlineStr">
+      <c r="J90" s="8" t="n"/>
+      <c r="K90" s="8" t="n"/>
+      <c r="L90" s="8" t="n"/>
+      <c r="M90" s="8" t="n"/>
+    </row>
+    <row r="91" ht="42" customHeight="1">
+      <c r="A91" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B92" s="7" t="inlineStr">
+      <c r="B91" s="7" t="inlineStr">
         <is>
           <t>video_68.mp4</t>
         </is>
       </c>
-      <c r="C92" s="8" t="inlineStr">
+      <c r="C91" s="8" t="inlineStr">
         <is>
           <t>2000 Yıllık Deniz Batığından Çıkan Dünyanın İlk Mekanik Bilgisayarı! ⚙️🏛️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D92" s="8" t="inlineStr">
+      <c r="D91" s="8" t="inlineStr">
         <is>
           <t>İki bin yıl önce batan bir antik Yunan gemisinden dünyanın ilk mekanik bilgisayarının (Antikythera Düzeneği) çıktığını biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -5798,53 +5743,53 @@
 #bilgidozu #shorts #tarih #arkeoloji #bilim</t>
         </is>
       </c>
-      <c r="E92" s="8" t="inlineStr">
+      <c r="E91" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #arkeoloji #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F92" s="8" t="inlineStr">
+      <c r="F91" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, antikythera düzeneği, antik bilgisayar, tarih, arkeoloji, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G92" s="8" t="inlineStr">
+      <c r="G91" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! ⚙️🏛️</t>
         </is>
       </c>
-      <c r="H92" s="8" t="inlineStr">
+      <c r="H91" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Arkeoloji</t>
         </is>
       </c>
-      <c r="I92" s="8" t="inlineStr">
+      <c r="I91" s="8" t="inlineStr">
         <is>
           <t>Nature / UCL Antikythera Research Team: https://www.nature.com/articles/s41598-021-84310-w</t>
         </is>
       </c>
-      <c r="J92" s="8" t="n"/>
-      <c r="K92" s="8" t="n"/>
-      <c r="L92" s="8" t="n"/>
-      <c r="M92" s="8" t="n"/>
-    </row>
-    <row r="93" ht="42" customHeight="1">
-      <c r="A93" s="7" t="inlineStr">
+      <c r="J91" s="8" t="n"/>
+      <c r="K91" s="8" t="n"/>
+      <c r="L91" s="8" t="n"/>
+      <c r="M91" s="8" t="n"/>
+    </row>
+    <row r="92" ht="42" customHeight="1">
+      <c r="A92" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B93" s="7" t="inlineStr">
+      <c r="B92" s="7" t="inlineStr">
         <is>
           <t>video_69.mp4</t>
         </is>
       </c>
-      <c r="C93" s="8" t="inlineStr">
+      <c r="C92" s="8" t="inlineStr">
         <is>
           <t>70 Derece Çölde Yuvasını Adımlarını Sayarak Bulan Gümüş Karınca! 🐜☀️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D93" s="8" t="inlineStr">
+      <c r="D92" s="8" t="inlineStr">
         <is>
           <t>70 derece sıcaklıktaki Sahra Çölü'nde yaşayan gümüş karıncaların yuvalarını adımlarını sayarak (pedometre) bulduğunu biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -5853,53 +5798,53 @@
 #bilgidozu #shorts #doğa #karınca #hayvanlar</t>
         </is>
       </c>
-      <c r="E93" s="8" t="inlineStr">
+      <c r="E92" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #karınca #hayvanlar #dozdışı</t>
         </is>
       </c>
-      <c r="F93" s="8" t="inlineStr">
+      <c r="F92" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, sahra çöl karıncası, adım sayar, doğa, hayvanlar, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G93" s="8" t="inlineStr">
+      <c r="G92" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🐜☀️</t>
         </is>
       </c>
-      <c r="H93" s="8" t="inlineStr">
+      <c r="H92" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I93" s="8" t="inlineStr">
+      <c r="I92" s="8" t="inlineStr">
         <is>
           <t>Science (2006) — Wittlinger et al.: https://www.science.org/doi/10.1126/science.1126912</t>
         </is>
       </c>
-      <c r="J93" s="8" t="n"/>
-      <c r="K93" s="8" t="n"/>
-      <c r="L93" s="8" t="n"/>
-      <c r="M93" s="8" t="n"/>
-    </row>
-    <row r="94" ht="42" customHeight="1">
-      <c r="A94" s="7" t="inlineStr">
+      <c r="J92" s="8" t="n"/>
+      <c r="K92" s="8" t="n"/>
+      <c r="L92" s="8" t="n"/>
+      <c r="M92" s="8" t="n"/>
+    </row>
+    <row r="93" ht="42" customHeight="1">
+      <c r="A93" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B94" s="7" t="inlineStr">
+      <c r="B93" s="7" t="inlineStr">
         <is>
           <t>video_70.mp4</t>
         </is>
       </c>
-      <c r="C94" s="8" t="inlineStr">
+      <c r="C93" s="8" t="inlineStr">
         <is>
           <t>Benzin Pompası Depo Dolunca Çipsiz ve Sensörsüz Nasıl Kendi Durur? ⛽⚡ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D94" s="8" t="inlineStr">
+      <c r="D93" s="8" t="inlineStr">
         <is>
           <t>Benzin istasyonlarındaki pompa tabancasının deponun tam dolduğunu içinde hiçbir kamera, çip veya elektrikli sensör olmadan nasıl anladığını biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -5908,53 +5853,53 @@
 #bilgidozu #shorts #fizik #mühendislik #bilim</t>
         </is>
       </c>
-      <c r="E94" s="8" t="inlineStr">
+      <c r="E93" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #fizik #mühendislik #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F94" s="8" t="inlineStr">
+      <c r="F93" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, benzin pompası, venturi etkisi, fizik, mühendislik, günlük bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G94" s="8" t="inlineStr">
+      <c r="G93" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! ⛽⚡</t>
         </is>
       </c>
-      <c r="H94" s="8" t="inlineStr">
+      <c r="H93" s="8" t="inlineStr">
         <is>
           <t>Fizik ve Mühendislik</t>
         </is>
       </c>
-      <c r="I94" s="8" t="inlineStr">
+      <c r="I93" s="8" t="inlineStr">
         <is>
           <t>PEI / Automatic Shut-Off Nozzle: https://pei.org/wiki_pei/automatic-nozzle/</t>
         </is>
       </c>
-      <c r="J94" s="8" t="n"/>
-      <c r="K94" s="8" t="n"/>
-      <c r="L94" s="8" t="n"/>
-      <c r="M94" s="8" t="n"/>
-    </row>
-    <row r="95" ht="42" customHeight="1">
-      <c r="A95" s="7" t="inlineStr">
+      <c r="J93" s="8" t="n"/>
+      <c r="K93" s="8" t="n"/>
+      <c r="L93" s="8" t="n"/>
+      <c r="M93" s="8" t="n"/>
+    </row>
+    <row r="94" ht="42" customHeight="1">
+      <c r="A94" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B95" s="7" t="inlineStr">
+      <c r="B94" s="7" t="inlineStr">
         <is>
           <t>video_71.mp4</t>
         </is>
       </c>
-      <c r="C95" s="8" t="inlineStr">
+      <c r="C94" s="8" t="inlineStr">
         <is>
           <t>Satürn'ün Kuzey Kutbundaki Dev Altıgen Fırtınanın Sırrı! 🪐🌪️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D95" s="8" t="inlineStr">
+      <c r="D94" s="8" t="inlineStr">
         <is>
           <t>Satürn gezegeninin kuzey kutbunda içine iki tane Dünya sığacak büyüklükte kusursuz bir altıgen fırtına döndüğünü biliyor muydun? 32.000 kilometrelik bu dev geometrik fırtınanın sırrını inceliyoruz.
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -5963,53 +5908,53 @@
 #bilgidozu #shorts #uzay #satürn #bilim</t>
         </is>
       </c>
-      <c r="E95" s="8" t="inlineStr">
+      <c r="E94" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #satürn #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F95" s="8" t="inlineStr">
+      <c r="F94" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, satürn, altıgen fırtına, uzay, astronomi, nasa, cassini, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G95" s="8" t="inlineStr">
+      <c r="G94" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🪐🌪️</t>
         </is>
       </c>
-      <c r="H95" s="8" t="inlineStr">
+      <c r="H94" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I95" s="8" t="inlineStr">
+      <c r="I94" s="8" t="inlineStr">
         <is>
           <t>NASA Cassini Mission / JPL: https://science.nasa.gov/mission/cassini/</t>
         </is>
       </c>
-      <c r="J95" s="8" t="n"/>
-      <c r="K95" s="8" t="n"/>
-      <c r="L95" s="8" t="n"/>
-      <c r="M95" s="8" t="n"/>
-    </row>
-    <row r="96" ht="42" customHeight="1">
-      <c r="A96" s="7" t="inlineStr">
+      <c r="J94" s="8" t="n"/>
+      <c r="K94" s="8" t="n"/>
+      <c r="L94" s="8" t="n"/>
+      <c r="M94" s="8" t="n"/>
+    </row>
+    <row r="95" ht="42" customHeight="1">
+      <c r="A95" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B96" s="7" t="inlineStr">
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>video_73.mp4</t>
         </is>
       </c>
-      <c r="C96" s="8" t="inlineStr">
+      <c r="C95" s="8" t="inlineStr">
         <is>
           <t>Efsanevi Şam Çeliği Kılıçların İçinden Karbon Nanotüp Çıktı! ⚔️🔬 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D96" s="8" t="inlineStr">
+      <c r="D95" s="8" t="inlineStr">
         <is>
           <t>Yüzyıllar önce üretilen efsanevi Şam çeliği kılıçların içinde modern bilimin ancak elektron mikroskobuyla görebildiği karbon nanotüpler bulunduğunu biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -6018,53 +5963,53 @@
 #bilgidozu #shorts #tarih #bilim #teknoloji</t>
         </is>
       </c>
-      <c r="E96" s="8" t="inlineStr">
+      <c r="E95" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #bilim #teknoloji #dozdışı</t>
         </is>
       </c>
-      <c r="F96" s="8" t="inlineStr">
+      <c r="F95" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, şam çeliği, karbon nanotüp, tarih, kılıç, bilim, mühendislik, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G96" s="8" t="inlineStr">
+      <c r="G95" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! ⚔️🔬</t>
         </is>
       </c>
-      <c r="H96" s="8" t="inlineStr">
+      <c r="H95" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Arkeoloji</t>
         </is>
       </c>
-      <c r="I96" s="8" t="inlineStr">
+      <c r="I95" s="8" t="inlineStr">
         <is>
           <t>Nature (2006) — Reibold et al., TU Dresden: https://www.nature.com/articles/444286a</t>
         </is>
       </c>
-      <c r="J96" s="8" t="n"/>
-      <c r="K96" s="8" t="n"/>
-      <c r="L96" s="8" t="n"/>
-      <c r="M96" s="8" t="n"/>
-    </row>
-    <row r="97" ht="42" customHeight="1">
-      <c r="A97" s="7" t="inlineStr">
+      <c r="J95" s="8" t="n"/>
+      <c r="K95" s="8" t="n"/>
+      <c r="L95" s="8" t="n"/>
+      <c r="M95" s="8" t="n"/>
+    </row>
+    <row r="96" ht="42" customHeight="1">
+      <c r="A96" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B97" s="7" t="inlineStr">
+      <c r="B96" s="7" t="inlineStr">
         <is>
           <t>video_74.mp4</t>
         </is>
       </c>
-      <c r="C97" s="8" t="inlineStr">
+      <c r="C96" s="8" t="inlineStr">
         <is>
           <t>Işığın Kırılmasını Hesaplayıp Böceği Suyla Vuran Keskin Nişancı Balık! 🐟🎯 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D97" s="8" t="inlineStr">
+      <c r="D96" s="8" t="inlineStr">
         <is>
           <t>Suyun altından dışarıdaki bir böceğe su fırlatarak tam on ikiden vuran okçu balığının ışığın kırılmasını nasıl hesapladığını biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -6073,53 +6018,53 @@
 #bilgidozu #shorts #doğa #hayvanlar #bilim</t>
         </is>
       </c>
-      <c r="E97" s="8" t="inlineStr">
+      <c r="E96" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #hayvanlar #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F97" s="8" t="inlineStr">
+      <c r="F96" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, okçu balığı, doğa, hayvanlar, optik kırılma, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G97" s="8" t="inlineStr">
+      <c r="G96" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🐟🎯</t>
         </is>
       </c>
-      <c r="H97" s="8" t="inlineStr">
+      <c r="H96" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I97" s="8" t="inlineStr">
+      <c r="I96" s="8" t="inlineStr">
         <is>
           <t>PLOS ONE (2012) — Vailati et al. (Archerfish Water Jet): https://journals.plos.org/plosone/article?id=10.1371/journal.pone.0047867</t>
         </is>
       </c>
-      <c r="J97" s="8" t="n"/>
-      <c r="K97" s="8" t="n"/>
-      <c r="L97" s="8" t="n"/>
-      <c r="M97" s="8" t="n"/>
-    </row>
-    <row r="98" ht="42" customHeight="1">
-      <c r="A98" s="7" t="inlineStr">
+      <c r="J96" s="8" t="n"/>
+      <c r="K96" s="8" t="n"/>
+      <c r="L96" s="8" t="n"/>
+      <c r="M96" s="8" t="n"/>
+    </row>
+    <row r="97" ht="42" customHeight="1">
+      <c r="A97" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B98" s="7" t="inlineStr">
+      <c r="B97" s="7" t="inlineStr">
         <is>
           <t>video_75.mp4</t>
         </is>
       </c>
-      <c r="C98" s="8" t="inlineStr">
+      <c r="C97" s="8" t="inlineStr">
         <is>
           <t>Mikrodalga Fırın Camındaki Delikli Siyah Tel Neden Var? ⚡🪟 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D98" s="8" t="inlineStr">
+      <c r="D97" s="8" t="inlineStr">
         <is>
           <t>Mikrodalga fırınların ön camındaki o siyah delikli metal ızgaranın içeriyi görmen için değil, seni radyasyondan korumak için konulduğunu biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -6128,53 +6073,53 @@
 #bilgidozu #shorts #fizik #teknoloji #bilim</t>
         </is>
       </c>
-      <c r="E98" s="8" t="inlineStr">
+      <c r="E97" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #fizik #teknoloji #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F98" s="8" t="inlineStr">
+      <c r="F97" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, mikrodalga fırın, faraday kafesi, fizik, günlük bilim, mühendislik, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G98" s="8" t="inlineStr">
+      <c r="G97" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! ⚡🪟</t>
         </is>
       </c>
-      <c r="H98" s="8" t="inlineStr">
+      <c r="H97" s="8" t="inlineStr">
         <is>
           <t>Fizik ve Mühendislik</t>
         </is>
       </c>
-      <c r="I98" s="8" t="inlineStr">
+      <c r="I97" s="8" t="inlineStr">
         <is>
           <t>IEEE Electromagnetic Shielding / Wikipedia — Faraday Cage: https://en.wikipedia.org/wiki/Faraday_cage</t>
         </is>
       </c>
-      <c r="J98" s="8" t="n"/>
-      <c r="K98" s="8" t="n"/>
-      <c r="L98" s="8" t="n"/>
-      <c r="M98" s="8" t="n"/>
-    </row>
-    <row r="99" ht="42" customHeight="1">
-      <c r="A99" s="7" t="inlineStr">
+      <c r="J97" s="8" t="n"/>
+      <c r="K97" s="8" t="n"/>
+      <c r="L97" s="8" t="n"/>
+      <c r="M97" s="8" t="n"/>
+    </row>
+    <row r="98" ht="42" customHeight="1">
+      <c r="A98" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B99" s="7" t="inlineStr">
+      <c r="B98" s="7" t="inlineStr">
         <is>
           <t>video_76.mp4</t>
         </is>
       </c>
-      <c r="C99" s="8" t="inlineStr">
+      <c r="C98" s="8" t="inlineStr">
         <is>
           <t>Uzayda Ses Yayılsaydı Güneş Dünya'dan 100 Desibel Tren Gibi Gürlerdi! ☀️🔊 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D99" s="8" t="inlineStr">
+      <c r="D98" s="8" t="inlineStr">
         <is>
           <t>Uzayda ses yayılmadığı için çok şanslı olduğumuzu, yoksa Güneş'in 150 milyon kilometre öteden bile 100 desibel şiddetinde gürleyeceğini biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -6183,53 +6128,53 @@
 #bilgidozu #shorts #uzay #güneş #bilim</t>
         </is>
       </c>
-      <c r="E99" s="8" t="inlineStr">
+      <c r="E98" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #güneş #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F99" s="8" t="inlineStr">
+      <c r="F98" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, güneşin sesi, uzayda ses, astronomi, nasa, güneş, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G99" s="8" t="inlineStr">
+      <c r="G98" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! ☀️🔊</t>
         </is>
       </c>
-      <c r="H99" s="8" t="inlineStr">
+      <c r="H98" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I99" s="8" t="inlineStr">
+      <c r="I98" s="8" t="inlineStr">
         <is>
           <t>NASA Heliophysics / SOHO — Solar Acoustics: https://sci.esa.int/web/soho/-/30851-solar-interior</t>
         </is>
       </c>
-      <c r="J99" s="8" t="n"/>
-      <c r="K99" s="8" t="n"/>
-      <c r="L99" s="8" t="n"/>
-      <c r="M99" s="8" t="n"/>
-    </row>
-    <row r="100" ht="42" customHeight="1">
-      <c r="A100" s="7" t="inlineStr">
+      <c r="J98" s="8" t="n"/>
+      <c r="K98" s="8" t="n"/>
+      <c r="L98" s="8" t="n"/>
+      <c r="M98" s="8" t="n"/>
+    </row>
+    <row r="99" ht="42" customHeight="1">
+      <c r="A99" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B100" s="7" t="inlineStr">
+      <c r="B99" s="7" t="inlineStr">
         <is>
           <t>video_78.mp4</t>
         </is>
       </c>
-      <c r="C100" s="8" t="inlineStr">
+      <c r="C99" s="8" t="inlineStr">
         <is>
           <t>Paskalya Adası'ndaki 80 Tonluk Dev Taş Heykeller Nasıl Yürütüldü? 🗿🏛️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D100" s="8" t="inlineStr">
+      <c r="D99" s="8" t="inlineStr">
         <is>
           <t>Paskalya Adası'ndaki 80 tonluk dev taş heykellerin tekerlek veya vinç olmadan üç halatla dik vaziyette yürütülerek taşındığını biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -6238,53 +6183,53 @@
 #bilgidozu #shorts #tarih #paskalyaadası #arkeoloji</t>
         </is>
       </c>
-      <c r="E100" s="8" t="inlineStr">
+      <c r="E99" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #paskalyaadası #arkeoloji #dozdışı</t>
         </is>
       </c>
-      <c r="F100" s="8" t="inlineStr">
+      <c r="F99" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, paskalya adası, moai heykelleri, tarih, arkeoloji, mühendislik, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G100" s="8" t="inlineStr">
+      <c r="G99" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🗿🏛️</t>
         </is>
       </c>
-      <c r="H100" s="8" t="inlineStr">
+      <c r="H99" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Arkeoloji</t>
         </is>
       </c>
-      <c r="I100" s="8" t="inlineStr">
+      <c r="I99" s="8" t="inlineStr">
         <is>
           <t>Journal of Archaeological Science (2012) — Lipo &amp; Hunt (Easter Island Moai): https://en.wikipedia.org/wiki/Moai</t>
         </is>
       </c>
-      <c r="J100" s="8" t="n"/>
-      <c r="K100" s="8" t="n"/>
-      <c r="L100" s="8" t="n"/>
-      <c r="M100" s="8" t="n"/>
-    </row>
-    <row r="101" ht="42" customHeight="1">
-      <c r="A101" s="7" t="inlineStr">
+      <c r="J99" s="8" t="n"/>
+      <c r="K99" s="8" t="n"/>
+      <c r="L99" s="8" t="n"/>
+      <c r="M99" s="8" t="n"/>
+    </row>
+    <row r="100" ht="42" customHeight="1">
+      <c r="A100" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B101" s="7" t="inlineStr">
+      <c r="B100" s="7" t="inlineStr">
         <is>
           <t>video_79.mp4</t>
         </is>
       </c>
-      <c r="C101" s="8" t="inlineStr">
+      <c r="C100" s="8" t="inlineStr">
         <is>
           <t>Elektrikli Yılan Balığı 860 Volt Elektrik Üretirken Kendini Neden Çarpmaz? ⚡🐍 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D101" s="8" t="inlineStr">
+      <c r="D100" s="8" t="inlineStr">
         <is>
           <t>Elektrikli yılan balığının suyun içinde 860 voltluk ölümcül bir elektriği kendi kendini hiç çarpmadan nasıl ürettiğini biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -6293,53 +6238,53 @@
 #bilgidozu #shorts #doğa #hayvanlar #bilim</t>
         </is>
       </c>
-      <c r="E101" s="8" t="inlineStr">
+      <c r="E100" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #hayvanlar #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F101" s="8" t="inlineStr">
+      <c r="F100" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, elektrikli yılan balığı, elektrosit, doğa, hayvanlar, biyoloji, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G101" s="8" t="inlineStr">
+      <c r="G100" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! ⚡🐍</t>
         </is>
       </c>
-      <c r="H101" s="8" t="inlineStr">
+      <c r="H100" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I101" s="8" t="inlineStr">
+      <c r="I100" s="8" t="inlineStr">
         <is>
           <t>Nature Communications (2019) — de Santana et al. (860V Electric Eel): https://www.nature.com/articles/s41467-019-11622-9</t>
         </is>
       </c>
-      <c r="J101" s="8" t="n"/>
-      <c r="K101" s="8" t="n"/>
-      <c r="L101" s="8" t="n"/>
-      <c r="M101" s="8" t="n"/>
-    </row>
-    <row r="102" ht="42" customHeight="1">
-      <c r="A102" s="7" t="inlineStr">
+      <c r="J100" s="8" t="n"/>
+      <c r="K100" s="8" t="n"/>
+      <c r="L100" s="8" t="n"/>
+      <c r="M100" s="8" t="n"/>
+    </row>
+    <row r="101" ht="42" customHeight="1">
+      <c r="A101" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B102" s="7" t="inlineStr">
+      <c r="B101" s="7" t="inlineStr">
         <is>
           <t>video_80.mp4</t>
         </is>
       </c>
-      <c r="C102" s="8" t="inlineStr">
+      <c r="C101" s="8" t="inlineStr">
         <is>
           <t>Yürüyen Merdiven Kenarındaki Fırçalar Ayakkabı Silmek İçin Değil! 👟⚠️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D102" s="8" t="inlineStr">
+      <c r="D101" s="8" t="inlineStr">
         <is>
           <t>Yürüyen merdivenlerin iki yanındaki o sert siyah fırçaların ayakkabılarını temizlemen için değil, kıyafetlerin dişlilere sıkışmasını önlemek için konulduğunu biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -6348,53 +6293,53 @@
 #bilgidozu #shorts #ilginçbilgiler #mühendislik #bilim</t>
         </is>
       </c>
-      <c r="E102" s="8" t="inlineStr">
+      <c r="E101" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #ilginçbilgiler #mühendislik #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F102" s="8" t="inlineStr">
+      <c r="F101" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, yürüyen merdiven fırçası, güvenlik, mühendislik, günlük bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G102" s="8" t="inlineStr">
+      <c r="G101" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 👟⚠️</t>
         </is>
       </c>
-      <c r="H102" s="8" t="inlineStr">
+      <c r="H101" s="8" t="inlineStr">
         <is>
           <t>Fizik ve Mühendislik</t>
         </is>
       </c>
-      <c r="I102" s="8" t="inlineStr">
+      <c r="I101" s="8" t="inlineStr">
         <is>
           <t>ASME A17.1 Escalator Safety Code — Escalator Skirt Deflector Brushes: https://en.wikipedia.org/wiki/Escalator</t>
         </is>
       </c>
-      <c r="J102" s="8" t="n"/>
-      <c r="K102" s="8" t="n"/>
-      <c r="L102" s="8" t="n"/>
-      <c r="M102" s="8" t="n"/>
-    </row>
-    <row r="103" ht="42" customHeight="1">
-      <c r="A103" s="7" t="inlineStr">
+      <c r="J101" s="8" t="n"/>
+      <c r="K101" s="8" t="n"/>
+      <c r="L101" s="8" t="n"/>
+      <c r="M101" s="8" t="n"/>
+    </row>
+    <row r="102" ht="42" customHeight="1">
+      <c r="A102" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B103" s="7" t="inlineStr">
+      <c r="B102" s="7" t="inlineStr">
         <is>
           <t>video_81.mp4</t>
         </is>
       </c>
-      <c r="C103" s="8" t="inlineStr">
+      <c r="C102" s="8" t="inlineStr">
         <is>
           <t>Neptün ve Uranüs'te Gökyüzünden Gerçek Elmas Yağıyor! 💎🪐 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D103" s="8" t="inlineStr">
+      <c r="D102" s="8" t="inlineStr">
         <is>
           <t>Neptün ve Uranüs atmosferindeki yüksek basınç karbon atomlarını sıkıştırarak gerçek elmasa dönüştürür.
 Peki sizce insanoğlu bir gün bu gezegenlerden elmas toplayabilir mi? Yorumlara yazın! 👇
@@ -6403,53 +6348,53 @@
 #bilgidozu #shorts #uzay #bilim #gezegenler</t>
         </is>
       </c>
-      <c r="E103" s="8" t="inlineStr">
+      <c r="E102" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim #gezegenler #dozdışı</t>
         </is>
       </c>
-      <c r="F103" s="8" t="inlineStr">
+      <c r="F102" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, uzay, neptün, uranüs, elmas yağmuru, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G103" s="8" t="inlineStr">
+      <c r="G102" s="8" t="inlineStr">
         <is>
           <t>Peki sizce insanoğlu bir gün bu gezegenlerden elmas toplayabilir mi? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H103" s="8" t="inlineStr">
+      <c r="H102" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Evren</t>
         </is>
       </c>
-      <c r="I103" s="8" t="inlineStr">
+      <c r="I102" s="8" t="inlineStr">
         <is>
           <t>Nature Astronomy / SLAC — Diamond Rain on Ice Giants: https://www6.slac.stanford.edu/news/2017-08-21-scientists-create-diamond-rain-forms-interior-icy-giant-planets</t>
         </is>
       </c>
-      <c r="J103" s="8" t="n"/>
-      <c r="K103" s="8" t="n"/>
-      <c r="L103" s="8" t="n"/>
-      <c r="M103" s="8" t="n"/>
-    </row>
-    <row r="104" ht="42" customHeight="1">
-      <c r="A104" s="7" t="inlineStr">
+      <c r="J102" s="8" t="n"/>
+      <c r="K102" s="8" t="n"/>
+      <c r="L102" s="8" t="n"/>
+      <c r="M102" s="8" t="n"/>
+    </row>
+    <row r="103" ht="42" customHeight="1">
+      <c r="A103" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B104" s="7" t="inlineStr">
+      <c r="B103" s="7" t="inlineStr">
         <is>
           <t>video_82.mp4</t>
         </is>
       </c>
-      <c r="C104" s="8" t="inlineStr">
+      <c r="C103" s="8" t="inlineStr">
         <is>
           <t>Uzay Boşluğunda Bile Hayatta Kalan Canlı: Su Ayısı Tardigrad! 🐻🌌 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D104" s="8" t="inlineStr">
+      <c r="D103" s="8" t="inlineStr">
         <is>
           <t>Mikroskobik su ayısı Tardigrad, kriptobiyoz özelliği sayesinde uzay boşluğunda ve radyasyonda bile hayatta kalabilir.
 Sizce Dünya'daki en dayanıklı canlı Tardigrad mı yoksa başka bir tür mü? Yorumlarda buluşalım! 👇
@@ -6458,53 +6403,53 @@
 #bilgidozu #shorts #doğa #bilim #tardigrad</t>
         </is>
       </c>
-      <c r="E104" s="8" t="inlineStr">
+      <c r="E103" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim #tardigrad #dozdışı</t>
         </is>
       </c>
-      <c r="F104" s="8" t="inlineStr">
+      <c r="F103" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, tardigrad, su ayısı, doğa, uzay, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G104" s="8" t="inlineStr">
+      <c r="G103" s="8" t="inlineStr">
         <is>
           <t>Sizce Dünya'daki en dayanıklı canlı Tardigrad mı yoksa başka bir tür mü? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H104" s="8" t="inlineStr">
+      <c r="H103" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Canlılar</t>
         </is>
       </c>
-      <c r="I104" s="8" t="inlineStr">
+      <c r="I103" s="8" t="inlineStr">
         <is>
           <t>ESA FOTON-M3 / Current Biology — Tardigrades in Space: https://en.wikipedia.org/wiki/Tardigrade</t>
         </is>
       </c>
-      <c r="J104" s="8" t="n"/>
-      <c r="K104" s="8" t="n"/>
-      <c r="L104" s="8" t="n"/>
-      <c r="M104" s="8" t="n"/>
-    </row>
-    <row r="105" ht="42" customHeight="1">
-      <c r="A105" s="7" t="inlineStr">
+      <c r="J103" s="8" t="n"/>
+      <c r="K103" s="8" t="n"/>
+      <c r="L103" s="8" t="n"/>
+      <c r="M103" s="8" t="n"/>
+    </row>
+    <row r="104" ht="42" customHeight="1">
+      <c r="A104" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B105" s="7" t="inlineStr">
+      <c r="B104" s="7" t="inlineStr">
         <is>
           <t>video_84.mp4</t>
         </is>
       </c>
-      <c r="C105" s="8" t="inlineStr">
+      <c r="C104" s="8" t="inlineStr">
         <is>
           <t>Tek Bir Ağaçtan Oluşan 47 Bin Gövdeli Dev Orman: Pando! 🌲🌍 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D105" s="8" t="inlineStr">
+      <c r="D104" s="8" t="inlineStr">
         <is>
           <t>Utah'taki Pando ormanı aslında 47 bin ayrı ağaç değil, yer altındaki tek bir kök sisteminden çıkan dev bir organizmadır.
 Bu ormanı ilk gördüğünüzde tek bir canlı olduğunu tahmin eder miydiniz? Yorumlara yazın! 👇
@@ -6513,53 +6458,53 @@
 #bilgidozu #shorts #doğa #orman #bilim</t>
         </is>
       </c>
-      <c r="E105" s="8" t="inlineStr">
+      <c r="E104" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #orman #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F105" s="8" t="inlineStr">
+      <c r="F104" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, pando ormanı, doğa, ağaç, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G105" s="8" t="inlineStr">
+      <c r="G104" s="8" t="inlineStr">
         <is>
           <t>Bu ormanı ilk gördüğünüzde tek bir canlı olduğunu tahmin eder miydiniz? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H105" s="8" t="inlineStr">
+      <c r="H104" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Canlılar</t>
         </is>
       </c>
-      <c r="I105" s="8" t="inlineStr">
+      <c r="I104" s="8" t="inlineStr">
         <is>
           <t>USDA Forest Service — Pando Clonal Colony: https://www.fs.usda.gov/detail/fishlake/home/?cid=stelprdb5444544</t>
         </is>
       </c>
-      <c r="J105" s="8" t="n"/>
-      <c r="K105" s="8" t="n"/>
-      <c r="L105" s="8" t="n"/>
-      <c r="M105" s="8" t="n"/>
-    </row>
-    <row r="106" ht="42" customHeight="1">
-      <c r="A106" s="7" t="inlineStr">
+      <c r="J104" s="8" t="n"/>
+      <c r="K104" s="8" t="n"/>
+      <c r="L104" s="8" t="n"/>
+      <c r="M104" s="8" t="n"/>
+    </row>
+    <row r="105" ht="42" customHeight="1">
+      <c r="A105" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B106" s="7" t="inlineStr">
+      <c r="B105" s="7" t="inlineStr">
         <is>
           <t>video_85.mp4</t>
         </is>
       </c>
-      <c r="C106" s="8" t="inlineStr">
+      <c r="C105" s="8" t="inlineStr">
         <is>
           <t>Yıldırım Yukarıdan Düşmez: Parlama Yerden Gökyüzüne Çıkar! ⚡🌩️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D106" s="8" t="inlineStr">
+      <c r="D105" s="8" t="inlineStr">
         <is>
           <t>Buluttan inen öncü akım yere yaklaştığında, yerden yükselen pozitif yüklerle birleşir ve gördüğümüz ana parlama yerden gökyüzüne çıkar.
 Yıldırımın yerden yukarı çıktığını ilk kez mi duydunuz? Yorumlarda belirtin! 👇
@@ -6568,328 +6513,53 @@
 #bilgidozu #shorts #bilim #yıldırım #doğaolayları</t>
         </is>
       </c>
-      <c r="E106" s="8" t="inlineStr">
+      <c r="E105" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #bilim #yıldırım #doğaolayları #dozdışı</t>
         </is>
       </c>
-      <c r="F106" s="8" t="inlineStr">
+      <c r="F105" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, yıldırım, günlük bilim, fizik, doğa olayları, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G106" s="8" t="inlineStr">
+      <c r="G105" s="8" t="inlineStr">
         <is>
           <t>Yıldırımın yerden yukarı çıktığını ilk kez mi duydunuz? Yorumlarda belirtin! 👇</t>
         </is>
       </c>
-      <c r="H106" s="8" t="inlineStr">
+      <c r="H105" s="8" t="inlineStr">
         <is>
           <t>Fizik ve Mühendislik</t>
         </is>
       </c>
-      <c r="I106" s="8" t="inlineStr">
+      <c r="I105" s="8" t="inlineStr">
         <is>
           <t>NOAA Severe Weather — Lightning Return Stroke Physics: https://www.weather.gov/safety/lightning-science</t>
         </is>
       </c>
-      <c r="J106" s="8" t="n"/>
-      <c r="K106" s="8" t="n"/>
-      <c r="L106" s="8" t="n"/>
-      <c r="M106" s="8" t="n"/>
-    </row>
-    <row r="107" ht="42" customHeight="1">
-      <c r="A107" s="7" t="inlineStr">
+      <c r="J105" s="8" t="n"/>
+      <c r="K105" s="8" t="n"/>
+      <c r="L105" s="8" t="n"/>
+      <c r="M105" s="8" t="n"/>
+    </row>
+    <row r="106" ht="42" customHeight="1">
+      <c r="A106" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B107" s="7" t="inlineStr">
-        <is>
-          <t>video_86.mp4</t>
-        </is>
-      </c>
-      <c r="C107" s="8" t="inlineStr">
-        <is>
-          <t>Jüpiter'de Dünya'dan Büyük 300 Yıllık Fırtına: Büyük Kırmızı Leke! 🌪️🪐 #bilgidozu #shorts</t>
-        </is>
-      </c>
-      <c r="D107" s="8" t="inlineStr">
-        <is>
-          <t>Jüpiter'deki Büyük Kırmızı Leke, içine Dünya'yı sığdırabilecek büyüklükte ve en az 300 yıldır aralıksız dönen bir fırtınadır.
-Sizce Jüpiter'deki bu dev fırtına bir gün tamamen durur mu? Tahmininizi yorumlara yazın! 👇
-📚 Kaynak: NASA Juno Mission — Great Red Spot
-🎨 Görseller temsilîdir (AI üretimi).
-#bilgidozu #shorts #uzay #jüpiter #bilim</t>
-        </is>
-      </c>
-      <c r="E107" s="8" t="inlineStr">
-        <is>
-          <t>#bilgidozu #shorts #uzay #jüpiter #bilim #dozdışı</t>
-        </is>
-      </c>
-      <c r="F107" s="8" t="inlineStr">
-        <is>
-          <t>bilgi dozu, jüpiter, büyük kırmızı leke, uzay, astronomi, shorts, doz dışı</t>
-        </is>
-      </c>
-      <c r="G107" s="8" t="inlineStr">
-        <is>
-          <t>Sizce Jüpiter'deki bu dev fırtına bir gün tamamen durur mu? Tahmininizi yorumlara yazın! 👇</t>
-        </is>
-      </c>
-      <c r="H107" s="8" t="inlineStr">
-        <is>
-          <t>Uzay ve Evren</t>
-        </is>
-      </c>
-      <c r="I107" s="8" t="inlineStr">
-        <is>
-          <t>NASA Juno Mission — Jupiter Great Red Spot: https://science.nasa.gov/jupiter/facts/</t>
-        </is>
-      </c>
-      <c r="J107" s="8" t="n"/>
-      <c r="K107" s="8" t="n"/>
-      <c r="L107" s="8" t="n"/>
-      <c r="M107" s="8" t="n"/>
-    </row>
-    <row r="108" ht="42" customHeight="1">
-      <c r="A108" s="7" t="inlineStr">
-        <is>
-          <t>ESKİ_STOK_ASKIDA</t>
-        </is>
-      </c>
-      <c r="B108" s="7" t="inlineStr">
+      <c r="B106" s="7" t="inlineStr">
         <is>
           <t>video_87.mp4</t>
         </is>
       </c>
-      <c r="C108" s="8" t="inlineStr">
-        <is>
-          <t>Everest'in 3 Katı Yüksekliğinde Dev Yanardağ: Olympus Mons! 🌋🔴 #bilgidozu #shorts</t>
-        </is>
-      </c>
-      <c r="D108" s="8" t="inlineStr">
-        <is>
-          <t>Mars'taki Olympus Mons yanardağı yaklaşık 22 kilometre yüksekliğiyle Everest Dağı'nın tam 3 katı büyüklüğündedir.
-Everest'in üç katı yüksekliğinde bir dağın zirvesine çıkmak ister miydiniz? Yorumlara yazın! 👇
-📚 Kaynak: NASA Mars Exploration — Olympus Mons
-🎨 Görseller temsilîdir (AI üretimi).
-#bilgidozu #shorts #mars #uzay #bilim</t>
-        </is>
-      </c>
-      <c r="E108" s="8" t="inlineStr">
-        <is>
-          <t>#bilgidozu #shorts #mars #uzay #bilim #dozdışı</t>
-        </is>
-      </c>
-      <c r="F108" s="8" t="inlineStr">
-        <is>
-          <t>bilgi dozu, mars, olympus mons, yanardağ, uzay, shorts, doz dışı</t>
-        </is>
-      </c>
-      <c r="G108" s="8" t="inlineStr">
-        <is>
-          <t>Everest'in üç katı yüksekliğinde bir dağın zirvesine çıkmak ister miydiniz? Yorumlara yazın! 👇</t>
-        </is>
-      </c>
-      <c r="H108" s="8" t="inlineStr">
-        <is>
-          <t>Uzay ve Evren</t>
-        </is>
-      </c>
-      <c r="I108" s="8" t="inlineStr">
-        <is>
-          <t>NASA Mars Exploration — Olympus Mons: https://science.nasa.gov/mars/facts/</t>
-        </is>
-      </c>
-      <c r="J108" s="8" t="n"/>
-      <c r="K108" s="8" t="n"/>
-      <c r="L108" s="8" t="n"/>
-      <c r="M108" s="8" t="n"/>
-    </row>
-    <row r="109" ht="42" customHeight="1">
-      <c r="A109" s="7" t="inlineStr">
-        <is>
-          <t>ESKİ_STOK_ASKIDA</t>
-        </is>
-      </c>
-      <c r="B109" s="7" t="inlineStr">
-        <is>
-          <t>video_88.mp4</t>
-        </is>
-      </c>
-      <c r="C109" s="8" t="inlineStr">
-        <is>
-          <t>Beyni ve Kanı Olmadan Denizde Avlanan Canlı: Denizyıldızı! ⭐🌊 #bilgidozu #shorts</t>
-        </is>
-      </c>
-      <c r="D109" s="8" t="inlineStr">
-        <is>
-          <t>Denizyıldızlarının merkezi bir beyni ve kanı yoktur; damarlarında kalp yerine pompalanan filtre edilmiş deniz suyu dolaşır.
-Beyni ve kanı olmadan yaşayan bu canlı hakkında siz ne düşünüyorsunuz? Yorumlara yazın! 👇
-📚 Kaynak: Smithsonian Ocean — Sea Stars Anatomy
-🎨 Görseller temsilîdir (AI üretimi).
-#bilgidozu #shorts #doğa #okyanus #bilim</t>
-        </is>
-      </c>
-      <c r="E109" s="8" t="inlineStr">
-        <is>
-          <t>#bilgidozu #shorts #doğa #okyanus #bilim #dozdışı</t>
-        </is>
-      </c>
-      <c r="F109" s="8" t="inlineStr">
-        <is>
-          <t>bilgi dozu, denizyıldızı, okyanus, doğa, hayvanlar, shorts, doz dışı</t>
-        </is>
-      </c>
-      <c r="G109" s="8" t="inlineStr">
-        <is>
-          <t>Beyni ve kanı olmadan yaşayan bu canlı hakkında siz ne düşünüyorsunuz? Yorumlara yazın! 👇</t>
-        </is>
-      </c>
-      <c r="H109" s="8" t="inlineStr">
-        <is>
-          <t>Doğa ve Canlılar</t>
-        </is>
-      </c>
-      <c r="I109" s="8" t="inlineStr">
-        <is>
-          <t>Smithsonian Ocean / Wikipedia — Sea Stars Anatomy: https://en.wikipedia.org/wiki/Starfish</t>
-        </is>
-      </c>
-      <c r="J109" s="8" t="n"/>
-      <c r="K109" s="8" t="n"/>
-      <c r="L109" s="8" t="n"/>
-      <c r="M109" s="8" t="n"/>
-    </row>
-    <row r="110" ht="42" customHeight="1">
-      <c r="A110" s="7" t="inlineStr">
-        <is>
-          <t>ESKİ_STOK_ASKIDA</t>
-        </is>
-      </c>
-      <c r="B110" s="7" t="inlineStr">
-        <is>
-          <t>video_89.mp4</t>
-        </is>
-      </c>
-      <c r="C110" s="8" t="inlineStr">
-        <is>
-          <t>Yunuslar Tek Gözü Açık ve Yarım Beyinle Nasıl Uyur? 🐬🌊 #bilgidozu #shorts</t>
-        </is>
-      </c>
-      <c r="D110" s="8" t="inlineStr">
-        <is>
-          <t>Yunuslar uykuda boğulmamak için beyinlerinin sadece bir yarısını uyuturken diğer yarısıyla nefes alıp çevreyi gözetler.
-Beyninizin yarısını uyutup diğer yarısıyla uyanık kalmak ister miydiniz? Yorumlara yazın! 👇
-📚 Kaynak: Neuroscience &amp; Biobehavioral Reviews — Unihemispheric Sleep
-🎨 Görseller temsilîdir (AI üretimi).
-#bilgidozu #shorts #yunus #doğa #bilim</t>
-        </is>
-      </c>
-      <c r="E110" s="8" t="inlineStr">
-        <is>
-          <t>#bilgidozu #shorts #yunus #doğa #bilim #dozdışı</t>
-        </is>
-      </c>
-      <c r="F110" s="8" t="inlineStr">
-        <is>
-          <t>bilgi dozu, yunuslar, doğa, hayvanlar alemi, uyku, shorts, doz dışı</t>
-        </is>
-      </c>
-      <c r="G110" s="8" t="inlineStr">
-        <is>
-          <t>Beyninizin yarısını uyutup diğer yarısıyla uyanık kalmak ister miydiniz? Yorumlara yazın! 👇</t>
-        </is>
-      </c>
-      <c r="H110" s="8" t="inlineStr">
-        <is>
-          <t>Doğa ve Canlılar</t>
-        </is>
-      </c>
-      <c r="I110" s="8" t="inlineStr">
-        <is>
-          <t>Sleep Foundation / Wikipedia — Unihemispheric Slow-Wave Sleep: https://en.wikipedia.org/wiki/Unihemispheric_slow-wave_sleep</t>
-        </is>
-      </c>
-      <c r="J110" s="8" t="n"/>
-      <c r="K110" s="8" t="n"/>
-      <c r="L110" s="8" t="n"/>
-      <c r="M110" s="8" t="n"/>
-    </row>
-    <row r="111" ht="42" customHeight="1">
-      <c r="A111" s="7" t="inlineStr">
-        <is>
-          <t>ESKİ_STOK_ASKIDA</t>
-        </is>
-      </c>
-      <c r="B111" s="7" t="inlineStr">
-        <is>
-          <t>video_90.mp4</t>
-        </is>
-      </c>
-      <c r="C111" s="8" t="inlineStr">
-        <is>
-          <t>Dev Bir Okyanusa Bırakılsa Suda Yüzecek Gezegen: Satürn! 🪐🌊 #bilgidozu #shorts</t>
-        </is>
-      </c>
-      <c r="D111" s="8" t="inlineStr">
-        <is>
-          <t>Satürn'ün ortalama yoğunluğu santimetreküp başına 0,68 gramdır; yani sudan daha hafif olduğu için dev bir okyanusta yüzebilir.
-Koca bir gezegenin sudan daha hafif olması sizi de şaşırttı mı? Yorumlara yazın! 👇
-📚 Kaynak: NASA Cassini Mission — Saturn Planetary Density
-🎨 Görseller temsilîdir (AI üretimi).
-#bilgidozu #shorts #satürn #uzay #bilim</t>
-        </is>
-      </c>
-      <c r="E111" s="8" t="inlineStr">
-        <is>
-          <t>#bilgidozu #shorts #satürn #uzay #bilim #dozdışı</t>
-        </is>
-      </c>
-      <c r="F111" s="8" t="inlineStr">
-        <is>
-          <t>bilgi dozu, satürn, uzay, gezegenler, astronomi, shorts, doz dışı</t>
-        </is>
-      </c>
-      <c r="G111" s="8" t="inlineStr">
-        <is>
-          <t>Koca bir gezegenin sudan daha hafif olması sizi de şaşırttı mı? Yorumlara yazın! 👇</t>
-        </is>
-      </c>
-      <c r="H111" s="8" t="inlineStr">
-        <is>
-          <t>Uzay ve Evren</t>
-        </is>
-      </c>
-      <c r="I111" s="8" t="inlineStr">
-        <is>
-          <t>NASA Cassini Mission — Saturn Planetary Density: https://science.nasa.gov/saturn/facts/</t>
-        </is>
-      </c>
-      <c r="J111" s="8" t="n"/>
-      <c r="K111" s="8" t="n"/>
-      <c r="L111" s="8" t="n"/>
-      <c r="M111" s="8" t="n"/>
-    </row>
-    <row r="112" ht="42" customHeight="1">
-      <c r="A112" s="7" t="inlineStr">
-        <is>
-          <t>ESKİ_STOK_ASKIDA</t>
-        </is>
-      </c>
-      <c r="B112" s="7" t="inlineStr">
-        <is>
-          <t>video_92.mp4</t>
-        </is>
-      </c>
-      <c r="C112" s="8" t="inlineStr">
+      <c r="C106" s="8" t="inlineStr">
         <is>
           <t>Cam Zamanla Akan Bir Sıvı Değil: En Büyük Bilim Efsanesi! 🪟🔬 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D112" s="8" t="inlineStr">
+      <c r="D106" s="8" t="inlineStr">
         <is>
           <t>Cam çok yavaş akan bir sıvı değil, amorf bir katıdır; eski pencerelerin altının kalın olması üretim tekniğinden kaynaklanır.
 Siz de okulda camın çok yavaş akan bir sıvı olduğunu duymuş muydunuz? Yorumlarda belirtin! 👇
@@ -6898,53 +6568,53 @@
 #bilgidozu #shorts #bilim #fizik #ilginçbilgiler</t>
         </is>
       </c>
-      <c r="E112" s="8" t="inlineStr">
+      <c r="E106" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #bilim #fizik #ilginçbilgiler #dozdışı</t>
         </is>
       </c>
-      <c r="F112" s="8" t="inlineStr">
+      <c r="F106" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, cam, fizik, günlük bilim, şehir efsanesi, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G112" s="8" t="inlineStr">
+      <c r="G106" s="8" t="inlineStr">
         <is>
           <t>Siz de okulda camın çok yavaş akan bir sıvı olduğunu duymuş muydunuz? Yorumlarda belirtin! 👇</t>
         </is>
       </c>
-      <c r="H112" s="8" t="inlineStr">
+      <c r="H106" s="8" t="inlineStr">
         <is>
           <t>Fizik ve Mühendislik</t>
         </is>
       </c>
-      <c r="I112" s="8" t="inlineStr">
+      <c r="I106" s="8" t="inlineStr">
         <is>
           <t>American Journal of Physics (Zanotto, 1998) — Do Cathedral Glasses Flow?: https://en.wikipedia.org/wiki/Glass</t>
         </is>
       </c>
-      <c r="J112" s="8" t="n"/>
-      <c r="K112" s="8" t="n"/>
-      <c r="L112" s="8" t="n"/>
-      <c r="M112" s="8" t="n"/>
-    </row>
-    <row r="113" ht="42" customHeight="1">
-      <c r="A113" s="7" t="inlineStr">
+      <c r="J106" s="8" t="n"/>
+      <c r="K106" s="8" t="n"/>
+      <c r="L106" s="8" t="n"/>
+      <c r="M106" s="8" t="n"/>
+    </row>
+    <row r="107" ht="42" customHeight="1">
+      <c r="A107" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B113" s="7" t="inlineStr">
-        <is>
-          <t>video_93.mp4</t>
-        </is>
-      </c>
-      <c r="C113" s="8" t="inlineStr">
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>video_88.mp4</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
         <is>
           <t>Ay Her Yıl Dünya'dan 3,8 Santimetre Uzaklaşıyor! 🌕🚀 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D113" s="8" t="inlineStr">
+      <c r="D107" s="8" t="inlineStr">
         <is>
           <t>Apollo astronotlarının bıraktığı lazer aynaları, Ay'ın gelgit kuvvetleri nedeniyle her yıl 3,8 cm uzaklaştığını kanıtlamıştır.
 Peki Ay'ın her yıl bizden uzaklaşması gelecekte Dünya'yı sizce nasıl etkiler? Yorumlara yazın! 👇
@@ -6953,53 +6623,53 @@
 #bilgidozu #shorts #ay #uzay #bilim</t>
         </is>
       </c>
-      <c r="E113" s="8" t="inlineStr">
+      <c r="E107" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #ay #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F113" s="8" t="inlineStr">
+      <c r="F107" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, ay, dünya, uzay, astronomi, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G113" s="8" t="inlineStr">
+      <c r="G107" s="8" t="inlineStr">
         <is>
           <t>Peki Ay'ın her yıl bizden uzaklaşması gelecekte Dünya'yı sizce nasıl etkiler? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H113" s="8" t="inlineStr">
+      <c r="H107" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Evren</t>
         </is>
       </c>
-      <c r="I113" s="8" t="inlineStr">
+      <c r="I107" s="8" t="inlineStr">
         <is>
           <t>NASA — Lunar Laser Ranging Experiment: https://science.nasa.gov/moon/facts/</t>
         </is>
       </c>
-      <c r="J113" s="8" t="n"/>
-      <c r="K113" s="8" t="n"/>
-      <c r="L113" s="8" t="n"/>
-      <c r="M113" s="8" t="n"/>
-    </row>
-    <row r="114" ht="42" customHeight="1">
-      <c r="A114" s="7" t="inlineStr">
+      <c r="J107" s="8" t="n"/>
+      <c r="K107" s="8" t="n"/>
+      <c r="L107" s="8" t="n"/>
+      <c r="M107" s="8" t="n"/>
+    </row>
+    <row r="108" ht="42" customHeight="1">
+      <c r="A108" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B114" s="7" t="inlineStr">
-        <is>
-          <t>video_94.mp4</t>
-        </is>
-      </c>
-      <c r="C114" s="8" t="inlineStr">
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>video_89.mp4</t>
+        </is>
+      </c>
+      <c r="C108" s="8" t="inlineStr">
         <is>
           <t>Yetişkin Kediler Birbirine Değil Sadece İnsanlara Miyavlar! 🐱🔊 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D114" s="8" t="inlineStr">
+      <c r="D108" s="8" t="inlineStr">
         <is>
           <t>Yetişkin kediler kendi aralarında koku ve beden diliyle anlaşır; miyavlama sesini sadece insanlarla iletişim kurmak için kullanır.
 Sizin kediniz bir şey istediğinde nasıl sesler çıkarıyor? Yorumlarda anlatın! 👇
@@ -7008,53 +6678,53 @@
 #bilgidozu #shorts #kediler #hayvanlar #doğa</t>
         </is>
       </c>
-      <c r="E114" s="8" t="inlineStr">
+      <c r="E108" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #kediler #hayvanlar #doğa #dozdışı</t>
         </is>
       </c>
-      <c r="F114" s="8" t="inlineStr">
+      <c r="F108" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, kediler, kedi miyavlaması, doğa, hayvanlar, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G114" s="8" t="inlineStr">
+      <c r="G108" s="8" t="inlineStr">
         <is>
           <t>Sizin kediniz bir şey istediğinde nasıl sesler çıkarıyor? Yorumlarda anlatın! 👇</t>
         </is>
       </c>
-      <c r="H114" s="8" t="inlineStr">
+      <c r="H108" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Canlılar</t>
         </is>
       </c>
-      <c r="I114" s="8" t="inlineStr">
+      <c r="I108" s="8" t="inlineStr">
         <is>
           <t>Cornell Feline Health Center / Wikipedia — Cat Vocalization: https://en.wikipedia.org/wiki/Cat_communication</t>
         </is>
       </c>
-      <c r="J114" s="8" t="n"/>
-      <c r="K114" s="8" t="n"/>
-      <c r="L114" s="8" t="n"/>
-      <c r="M114" s="8" t="n"/>
-    </row>
-    <row r="115" ht="42" customHeight="1">
-      <c r="A115" s="7" t="inlineStr">
+      <c r="J108" s="8" t="n"/>
+      <c r="K108" s="8" t="n"/>
+      <c r="L108" s="8" t="n"/>
+      <c r="M108" s="8" t="n"/>
+    </row>
+    <row r="109" ht="42" customHeight="1">
+      <c r="A109" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B115" s="7" t="inlineStr">
-        <is>
-          <t>video_95.mp4</t>
-        </is>
-      </c>
-      <c r="C115" s="8" t="inlineStr">
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>video_90.mp4</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="inlineStr">
         <is>
           <t>Dünya Uzayda Saniyede 30 Kilometre Hızla Uçuyor! 🌍⚡ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D115" s="8" t="inlineStr">
+      <c r="D109" s="8" t="inlineStr">
         <is>
           <t>Dünya Güneş etrafındaki yörüngesinde saniyede 30 km, yani saatte 108 bin km hızla ilerler.
 Dünya'nın uzayda saniyede otuz kilometre hızla uçtuğunu bilmek başınızı döndürdü mü? Yorumlara yazın! 👇
@@ -7063,273 +6733,53 @@
 #bilgidozu #shorts #dünya #uzay #bilim</t>
         </is>
       </c>
-      <c r="E115" s="8" t="inlineStr">
+      <c r="E109" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #dünya #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F115" s="8" t="inlineStr">
+      <c r="F109" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, dünya, uzay, güneş sistemi, hız, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G115" s="8" t="inlineStr">
+      <c r="G109" s="8" t="inlineStr">
         <is>
           <t>Dünya'nın uzayda saniyede otuz kilometre hızla uçtuğunu bilmek başınızı döndürdü mü? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H115" s="8" t="inlineStr">
+      <c r="H109" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Evren</t>
         </is>
       </c>
-      <c r="I115" s="8" t="inlineStr">
+      <c r="I109" s="8" t="inlineStr">
         <is>
           <t>NASA Earth Fact Sheet — Orbital Velocity: https://science.nasa.gov/earth/facts/</t>
         </is>
       </c>
-      <c r="J115" s="8" t="n"/>
-      <c r="K115" s="8" t="n"/>
-      <c r="L115" s="8" t="n"/>
-      <c r="M115" s="8" t="n"/>
-    </row>
-    <row r="116" ht="42" customHeight="1">
-      <c r="A116" s="7" t="inlineStr">
+      <c r="J109" s="8" t="n"/>
+      <c r="K109" s="8" t="n"/>
+      <c r="L109" s="8" t="n"/>
+      <c r="M109" s="8" t="n"/>
+    </row>
+    <row r="110" ht="42" customHeight="1">
+      <c r="A110" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B116" s="7" t="inlineStr">
-        <is>
-          <t>video_96.mp4</t>
-        </is>
-      </c>
-      <c r="C116" s="8" t="inlineStr">
-        <is>
-          <t>Mısır Piramitlerinden Çıkan 3000 Yıllık Yenebilir Bal! 🍯🏺 #bilgidozu #shorts</t>
-        </is>
-      </c>
-      <c r="D116" s="8" t="inlineStr">
-        <is>
-          <t>Mısır firavun mezarlarında bulunan 3000 yıllık mühürlü bal küpleri, düşük nem ve asidik yapı sayesinde bozulmadan kalmıştır.
-Peki üç bin yıllık bir mezardan çıkan balı tatmaya cesaret eder miydiniz? Yorumlara yazın! 👇
-📚 Kaynak: Smithsonian Magazine — The Science Behind Honey's Eternal Shelf Life
-🎨 Görseller temsilîdir (AI üretimi).
-#bilgidozu #shorts #tarih #mısır #bilim</t>
-        </is>
-      </c>
-      <c r="E116" s="8" t="inlineStr">
-        <is>
-          <t>#bilgidozu #shorts #tarih #mısır #bilim #dozdışı</t>
-        </is>
-      </c>
-      <c r="F116" s="8" t="inlineStr">
-        <is>
-          <t>bilgi dozu, mısır piramitleri, bal, tarih, arkeoloji, shorts, doz dışı</t>
-        </is>
-      </c>
-      <c r="G116" s="8" t="inlineStr">
-        <is>
-          <t>Peki üç bin yıllık bir mezardan çıkan balı tatmaya cesaret eder miydiniz? Yorumlara yazın! 👇</t>
-        </is>
-      </c>
-      <c r="H116" s="8" t="inlineStr">
-        <is>
-          <t>Tarih ve Arkeoloji</t>
-        </is>
-      </c>
-      <c r="I116" s="8" t="inlineStr">
-        <is>
-          <t>Smithsonian Magazine — The Science Behind Honey's Eternal Shelf Life: https://en.wikipedia.org/wiki/Honey</t>
-        </is>
-      </c>
-      <c r="J116" s="8" t="n"/>
-      <c r="K116" s="8" t="n"/>
-      <c r="L116" s="8" t="n"/>
-      <c r="M116" s="8" t="n"/>
-    </row>
-    <row r="117" ht="42" customHeight="1">
-      <c r="A117" s="7" t="inlineStr">
-        <is>
-          <t>ESKİ_STOK_ASKIDA</t>
-        </is>
-      </c>
-      <c r="B117" s="7" t="inlineStr">
-        <is>
-          <t>video_97.mp4</t>
-        </is>
-      </c>
-      <c r="C117" s="8" t="inlineStr">
-        <is>
-          <t>Dünya'nın Çekirdeği Güneş Yüzeyi Kadar Sıcak: 5400 Derece! 🌋🔥 #bilgidozu #shorts</t>
-        </is>
-      </c>
-      <c r="D117" s="8" t="inlineStr">
-        <is>
-          <t>Dünya'nın iç çekirdeği yaklaşık 5400 santigrat derece sıcaklığıyla Güneş'in yüzeyi kadar sıcaktır ancak dev basınç nedeniyle katıdır.
-Ayaklarımızın altında Güneş kadar sıcak bir çekirdek olması sizi de şaşırttı mı? Yorumlarda buluşalım! 👇
-📚 Kaynak: Science — Melting of Iron at Earth's Inner Core Boundary
-🎨 Görseller temsilîdir (AI üretimi).
-#bilgidozu #shorts #dünya #bilim #jeoloji</t>
-        </is>
-      </c>
-      <c r="E117" s="8" t="inlineStr">
-        <is>
-          <t>#bilgidozu #shorts #dünya #bilim #jeoloji #dozdışı</t>
-        </is>
-      </c>
-      <c r="F117" s="8" t="inlineStr">
-        <is>
-          <t>bilgi dozu, dünya çekirdeği, güneş, jeoloji, bilim, shorts, doz dışı</t>
-        </is>
-      </c>
-      <c r="G117" s="8" t="inlineStr">
-        <is>
-          <t>Ayaklarımızın altında Güneş kadar sıcak bir çekirdek olması sizi de şaşırttı mı? Yorumlarda buluşalım! 👇</t>
-        </is>
-      </c>
-      <c r="H117" s="8" t="inlineStr">
-        <is>
-          <t>Fizik ve Mühendislik</t>
-        </is>
-      </c>
-      <c r="I117" s="8" t="inlineStr">
-        <is>
-          <t>Science / Wikipedia — Earth's Inner Core Temperature: https://en.wikipedia.org/wiki/Earth%27s_inner_core</t>
-        </is>
-      </c>
-      <c r="J117" s="8" t="n"/>
-      <c r="K117" s="8" t="n"/>
-      <c r="L117" s="8" t="n"/>
-      <c r="M117" s="8" t="n"/>
-    </row>
-    <row r="118" ht="42" customHeight="1">
-      <c r="A118" s="7" t="inlineStr">
-        <is>
-          <t>ESKİ_STOK_ASKIDA</t>
-        </is>
-      </c>
-      <c r="B118" s="7" t="inlineStr">
-        <is>
-          <t>video_98.mp4</t>
-        </is>
-      </c>
-      <c r="C118" s="8" t="inlineStr">
-        <is>
-          <t>Filler Kilometrelerce Uzaktaki Sesi Ayak Tabanıyla Duyar! 🐘🌍 #bilgidozu #shorts</t>
-        </is>
-      </c>
-      <c r="D118" s="8" t="inlineStr">
-        <is>
-          <t>Filler çıkardıkları düşük frekanslı seslerin topraktaki sismik titreşimlerini hassas ayak tabanlarıyla kilometrelerce uzaktan algılar.
-Fillerin ayak tabanlarıyla yeri dinleyerek anlaşması hakkında ne düşünüyorsunuz? Yorumlara yazın! 👇
-📚 Kaynak: Stanford University — Seismic Communication in Elephants
-🎨 Görseller temsilîdir (AI üretimi).
-#bilgidozu #shorts #filler #doğa #bilim</t>
-        </is>
-      </c>
-      <c r="E118" s="8" t="inlineStr">
-        <is>
-          <t>#bilgidozu #shorts #filler #doğa #bilim #dozdışı</t>
-        </is>
-      </c>
-      <c r="F118" s="8" t="inlineStr">
-        <is>
-          <t>bilgi dozu, filler, doğa, hayvanlar, sismik ses, shorts, doz dışı</t>
-        </is>
-      </c>
-      <c r="G118" s="8" t="inlineStr">
-        <is>
-          <t>Fillerin ayak tabanlarıyla yeri dinleyerek anlaşması hakkında ne düşünüyorsunuz? Yorumlara yazın! 👇</t>
-        </is>
-      </c>
-      <c r="H118" s="8" t="inlineStr">
-        <is>
-          <t>Doğa ve Canlılar</t>
-        </is>
-      </c>
-      <c r="I118" s="8" t="inlineStr">
-        <is>
-          <t>Stanford University / Wikipedia — Elephant Seismic Communication: https://en.wikipedia.org/wiki/Elephant_cognition</t>
-        </is>
-      </c>
-      <c r="J118" s="8" t="n"/>
-      <c r="K118" s="8" t="n"/>
-      <c r="L118" s="8" t="n"/>
-      <c r="M118" s="8" t="n"/>
-    </row>
-    <row r="119" ht="42" customHeight="1">
-      <c r="A119" s="7" t="inlineStr">
-        <is>
-          <t>ESKİ_STOK_ASKIDA</t>
-        </is>
-      </c>
-      <c r="B119" s="7" t="inlineStr">
-        <is>
-          <t>video_99.mp4</t>
-        </is>
-      </c>
-      <c r="C119" s="8" t="inlineStr">
-        <is>
-          <t>Yan Yatarak Dönen Gezegen Uranüs'te 1 Gece 42 Yıl Sürüyor! 🪐❄️ #bilgidozu #shorts</t>
-        </is>
-      </c>
-      <c r="D119" s="8" t="inlineStr">
-        <is>
-          <t>Yörüngesinde 98 derece yan yatmış olan Uranüs'ün kutuplarında bir gündüz ve bir gece aralıksız 42 Dünya yılı sürer.
-Kırk iki yıl süren bir gecede mi yoksa kırk iki yıl süren gündüzde mi yaşamak isterdiniz? Yorumlara yazın! 👇
-📚 Kaynak: NASA Uranus Planetary Fact Sheet
-🎨 Görseller temsilîdir (AI üretimi).
-#bilgidozu #shorts #uranüs #uzay #bilim</t>
-        </is>
-      </c>
-      <c r="E119" s="8" t="inlineStr">
-        <is>
-          <t>#bilgidozu #shorts #uranüs #uzay #bilim #dozdışı</t>
-        </is>
-      </c>
-      <c r="F119" s="8" t="inlineStr">
-        <is>
-          <t>bilgi dozu, uranüs, uzay, gezegenler, astronomi, shorts, doz dışı</t>
-        </is>
-      </c>
-      <c r="G119" s="8" t="inlineStr">
-        <is>
-          <t>Kırk iki yıl süren bir gecede mi yoksa kırk iki yıl süren gündüzde mi yaşamak isterdiniz? Yorumlara yazın! 👇</t>
-        </is>
-      </c>
-      <c r="H119" s="8" t="inlineStr">
-        <is>
-          <t>Uzay ve Evren</t>
-        </is>
-      </c>
-      <c r="I119" s="8" t="inlineStr">
-        <is>
-          <t>NASA — Uranus Planetary Fact Sheet: https://science.nasa.gov/uranus/facts/</t>
-        </is>
-      </c>
-      <c r="J119" s="8" t="n"/>
-      <c r="K119" s="8" t="n"/>
-      <c r="L119" s="8" t="n"/>
-      <c r="M119" s="8" t="n"/>
-    </row>
-    <row r="120" ht="42" customHeight="1">
-      <c r="A120" s="7" t="inlineStr">
-        <is>
-          <t>ESKİ_STOK_ASKIDA</t>
-        </is>
-      </c>
-      <c r="B120" s="7" t="inlineStr">
-        <is>
-          <t>video_101.mp4</t>
-        </is>
-      </c>
-      <c r="C120" s="8" t="inlineStr">
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>video_91.mp4</t>
+        </is>
+      </c>
+      <c r="C110" s="8" t="inlineStr">
         <is>
           <t>Güneş Bir Saniyeliğine Sönseydi Ne Olurdu? ☀️🌑 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D120" s="8" t="inlineStr">
+      <c r="D110" s="8" t="inlineStr">
         <is>
           <t>Şu an başını kaldırıp gökyüzüne baktığında, Güneş'in hâlâ orada olduğundan gerçekten emin misin? Ya tam şu saniye sessizce söndüyse? İşin en ürpertici kısmı ne biliyor musun? Bunu tam sekiz dakika yirmi saniye boyunca ruhun bile duymayacak. Çünkü Güneş'ten çıkan son ışık gözüne ulaşana kadar gökyüzü masmavi kalır. Ama sekizinci dakikanın sonunda gökyüzü bir anda zifiri karanlığa gömülür ve Dünya yörüngeden kopup buzlu boşluğa savrulur. Peki sen o son sekiz dakikayı dışarıda gökyüzünü izleyerek mi geçirirdin, yoksa yeraltı sığınaklarına inerek mi? Yorumlarda buluşalım.
 💬 Peki böyle bir kırılma anında sen sekiz dakikalık son gün ışığını dışarıda izlemeyi mi seçerdin, yoksa doğrudan yeraltı sığınaklarına inmeyi mi? Yorumlarda buluşalım! 👇
@@ -7338,53 +6788,53 @@
 #bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
-      <c r="E120" s="8" t="inlineStr">
+      <c r="E110" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F120" s="8" t="inlineStr">
+      <c r="F110" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, güneş, uzay, kozmik felaket, astronomi, bilim, dünya, ışık hızı, ilginç bilgiler, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G120" s="8" t="inlineStr">
+      <c r="G110" s="8" t="inlineStr">
         <is>
           <t>Peki böyle bir kırılma anında sen sekiz dakikalık son gün ışığını dışarıda izlemeyi mi seçerdin, yoksa doğrudan yeraltı sığınaklarına inmeyi mi? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H120" s="8" t="inlineStr">
+      <c r="H110" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I120" s="8" t="inlineStr">
+      <c r="I110" s="8" t="inlineStr">
         <is>
           <t>NASA / Wikipedia — Sunlight (Işık Hızı ve Güneş Işığı Süresi): https://en.wikipedia.org/wiki/Sunlight</t>
         </is>
       </c>
-      <c r="J120" s="8" t="n"/>
-      <c r="K120" s="8" t="n"/>
-      <c r="L120" s="8" t="n"/>
-      <c r="M120" s="8" t="n"/>
-    </row>
-    <row r="121" ht="42" customHeight="1">
-      <c r="A121" s="7" t="inlineStr">
+      <c r="J110" s="8" t="n"/>
+      <c r="K110" s="8" t="n"/>
+      <c r="L110" s="8" t="n"/>
+      <c r="M110" s="8" t="n"/>
+    </row>
+    <row r="111" ht="42" customHeight="1">
+      <c r="A111" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B121" s="7" t="inlineStr">
-        <is>
-          <t>video_102.mp4</t>
-        </is>
-      </c>
-      <c r="C121" s="8" t="inlineStr">
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>video_92.mp4</t>
+        </is>
+      </c>
+      <c r="C111" s="8" t="inlineStr">
         <is>
           <t>Ay Dünya'ya Yaklaşsaydı Okyanuslara Ne Olurdu? 🌕🌊 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D121" s="8" t="inlineStr">
+      <c r="D111" s="8" t="inlineStr">
         <is>
           <t>Gece gökyüzüne baktığında, Ay'ın hep aynı yerde durduğunu sanıyorsun değil mi? Peki ya Ay Dünya'ya doğru yaklaşmaya başlasaydı ne olurdu? İlk başta gökyüzünde devasa görünürdü ama hemen ardından kütle çekim kabusu başlardı. Okyanuslar yüzlerce metre yükselip kıyı şehirlerini yutardı. Dünya'ya on sekiz bin kilometre mesafedeki Roche sınırına girdiği anda ise Ay gökyüzünde paramparça olur ve Dünya'nın etrafında tıpkı Satürn gibi parlak bir halka oluştururdu. Peki sen gökyüzünde Satürn gibi dev bir halka görmeyi mi isterdin, yoksa Ay'ın olduğu yerde kalmasını mı? Yorumlarda buluşalım.
 💬 Peki sen gökyüzünde dev bir Ay yerine Satürn gibi muazzam bir halka görmeyi mi isterdin, yoksa Ay'ın olduğu yerde kalmasını mı? Yorumlarda buluşalım! 👇
@@ -7393,53 +6843,53 @@
 #bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
-      <c r="E121" s="8" t="inlineStr">
+      <c r="E111" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F121" s="8" t="inlineStr">
+      <c r="F111" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, ay, dünya, roche sınırı, satürn, uzay, astronomi, bilim, kozmik felaket, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G121" s="8" t="inlineStr">
+      <c r="G111" s="8" t="inlineStr">
         <is>
           <t>Peki sen gökyüzünde dev bir Ay yerine Satürn gibi muazzam bir halka görmeyi mi isterdin, yoksa Ay'ın olduğu yerde kalmasını mı? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H121" s="8" t="inlineStr">
+      <c r="H111" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I121" s="8" t="inlineStr">
+      <c r="I111" s="8" t="inlineStr">
         <is>
           <t>NASA / Wikipedia — Roche Limit (Gelgit Parçalanma Sınırı): https://en.wikipedia.org/wiki/Roche_limit</t>
         </is>
       </c>
-      <c r="J121" s="8" t="n"/>
-      <c r="K121" s="8" t="n"/>
-      <c r="L121" s="8" t="n"/>
-      <c r="M121" s="8" t="n"/>
-    </row>
-    <row r="122" ht="42" customHeight="1">
-      <c r="A122" s="7" t="inlineStr">
+      <c r="J111" s="8" t="n"/>
+      <c r="K111" s="8" t="n"/>
+      <c r="L111" s="8" t="n"/>
+      <c r="M111" s="8" t="n"/>
+    </row>
+    <row r="112" ht="42" customHeight="1">
+      <c r="A112" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B122" s="7" t="inlineStr">
-        <is>
-          <t>video_103.mp4</t>
-        </is>
-      </c>
-      <c r="C122" s="8" t="inlineStr">
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>video_93.mp4</t>
+        </is>
+      </c>
+      <c r="C112" s="8" t="inlineStr">
         <is>
           <t>Uzayda Ağlarsan Gözyaşların Neden Yanağından Akmaz? 🧑‍🚀💧 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D122" s="8" t="inlineStr">
+      <c r="D112" s="8" t="inlineStr">
         <is>
           <t>Uzayda tek başına süzülürken bir anda ağlamaya başlasan gözyaşlarının yanağından aşağı süzüleceğini mi sanıyorsun? Hiç de öyle olmaz. Dünya'da gözyaşını aşağı çeken şey yerçekimidir. Ama uzayın ağırlıksız boşluğunda, su moleküllerini birbirine kenetleyen yüzey gerilimi tek patron haline gelir. Gözünden çıkan her damla, akmak yerine göz pınarının tam üzerinde şeffaf, titreyen bir su küresine dönüşür ve sen bir bezle silene kadar yüzünden asla ayrılmaz. Peki sen yerçekimsiz ortamda yaşamayı deneyimlemek mi isterdin, yoksa ayağının yere bastığı Dünya'da kalmayı mı? Yorumlarda buluşalım.
 💬 Peki sen yerçekimsiz ortamda haftalarca yaşamayı deneyimlemek mi isterdin, yoksa ayağının sağlamca yere bastığı Dünya'da kalmayı mı? Yorumlarda buluşalım! 👇
@@ -7448,53 +6898,53 @@
 #bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
-      <c r="E122" s="8" t="inlineStr">
+      <c r="E112" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F122" s="8" t="inlineStr">
+      <c r="F112" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, uzay, astronot, yerçekimi, yüzey gerilimi, bilim, fizik, uzay istasyonu, ilginç bilgiler, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G122" s="8" t="inlineStr">
+      <c r="G112" s="8" t="inlineStr">
         <is>
           <t>Peki sen yerçekimsiz ortamda haftalarca yaşamayı deneyimlemek mi isterdin, yoksa ayağının sağlamca yere bastığı Dünya'da kalmayı mı? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H122" s="8" t="inlineStr">
+      <c r="H112" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I122" s="8" t="inlineStr">
+      <c r="I112" s="8" t="inlineStr">
         <is>
           <t>CSA / Wikipedia — Surface Tension in Microgravity (Uzayda Yüzey Gerilimi): https://en.wikipedia.org/wiki/Surface_tension</t>
         </is>
       </c>
-      <c r="J122" s="8" t="n"/>
-      <c r="K122" s="8" t="n"/>
-      <c r="L122" s="8" t="n"/>
-      <c r="M122" s="8" t="n"/>
-    </row>
-    <row r="123" ht="42" customHeight="1">
-      <c r="A123" s="7" t="inlineStr">
+      <c r="J112" s="8" t="n"/>
+      <c r="K112" s="8" t="n"/>
+      <c r="L112" s="8" t="n"/>
+      <c r="M112" s="8" t="n"/>
+    </row>
+    <row r="113" ht="42" customHeight="1">
+      <c r="A113" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B123" s="7" t="inlineStr">
-        <is>
-          <t>video_104.mp4</t>
-        </is>
-      </c>
-      <c r="C123" s="8" t="inlineStr">
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>video_94.mp4</t>
+        </is>
+      </c>
+      <c r="C113" s="8" t="inlineStr">
         <is>
           <t>Dünya'ya 50 Işık Yılı Mesafede Süpernova Patlasa Ne Olur? 💥🌟 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D123" s="8" t="inlineStr">
+      <c r="D113" s="8" t="inlineStr">
         <is>
           <t>Gündüz vakti masmavi gökyüzünde bir anda ikinci bir Güneş'in parladığını hayal et. Dünya'ya elli ışık yılı mesafede dev bir yıldız süpernova olarak patlasaydı tam olarak bunu yaşardık. Haftalarca geceleri bile gökyüzü hiç kararmazdı. Ama asıl tehlike o parlak ışık değil, görünmez gama ışınları olurdu. Üst atmosferdeki ozon tabakası hızla erir ve yüzeye inen radyasyon okyanuslardaki besin zincirini altüst ederdi. Peki böyle bir kozmik patlama görsen, önce teleskopla izlemeye mi koşardın yoksa radyasyondan korunacak bir yer mi arardın? Yorumlarda buluşalım.
 💬 Peki böyle bir kozmik patlama görsen önce teleskopla izlemeye mi koşardın, yoksa radyasyondan korunacak bir yer mi arardın? Yorumlarda buluşalım! 👇
@@ -7503,53 +6953,53 @@
 #bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
-      <c r="E123" s="8" t="inlineStr">
+      <c r="E113" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F123" s="8" t="inlineStr">
+      <c r="F113" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, süpernova, uzay, gama ışınları, kozmik felaket, yıldız, astronomi, bilim, dünya, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G123" s="8" t="inlineStr">
+      <c r="G113" s="8" t="inlineStr">
         <is>
           <t>Peki böyle bir kozmik patlama görsen önce teleskopla izlemeye mi koşardın, yoksa radyasyondan korunacak bir yer mi arardın? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H123" s="8" t="inlineStr">
+      <c r="H113" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I123" s="8" t="inlineStr">
+      <c r="I113" s="8" t="inlineStr">
         <is>
           <t>NASA / Wikipedia — Near-Earth Supernova (Yakın Süpernova Etkileri): https://en.wikipedia.org/wiki/Near-Earth_supernova</t>
         </is>
       </c>
-      <c r="J123" s="8" t="n"/>
-      <c r="K123" s="8" t="n"/>
-      <c r="L123" s="8" t="n"/>
-      <c r="M123" s="8" t="n"/>
-    </row>
-    <row r="124" ht="42" customHeight="1">
-      <c r="A124" s="7" t="inlineStr">
+      <c r="J113" s="8" t="n"/>
+      <c r="K113" s="8" t="n"/>
+      <c r="L113" s="8" t="n"/>
+      <c r="M113" s="8" t="n"/>
+    </row>
+    <row r="114" ht="42" customHeight="1">
+      <c r="A114" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B124" s="7" t="inlineStr">
-        <is>
-          <t>video_105.mp4</t>
-        </is>
-      </c>
-      <c r="C124" s="8" t="inlineStr">
+      <c r="B114" s="7" t="inlineStr">
+        <is>
+          <t>video_95.mp4</t>
+        </is>
+      </c>
+      <c r="C114" s="8" t="inlineStr">
         <is>
           <t>Bir Çay Kaşığı Nötron Yıldızı Dünya'ya Düşse Ne Olur? 🥄🌌 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D124" s="8" t="inlineStr">
+      <c r="D114" s="8" t="inlineStr">
         <is>
           <t>Elindeki küçücük bir çay kaşığının Everest Dağı kadar ağır olabileceğini hayal edebilir misin? Evrenin en ekstrem canavarı olan nötron yıldızlarıyla tanış. Dev bir yıldız çöktüğünde çekirdeği o kadar korkunç sıkışır ki, koca bir Güneş sadece yirmi kilometre çapında bir küreye hapsolur. Bu yıldızdan alacağın tek bir çay kaşığı madde tam bir milyar ton ağırlığındadır. Onu Dünya'da elinden bıraksan toprağı ve kayaları delip doğrudan gezegenin çekirdeğine kadar batardı. Peki seni uzayda en çok büyüleyen şey, kara delikler mi yoksa nötron yıldızları mı? Yorumlarda buluşalım.
 💬 Peki seni uzayda en çok büyüleyen şey her şeyi yutan kara delikler mi, yoksa bu inanılmaz yoğunluktaki nötron yıldızları mı? Yorumlarda buluşalım! 👇
@@ -7558,53 +7008,53 @@
 #bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
-      <c r="E124" s="8" t="inlineStr">
+      <c r="E114" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F124" s="8" t="inlineStr">
+      <c r="F114" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, nötron yıldızı, kara delik, uzay, astronomi, fizik, bilim, evren, ilginç bilgiler, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G124" s="8" t="inlineStr">
+      <c r="G114" s="8" t="inlineStr">
         <is>
           <t>Peki seni uzayda en çok büyüleyen şey her şeyi yutan kara delikler mi, yoksa bu inanılmaz yoğunluktaki nötron yıldızları mı? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H124" s="8" t="inlineStr">
+      <c r="H114" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I124" s="8" t="inlineStr">
+      <c r="I114" s="8" t="inlineStr">
         <is>
           <t>NASA / Wikipedia — Neutron Star (Nötron Yıldızı Yoğunluğu): https://en.wikipedia.org/wiki/Neutron_star</t>
         </is>
       </c>
-      <c r="J124" s="8" t="n"/>
-      <c r="K124" s="8" t="n"/>
-      <c r="L124" s="8" t="n"/>
-      <c r="M124" s="8" t="n"/>
-    </row>
-    <row r="125" ht="42" customHeight="1">
-      <c r="A125" s="7" t="inlineStr">
+      <c r="J114" s="8" t="n"/>
+      <c r="K114" s="8" t="n"/>
+      <c r="L114" s="8" t="n"/>
+      <c r="M114" s="8" t="n"/>
+    </row>
+    <row r="115" ht="42" customHeight="1">
+      <c r="A115" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B125" s="7" t="inlineStr">
-        <is>
-          <t>video_111.mp4</t>
-        </is>
-      </c>
-      <c r="C125" s="8" t="inlineStr">
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>video_101.mp4</t>
+        </is>
+      </c>
+      <c r="C115" s="8" t="inlineStr">
         <is>
           <t>Dünya'nın En Issız Noktası Point Nemo: En Yakın İnsanlar Uzayda! 🌊🛰️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D125" s="8" t="inlineStr">
+      <c r="D115" s="8" t="inlineStr">
         <is>
           <t>Dünya üzerinde öyle ıssız bir nokta var ki, orada bir tekneyle mahsur kalsan sana en yakın insanlar Dünya'da değil, uzayda olurdu. Güney Pasifik Okyanusu'nun ortasındaki Point Nemo ile tanış. Burası en yakın kara parçasına tam 2.688 kilometre uzaklıktadır. Buna karşılık, Uluslararası Uzay İstasyonu başının sadece 400 kilometre üzerinden geçer. Yani gökyüzündeki astronotlar, sana karadaki insanlardan tam 6 kat daha yakındır. Uzay ajansları da ömrü biten uyduları bu dev su mezarlığına düşürür. Peki sen böyle mutlak bir sessizliğin ortasında tek başına bir gece geçirmeye cesaret edebilir miydin, yoksa kıyıdan asla ayrılmaz mıydın? Yorumlarda buluşalım!
 💬 Peki sen böyle mutlak bir sessizliğin ortasında tek başına bir gece geçirmeye cesaret edebilir miydin, yoksa kıyıdan asla ayrılmaz mıydın? Yorumlarda buluşalım! 👇
@@ -7613,53 +7063,53 @@
 #bilgidozu #shorts #doğa #okyanus #coğrafya #bilim</t>
         </is>
       </c>
-      <c r="E125" s="8" t="inlineStr">
+      <c r="E115" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #okyanus #coğrafya #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F125" s="8" t="inlineStr">
+      <c r="F115" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, point nemo, güney pasifik, dünyanın en ıssız noktası, uydu mezarlığı, uluslararası uzay istasyonu, coğrafya, doğa, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G125" s="8" t="inlineStr">
+      <c r="G115" s="8" t="inlineStr">
         <is>
           <t>Peki sen böyle mutlak bir sessizliğin ortasında tek başına bir gece geçirmeye cesaret edebilir miydin, yoksa kıyıdan asla ayrılmaz mıydın? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H125" s="8" t="inlineStr">
+      <c r="H115" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I125" s="8" t="inlineStr">
+      <c r="I115" s="8" t="inlineStr">
         <is>
           <t>NOAA / Wikipedia — Oceanic Pole of Inaccessibility (Point Nemo): https://en.wikipedia.org/wiki/Pole_of_inaccessibility</t>
         </is>
       </c>
-      <c r="J125" s="8" t="n"/>
-      <c r="K125" s="8" t="n"/>
-      <c r="L125" s="8" t="n"/>
-      <c r="M125" s="8" t="n"/>
-    </row>
-    <row r="126" ht="42" customHeight="1">
-      <c r="A126" s="7" t="inlineStr">
+      <c r="J115" s="8" t="n"/>
+      <c r="K115" s="8" t="n"/>
+      <c r="L115" s="8" t="n"/>
+      <c r="M115" s="8" t="n"/>
+    </row>
+    <row r="116" ht="42" customHeight="1">
+      <c r="A116" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B126" s="7" t="inlineStr">
-        <is>
-          <t>video_112.mp4</t>
-        </is>
-      </c>
-      <c r="C126" s="8" t="inlineStr">
+      <c r="B116" s="7" t="inlineStr">
+        <is>
+          <t>video_102.mp4</t>
+        </is>
+      </c>
+      <c r="C116" s="8" t="inlineStr">
         <is>
           <t>Antarktika'daki Buzuldan Neden Kan Kırmızısı Şelale Akıyor? 🧊🩸 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D126" s="8" t="inlineStr">
+      <c r="D116" s="8" t="inlineStr">
         <is>
           <t>Antarktika'nın bembeyaz, dondurucu buzullarının arasından bir anda kıpkırmızı, kan renginde bir şelalenin aktığını görsen ne düşünürdün? Taylor Buzulu'ndaki bu ürpertici manzaranın sebebi kan ya da yosun değil, tam 5 milyon yıl önce buzulun 400 metre altına hapsolmuş antik bir yeraltı gölü. Bu gizli gölün suyu okyanuslardan 3 kat daha tuzlu olduğu için dondurucu soğukta bile asla donmuyor. İçindeki yoğun demir, buzulun çatlaklarından sızıp milyonlarca yıl sonra ilk kez havadaki oksijenle temas ettiği anda saniyeler içinde paslanarak kıpkırmızı bir şelaleye dönüşüyor. Peki sen Antarktika'daki bu gizemli buzulun yanına gitmeyi mi seçerdin, yoksa sıcak bir tropik adada kalmayı mı? Yorumlarda buluşalım!
 💬 Peki sen Antarktika'daki bu gizemli buzulun yanına gitmeyi mi seçerdin, yoksa sıcak bir tropik adada kalmayı mı? Yorumlarda buluşalım! 👇
@@ -7668,53 +7118,53 @@
 #bilgidozu #shorts #antarktika #doğa #coğrafya #bilim</t>
         </is>
       </c>
-      <c r="E126" s="8" t="inlineStr">
+      <c r="E116" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #antarktika #doğa #coğrafya #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F126" s="8" t="inlineStr">
+      <c r="F116" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, kan şelalesi, blood falls, antarktika, taylor buzulu, doğa olayları, coğrafya, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G126" s="8" t="inlineStr">
+      <c r="G116" s="8" t="inlineStr">
         <is>
           <t>Peki sen Antarktika'daki bu gizemli buzulun yanına gitmeyi mi seçerdin, yoksa sıcak bir tropik adada kalmayı mı? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H126" s="8" t="inlineStr">
+      <c r="H116" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I126" s="8" t="inlineStr">
+      <c r="I116" s="8" t="inlineStr">
         <is>
           <t>NSF / Wikipedia — Blood Falls, Taylor Glacier Antarctica (Kan Şelalesi): https://en.wikipedia.org/wiki/Blood_Falls</t>
         </is>
       </c>
-      <c r="J126" s="8" t="n"/>
-      <c r="K126" s="8" t="n"/>
-      <c r="L126" s="8" t="n"/>
-      <c r="M126" s="8" t="n"/>
-    </row>
-    <row r="127" ht="42" customHeight="1">
-      <c r="A127" s="7" t="inlineStr">
+      <c r="J116" s="8" t="n"/>
+      <c r="K116" s="8" t="n"/>
+      <c r="L116" s="8" t="n"/>
+      <c r="M116" s="8" t="n"/>
+    </row>
+    <row r="117" ht="42" customHeight="1">
+      <c r="A117" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B127" s="7" t="inlineStr">
-        <is>
-          <t>video_113.mp4</t>
-        </is>
-      </c>
-      <c r="C127" s="8" t="inlineStr">
+      <c r="B117" s="7" t="inlineStr">
+        <is>
+          <t>video_103.mp4</t>
+        </is>
+      </c>
+      <c r="C117" s="8" t="inlineStr">
         <is>
           <t>5,5 Milyon Yıldır Güneş Görmeyen Mühürlü Mağara: Movile! 🕳️🕷️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D127" s="8" t="inlineStr">
+      <c r="D117" s="8" t="inlineStr">
         <is>
           <t>Tam 5,5 milyon yıl boyunca güneş ışığının tek bir zerresini bile görmemiş, mühürlü bir yeraltı dünyasının kapısını açtığını hayal et. Romanya'da tesadüfen keşfedilen Movile Mağarası, dış dünyadan tamamen kopuk bambaşka bir gezegen gibi. İçerideki havada oksijen normalin yarısından bile az, atmosferi ise zehirli hidrojen sülfür ve karbondioksitle dolu. Güneş ışığı olmadığı için buradaki yaşam tamamen kimyasal enerjiyle ayakta kalıyor ve içeride gözleri yok olmuş, sadece buraya özgü 30'dan fazla gizemli canlı türü yaşıyor. Peki özel bir oksijen tüpüyle bu karanlık mağaraya inme şansın olsa içeri adım atar mıydın, yoksa kapısını mühürlü mü bırakırdın? Yorumlarda buluşalım!
 💬 Peki özel bir oksijen tüpüyle bu karanlık mağaraya inme şansın olsa içeri adım atar mıydın, yoksa kapısını mühürlü mü bırakırdın? Yorumlarda buluşalım! 👇
@@ -7723,53 +7173,53 @@
 #bilgidozu #shorts #mağara #doğa #biyoloji #bilim</t>
         </is>
       </c>
-      <c r="E127" s="8" t="inlineStr">
+      <c r="E117" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #mağara #doğa #biyoloji #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F127" s="8" t="inlineStr">
+      <c r="F117" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, movile mağarası, mühürlü mağara, romanya, kemosentez, gizemli yerler, doğa, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G127" s="8" t="inlineStr">
+      <c r="G117" s="8" t="inlineStr">
         <is>
           <t>Peki özel bir oksijen tüpüyle bu karanlık mağaraya inme şansın olsa içeri adım atar mıydın, yoksa kapısını mühürlü mü bırakırdın? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H127" s="8" t="inlineStr">
+      <c r="H117" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I127" s="8" t="inlineStr">
+      <c r="I117" s="8" t="inlineStr">
         <is>
           <t>BBC / Wikipedia — Movile Cave Chemosynthesis Ecosystem (Movile Mağarası): https://en.wikipedia.org/wiki/Movile_Cave</t>
         </is>
       </c>
-      <c r="J127" s="8" t="n"/>
-      <c r="K127" s="8" t="n"/>
-      <c r="L127" s="8" t="n"/>
-      <c r="M127" s="8" t="n"/>
-    </row>
-    <row r="128" ht="42" customHeight="1">
-      <c r="A128" s="7" t="inlineStr">
+      <c r="J117" s="8" t="n"/>
+      <c r="K117" s="8" t="n"/>
+      <c r="L117" s="8" t="n"/>
+      <c r="M117" s="8" t="n"/>
+    </row>
+    <row r="118" ht="42" customHeight="1">
+      <c r="A118" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B128" s="7" t="inlineStr">
-        <is>
-          <t>video_114.mp4</t>
-        </is>
-      </c>
-      <c r="C128" s="8" t="inlineStr">
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t>video_104.mp4</t>
+        </is>
+      </c>
+      <c r="C118" s="8" t="inlineStr">
         <is>
           <t>Dallol Volkanı: Dünya Üzerindeki En Asidik ve Renkli Cehennem! 🌋🧪 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D128" s="8" t="inlineStr">
+      <c r="D118" s="8" t="inlineStr">
         <is>
           <t>Şu gördüğün neon sarısı ve zümrüt yeşili göller başka bir gezegene değil, Dünya üzerindeki en tehlikeli cehenneme ait. Etiyopya'daki Danakil Çöküntüsü'nde yer alan Dallol Volkanı, deniz seviyesinin 48 metre altında kaynayan dev bir kimya laboratuvarı gibidir. Yerin altındaki kızgın magma, kalın tuz ve kükürt yataklarıyla buluştuğunda, yüzeye akü asidinden bile daha yakıcı kaynar sular ve zehirli klor gazları fışkırır. Burada maskesiz uzun süre nefes almak bile imkânsızdır. Peki sen uzaylı bir gezegeni andıran bu yeri uzaktan dronelarla izlemeyi mi seçerdin, yoksa özel koruyucu kıyafetle yanına kadar yürümeyi mi? Yorumlarda buluşalım!
 💬 Peki sen uzaylı bir gezegeni andıran bu yeri uzaktan dronelarla izlemeyi mi seçerdin, yoksa özel koruyucu kıyafetle yanına kadar yürümeyi mi? Yorumlarda buluşalım! 👇
@@ -7778,53 +7228,53 @@
 #bilgidozu #shorts #volkan #doğa #coğrafya #bilim</t>
         </is>
       </c>
-      <c r="E128" s="8" t="inlineStr">
+      <c r="E118" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #volkan #doğa #coğrafya #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F128" s="8" t="inlineStr">
+      <c r="F118" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, dallol volkanı, danakil çöküntüsü, etiyopya, asit gölleri, ekstrem doğa, coğrafya, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G128" s="8" t="inlineStr">
+      <c r="G118" s="8" t="inlineStr">
         <is>
           <t>Peki sen uzaylı bir gezegeni andıran bu yeri uzaktan dronelarla izlemeyi mi seçerdin, yoksa özel koruyucu kıyafetle yanına kadar yürümeyi mi? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H128" s="8" t="inlineStr">
+      <c r="H118" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I128" s="8" t="inlineStr">
+      <c r="I118" s="8" t="inlineStr">
         <is>
           <t>Nature Ecology &amp; Evolution / Wikipedia — Dallol Hydrothermal System: https://en.wikipedia.org/wiki/Dallol_(hydrothermal_system)</t>
         </is>
       </c>
-      <c r="J128" s="8" t="n"/>
-      <c r="K128" s="8" t="n"/>
-      <c r="L128" s="8" t="n"/>
-      <c r="M128" s="8" t="n"/>
-    </row>
-    <row r="129" ht="42" customHeight="1">
-      <c r="A129" s="7" t="inlineStr">
+      <c r="J118" s="8" t="n"/>
+      <c r="K118" s="8" t="n"/>
+      <c r="L118" s="8" t="n"/>
+      <c r="M118" s="8" t="n"/>
+    </row>
+    <row r="119" ht="42" customHeight="1">
+      <c r="A119" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B129" s="7" t="inlineStr">
-        <is>
-          <t>video_115.mp4</t>
-        </is>
-      </c>
-      <c r="C129" s="8" t="inlineStr">
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>video_105.mp4</t>
+        </is>
+      </c>
+      <c r="C119" s="8" t="inlineStr">
         <is>
           <t>Yerin 2.224 Metre Altında Ne Var? Dünya'nın En Derin Mağarası! 🧗‍♂️🌑 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D129" s="8" t="inlineStr">
+      <c r="D119" s="8" t="inlineStr">
         <is>
           <t>Yerin tam 2.224 metre altına, yani üst üste dizilmiş 7 Eyfel Kulesi derinliğine karanlık bir kuyudan indiğini hayal et. Kafkas Dağları'ndaki Krubera Mağarası, Dünya'nın bilinen en derin uçurumlarından biridir. Buraya inen mağaracıların en dibe ulaşması haftalar sürer ve içeride yeraltı şelaleleriyle buz gibi su tünelleri vardır. En şaşırtıcı olanı ise, 2.000 metre derinlikteki o dondurucu ve ışıksız sularda bile dış dünyayı hiç görmemiş şeffaf canlıların yaşamaya devam etmesidir. Peki sana sınırsız ekipman verilse okyanusun en derin çukuruna dalmayı mı seçerdin, yoksa Dünya'nın en derin mağarasına inmeyi mi? Yorumlarda buluşalım!
 💬 Peki sana sınırsız ekipman verilse okyanusun en derin çukuruna dalmayı mı seçerdin, yoksa Dünya'nın en derin mağarasına inmeyi mi? Yorumlarda buluşalım! 👇
@@ -7833,53 +7283,53 @@
 #bilgidozu #shorts #mağara #doğa #keşif #bilim</t>
         </is>
       </c>
-      <c r="E129" s="8" t="inlineStr">
+      <c r="E119" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #mağara #doğa #keşif #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F129" s="8" t="inlineStr">
+      <c r="F119" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, krubera mağarası, dünyanın en derin mağarası, kafkas dağları, mağaracılık, doğa, coğrafya, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G129" s="8" t="inlineStr">
+      <c r="G119" s="8" t="inlineStr">
         <is>
           <t>Peki sana sınırsız ekipman verilse okyanusun en derin çukuruna dalmayı mı seçerdin, yoksa Dünya'nın en derin mağarasına inmeyi mi? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H129" s="8" t="inlineStr">
+      <c r="H119" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I129" s="8" t="inlineStr">
+      <c r="I119" s="8" t="inlineStr">
         <is>
           <t>National Geographic / Wikipedia — Krubera Cave (Dünya'nın En Derin Mağaraları): https://en.wikipedia.org/wiki/Krubera_Cave</t>
         </is>
       </c>
-      <c r="J129" s="8" t="n"/>
-      <c r="K129" s="8" t="n"/>
-      <c r="L129" s="8" t="n"/>
-      <c r="M129" s="8" t="n"/>
-    </row>
-    <row r="130" ht="42" customHeight="1">
-      <c r="A130" s="7" t="inlineStr">
+      <c r="J119" s="8" t="n"/>
+      <c r="K119" s="8" t="n"/>
+      <c r="L119" s="8" t="n"/>
+      <c r="M119" s="8" t="n"/>
+    </row>
+    <row r="120" ht="42" customHeight="1">
+      <c r="A120" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B130" s="7" t="inlineStr">
-        <is>
-          <t>video_116.mp4</t>
-        </is>
-      </c>
-      <c r="C130" s="8" t="inlineStr">
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t>video_106.mp4</t>
+        </is>
+      </c>
+      <c r="C120" s="8" t="inlineStr">
         <is>
           <t>2.100 Yıllık Batıktan Çıkan İlk Analog Bilgisayar: Antikythera! ⚙️🏛️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D130" s="8" t="inlineStr">
+      <c r="D120" s="8" t="inlineStr">
         <is>
           <t>Denizin dibinde iki bin yıl boyunca paslanmış bir Yunan batığından, modern saatler kadar karmaşık dişlilere sahip antik bir bilgisayar çıktığını biliyor muydun?
 💬 Peki sence antik dünyada bunun gibi henüz keşfedemediğimiz başka yüksek teknolojiler de var mıdır, yoksa bu tek bir dahinin eseri miydi? Yorumlarda buluşalım! 👇
@@ -7888,53 +7338,53 @@
 #bilgidozu #shorts #tarih #arkeoloji #bilim</t>
         </is>
       </c>
-      <c r="E130" s="8" t="inlineStr">
+      <c r="E120" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #arkeoloji #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F130" s="8" t="inlineStr">
+      <c r="F120" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, antik mühendislik, tarih, arkeoloji, gizemli yapılar, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G130" s="8" t="inlineStr">
+      <c r="G120" s="8" t="inlineStr">
         <is>
           <t>Peki sence antik dünyada bunun gibi henüz keşfedemediğimiz başka yüksek teknolojiler de var mıdır, yoksa bu tek bir dahinin eseri miydi? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H130" s="8" t="inlineStr">
+      <c r="H120" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Antik Mühendislik</t>
         </is>
       </c>
-      <c r="I130" s="8" t="inlineStr">
+      <c r="I120" s="8" t="inlineStr">
         <is>
           <t>Nature / Wikipedia — Antikythera Mechanism (2.100 Yıllık Antik Analog Bilgisayar): https://en.wikipedia.org/wiki/Antikythera_mechanism</t>
         </is>
       </c>
-      <c r="J130" s="8" t="n"/>
-      <c r="K130" s="8" t="n"/>
-      <c r="L130" s="8" t="n"/>
-      <c r="M130" s="8" t="n"/>
-    </row>
-    <row r="131" ht="42" customHeight="1">
-      <c r="A131" s="7" t="inlineStr">
+      <c r="J120" s="8" t="n"/>
+      <c r="K120" s="8" t="n"/>
+      <c r="L120" s="8" t="n"/>
+      <c r="M120" s="8" t="n"/>
+    </row>
+    <row r="121" ht="42" customHeight="1">
+      <c r="A121" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B131" s="7" t="inlineStr">
-        <is>
-          <t>video_117.mp4</t>
-        </is>
-      </c>
-      <c r="C131" s="8" t="inlineStr">
+      <c r="B121" s="7" t="inlineStr">
+        <is>
+          <t>video_107.mp4</t>
+        </is>
+      </c>
+      <c r="C121" s="8" t="inlineStr">
         <is>
           <t>Derinkuyu Yeraltı Şehri: 20 Bin Kişi Yerin Altında Nasıl Nefes Aldı? 🏺🕯️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D131" s="8" t="inlineStr">
+      <c r="D121" s="8" t="inlineStr">
         <is>
           <t>Kapadokya'nın altında, yirmi bin insanın hayvanları ve erzaklarıyla birlikte haftalarca hiç yeryüzüne çıkmadan yaşayabildiği sekiz katlı dev bir yeraltı şehri var: Derinkuyu.
 💬 Peki sen tehlike anında haftalarca böyle bir yeraltı şehrinde yaşayabilir miydin, yoksa kapalı alanda daralır mıydın? Yorumlarda buluşalım! 👇
@@ -7943,53 +7393,53 @@
 #bilgidozu #shorts #tarih #arkeoloji #bilim</t>
         </is>
       </c>
-      <c r="E131" s="8" t="inlineStr">
+      <c r="E121" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #arkeoloji #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F131" s="8" t="inlineStr">
+      <c r="F121" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, antik mühendislik, tarih, arkeoloji, gizemli yapılar, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G131" s="8" t="inlineStr">
+      <c r="G121" s="8" t="inlineStr">
         <is>
           <t>Peki sen tehlike anında haftalarca böyle bir yeraltı şehrinde yaşayabilir miydin, yoksa kapalı alanda daralır mıydın? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H131" s="8" t="inlineStr">
+      <c r="H121" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Antik Mühendislik</t>
         </is>
       </c>
-      <c r="I131" s="8" t="inlineStr">
+      <c r="I121" s="8" t="inlineStr">
         <is>
           <t>UNESCO / Wikipedia — Derinkuyu Underground City (Derinkuyu Yeraltı Şehri): https://en.wikipedia.org/wiki/Derinkuyu_underground_city</t>
         </is>
       </c>
-      <c r="J131" s="8" t="n"/>
-      <c r="K131" s="8" t="n"/>
-      <c r="L131" s="8" t="n"/>
-      <c r="M131" s="8" t="n"/>
-    </row>
-    <row r="132" ht="42" customHeight="1">
-      <c r="A132" s="7" t="inlineStr">
+      <c r="J121" s="8" t="n"/>
+      <c r="K121" s="8" t="n"/>
+      <c r="L121" s="8" t="n"/>
+      <c r="M121" s="8" t="n"/>
+    </row>
+    <row r="122" ht="42" customHeight="1">
+      <c r="A122" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B132" s="7" t="inlineStr">
-        <is>
-          <t>video_118.mp4</t>
-        </is>
-      </c>
-      <c r="C132" s="8" t="inlineStr">
+      <c r="B122" s="7" t="inlineStr">
+        <is>
+          <t>video_108.mp4</t>
+        </is>
+      </c>
+      <c r="C122" s="8" t="inlineStr">
         <is>
           <t>Voynich El Yazması: 600 Yıldır Kimsenin Okuyamadığı Şifreli Kitap! 📜🔍 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D132" s="8" t="inlineStr">
+      <c r="D122" s="8" t="inlineStr">
         <is>
           <t>Dünyanın en iyi şifre çözücüleri, dilbilimcileri ve yapay zekâları bir araya geldi ama altı yüz yıllık bu kitabın tek bir cümlesini bile okuyamadı: Voynich El Yazması.
 💬 Peki sence bu kitap unutulmuş gizli bir bilimin şifreli kaydı mı, yoksa tarihin en zekice kurgulanmış bilmecesi mi? Yorumlarda buluşalım! 👇
@@ -7998,53 +7448,53 @@
 #bilgidozu #shorts #tarih #arkeoloji #bilim</t>
         </is>
       </c>
-      <c r="E132" s="8" t="inlineStr">
+      <c r="E122" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #arkeoloji #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F132" s="8" t="inlineStr">
+      <c r="F122" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, antik mühendislik, tarih, arkeoloji, gizemli yapılar, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G132" s="8" t="inlineStr">
+      <c r="G122" s="8" t="inlineStr">
         <is>
           <t>Peki sence bu kitap unutulmuş gizli bir bilimin şifreli kaydı mı, yoksa tarihin en zekice kurgulanmış bilmecesi mi? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H132" s="8" t="inlineStr">
+      <c r="H122" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Antik Mühendislik</t>
         </is>
       </c>
-      <c r="I132" s="8" t="inlineStr">
+      <c r="I122" s="8" t="inlineStr">
         <is>
           <t>Yale Beinecke Library / Wikipedia — Voynich Manuscript (Voynich El Yazması): https://en.wikipedia.org/wiki/Voynich_manuscript</t>
         </is>
       </c>
-      <c r="J132" s="8" t="n"/>
-      <c r="K132" s="8" t="n"/>
-      <c r="L132" s="8" t="n"/>
-      <c r="M132" s="8" t="n"/>
-    </row>
-    <row r="133" ht="42" customHeight="1">
-      <c r="A133" s="7" t="inlineStr">
+      <c r="J122" s="8" t="n"/>
+      <c r="K122" s="8" t="n"/>
+      <c r="L122" s="8" t="n"/>
+      <c r="M122" s="8" t="n"/>
+    </row>
+    <row r="123" ht="42" customHeight="1">
+      <c r="A123" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B133" s="7" t="inlineStr">
-        <is>
-          <t>video_119.mp4</t>
-        </is>
-      </c>
-      <c r="C133" s="8" t="inlineStr">
+      <c r="B123" s="7" t="inlineStr">
+        <is>
+          <t>video_109.mp4</t>
+        </is>
+      </c>
+      <c r="C123" s="8" t="inlineStr">
         <is>
           <t>Puma Punku H-Blokları: Jilet Bile Girmeyen Antik Taşların Sırrı! 🪨📐 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D133" s="8" t="inlineStr">
+      <c r="D123" s="8" t="inlineStr">
         <is>
           <t>Deniz seviyesinden üç bin sekiz yüz metre yüksekte, aralarına jilet bile girmeyecek kadar kusursuz kesilmiş yüz tonluk taş bloklar düşün: Puma Punku.
 💬 Peki sence antik ustalar bu kusursuz taş işçiliğini sabırlı el aletleriyle mi başardı, yoksa bugün unuttuğumuz özel bir teknikleri mi vardı? Yorumlarda buluşalım! 👇
@@ -8053,53 +7503,53 @@
 #bilgidozu #shorts #tarih #arkeoloji #bilim</t>
         </is>
       </c>
-      <c r="E133" s="8" t="inlineStr">
+      <c r="E123" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #arkeoloji #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F133" s="8" t="inlineStr">
+      <c r="F123" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, antik mühendislik, tarih, arkeoloji, gizemli yapılar, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G133" s="8" t="inlineStr">
+      <c r="G123" s="8" t="inlineStr">
         <is>
           <t>Peki sence antik ustalar bu kusursuz taş işçiliğini sabırlı el aletleriyle mi başardı, yoksa bugün unuttuğumuz özel bir teknikleri mi vardı? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H133" s="8" t="inlineStr">
+      <c r="H123" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Antik Mühendislik</t>
         </is>
       </c>
-      <c r="I133" s="8" t="inlineStr">
+      <c r="I123" s="8" t="inlineStr">
         <is>
           <t>UNESCO / Wikipedia — Pumapunku Andesite Megaliths (Puma Punku H-Blokları): https://en.wikipedia.org/wiki/Pumapunku</t>
         </is>
       </c>
-      <c r="J133" s="8" t="n"/>
-      <c r="K133" s="8" t="n"/>
-      <c r="L133" s="8" t="n"/>
-      <c r="M133" s="8" t="n"/>
-    </row>
-    <row r="134" ht="42" customHeight="1">
-      <c r="A134" s="7" t="inlineStr">
+      <c r="J123" s="8" t="n"/>
+      <c r="K123" s="8" t="n"/>
+      <c r="L123" s="8" t="n"/>
+      <c r="M123" s="8" t="n"/>
+    </row>
+    <row r="124" ht="42" customHeight="1">
+      <c r="A124" s="7" t="inlineStr">
         <is>
           <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
-      <c r="B134" s="7" t="inlineStr">
-        <is>
-          <t>video_120.mp4</t>
-        </is>
-      </c>
-      <c r="C134" s="8" t="inlineStr">
+      <c r="B124" s="7" t="inlineStr">
+        <is>
+          <t>video_110.mp4</t>
+        </is>
+      </c>
+      <c r="C124" s="8" t="inlineStr">
         <is>
           <t>Babil'in Asma Bahçeleri Gerçekte Babil'de Değil Miydi? 🌿🏛️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D134" s="8" t="inlineStr">
+      <c r="D124" s="8" t="inlineStr">
         <is>
           <t>Dünyanın Yedi Harikası'ndan biri sayılan Babil'in Asma Bahçeleri'nin aslında hiçbir zaman Babil'de olmadığını duysan ne derdin?
 💬 Peki sen geçmişe gidebilsen önce bu efsanevi Asma Bahçeleri'ni mi görmek isterdin, yoksa İskenderiye Kütüphanesi'ni mi? Yorumlarda buluşalım! 👇
@@ -8108,53 +7558,53 @@
 #bilgidozu #shorts #tarih #arkeoloji #bilim</t>
         </is>
       </c>
-      <c r="E134" s="8" t="inlineStr">
+      <c r="E124" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #arkeoloji #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F134" s="8" t="inlineStr">
+      <c r="F124" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, antik mühendislik, tarih, arkeoloji, gizemli yapılar, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G134" s="8" t="inlineStr">
+      <c r="G124" s="8" t="inlineStr">
         <is>
           <t>Peki sen geçmişe gidebilsen önce bu efsanevi Asma Bahçeleri'ni mi görmek isterdin, yoksa İskenderiye Kütüphanesi'ni mi? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H134" s="8" t="inlineStr">
+      <c r="H124" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Antik Mühendislik</t>
         </is>
       </c>
-      <c r="I134" s="8" t="inlineStr">
+      <c r="I124" s="8" t="inlineStr">
         <is>
           <t>Oxford University (Stephanie Dalley) / Wikipedia — Hanging Gardens of Babylon: https://en.wikipedia.org/wiki/Hanging_Gardens_of_Babylon</t>
         </is>
       </c>
-      <c r="J134" s="8" t="n"/>
-      <c r="K134" s="8" t="n"/>
-      <c r="L134" s="8" t="n"/>
-      <c r="M134" s="8" t="n"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="9" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B135" s="9" t="inlineStr">
+      <c r="J124" s="8" t="n"/>
+      <c r="K124" s="8" t="n"/>
+      <c r="L124" s="8" t="n"/>
+      <c r="M124" s="8" t="n"/>
+    </row>
+    <row r="125" ht="42" customHeight="1">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>video_131.mp4</t>
         </is>
       </c>
-      <c r="C135" s="9" t="inlineStr">
+      <c r="C125" s="3" t="inlineStr">
         <is>
           <t>Küçücük Kâğıt Kesiği Neden Bu Kadar Çok Acıtır? 🩹⚡ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D135" s="9" t="inlineStr">
+      <c r="D125" s="3" t="inlineStr">
         <is>
           <t>Küçücük bir kâğıt kesiği neden beklediğinden çok daha fazla can yakar? Parmak uçlarımız dokunma ve ağrıyı algılayan yoğun duyu sinirleriyle donatılmıştır. Üstelik çıplak gözle düz görünen kâğıt kenarı, mikroskobik ölçekte lifli ve düzensiz bir yapıya sahiptir; gün boyu ellerimizi kullanmaya devam etmemiz de hassaslaşan dokuyu tekrar tekrar uyarır.
 💬 Senin de başına geldi mi? En son ne zaman kâğıt kesiği yaşadın, yorumlara yaz! 👇
@@ -8163,53 +7613,61 @@
 #bilgidozu #shorts #insanvücudu #beyin #bilim</t>
         </is>
       </c>
-      <c r="E135" s="9" t="inlineStr">
+      <c r="E125" s="3" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #insanvücudu #beyin #bilim</t>
         </is>
       </c>
-      <c r="F135" s="9" t="inlineStr">
+      <c r="F125" s="3" t="inlineStr">
         <is>
           <t>bilgi dozu, kağıt kesiği, insan vücudu, duyu sinirleri, bilim, ilginç bilgiler, shorts</t>
         </is>
       </c>
-      <c r="G135" s="9" t="inlineStr">
+      <c r="G125" s="3" t="inlineStr">
         <is>
           <t>Senin de başına geldi mi? En son ne zaman kâğıt kesiği yaşadın, yorumlara yaz! 👇</t>
         </is>
       </c>
-      <c r="H135" s="9" t="inlineStr">
+      <c r="H125" s="3" t="inlineStr">
         <is>
           <t>İnsan Vücudu ve Beyin</t>
         </is>
       </c>
-      <c r="I135" s="9" t="inlineStr">
+      <c r="I125" s="3" t="inlineStr">
         <is>
           <t>BBC Future (Dr. H. Goldbach, UCLA, 2016) &amp; StatPearls</t>
         </is>
       </c>
-      <c r="J135" s="9" t="n"/>
-      <c r="K135" s="9" t="n"/>
-      <c r="L135" s="9" t="n"/>
-      <c r="M135" s="9" t="n"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="10" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B136" s="10" t="inlineStr">
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>https://youtu.be/MOxaXPkS0zw</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 19:36</t>
+        </is>
+      </c>
+      <c r="L125" s="3" t="n"/>
+      <c r="M125" s="3" t="n"/>
+    </row>
+    <row r="126" ht="42" customHeight="1">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>video_132.mp4</t>
         </is>
       </c>
-      <c r="C136" s="11" t="inlineStr">
+      <c r="C126" s="3" t="inlineStr">
         <is>
           <t>Baldır Kasların Aslında İkinci Kalbin! Kanı Kalbe Nasıl Taşıyor? 🦵💪 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D136" s="11" t="inlineStr">
+      <c r="D126" s="3" t="inlineStr">
         <is>
           <t>Kalp kanı bacaklara gönderir; peki kan, yerçekimine karşı nasıl kalbe geri çıkar? Bu işi aslında baldırındaki kaslar yapıyor — "İkinci Kalp".
 📍 BÖLÜMLER
@@ -8230,53 +7688,61 @@
 #bilgidozu #shorts #ikincikalp #baldır #kandolaşımı</t>
         </is>
       </c>
-      <c r="E136" s="11" t="inlineStr">
+      <c r="E126" s="3" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #ikincikalp #baldır #kandolaşımı</t>
         </is>
       </c>
-      <c r="F136" s="11" t="inlineStr">
+      <c r="F126" s="3" t="inlineStr">
         <is>
           <t>bilgidozu, shorts, ikinci kalp, baldır kasları, venöz pompa, kas pompası, toplardamar, kan kalbe nasıl döner, dolaşım sistemi, insan vücudu, bilgi dozu</t>
         </is>
       </c>
-      <c r="G136" s="11" t="inlineStr">
+      <c r="G126" s="3" t="inlineStr">
         <is>
           <t>Bacaklarında akşamları ağırlık hissedenler 1 yazsın, hissetmeyenler 2! 👇</t>
         </is>
       </c>
-      <c r="H136" s="11" t="inlineStr">
+      <c r="H126" s="3" t="inlineStr">
         <is>
           <t>İnsan Vücudu ve Beyin</t>
         </is>
       </c>
-      <c r="I136" s="11" t="inlineStr">
+      <c r="I126" s="3" t="inlineStr">
         <is>
           <t>StatPearls (NBK430975, NBK534256, NBK537340) &amp; Cleveland Clinic</t>
         </is>
       </c>
-      <c r="J136" s="11" t="n"/>
-      <c r="K136" s="11" t="n"/>
-      <c r="L136" s="11" t="n"/>
-      <c r="M136" s="11" t="n"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="10" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B137" s="10" t="inlineStr">
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>https://youtu.be/8HI5KUWLQuM</t>
+        </is>
+      </c>
+      <c r="K126" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:48</t>
+        </is>
+      </c>
+      <c r="L126" s="3" t="n"/>
+      <c r="M126" s="3" t="n"/>
+    </row>
+    <row r="127" ht="42" customHeight="1">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>video_133.mp4</t>
         </is>
       </c>
-      <c r="C137" s="11" t="inlineStr">
+      <c r="C127" s="3" t="inlineStr">
         <is>
           <t>Göz Kapağın Neden Kendi Kendine Seğirir? Anlamı Bu! 👁🧠 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D137" s="11" t="inlineStr">
+      <c r="D127" s="3" t="inlineStr">
         <is>
           <t>Gözünün altındaki o minik seğirme ne anlama geliyor? Tıbbi adı miyokimi; çoğu zaman zararsız ve kendiliğinden geçiyor.
 📍 BÖLÜMLER
@@ -8296,53 +7762,61 @@
 #bilgidozu #shorts #gözkapağı #miyokimi #beyinsağlığı</t>
         </is>
       </c>
-      <c r="E137" s="11" t="inlineStr">
+      <c r="E127" s="3" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #gözkapağı #miyokimi #beyinsağlığı</t>
         </is>
       </c>
-      <c r="F137" s="11" t="inlineStr">
+      <c r="F127" s="3" t="inlineStr">
         <is>
           <t>bilgidozu, shorts, göz kapağı seğirmesi, miyokimi, göz seğirmesi, göz tiki, stres, kafein, uykusuzluk, insan vücudu, bilgi dozu</t>
         </is>
       </c>
-      <c r="G137" s="11" t="inlineStr">
+      <c r="G127" s="3" t="inlineStr">
         <is>
           <t>Göz kapağı seğirmesi daha önce yaşayanlar 1, ilk kez duyanlar 2 yazsın! 👇</t>
         </is>
       </c>
-      <c r="H137" s="11" t="inlineStr">
+      <c r="H127" s="3" t="inlineStr">
         <is>
           <t>İnsan Vücudu ve Beyin</t>
         </is>
       </c>
-      <c r="I137" s="11" t="inlineStr">
+      <c r="I127" s="3" t="inlineStr">
         <is>
           <t>Mayo Clinic, Cleveland Clinic &amp; UCLA Health — Eyelid Myokymia</t>
         </is>
       </c>
-      <c r="J137" s="11" t="n"/>
-      <c r="K137" s="11" t="n"/>
-      <c r="L137" s="11" t="n"/>
-      <c r="M137" s="11" t="n"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="10" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B138" s="10" t="inlineStr">
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>https://youtu.be/obPceKVDg3k</t>
+        </is>
+      </c>
+      <c r="K127" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 19:34</t>
+        </is>
+      </c>
+      <c r="L127" s="3" t="n"/>
+      <c r="M127" s="3" t="n"/>
+    </row>
+    <row r="128" ht="42" customHeight="1">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>video_134.mp4</t>
         </is>
       </c>
-      <c r="C138" s="11" t="inlineStr">
+      <c r="C128" s="3" t="inlineStr">
         <is>
           <t>Bir Esnedin, Etraf da Esnedi! Esnemenin Bulaşma Sırrı 😮🧠 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D138" s="11" t="inlineStr">
+      <c r="D128" s="3" t="inlineStr">
         <is>
           <t>Esneme neden bu kadar kolay bulaşıyor — ve neden bazı insanlara hiç bulaşmıyor? Cevap, yakınlık sırasına gizlenmiş.
 📍 BÖLÜMLER
@@ -8361,53 +7835,61 @@
 #bilgidozu #shorts #esneme #empati #beyin</t>
         </is>
       </c>
-      <c r="E138" s="11" t="inlineStr">
+      <c r="E128" s="3" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #esneme #empati #beyin</t>
         </is>
       </c>
-      <c r="F138" s="11" t="inlineStr">
+      <c r="F128" s="3" t="inlineStr">
         <is>
           <t>bilgidozu, shorts, bulaşıcı esneme, esneme neden bulaşır, empati, şempanze, sosyal davranış, beyin, psikoloji, bilgi dozu</t>
         </is>
       </c>
-      <c r="G138" s="11" t="inlineStr">
+      <c r="G128" s="3" t="inlineStr">
         <is>
           <t>Sana en çok kim esneme bulaştırır? Akraba 1, arkadaş 2, yabancı 3 yazsın! 👇</t>
         </is>
       </c>
-      <c r="H138" s="11" t="inlineStr">
+      <c r="H128" s="3" t="inlineStr">
         <is>
           <t>İnsan Vücudu ve Beyin</t>
         </is>
       </c>
-      <c r="I138" s="11" t="inlineStr">
+      <c r="I128" s="3" t="inlineStr">
         <is>
           <t>Norscia &amp; Palagi (2011) PLoS ONE &amp; Campbell &amp; de Waal (2011)</t>
         </is>
       </c>
-      <c r="J138" s="11" t="n"/>
-      <c r="K138" s="11" t="n"/>
-      <c r="L138" s="11" t="n"/>
-      <c r="M138" s="11" t="n"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="10" t="inlineStr">
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>https://youtu.be/zynVVf8GQTw</t>
+        </is>
+      </c>
+      <c r="K128" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:09</t>
+        </is>
+      </c>
+      <c r="L128" s="3" t="n"/>
+      <c r="M128" s="3" t="n"/>
+    </row>
+    <row r="129" ht="42" customHeight="1">
+      <c r="A129" s="10" t="inlineStr">
         <is>
           <t>BEKLEMEDE</t>
         </is>
       </c>
-      <c r="B139" s="10" t="inlineStr">
+      <c r="B129" s="10" t="inlineStr">
         <is>
           <t>video_135.mp4</t>
         </is>
       </c>
-      <c r="C139" s="11" t="inlineStr">
+      <c r="C129" s="11" t="inlineStr">
         <is>
           <t>Güneşe Dönünce Hapşırıyor musun? Bu Bir Refleks: ACHOO! ☀️🤧 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D139" s="11" t="inlineStr">
+      <c r="D129" s="11" t="inlineStr">
         <is>
           <t>Güneşli havada hapşırıyorsan bu bir alerji değil: fotik hapşırma refleksi, yani ACHOO. Toplumun yaklaşık %18–%35'inde var.
 📍 BÖLÜMLER
@@ -8426,53 +7908,53 @@
 #bilgidozu #shorts #ACHOO #hapşırma #genetik</t>
         </is>
       </c>
-      <c r="E139" s="11" t="inlineStr">
+      <c r="E129" s="11" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #ACHOO #hapşırma #genetik</t>
         </is>
       </c>
-      <c r="F139" s="11" t="inlineStr">
+      <c r="F129" s="11" t="inlineStr">
         <is>
           <t>bilgidozu, shorts, ACHOO, fotik hapşırma, güneş hapşırması, hapşırma refleksi, genetik, otozomal dominant, insan vücudu, bilgi dozu</t>
         </is>
       </c>
-      <c r="G139" s="11" t="inlineStr">
+      <c r="G129" s="11" t="inlineStr">
         <is>
           <t>Güneşte hapşırıyorsan 1 yaz, hiç tepki vermeyen 2 yazsın! 👇</t>
         </is>
       </c>
-      <c r="H139" s="11" t="inlineStr">
+      <c r="H129" s="11" t="inlineStr">
         <is>
           <t>İnsan Vücudu ve Beyin</t>
         </is>
       </c>
-      <c r="I139" s="11" t="inlineStr">
+      <c r="I129" s="11" t="inlineStr">
         <is>
           <t>Nature Scientific Reports (2019) &amp; Cleveland Clinic JM</t>
         </is>
       </c>
-      <c r="J139" s="11" t="n"/>
-      <c r="K139" s="11" t="n"/>
-      <c r="L139" s="11" t="n"/>
-      <c r="M139" s="11" t="n"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="10" t="inlineStr">
+      <c r="J129" s="11" t="n"/>
+      <c r="K129" s="11" t="n"/>
+      <c r="L129" s="11" t="n"/>
+      <c r="M129" s="11" t="n"/>
+    </row>
+    <row r="130" ht="42" customHeight="1">
+      <c r="A130" s="10" t="inlineStr">
         <is>
           <t>BEKLEMEDE</t>
         </is>
       </c>
-      <c r="B140" s="10" t="inlineStr">
+      <c r="B130" s="10" t="inlineStr">
         <is>
           <t>video_136.mp4</t>
         </is>
       </c>
-      <c r="C140" s="11" t="inlineStr">
+      <c r="C130" s="11" t="inlineStr">
         <is>
           <t>Dondurma Damağına Değer Ama Neden Alnın Sızlar? 🧊🧠 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D140" s="11" t="inlineStr">
+      <c r="D130" s="11" t="inlineStr">
         <is>
           <t>Soğuk bir dondurma ya da buzlu su üst damağına değdiği halde sızı neden bir anda alnının ortasına vurur? Cevap beynin acil ısınma savunmasında gizli.
 📍 BÖLÜMLER
@@ -8492,36 +7974,40 @@
 #bilgidozu #shorts #beyin #dondurma #insanvücudu</t>
         </is>
       </c>
-      <c r="E140" s="11" t="inlineStr">
+      <c r="E130" s="11" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #beyin #dondurma #insanvücudu</t>
         </is>
       </c>
-      <c r="F140" s="11" t="inlineStr">
+      <c r="F130" s="11" t="inlineStr">
         <is>
           <t>bilgidozu, shorts, dondurma baş ağrısı, brain freeze, ön beyin atardamarı, trigeminal sinir, yansıyan ağrı, beyin, insan vücudu, bilgi dozu</t>
         </is>
       </c>
-      <c r="G140" s="11" t="inlineStr">
+      <c r="G130" s="11" t="inlineStr">
         <is>
           <t>Dondurma ya da buzlu suda alnı sızlayanlar 1, hiç yaşamayanlar 2 yazsın! 👇</t>
         </is>
       </c>
-      <c r="H140" s="11" t="inlineStr">
+      <c r="H130" s="11" t="inlineStr">
         <is>
           <t>İnsan Vücudu ve Beyin</t>
         </is>
       </c>
-      <c r="I140" s="11" t="inlineStr">
+      <c r="I130" s="11" t="inlineStr">
         <is>
           <t>Harvard Medical School — Jorge Serrador et al. (2012) FASEB Journal</t>
         </is>
       </c>
-      <c r="J140" s="11" t="n"/>
-      <c r="K140" s="11" t="n"/>
-      <c r="L140" s="11" t="n"/>
-      <c r="M140" s="11" t="n"/>
-    </row>
+      <c r="J130" s="11" t="n"/>
+      <c r="K130" s="11" t="n"/>
+      <c r="L130" s="11" t="n"/>
+      <c r="M130" s="11" t="n"/>
+    </row>
+    <row r="131" ht="42" customHeight="1"/>
+    <row r="132" ht="42" customHeight="1"/>
+    <row r="133" ht="42" customHeight="1"/>
+    <row r="134" ht="42" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilgidozu_yukleme_tablosu.xlsx
+++ b/bilgidozu_yukleme_tablosu.xlsx
@@ -3422,7 +3422,7 @@
     <row r="49" ht="42" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
@@ -3474,7 +3474,7 @@
     <row r="50" ht="42" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -3526,7 +3526,7 @@
     <row r="51" ht="42" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
@@ -3578,7 +3578,7 @@
     <row r="52" ht="42" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -3633,7 +3633,7 @@
     <row r="53" ht="42" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
@@ -3688,7 +3688,7 @@
     <row r="54" ht="42" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -3743,7 +3743,7 @@
     <row r="55" ht="42" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
@@ -3798,7 +3798,7 @@
     <row r="56" ht="42" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -3853,7 +3853,7 @@
     <row r="57" ht="42" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
@@ -3908,7 +3908,7 @@
     <row r="58" ht="42" customHeight="1">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -3963,7 +3963,7 @@
     <row r="59" ht="42" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
@@ -4018,7 +4018,7 @@
     <row r="60" ht="42" customHeight="1">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -4073,7 +4073,7 @@
     <row r="61" ht="42" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
@@ -4128,7 +4128,7 @@
     <row r="62" ht="42" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -4183,7 +4183,7 @@
     <row r="63" ht="42" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
@@ -4922,7 +4922,7 @@
     <row r="76" ht="42" customHeight="1">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
@@ -4974,7 +4974,7 @@
     <row r="77" ht="42" customHeight="1">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
@@ -5026,7 +5026,7 @@
     <row r="78" ht="42" customHeight="1">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
@@ -5078,7 +5078,7 @@
     <row r="79" ht="42" customHeight="1">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
@@ -5130,7 +5130,7 @@
     <row r="80" ht="42" customHeight="1">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
@@ -5186,7 +5186,7 @@
     <row r="81" ht="42" customHeight="1">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
@@ -5238,7 +5238,7 @@
     <row r="82" ht="42" customHeight="1">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
@@ -5290,7 +5290,7 @@
     <row r="83" ht="42" customHeight="1">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
@@ -5342,7 +5342,7 @@
     <row r="84" ht="42" customHeight="1">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
@@ -5394,7 +5394,7 @@
     <row r="85" ht="42" customHeight="1">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
@@ -5446,7 +5446,7 @@
     <row r="86" ht="42" customHeight="1">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
@@ -5501,7 +5501,7 @@
     <row r="87" ht="42" customHeight="1">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
@@ -5556,7 +5556,7 @@
     <row r="88" ht="42" customHeight="1">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
@@ -5611,7 +5611,7 @@
     <row r="89" ht="42" customHeight="1">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
@@ -5666,7 +5666,7 @@
     <row r="90" ht="42" customHeight="1">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
@@ -5721,7 +5721,7 @@
     <row r="91" ht="42" customHeight="1">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
@@ -5776,7 +5776,7 @@
     <row r="92" ht="42" customHeight="1">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
@@ -5831,7 +5831,7 @@
     <row r="93" ht="42" customHeight="1">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
@@ -5886,7 +5886,7 @@
     <row r="94" ht="42" customHeight="1">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
@@ -5941,7 +5941,7 @@
     <row r="95" ht="42" customHeight="1">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
@@ -5996,7 +5996,7 @@
     <row r="96" ht="42" customHeight="1">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
@@ -6051,7 +6051,7 @@
     <row r="97" ht="42" customHeight="1">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
@@ -6106,7 +6106,7 @@
     <row r="98" ht="42" customHeight="1">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
@@ -6161,7 +6161,7 @@
     <row r="99" ht="42" customHeight="1">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
@@ -6216,7 +6216,7 @@
     <row r="100" ht="42" customHeight="1">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -6271,7 +6271,7 @@
     <row r="101" ht="42" customHeight="1">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
@@ -6326,7 +6326,7 @@
     <row r="102" ht="42" customHeight="1">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
@@ -6381,7 +6381,7 @@
     <row r="103" ht="42" customHeight="1">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
@@ -6436,7 +6436,7 @@
     <row r="104" ht="42" customHeight="1">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
@@ -6491,7 +6491,7 @@
     <row r="105" ht="42" customHeight="1">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
@@ -6546,7 +6546,7 @@
     <row r="106" ht="42" customHeight="1">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
@@ -6601,7 +6601,7 @@
     <row r="107" ht="42" customHeight="1">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
@@ -6656,7 +6656,7 @@
     <row r="108" ht="42" customHeight="1">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
@@ -6711,7 +6711,7 @@
     <row r="109" ht="42" customHeight="1">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
@@ -6766,7 +6766,7 @@
     <row r="110" ht="42" customHeight="1">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
@@ -6821,7 +6821,7 @@
     <row r="111" ht="42" customHeight="1">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
@@ -6876,7 +6876,7 @@
     <row r="112" ht="42" customHeight="1">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
@@ -6931,7 +6931,7 @@
     <row r="113" ht="42" customHeight="1">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
@@ -6986,7 +6986,7 @@
     <row r="114" ht="42" customHeight="1">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
@@ -7041,7 +7041,7 @@
     <row r="115" ht="42" customHeight="1">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
@@ -7096,7 +7096,7 @@
     <row r="116" ht="42" customHeight="1">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
@@ -7151,7 +7151,7 @@
     <row r="117" ht="42" customHeight="1">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="118" ht="42" customHeight="1">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
@@ -7261,7 +7261,7 @@
     <row r="119" ht="42" customHeight="1">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
@@ -7316,7 +7316,7 @@
     <row r="120" ht="42" customHeight="1">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
@@ -7371,7 +7371,7 @@
     <row r="121" ht="42" customHeight="1">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
@@ -7426,7 +7426,7 @@
     <row r="122" ht="42" customHeight="1">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
@@ -7481,7 +7481,7 @@
     <row r="123" ht="42" customHeight="1">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
@@ -7536,7 +7536,7 @@
     <row r="124" ht="42" customHeight="1">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">

--- a/bilgidozu_yukleme_tablosu.xlsx
+++ b/bilgidozu_yukleme_tablosu.xlsx
@@ -3484,7 +3484,7 @@
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Vücudunda Kanla Değil, Doğrudan Havadan Nefes Alan Tek Doku! 👁️🌬️ #bilgidozu #shorts</t>
+          <t>Vücudunda Kanla Değil, Doğrudan Havadan Nefes Alan Tek Doku! 👁️ #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>Bacak Kasların Yorulurken Kalbin Neden Hayat Boyu Hiç Yorulmaz? ❤️⚡ #bilgidozu #shorts</t>
+          <t>Bacak Kasların Yorulurken Kalbin Neden Hayat Boyu Hiç Yorulmaz? ❤️ #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Suda Kalan Parmaklarımız Su Çektiği İçin Buruşmuyor! İşte Gerçek Sebebi! 🖐️💧 #bilgidozu #shorts</t>
+          <t>Suda Kalan Parmaklarımız Su Çektiği İçin Buruşmuyor! İşte Gerçek Sebebi! 🖐️ #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Ses Kaydındaki Sesin Sana Neden Bambaşka Geliyor? 🎙️🧠 #bilgidozu #shorts</t>
+          <t>Ses Kaydındaki Sesin Sana Neden Bambaşka Geliyor? 🎙️ #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>Gözlerin Açıkken Hapşırmak Neden İmkansız? Beynin O Salisede Ne Yapar? 🤧👁️ #bilgidozu #shorts</t>
+          <t>Gözlerin Açıkken Hapşırmak Neden İmkansız? Beynin O Salisede Ne Yapar? 🤧 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Kendi Sesini Kayıtta Dinleyince Neden Tuhaf Gelir? 🎙️🧠 #bilgidozu #shorts</t>
+          <t>Kendi Sesini Kayıtta Dinleyince Neden Tuhaf Gelir? 🎙️ #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>Yüksek Bir Yerden Bakınca Beyin Neden 'Atla' Diye Fısıldar? 🧗‍♂️🧠 #bilgidozu #shorts</t>
+          <t>Yüksek Bir Yerden Bakınca Beyin Neden 'Atla' Diye Fısıldar? 🧗 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Acı Biber Aslında Ağzını Yakmaz — Beynini Nasıl Kandırır? 🌶️🔥 #bilgidozu #shorts</t>
+          <t>Acı Biber Aslında Ağzını Yakmaz — Beynini Nasıl Kandırır? 🌶️ #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>Sevdiğin Birine Bakınca Göz Bebeğin Neden Otomatik Büyür? 👀❤️ #bilgidozu #shorts</t>
+          <t>Sevdiğin Birine Bakınca Göz Bebeğin Neden Otomatik Büyür? 👀 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>Uzay Boşluk Olmasaydı Güneş'in Devasa Uğultusunu Dünya'dan Duyardık! ☀️🔊 #bilgidozu #shorts</t>
+          <t>Uzay Boşluk Olmasaydı Güneş'in Devasa Uğultusunu Dünya'dan Duyardık! ☀️ #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>Tutankhamun'un Mezarındaki Hançer Uzaydan Gelen Göktaşından Yapılmış! 🗡️☄️ #bilgidozu #shorts</t>
+          <t>Tutankhamun'un Mezarındaki Hançer Uzaydan Gelen Göktaşından Yapılmış! 🗡️ #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>Uçak Pencerelerinin Altındaki O Minik Delik Neden Var? ✈️🪟 #bilgidozu #shorts</t>
+          <t>Uçak Pencerelerinin Altındaki O Minik Delik Neden Var? ✈️ #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>Harç ve Çimento Olmadan Depremde Yıkılmayan 500 Yıllık İnka Duvarları! 🏛️🪨 #bilgidozu #shorts</t>
+          <t>Harç ve Çimento Olmadan Depremde Yıkılmayan 500 Yıllık İnka Duvarları! 🏛️ #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>Tükenmez Kalem Kapağındaki O Küçük Delik Neden Hayat Kurtarır? 🖊️⚡ #bilgidozu #shorts</t>
+          <t>Tükenmez Kalem Kapağındaki O Küçük Delik Neden Hayat Kurtarır? 🖊️ #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>2000 Yıllık Deniz Batığından Çıkan Dünyanın İlk Mekanik Bilgisayarı! ⚙️🏛️ #bilgidozu #shorts</t>
+          <t>2000 Yıllık Deniz Batığından Çıkan Dünyanın İlk Mekanik Bilgisayarı! ⚙️ #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>70 Derece Çölde Yuvasını Adımlarını Sayarak Bulan Gümüş Karınca! 🐜☀️ #bilgidozu #shorts</t>
+          <t>70 Derece Çölde Yuvasını Adımlarını Sayarak Bulan Gümüş Karınca! 🐜 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>Satürn'ün Kuzey Kutbundaki Dev Altıgen Fırtınanın Sırrı! 🪐🌪️ #bilgidozu #shorts</t>
+          <t>Satürn'ün Kuzey Kutbundaki Dev Altıgen Fırtınanın Sırrı! 🪐 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>Efsanevi Şam Çeliği Kılıçların İçinden Karbon Nanotüp Çıktı! ⚔️🔬 #bilgidozu #shorts</t>
+          <t>Efsanevi Şam Çeliği Kılıçların İçinden Karbon Nanotüp Çıktı! ⚔️ #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Uzayda Ses Yayılsaydı Güneş Dünya'dan 100 Desibel Tren Gibi Gürlerdi! ☀️🔊 #bilgidozu #shorts</t>
+          <t>Uzayda Ses Yayılsaydı Güneş Dünya'dan 100 Desibel Tren Gibi Gürlerdi! ☀️ #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>Paskalya Adası'ndaki 80 Tonluk Dev Taş Heykeller Nasıl Yürütüldü? 🗿🏛️ #bilgidozu #shorts</t>
+          <t>Paskalya Adası'ndaki 80 Tonluk Dev Taş Heykeller Nasıl Yürütüldü? 🗿 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>Yürüyen Merdiven Kenarındaki Fırçalar Ayakkabı Silmek İçin Değil! 👟⚠️ #bilgidozu #shorts</t>
+          <t>Yürüyen Merdiven Kenarındaki Fırçalar Ayakkabı Silmek İçin Değil! 👟 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>Yıldırım Yukarıdan Düşmez: Parlama Yerden Gökyüzüne Çıkar! ⚡🌩️ #bilgidozu #shorts</t>
+          <t>Yıldırım Yukarıdan Düşmez: Parlama Yerden Gökyüzüne Çıkar! ⚡ #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Güneş Bir Saniyeliğine Sönseydi Ne Olurdu? ☀️🌑 #bilgidozu #shorts</t>
+          <t>Güneş Bir Saniyeliğine Sönseydi Ne Olurdu? ☀️ #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>Uzayda Ağlarsan Gözyaşların Neden Yanağından Akmaz? 🧑‍🚀💧 #bilgidozu #shorts</t>
+          <t>Uzayda Ağlarsan Gözyaşların Neden Yanağından Akmaz? 🧑 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>Dünya'nın En Issız Noktası Point Nemo: En Yakın İnsanlar Uzayda! 🌊🛰️ #bilgidozu #shorts</t>
+          <t>Dünya'nın En Issız Noktası Point Nemo: En Yakın İnsanlar Uzayda! 🌊 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D115" s="8" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>5,5 Milyon Yıldır Güneş Görmeyen Mühürlü Mağara: Movile! 🕳️🕷️ #bilgidozu #shorts</t>
+          <t>5,5 Milyon Yıldır Güneş Görmeyen Mühürlü Mağara: Movile! 🕳️ #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>Yerin 2.224 Metre Altında Ne Var? Dünya'nın En Derin Mağarası! 🧗‍♂️🌑 #bilgidozu #shorts</t>
+          <t>Yerin 2.224 Metre Altında Ne Var? Dünya'nın En Derin Mağarası! 🧗 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>2.100 Yıllık Batıktan Çıkan İlk Analog Bilgisayar: Antikythera! ⚙️🏛️ #bilgidozu #shorts</t>
+          <t>2.100 Yıllık Batıktan Çıkan İlk Analog Bilgisayar: Antikythera! ⚙️ #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>Derinkuyu Yeraltı Şehri: 20 Bin Kişi Yerin Altında Nasıl Nefes Aldı? 🏺🕯️ #bilgidozu #shorts</t>
+          <t>Derinkuyu Yeraltı Şehri: 20 Bin Kişi Yerin Altında Nasıl Nefes Aldı? 🏺 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>Babil'in Asma Bahçeleri Gerçekte Babil'de Değil Miydi? 🌿🏛️ #bilgidozu #shorts</t>
+          <t>Babil'in Asma Bahçeleri Gerçekte Babil'de Değil Miydi? 🌿 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>Güneşe Dönünce Hapşırıyor musun? Bu Bir Refleks: ACHOO! ☀️🤧 #bilgidozu #shorts</t>
+          <t>Güneşe Dönünce Hapşırıyor musun? Bu Bir Refleks: ACHOO! ☀️ #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">

--- a/bilgidozu_yukleme_tablosu.xlsx
+++ b/bilgidozu_yukleme_tablosu.xlsx
@@ -3432,7 +3432,7 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>Mide Asidi Bu Kadar Güçlüyken Miden Kendi Kendini Neden Sindirmez? 🧬🔥 #bilgidozu #shorts</t>
+          <t>Mide Asidi Bu Kadar Güçlüyken Miden Kendi Kendini Neden Sindirmez? 🧬 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>İnsan Vücudu Karanlıkta Gerçekten Işık Saçıyor Ama Gözümüz Göremiyor! ✨🧠 #bilgidozu #shorts</t>
+          <t>İnsan Vücudu Karanlıkta Gerçekten Işık Saçıyor Ama Gözümüz Göremiyor! ✨ #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>Soğukta Dişlerin Neden İrade Dışı Takırdar? 🥶🦷 #bilgidozu #shorts</t>
+          <t>Soğukta Dişlerin Neden İrade Dışı Takırdar? 🥶 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Utandığında Neden Sadece Yüzün ve Kulakların Kızarır? 😳🧠 #bilgidozu #shorts</t>
+          <t>Utandığında Neden Sadece Yüzün ve Kulakların Kızarır? 😳 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>Vücudundaki Hücrelerin Yarısından Fazlası Aslında Bakteri! 🦠🧬 #bilgidozu #shorts</t>
+          <t>Vücudundaki Hücrelerin Yarısından Fazlası Aslında Bakteri! 🦠 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>Bu Hayvanın Parmak İzi İnsanla O Kadar Aynı ki Mikroskopta Bile Karışıyor! 🐨🔍 #bilgidozu #shorts</t>
+          <t>Bu Hayvanın Parmak İzi İnsanla O Kadar Aynı ki Mikroskopta Bile Karışıyor! 🐨 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>Mikrodalga Fırın Yemeği İçeriden Dışarıya Doğru Pişirmez! İşte Gerçek! ⚡🔬 #bilgidozu #shorts</t>
+          <t>Mikrodalga Fırın Yemeği İçeriden Dışarıya Doğru Pişirmez! İşte Gerçek! ⚡ #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>Koltuk Altındaki Gizli Cebinde Kendi Çekiç Taşını Taşıyan Hayvan! 🦦🪨 #bilgidozu #shorts</t>
+          <t>Koltuk Altındaki Gizli Cebinde Kendi Çekiç Taşını Taşıyan Hayvan! 🦦 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>Bir Kibrit Kutusu Kadar Parçası 3 Milyar Ton Çeken Yıldız! 🪐⚡ #bilgidozu #shorts</t>
+          <t>Bir Kibrit Kutusu Kadar Parçası 3 Milyar Ton Çeken Yıldız! 🪐 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>Vezüv Patlamasında Beyni Gerçek Siyah Cama Dönüşen Romalı! 🌋🖤 #bilgidozu #shorts</t>
+          <t>Vezüv Patlamasında Beyni Gerçek Siyah Cama Dönüşen Romalı! 🌋 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>Bu Hayvan Su Altında Nefesini Yunuslardan 4 Kat Uzun Tutuyor! 🦥🌊 #bilgidozu #shorts</t>
+          <t>Bu Hayvan Su Altında Nefesini Yunuslardan 4 Kat Uzun Tutuyor! 🦥 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>Araba Ön Camlarındaki Siyah Noktalar Neden Var? Süs Değilmiş! 🚗⚫ #bilgidozu #shorts</t>
+          <t>Araba Ön Camlarındaki Siyah Noktalar Neden Var? Süs Değilmiş! 🚗 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>Tepesinden Atlayınca Dibe Düşmenin 12 Dakika Sürdüğü 20 Km'lik Uçurum! 🪐🧗 #bilgidozu #shorts</t>
+          <t>Tepesinden Atlayınca Dibe Düşmenin 12 Dakika Sürdüğü 20 Km'lik Uçurum! 🪐 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Baykuşlar Karanlıkta Uçarken Nasıl Sıfır Ses Çıkarır? Hayalet Kanat Sırrı! 🦉🌙 #bilgidozu #shorts</t>
+          <t>Baykuşlar Karanlıkta Uçarken Nasıl Sıfır Ses Çıkarır? Hayalet Kanat Sırrı! 🦉 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>Su Değil Sert Kaya Zemini Her Gün 100 Metre Yükselip Alçalan Uydu! 🪐🌋 #bilgidozu #shorts</t>
+          <t>Su Değil Sert Kaya Zemini Her Gün 100 Metre Yükselip Alçalan Uydu! 🪐 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>Benzin Pompası Depo Dolunca Çipsiz ve Sensörsüz Nasıl Kendi Durur? ⛽⚡ #bilgidozu #shorts</t>
+          <t>Benzin Pompası Depo Dolunca Çipsiz ve Sensörsüz Nasıl Kendi Durur? ⛽ #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Işığın Kırılmasını Hesaplayıp Böceği Suyla Vuran Keskin Nişancı Balık! 🐟🎯 #bilgidozu #shorts</t>
+          <t>Işığın Kırılmasını Hesaplayıp Böceği Suyla Vuran Keskin Nişancı Balık! 🐟 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>Mikrodalga Fırın Camındaki Delikli Siyah Tel Neden Var? ⚡🪟 #bilgidozu #shorts</t>
+          <t>Mikrodalga Fırın Camındaki Delikli Siyah Tel Neden Var? ⚡ #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>Elektrikli Yılan Balığı 860 Volt Elektrik Üretirken Kendini Neden Çarpmaz? ⚡🐍 #bilgidozu #shorts</t>
+          <t>Elektrikli Yılan Balığı 860 Volt Elektrik Üretirken Kendini Neden Çarpmaz? ⚡ #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Neptün ve Uranüs'te Gökyüzünden Gerçek Elmas Yağıyor! 💎🪐 #bilgidozu #shorts</t>
+          <t>Neptün ve Uranüs'te Gökyüzünden Gerçek Elmas Yağıyor! 💎 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>Uzay Boşluğunda Bile Hayatta Kalan Canlı: Su Ayısı Tardigrad! 🐻🌌 #bilgidozu #shorts</t>
+          <t>Uzay Boşluğunda Bile Hayatta Kalan Canlı: Su Ayısı Tardigrad! 🐻 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Tek Bir Ağaçtan Oluşan 47 Bin Gövdeli Dev Orman: Pando! 🌲🌍 #bilgidozu #shorts</t>
+          <t>Tek Bir Ağaçtan Oluşan 47 Bin Gövdeli Dev Orman: Pando! 🌲 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Cam Zamanla Akan Bir Sıvı Değil: En Büyük Bilim Efsanesi! 🪟🔬 #bilgidozu #shorts</t>
+          <t>Cam Zamanla Akan Bir Sıvı Değil: En Büyük Bilim Efsanesi! 🪟 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>Ay Her Yıl Dünya'dan 3,8 Santimetre Uzaklaşıyor! 🌕🚀 #bilgidozu #shorts</t>
+          <t>Ay Her Yıl Dünya'dan 3,8 Santimetre Uzaklaşıyor! 🌕 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>Yetişkin Kediler Birbirine Değil Sadece İnsanlara Miyavlar! 🐱🔊 #bilgidozu #shorts</t>
+          <t>Yetişkin Kediler Birbirine Değil Sadece İnsanlara Miyavlar! 🐱 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>Dünya Uzayda Saniyede 30 Kilometre Hızla Uçuyor! 🌍⚡ #bilgidozu #shorts</t>
+          <t>Dünya Uzayda Saniyede 30 Kilometre Hızla Uçuyor! 🌍 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D109" s="8" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>Ay Dünya'ya Yaklaşsaydı Okyanuslara Ne Olurdu? 🌕🌊 #bilgidozu #shorts</t>
+          <t>Ay Dünya'ya Yaklaşsaydı Okyanuslara Ne Olurdu? 🌕 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D111" s="8" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>Dünya'ya 50 Işık Yılı Mesafede Süpernova Patlasa Ne Olur? 💥🌟 #bilgidozu #shorts</t>
+          <t>Dünya'ya 50 Işık Yılı Mesafede Süpernova Patlasa Ne Olur? 💥 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>Bir Çay Kaşığı Nötron Yıldızı Dünya'ya Düşse Ne Olur? 🥄🌌 #bilgidozu #shorts</t>
+          <t>Bir Çay Kaşığı Nötron Yıldızı Dünya'ya Düşse Ne Olur? 🥄 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>Antarktika'daki Buzuldan Neden Kan Kırmızısı Şelale Akıyor? 🧊🩸 #bilgidozu #shorts</t>
+          <t>Antarktika'daki Buzuldan Neden Kan Kırmızısı Şelale Akıyor? 🧊 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>Dallol Volkanı: Dünya Üzerindeki En Asidik ve Renkli Cehennem! 🌋🧪 #bilgidozu #shorts</t>
+          <t>Dallol Volkanı: Dünya Üzerindeki En Asidik ve Renkli Cehennem! 🌋 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>Voynich El Yazması: 600 Yıldır Kimsenin Okuyamadığı Şifreli Kitap! 📜🔍 #bilgidozu #shorts</t>
+          <t>Voynich El Yazması: 600 Yıldır Kimsenin Okuyamadığı Şifreli Kitap! 📜 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>Puma Punku H-Blokları: Jilet Bile Girmeyen Antik Taşların Sırrı! 🪨📐 #bilgidozu #shorts</t>
+          <t>Puma Punku H-Blokları: Jilet Bile Girmeyen Antik Taşların Sırrı! 🪨 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>Dondurma Damağına Değer Ama Neden Alnın Sızlar? 🧊🧠 #bilgidozu #shorts</t>
+          <t>Dondurma Damağına Değer Ama Neden Alnın Sızlar? 🧊 #bilgidozu #shorts</t>
         </is>
       </c>
       <c r="D130" s="11" t="inlineStr">

--- a/bilgidozu_yukleme_tablosu.xlsx
+++ b/bilgidozu_yukleme_tablosu.xlsx
@@ -3422,7 +3422,7 @@
     <row r="49" ht="42" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>BEKLEMEDE</t>
+          <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
@@ -4922,7 +4922,7 @@
     <row r="76" ht="42" customHeight="1">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>BEKLEMEDE</t>
+          <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
@@ -4974,7 +4974,7 @@
     <row r="77" ht="42" customHeight="1">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>BEKLEMEDE</t>
+          <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">

--- a/bilgidozu_yukleme_tablosu.xlsx
+++ b/bilgidozu_yukleme_tablosu.xlsx
@@ -1840,7 +1840,7 @@
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>YÜKLENDİ</t>
+          <t>SİLİNDİ</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>YÜKLENDİ</t>
+          <t>SİLİNDİ</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -2013,7 +2013,7 @@
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>YÜKLENDİ</t>
+          <t>SİLİNDİ</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -2076,7 +2076,7 @@
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>YÜKLENDİ</t>
+          <t>SİLİNDİ</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">

--- a/bilgidozu_yukleme_tablosu.xlsx
+++ b/bilgidozu_yukleme_tablosu.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DRIVE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ISCILER" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UYARILAR" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="DRIVE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ISCILER" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="UYARILAR" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L2" s="3" t="n">
-        <v>1233</v>
+        <v>1200</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>0</v>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="L3" s="3" t="n">
-        <v>1140</v>
+        <v>1100</v>
       </c>
       <c r="M3" s="3" t="n">
         <v>1</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>2</v>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="L5" s="3" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>1</v>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>3</v>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>964</v>
+        <v>972</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>1</v>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>1</v>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>1086</v>
+        <v>1100</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>1</v>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>1023</v>
+        <v>1000</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>1</v>
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>1</v>
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>975</v>
+        <v>986</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>1</v>
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>1288</v>
+        <v>1300</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>1</v>
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>1014</v>
+        <v>1000</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>1</v>
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="L15" s="3" t="n">
-        <v>1111</v>
+        <v>1100</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>1</v>
@@ -1562,7 +1562,7 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1007</v>
+        <v>1000</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>1</v>
@@ -1632,7 +1632,7 @@
         </is>
       </c>
       <c r="L17" s="3" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>1</v>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="L18" s="3" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>0</v>
@@ -1771,7 +1771,9 @@
           <t>2026-10-25 18:20</t>
         </is>
       </c>
-      <c r="L19" s="3" t="n"/>
+      <c r="L19" s="3" t="n">
+        <v>70</v>
+      </c>
       <c r="M19" s="3" t="n"/>
     </row>
     <row r="20" ht="42" customHeight="1">
@@ -1831,7 +1833,7 @@
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>962</v>
+        <v>1000</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>3</v>
@@ -2809,7 +2811,7 @@
         </is>
       </c>
       <c r="L38" s="3" t="n">
-        <v>208</v>
+        <v>454</v>
       </c>
       <c r="M38" s="3" t="n">
         <v>1</v>
@@ -2873,7 +2875,7 @@
         </is>
       </c>
       <c r="L39" s="3" t="n">
-        <v>338</v>
+        <v>962</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>1</v>
@@ -2936,7 +2938,9 @@
           <t>2026-10-23 18:24</t>
         </is>
       </c>
-      <c r="L40" s="3" t="n"/>
+      <c r="L40" s="3" t="n">
+        <v>80</v>
+      </c>
       <c r="M40" s="3" t="n"/>
     </row>
     <row r="41" ht="42" customHeight="1">
@@ -2996,7 +3000,9 @@
           <t>2026-10-24 11:24</t>
         </is>
       </c>
-      <c r="L41" s="3" t="n"/>
+      <c r="L41" s="3" t="n">
+        <v>111</v>
+      </c>
       <c r="M41" s="3" t="n"/>
     </row>
     <row r="42" ht="42" customHeight="1">
@@ -3056,7 +3062,9 @@
           <t>2026-10-24 15:22</t>
         </is>
       </c>
-      <c r="L42" s="3" t="n"/>
+      <c r="L42" s="3" t="n">
+        <v>187</v>
+      </c>
       <c r="M42" s="3" t="n"/>
     </row>
     <row r="43" ht="42" customHeight="1">
@@ -3116,7 +3124,9 @@
           <t>2026-10-24 18:18</t>
         </is>
       </c>
-      <c r="L43" s="3" t="n"/>
+      <c r="L43" s="3" t="n">
+        <v>104</v>
+      </c>
       <c r="M43" s="3" t="n"/>
     </row>
     <row r="44" ht="42" customHeight="1">
@@ -3176,7 +3186,9 @@
           <t>2026-10-24 20:18</t>
         </is>
       </c>
-      <c r="L44" s="3" t="n"/>
+      <c r="L44" s="3" t="n">
+        <v>313</v>
+      </c>
       <c r="M44" s="3" t="n"/>
     </row>
     <row r="45" ht="42" customHeight="1">
@@ -3236,7 +3248,9 @@
           <t>2026-10-24 20:23</t>
         </is>
       </c>
-      <c r="L45" s="3" t="n"/>
+      <c r="L45" s="3" t="n">
+        <v>146</v>
+      </c>
       <c r="M45" s="3" t="n"/>
     </row>
     <row r="46" ht="42" customHeight="1">
@@ -3296,7 +3310,9 @@
           <t>2026-10-25 11:24</t>
         </is>
       </c>
-      <c r="L46" s="3" t="n"/>
+      <c r="L46" s="3" t="n">
+        <v>147</v>
+      </c>
       <c r="M46" s="3" t="n"/>
     </row>
     <row r="47" ht="42" customHeight="1">
@@ -3356,7 +3372,9 @@
           <t>2026-10-25 15:22</t>
         </is>
       </c>
-      <c r="L47" s="3" t="n"/>
+      <c r="L47" s="3" t="n">
+        <v>103</v>
+      </c>
       <c r="M47" s="3" t="n"/>
     </row>
     <row r="48" ht="42" customHeight="1">
@@ -3416,7 +3434,9 @@
           <t>2026-10-25 15:29</t>
         </is>
       </c>
-      <c r="L48" s="3" t="n"/>
+      <c r="L48" s="3" t="n">
+        <v>42</v>
+      </c>
       <c r="M48" s="3" t="n"/>
     </row>
     <row r="49" ht="42" customHeight="1">
@@ -4656,7 +4676,9 @@
           <t>2026-10-26 11:39</t>
         </is>
       </c>
-      <c r="L70" s="3" t="n"/>
+      <c r="L70" s="3" t="n">
+        <v>649</v>
+      </c>
       <c r="M70" s="3" t="n"/>
     </row>
     <row r="71" ht="42" customHeight="1">
@@ -7648,7 +7670,9 @@
           <t>2026-10-26 19:36</t>
         </is>
       </c>
-      <c r="L125" s="3" t="n"/>
+      <c r="L125" s="3" t="n">
+        <v>731</v>
+      </c>
       <c r="M125" s="3" t="n"/>
     </row>
     <row r="126" ht="42" customHeight="1">
@@ -7723,7 +7747,9 @@
           <t>2026-10-27 10:48</t>
         </is>
       </c>
-      <c r="L126" s="3" t="n"/>
+      <c r="L126" s="3" t="n">
+        <v>649</v>
+      </c>
       <c r="M126" s="3" t="n"/>
     </row>
     <row r="127" ht="42" customHeight="1">
@@ -7797,7 +7823,9 @@
           <t>2026-10-27 19:34</t>
         </is>
       </c>
-      <c r="L127" s="3" t="n"/>
+      <c r="L127" s="3" t="n">
+        <v>204</v>
+      </c>
       <c r="M127" s="3" t="n"/>
     </row>
     <row r="128" ht="42" customHeight="1">
@@ -7870,7 +7898,9 @@
           <t>2026-10-27 23:09</t>
         </is>
       </c>
-      <c r="L128" s="3" t="n"/>
+      <c r="L128" s="3" t="n">
+        <v>52</v>
+      </c>
       <c r="M128" s="3" t="n"/>
     </row>
     <row r="129" ht="42" customHeight="1">

--- a/bilgidozu_yukleme_tablosu.xlsx
+++ b/bilgidozu_yukleme_tablosu.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="DRIVE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ISCILER" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="UYARILAR" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DRIVE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ISCILER" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UYARILAR" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M130"/>
+  <dimension ref="A1:M131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3598,7 +3598,7 @@
     <row r="52" ht="42" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>BEKLEMEDE</t>
+          <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -8034,7 +8034,54 @@
       <c r="L130" s="11" t="n"/>
       <c r="M130" s="11" t="n"/>
     </row>
-    <row r="131" ht="42" customHeight="1"/>
+    <row r="131" ht="42" customHeight="1">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>bilgi_dozu_suda_parmaklar_neden_burusur_shorts.mp4</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Suda Kalınca Parmak Uçların Neden Buruşur? Sebebi Su Değil! 🖐️ #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Duşta, denizde ya da havuzda biraz fazla kaldığında parmak uçların neden buruşur? Çoğumuz derinin suyu sünger gibi emip şiştiğini sanırız; ancak gerçek bambaşka! Suya girdiğinde ter kanallarından sızan su ciltteki tuz dengesini düşürür ve otonom sinir sistemin kılcal damarları büzerek deriyi içeri doğru çeker. Üstelik oluşan bu "yağmur lastiği" kanalları ıslak nesneleri %12 daha hızlı kavramamızı sağlar ve her seferinde tıpkı parmak izi gibi aynı desende oluşur!
+Daha fazla bilgi dozu için takip etmeyi unutma!</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #insanvücudu #nörobilim #bilim</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, buruşuk parmak, parmak uçları, biyoloji, insan vücudu, yağmur lastiği refleksi</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Bunun su emilimi değil de beynin "yağmur lastiği" refleksi olduğunu daha önce duymuş muydun? 🖐️ Bilenler "1", ilk kez öğrenip şaşıranlar "2" yazsın! 👇</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Biyoloji ve Vücut</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Laytin &amp; German (2025) Binghamton University — J. Mech. Behavior of Biomedical Materials + Kareklas, Nettle &amp; Smulders (2013) Newcastle University — Biology Letters</t>
+        </is>
+      </c>
+    </row>
     <row r="132" ht="42" customHeight="1"/>
     <row r="133" ht="42" customHeight="1"/>
     <row r="134" ht="42" customHeight="1"/>

--- a/bilgidozu_yukleme_tablosu.xlsx
+++ b/bilgidozu_yukleme_tablosu.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M131"/>
+  <dimension ref="A1:M143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8082,9 +8082,748 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="42" customHeight="1"/>
-    <row r="133" ht="42" customHeight="1"/>
-    <row r="134" ht="42" customHeight="1"/>
+    <row r="132" ht="42" customHeight="1">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>video_139.mp4</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Dirseğini Çarpınca Neden Elektrik Çarpmış Gibi Olur? ⚡ #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Dirseğini masanın köşesine çarptığında yüzük ve serçe parmağına kadar yayılan o elektrik şoku kemikten değil, zırhsız kalan ulnar sinirden kaynaklanır.
+📍 BÖLÜMLER
+00:00 Dirsek çarpınca yayılan elektrik hissi
+00:12 Kemik değil: büyük ulnar sinir hattı
+00:19 Kübital tünelde incecik deri altı geçiş
+00:28 Kemik ile sert yüzey arasında sıkışma
+00:36 Yüzük ve serçe parmakta karıncalanma
+00:43 Sıradaki bölüm: parmak çıtlatma sesi
+📊 Kaynaklar:
+• Johns Hopkins Medicine — Cubital Tunnel Syndrome &amp; Ulnar Nerve: https://www.hopkinsmedicine.org/health/conditions-and-diseases/cubital-tunnel-syndrome
+• Cleveland Clinic — Ulnar Nerve Entrapment: https://my.clevelandclinic.org/health/diseases/22272-ulnar-nerve-entrapment
+🩺 Uyarı: Genel bilimsel bilgi amaçlıdır, tıbbi tanı veya tavsiye değildir.
+🖼️ Görseller temsilîdir (bilimsel görselleştirme).
+Bir doz bilgi, her gün: 💊 ABONE OL!
+#bilgidozu #shorts #insanvücudu #ulnarsinir #bilim</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #insanvücudu #ulnarsinir #bilim</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, dirsek çarpınca elektrik çarpması, ulnar sinir, kübital tünel, komik kemik, parmak uyuşması, sinir sistemi, insan vücudu, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Dirseğini çarpıp bu elektrik şokunu yaşayanlar 1, hiç yaşamayanlar 2 yazsın! 👇</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Biyoloji ve Vücut</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Johns Hopkins Medicine &amp; Cleveland Clinic — Cubital Tunnel / Ulnar Nerve</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="42" customHeight="1">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>video_140.mp4</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Parmak Çıtlatınca Çıkan Ses Kemik Sesi Değilmiş! 🦴 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Parmak çıtlattığında duyduğun o keskin ses kemiklerin sürtünmesi ya da baloncuk patlaması değil; eklem sıvısında milisaniyeler içinde oluşan vakum boşluğudur.
+📍 BÖLÜMLER
+00:00 Parmak çıtlatma sesi nereden gelir?
+00:11 Sinovyal sıvı ve vakum olayı
+00:21 Gerçek zamanlı MRI deneyi (Kawchuk 2015)
+00:30 Tribonükleasyon: 310 milisaniyede boşluk oluşumu
+00:39 Dr. Donald Unger'in 50 yıllık kireçlenme deneyi
+00:46 Sıradaki bölüm: ayak uyuşması ve karıncalanma
+📊 Kaynaklar:
+• Kawchuk GN et al. (2015) Real-Time MRI of Joint Cavitation, PLOS ONE: https://doi.org/10.1371/journal.pone.0119470
+• Unger DL (1998) Does Knuckle Cracking Lead to Arthritis of the Fingers?, Arthritis &amp; Rheumatism, 41(5): 949–950
+🩺 Uyarı: Genel bilimsel bilgi amaçlıdır, tıbbi tanı veya tavsiye değildir.
+🖼️ Görseller temsilîdir (bilimsel görselleştirme).
+Bir doz bilgi, her gün: 💊 ABONE OL!
+#bilgidozu #shorts #parmakçıtlatma #eklem #bilim</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #parmakçıtlatma #eklem #bilim</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, parmak çıtlatmak, parmak çıtlatma sesi, kireçlenme yapar mı, sinovyal sıvı, tribonükleasyon, donald unger, insan vücudu, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Gün içinde parmaklarını çıtlatanlar 1, o sese hiç dayanamayanlar 2 yazsın! 👇</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Biyoloji ve Vücut</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Kawchuk et al. (2015) PLOS ONE Real-Time MRI &amp; Unger (1998) Arthritis &amp; Rheumatism</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="42" customHeight="1">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>video_141.mp4</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Uyuşan Ayağın Açılırken Neden Binlerce İğne Batar? 🦶 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Uzun süre bacak bacak üstüne attığında ayağının uyuşup kalkarken binlerce iğne batması kanın durmasından çok, çevresel sinir hatlarının yeniden uyanma fırtınasıdır.
+📍 BÖLÜMLER
+00:00 Ayak uyuşması ve iğnelenme neden olur?
+00:10 Damar mı yoksa çevresel sinir kabloları mı?
+00:18 Sinir lifleri ve kılcal damar basısı
+00:27 Geçici parestezi: uyanan sinirlerin sinyal fırtınası
+00:34 Beynin parazit sinyalleri karıncalanma okuması
+00:43 Sıradaki bölüm: tüylerin diken diken olması
+📊 Kaynaklar:
+• Cleveland Clinic — Paresthesia (Pins and Needles): https://my.clevelandclinic.org/health/symptoms/24932-paresthesia
+• NINDS / NIH — Peripheral Neuropathy &amp; Nerve Compression Overview
+🩺 Uyarı: Genel bilimsel bilgi amaçlıdır, tıbbi tanı veya tavsiye değildir.
+🖼️ Görseller temsilîdir (bilimsel görselleştirme).
+Bir doz bilgi, her gün: 💊 ABONE OL!
+#bilgidozu #shorts #ayakuyuşması #parestezi #sinirsistemi</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #ayakuyuşması #parestezi #sinirsistemi</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, ayak uyuşması, bacak uyuşması, karıncalanma neden olur, parestezi, sinir sıkışması, iğne batması hissi, insan vücudu, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Ayağı uyuşunca sekerek yürüyenler 1, kıpırdamadan geçmesini bekleyenler 2 yazsın! 👇</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Beyin ve Psikoloji</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Cleveland Clinic &amp; NINDS/NIH — Paresthesia &amp; Peripheral Nerve Compression</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>uzun_video_14.mp4</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Dirsek Elektriği, Parmak Çıtlatma ve Ayak Uyuşmasının Gerçek Bilimi 🧠 #bilgidozu</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Vücudunda her gün yaşadığın ama gerçek mekanizmasını çoğu kişinin yanlış bildiği 3 büyüleyici sinir ve eklem olayını tek belgeselde inceliyoruz: dirsekteki kübital tünel elektrik şoku, parmak çıtlatmanın gerçek zamanlı MRI sırrı ve uyuşan bacakta kopan parestezi fırtınası.
+📍 BÖLÜMLER
+00:00 Giriş ve dirsekteki elektrik şoku
+00:28 Ulnar sinir ve kübital tünel zırhsızlığı
+00:52 Parmak çıtlatma sesi kemikten mi gelir?
+01:20 Tribonükleasyon vakumu ve 50 yıllık deney
+01:46 Ayak uyuşması: damar mı sinir mi?
+02:11 Sinir lifleri ve mikro damar basısı
+02:27 Geçici parestezi: karıncalanma fırtınası
+02:36 Özet: tek bir sinir ağı
+📊 Kaynaklar:
+• Johns Hopkins Medicine — Cubital Tunnel Syndrome: https://www.hopkinsmedicine.org/health/conditions-and-diseases/cubital-tunnel-syndrome
+• Kawchuk GN et al. (2015) PLOS ONE — Joint Cavitation MRI: https://doi.org/10.1371/journal.pone.0119470
+• Unger DL (1998) Arthritis &amp; Rheumatism 41(5): 949–950
+• Cleveland Clinic — Paresthesia: https://my.clevelandclinic.org/health/symptoms/24932-paresthesia
+🩺 Uyarı: Genel bilimsel bilgi amaçlıdır, tıbbi tanı veya tavsiye değildir.
+🖼️ Görseller temsilîdir (bilimsel görselleştirme).
+Bir doz bilgi, her gün: 💊 ABONE OL!
+#bilgidozu #insanvücudu #sinirsistemi #bilim #belgesel</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>#bilgidozu #insanvücudu #sinirsistemi #bilim #belgesel</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>bilgidozu, insan vücudu sırları, dirsek elektrik çarpması, ulnar sinir, parmak çıtlatma sesi, ayak uyuşması neden olur, parestezi, sinir sistemi belgeseli, bilim, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Bu 3 sinir ve eklem olayından en sık hangisini yaşıyorsun? ⚡ 1-Dirsek şoku 2-Parmak çıtlatma 3-Ayak uyuşması — Numaranı yorumlara bırak! 👇</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Uzun — Biyoloji ve Vücut</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Johns Hopkins Medicine, Kawchuk et al. (2015) PLOS ONE &amp; Cleveland Clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>video_142.mp4</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Üşüyünce ve Müzik Dinleyince Tüyler Neden Diken Diken Olur? 🧠 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Üşüdüğünde ya da duygulandığında tüylerinin diken diken olması sadece atalarımızdan kalan bir yalıtım refleksi değil; Harvard araştırmacıları bu sinirlerin kıl kökü kök hücrelerini de uyardığını keşfetti!
+📍 BÖLÜMLER
+00:00 Üşüyünce ve ürperince kabaran deri
+00:11 Arrector pili: kıl köklerindeki mikroskobik kaslar
+00:19 Sempatik sinir sistemi ve kasılma emri
+00:28 Harvard 2020 keşfi: kök hücrelerle ikili hat
+00:36 Uzun süreli soğukta yeni tüy üretimi emri
+00:45 Sıradaki bölüm: hıçkırık refleksinin sırrı
+📊 Kaynaklar:
+• Shwartz Y, Gonzalez-Celeiro M, Chen CL, Hsu YC et al. (2020) Cell Types Promoting Goosebumps Form a Niche to Regulate Hair Follicle Stem Cells, Cell, 182(3): 578–593: https://doi.org/10.1016/j.cell.2020.06.031
+• Harvard Stem Cell Institute News: https://hscrb.harvard.edu/news/the-real-reason-behind-goosebumps/
+🩺 Uyarı: Genel bilimsel bilgi amaçlıdır, tıbbi tanı veya tavsiye değildir.
+🖼️ Görseller temsilîdir (bilimsel görselleştirme).
+Bir doz bilgi, her gün: 💊 ABONE OL!
+#bilgidozu #shorts #ürperti #kökhücre #harvard</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #ürperti #kökhücre #harvard</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, tüyler neden diken diken olur, ürperti bilimi, arrector pili, harvard araştırması, kıl kökü kök hücre, sempatik sinir sistemi, insan vücudu, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Tüyleri müzik dinlerken bile diken diken olanlar 1, sadece soğukta yaşayanlar 2 yazsın! 👇</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Biyoloji ve Vücut</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Harvard University — Shwartz, Hsu et al. (2020) Cell 182(3): 578–593</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>video_143.mp4</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Hıçkırık Mideden Gelmiyor: 35 Milisaniyelik Antik Refleks! 🫁 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Hiç beklemediğin anda başlayan hıçkırık diyafram kasının ani spazmı ve sadece 35 milisaniye sonra ses tellerinin kilitlenmesidir; kökeni ise yüz milyonlarca yıllık amfibi solunum mirasına uzanır.
+📍 BÖLÜMLER
+00:00 Aniden başlayan hıçkırık krizi
+00:11 Frenik ve vagus siniri — diyafram spazmı
+00:20 35 milisaniye sonra kapanan ses telleri (glottis)
+00:30 Amfibi solungaç-akciğer evrimsel mirası
+00:39 Bebeklerde beslenme sırasında hava tahliyesi
+00:48 Sıradaki bölüm: soğan doğrarken göz yanması
+📊 Kaynaklar:
+• Straus C et al. (2003) A phylogenetic hypothesis for the origin of hiccough, BioEssays, 25(2): 182–188: https://doi.org/10.1002/bies.10257
+• Cleveland Clinic — Hiccups Causes &amp; Reflex Arc: https://my.clevelandclinic.org/health/diseases/17672-hiccups
+🩺 Uyarı: Genel bilimsel bilgi amaçlıdır, tıbbi tanı veya tavsiye değildir.
+🖼️ Görseller temsilîdir (bilimsel görselleştirme).
+Bir doz bilgi, her gün: 💊 ABONE OL!
+#bilgidozu #shorts #hıçkırık #diyafram #evrim</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #hıçkırık #diyafram #evrim</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, hıçkırık neden tutar, hıçkırık nasıl geçer, diyafram spazmı, vagus siniri, glottis, evrimsel miras, insan vücudu, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Hıçkırığı nefes tutarak geçirenler 1, soğuk su içenler 2 yazsın! 👇</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Biyoloji ve Vücut</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Straus et al. (2003) BioEssays &amp; Cleveland Clinic — Hiccup Reflex Arc</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>video_144.mp4</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Soğan Doğrarken Gözlerin Kokusundan Değil Kimyasal Gazdan Yanıyor! 🧅 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Soğan doğrarken gözlerinin yanıp yaşarması kokusundan değil; bıçak darbesiyle birleşen enzimlerin havaya saldığı uçucu kükürt gazının göz neminde mikroskobik sülfürik aside dönüşmesindendir.
+📍 BÖLÜMLER
+00:00 Soğan doğrarken başlayan kimyasal savunma
+00:11 Hücrelerde ayrı kilitli tutulan kükürt ve enzimler
+00:19 Gözyaşı faktörü sentaz enzimi (Nature 2002)
+00:28 Göz neminde mikroskobik sülfürik asit oluşumu
+00:36 Kornea sinirleri ve acil gözyaşı yıkama emri
+00:44 Sıradaki bölüm: göz ovunca görülen renkli ışıklar
+📊 Kaynaklar:
+• Imai S et al. (2002) An onion enzyme that makes the eyes water, Nature, 419: 685: https://doi.org/10.1038/419685a
+• Library of Congress — Why does chopping an onion make you cry?: https://www.loc.gov/everyday-mysteries/food-and-nutrition/item/why-does-chopping-an-onion-make-you-cry/
+🩺 Uyarı: Genel bilimsel bilgi amaçlıdır, tıbbi tanı veya tavsiye değildir.
+🖼️ Görseller temsilîdir (bilimsel görselleştirme).
+Bir doz bilgi, her gün: 💊 ABONE OL!
+#bilgidozu #shorts #soğan #kimya #insanvücudu</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #soğan #kimya #insanvücudu</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, soğan neden göz yaşartır, soğan doğrarken göz yanması, gözyaşı faktörü sentaz, sülfürik asit, kornea refleksi, günlük bilim, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Soğan doğrarken hemen ağlayanlar 1, hiç etkilenmeyenler 2 yazsın! 👇</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Fizik ve Kimya</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Imai et al. (2002) Nature 419:685 &amp; Library of Congress</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>uzun_video_15.mp4</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Diken Diken Tüyler, Hıçkırık ve Soğan Gazının Gizli Mekanizması 🔬 #bilgidozu</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Vücudunun senden izin almadan saniyeler içinde devreye soktuğu 3 otomatik savunma ve alarm mekanizmasını inceliyoruz: tüyleri diken diken eden kasların kök hücre bağlantısı, 35 milisaniyelik antik hıçkırık refleksi ve soğanın kimyasal gazına karşı korneanın acil yıkama kalkanı.
+📍 BÖLÜMLER
+00:00 Giriş: bedenin 3 otomatik savunma alarmı
+00:28 Arrector pili kasları ve Harvard kök hücre keşfi
+00:54 Hıçkırık refleksi ve diyafram spazmı
+01:21 35 milisaniye kilitlenme ve amfibi mirası
+01:49 Mutfaktaki kimyasal savunma: soğan hücreleri
+02:15 Gözyaşı faktörü sentaz ve uçucu gaz
+02:33 Kornea sinirleri ve gözyaşı kalkanı
+02:41 Özet: üç otomatik koruma sistemi
+📊 Kaynaklar:
+• Shwartz Y et al. (2020) Cell 182(3): 578–593 (Harvard Univ.): https://doi.org/10.1016/j.cell.2020.06.031
+• Straus C et al. (2003) BioEssays 25(2): 182–188 &amp; Cleveland Clinic
+• Imai S et al. (2002) Nature 419: 685 &amp; Library of Congress
+🩺 Uyarı: Genel bilimsel bilgi amaçlıdır, tıbbi tanı veya tavsiye değildir.
+🖼️ Görseller temsilîdir (bilimsel görselleştirme).
+Bir doz bilgi, her gün: 💊 ABONE OL!
+#bilgidozu #insanvücudu #refleks #bilim #belgesel</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>#bilgidozu #insanvücudu #refleks #bilim #belgesel</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>bilgidozu, vücudun savunma mekanizmaları, tüylerin diken diken olması, hıçkırık neden olur, soğan neden göz yakar, harvard kök hücre, biyoloji belgeseli, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Vücudun bu 3 otomatik kalkanından hangisi seni daha çok şaşırttı? 🛡️ 1-Ürperti ve kök hücre 2-Hıçkırık mirası 3-Soğan kimyası — Numaranı yaz! 👇</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Uzun — Biyoloji ve Vücut</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Harvard Cell (2020), Straus BioEssays (2003) &amp; Imai Nature (2002)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>video_145.mp4</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Gözünü Ovunca Karanlıkta Çıkan Renkli Işıklar Hayal Değil! 👁️ #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Gözlerini kapatıp hafifçe ovuşturduğunda karanlıkta beliren renkli yıldızlar ve halkalar hayal ürünü değil; göze tek foton girmeden retina hücrelerinin basınçla ateşlediği gerçek 'fosfen' sinyalleridir!
+📍 BÖLÜMLER
+00:00 Karanlıkta beliren renkli yıldızlar ve halkalar
+00:10 Fosfen: ışıksız görme deneyimi nedir?
+00:18 Retina hücrelerinin fiziksel basınca duyarlılığı
+00:27 Mekanik baskıyla ateşlenen elektrik sinyali
+00:36 Görsel korteksin sinyali ışık gibi çizmesi
+00:45 Sıradaki bölüm: uçakta kulak tıkanması
+📊 Kaynaklar:
+• Cleveland Clinic — Phosphenes (Seeing Stars): https://my.clevelandclinic.org/health/symptoms/24888-phosphenes
+• StatPearls / NCBI — Physiology, Phototransduction &amp; Retinal Ganglion Signaling
+🩺 Uyarı: Genel bilimsel bilgi amaçlıdır, tıbbi tanı veya tavsiye değildir.
+🖼️ Görseller temsilîdir (bilimsel görselleştirme).
+Bir doz bilgi, her gün: 💊 ABONE OL!
+#bilgidozu #shorts #fosfen #gözsağlığı #beyin</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #fosfen #gözsağlığı #beyin</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, göz ovunca görülen ışıklar, fosfen nedir, karanlıkta renkli halkalar, retina, görsel korteks, nörobilim, insan vücudu, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Gözünü kapatınca o renkli halkaları görenler 1, adını ilk kez duyanlar 2 yazsın! 👇</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Beyin ve Psikoloji</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Cleveland Clinic — Mechanical Phosphenes &amp; Retinal Ganglion Physiology</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>video_146.mp4</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Uçakta Tıkanan Kulağın Yutkununca Neden Çıt Sesiyle Açılır? ✈️ #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Uçak yükselirken ya da dağ yolunda çıkarken kulaklarının boğuklaşıp yutkunduğun an 'çıt' sesiyle açılması, orta kulaktaki kapalı basınç odasını dengeleyen gizli Östaki borusunun marifetidir.
+📍 BÖLÜMLER
+00:00 Yükseldikçe tıkanan kulak ve çıt sesi
+00:10 Kulak zarının arkasındaki yalıtılmış orta kulak
+00:18 İrtifa arttıkça zarı dışa iten basınç farkı
+00:27 Gerilen zarda su altı gibi boğuklaşan sesler
+00:34 Yutkunma ile açılan Östaki borusu ve denge
+00:44 Sıradaki bölüm: karın guruldamasının sırrı
+📊 Kaynaklar:
+• Cleveland Clinic — Ear Barotrauma &amp; Retracted Eardrum: https://my.clevelandclinic.org/health/diseases/25019-retracted-eardrum
+• Mayo Clinic — Airplane Ear (Ear Barotrauma) &amp; Eustachian Tube Function
+🩺 Uyarı: Genel bilimsel bilgi amaçlıdır, tıbbi tanı veya tavsiye değildir.
+🖼️ Görseller temsilîdir (bilimsel görselleştirme).
+Bir doz bilgi, her gün: 💊 ABONE OL!
+#bilgidozu #shorts #kulaktıkanması #uçak #bilim</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #kulaktıkanması #uçak #bilim</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, uçakta kulak tıkanması, yüksekte kulak neden tıkanır, östaki borusu, orta kulak basıncı, kulak çıtlaması, insan vücudu, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Yolculukta kulağı hemen tıkananlar 1, sakız veya esnemeyle anında açanlar 2 yazsın! 👇</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Biyoloji ve Vücut</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Cleveland Clinic &amp; Mayo Clinic — Ear Barotrauma &amp; Eustachian Tube</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>video_147.mp4</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Karın Guruldaması Açlık Değil: 90 Dakikalık Otomatik Temizlik! 🔬 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Sessiz bir ortamda karnından yükselen gurultu (borborygmi) sadece açlık alarmı değil; sindirim sisteminin her 90 dakikada bir başlattığı 'Göç Eden Motor Kompleks' adlı otomatik iç temizlik dalgasıdır!
+📍 BÖLÜMLER
+00:00 Sessiz odada yankılanan karın gurultusu
+00:11 Borborygmi: mide ve ince bağırsak kanalları
+00:18 Her 90 dakikada başlayan Göç Eden Motor Kompleks
+00:27 Boş kanallarda akustik yankı ve iç süpürme
+00:36 Açlık alarmı değil, dip köşe bağırsak temizliği
+00:43 Yeni seri köprüsü: sabah ağız kokusunun sırrı
+📊 Kaynaklar:
+• Deloose E, Janssen P, Depoortere I, Tack J (2012) The migrating motor complex: control mechanisms and its role in health and disease, Nat. Rev. Gastroenterol. Hepatol., 9(5): 271–285: https://pubmed.ncbi.nlm.nih.gov/22450306/
+• Cleveland Clinic — Stomach Growling (Borborygmi)
+🩺 Uyarı: Genel bilimsel bilgi amaçlıdır, tıbbi tanı veya tavsiye değildir.
+🖼️ Görseller temsilîdir (bilimsel görselleştirme).
+Bir doz bilgi, her gün: 💊 ABONE OL!
+#bilgidozu #shorts #karıngurultusu #sindirim #bilim</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #karıngurultusu #sindirim #bilim</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, karın neden guruldar, mide guruldaması, borborygmi, göç eden motor kompleks, bağırsak temizliği, sindirim sistemi, insan vücudu, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>En sessiz ortamda karnı guruldayanlar 1, su içip bastırmaya çalışanlar 2 yazsın! 👇</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Biyoloji ve Vücut</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Deloose et al. (2012) Nature Reviews Gastroenterology &amp; Hepatology (PMID: 22450306)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>uzun_video_16.mp4</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Karanlıkta Renkli Işıklar, Kulak Tıkanması ve Karın Gurultusunun Sırrı ⚡ #bilgidozu</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Gözünün, kulağının ve sindirim sisteminin her gün gönderdiği 3 gizemli iç sinyali tek belgeselde çözüyoruz: karanlıkta göz ovunca çakan mekanik fosfen ışıkları, yüksek irtifada kilitlenen orta kulak basıncı ve her 90 dakikada bağırsakları süpüren Göç Eden Motor Kompleks.
+📍 BÖLÜMLER
+00:00 Giriş: duyuların ve iç organların gizli sinyalleri
+00:28 Mekanik fosfen: ışıksız retina ve görsel korteks
+00:56 Uçakta ve dağ yolunda kulak tıkanması
+01:22 Orta kulak basıncı ve Östaki borusu kilidi
+01:47 Karın gurultusu (borborygmi) nereden gelir?
+02:14 Göç Eden Motor Kompleks: 90 dakikalık dalga
+02:32 Boş kanallarda akustik yankı ve iç temizlik
+02:39 Özet ve yeni seri duyurusu
+📊 Kaynaklar:
+• Cleveland Clinic — Phosphenes: https://my.clevelandclinic.org/health/symptoms/24888-phosphenes
+• Cleveland Clinic — Ear Barotrauma &amp; Eustachian Tube: https://my.clevelandclinic.org/health/diseases/25019-retracted-eardrum
+• Deloose E et al. (2012) Nat. Rev. Gastroenterol. Hepatol. 9(5): 271–285: https://pubmed.ncbi.nlm.nih.gov/22450306/
+🩺 Uyarı: Genel bilimsel bilgi amaçlıdır, tıbbi tanı veya tavsiye değildir.
+🖼️ Görseller temsilîdir (bilimsel görselleştirme).
+Bir doz bilgi, her gün: 💊 ABONE OL!
+#bilgidozu #insanvücudu #beyin #bilim #belgesel</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>#bilgidozu #insanvücudu #beyin #bilim #belgesel</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>bilgidozu, duyuların gizli sinyalleri, fosfen nedir, uçakta kulak tıkanması, östaki borusu, karın guruldaması neden olur, borborygmi, insan vücudu belgeseli, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Vücudun bu 3 gizli sinyalinden hangisini daha sık yaşıyorsun? 👁️ 1-Karanlıkta ışık halkaları 2-Kulak tıkanması 3-Karın gurultusu — Numaranı bırak! 👇</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Uzun — Beyin ve Psikoloji</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Cleveland Clinic (Phosphenes &amp; Barotrauma) &amp; Deloose et al. (2012) Nat. Rev.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilgidozu_yukleme_tablosu.xlsx
+++ b/bilgidozu_yukleme_tablosu.xlsx
@@ -8085,7 +8085,7 @@
     <row r="132" ht="42" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BEKLEMEDE</t>
+          <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8146,7 +8146,7 @@
     <row r="133" ht="42" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BEKLEMEDE</t>
+          <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8207,7 +8207,7 @@
     <row r="134" ht="42" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BEKLEMEDE</t>
+          <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8268,7 +8268,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BEKLEMEDE</t>
+          <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8333,7 +8333,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BEKLEMEDE</t>
+          <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8394,7 +8394,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>BEKLEMEDE</t>
+          <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8455,7 +8455,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>BEKLEMEDE</t>
+          <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8516,7 +8516,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>BEKLEMEDE</t>
+          <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8580,7 +8580,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BEKLEMEDE</t>
+          <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8641,7 +8641,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BEKLEMEDE</t>
+          <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -8702,7 +8702,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BEKLEMEDE</t>
+          <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -8763,7 +8763,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BEKLEMEDE</t>
+          <t>ESKİ_STOK_ASKIDA</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">

--- a/bilgidozu_yukleme_tablosu.xlsx
+++ b/bilgidozu_yukleme_tablosu.xlsx
@@ -8085,7 +8085,7 @@
     <row r="132" ht="42" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8146,7 +8146,7 @@
     <row r="133" ht="42" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8207,7 +8207,7 @@
     <row r="134" ht="42" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8333,7 +8333,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8394,7 +8394,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8455,7 +8455,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8580,7 +8580,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8641,7 +8641,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -8702,7 +8702,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">

--- a/bilgidozu_yukleme_tablosu.xlsx
+++ b/bilgidozu_yukleme_tablosu.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M143"/>
+  <dimension ref="A1:N143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -605,6 +605,11 @@
       <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Yorum Sayısı</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>İlgili Video</t>
         </is>
       </c>
     </row>
@@ -8329,6 +8334,11 @@
           <t>Johns Hopkins Medicine, Kawchuk et al. (2015) PLOS ONE &amp; Cleveland Clinic</t>
         </is>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>video_139.mp4, video_140.mp4, video_141.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8576,6 +8586,11 @@
           <t>Harvard Cell (2020), Straus BioEssays (2003) &amp; Imai Nature (2002)</t>
         </is>
       </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>video_142.mp4, video_143.mp4, video_144.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8823,6 +8838,11 @@
           <t>Cleveland Clinic (Phosphenes &amp; Barotrauma) &amp; Deloose et al. (2012) Nat. Rev.</t>
         </is>
       </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>video_145.mp4, video_146.mp4, video_147.mp4</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/bilgidozu_yukleme_tablosu.xlsx
+++ b/bilgidozu_yukleme_tablosu.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DRIVE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ISCILER" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UYARILAR" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="DRIVE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ISCILER" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="UYARILAR" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="L19" s="3" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="M19" s="3" t="n"/>
     </row>
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="L43" s="3" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M43" s="3" t="n"/>
     </row>
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="L46" s="3" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="M46" s="3" t="n"/>
     </row>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="L70" s="3" t="n">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="M70" s="3" t="n"/>
     </row>
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="L125" s="3" t="n">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="M125" s="3" t="n"/>
     </row>
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="L126" s="3" t="n">
-        <v>649</v>
+        <v>700</v>
       </c>
       <c r="M126" s="3" t="n"/>
     </row>
@@ -7829,7 +7829,7 @@
         </is>
       </c>
       <c r="L127" s="3" t="n">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="M127" s="3" t="n"/>
     </row>
@@ -7904,7 +7904,7 @@
         </is>
       </c>
       <c r="L128" s="3" t="n">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="M128" s="3" t="n"/>
     </row>

--- a/bilgidozu_yukleme_tablosu.xlsx
+++ b/bilgidozu_yukleme_tablosu.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="DRIVE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ISCILER" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="UYARILAR" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DRIVE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ISCILER" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UYARILAR" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8273,7 +8273,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8526,7 +8526,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8778,7 +8778,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ESKİ_STOK_ASKIDA</t>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">

--- a/bilgidozu_yukleme_tablosu.xlsx
+++ b/bilgidozu_yukleme_tablosu.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N143"/>
+  <dimension ref="A1:N144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8844,6 +8844,66 @@
         </is>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>video_157.mp4</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Üçgen ve Açı Kelimelerini Atatürk'ün Bizzat Türettiğini Biliyor muydun? 🇹🇷 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Bugün okulda tek nefeste söylediğin üçgen, kare, açı ve artı kelimelerini kimin oturup türettiğini hiç düşündün mü? Bin dokuz yüz otuz altı kışında Atatürk masa başına geçti ve adını bile koymadığı kırk dört sayfalık Geometri kitabını yazdı.
+📍 BÖLÜMLER
+00:00 Üçgen, kare ve açi adini — Ki̇m türetti̇ bi̇li̇yor musun?
+00:08 Cumhuri̇yet'ten önce üçgen: — Ezberi̇ zor ağir teri̇mler!
+00:17 1936 kişi i̇si̇msi̇z eser: — 44 sayfalik geometri̇ ki̇tabi!
+00:26 Arti, eksi̇, çap, uzay: — Bi̇li̇m di̇li̇ tertemi̇z oldu!
+00:37 29 eki̇m'i̇n gerçek ruhu: — Akil ve bi̇li̇m devri̇mi̇!
+00:46 103. yilimiz kutlu olsun! — Yoruma yaz &amp; taki̇p et!
+📊 Kaynaklar:
+• Kaynak: Türk Dil Kurumu &amp; Kültür Bakanlığı Geometri Kılavuzu (1937)
+• https://tdk.gov.tr/
+🖼️ Görseller temsili (AI bilimsel canlandırma).
+Cumhuriyetimizin 103. yılı kutlu olsun! Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+#bilgidozu #shorts #29ekim #cumhuriyetbayramı #bilim #tarih</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #29ekim #cumhuriyetbayramı #bilim #tarih</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, 29 ekim, cumhuriyet bayramı, atatürk geometri kitabı, üçgen kelimesini kim buldu, bilim tarihi, türkçe matematik terimleri, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Üçgen, açı, uzay, köşegen, artı, eksi... Senin en sevdiğin Türkçe bilim kelimesi hangisi? 29 Ekim Cumhuriyet Bayramımız kutlu olsun! 👇</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>29 Ekim Özel — Bilim Tarihi</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Türk Dil Kurumu (TDK) &amp; Kültür Bakanlığı Geometri Kılavuzu (1937)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilgidozu_yukleme_tablosu.xlsx
+++ b/bilgidozu_yukleme_tablosu.xlsx
@@ -8847,7 +8847,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BEKLEMEDE</t>
+          <t>YÜKLENDİ</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -8901,6 +8901,16 @@
       <c r="I144" t="inlineStr">
         <is>
           <t>Türk Dil Kurumu (TDK) &amp; Kültür Bakanlığı Geometri Kılavuzu (1937)</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>https://youtu.be/t2lphcITKXs</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>2026-10-29 19:30</t>
         </is>
       </c>
     </row>

--- a/bilgidozu_yukleme_tablosu.xlsx
+++ b/bilgidozu_yukleme_tablosu.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DRIVE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ISCILER" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UYARILAR" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="DRIVE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ISCILER" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="UYARILAR" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>1</v>
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="L19" s="3" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="M19" s="3" t="n"/>
     </row>
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="L38" s="3" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M38" s="3" t="n">
         <v>1</v>
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="L43" s="3" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M43" s="3" t="n"/>
     </row>
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="L45" s="3" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="M45" s="3" t="n"/>
     </row>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="L70" s="3" t="n">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="M70" s="3" t="n"/>
     </row>
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="L126" s="3" t="n">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="M126" s="3" t="n"/>
     </row>
@@ -7829,7 +7829,7 @@
         </is>
       </c>
       <c r="L127" s="3" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="M127" s="3" t="n"/>
     </row>
@@ -7904,7 +7904,7 @@
         </is>
       </c>
       <c r="L128" s="3" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="M128" s="3" t="n"/>
     </row>
@@ -8913,6 +8913,9 @@
           <t>2026-10-29 19:30</t>
         </is>
       </c>
+      <c r="L144" t="n">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/bilgidozu_yukleme_tablosu.xlsx
+++ b/bilgidozu_yukleme_tablosu.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="DRIVE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ISCILER" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="UYARILAR" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DRIVE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ISCILER" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UYARILAR" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -124,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -159,6 +159,8 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -524,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N144"/>
+  <dimension ref="A1:N168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1247,7 +1249,7 @@
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>1</v>
@@ -1777,7 +1779,7 @@
         </is>
       </c>
       <c r="L19" s="3" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M19" s="3" t="n"/>
     </row>
@@ -1847,7 +1849,7 @@
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>SİLİNDİ</t>
+          <t>YÜKLENDİ</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1906,7 +1908,7 @@
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>SİLİNDİ</t>
+          <t>YÜKLENDİ</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -2020,7 +2022,7 @@
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>SİLİNDİ</t>
+          <t>YÜKLENDİ</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -2083,7 +2085,7 @@
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>SİLİNDİ</t>
+          <t>YÜKLENDİ</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -2816,7 +2818,7 @@
         </is>
       </c>
       <c r="L38" s="3" t="n">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="M38" s="3" t="n">
         <v>1</v>
@@ -3130,7 +3132,7 @@
         </is>
       </c>
       <c r="L43" s="3" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="M43" s="3" t="n"/>
     </row>
@@ -3254,7 +3256,7 @@
         </is>
       </c>
       <c r="L45" s="3" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M45" s="3" t="n"/>
     </row>
@@ -3821,22 +3823,22 @@
       <c r="M55" s="8" t="n"/>
     </row>
     <row r="56" ht="42" customHeight="1">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>video_96.mp4</t>
         </is>
       </c>
-      <c r="C56" s="8" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>Kendi Sesini Kayıtta Dinleyince Neden Tuhaf Gelir? 🎙️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D56" s="8" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>Bir ses kaydında kendi sesini duyduğun an “Bu gerçekten benim sesim mi?” diye yüzünü buruşturduğun oldu mu? Merak etme, yalnız değilsin. Sen konuşurken sesini iki farklı yoldan aynı anda duyarsın. Hem havadan kulağına gelen dalgalarla, hem de ses tellerinin kafatası kemiklerini titreştirerek iç kulağına gönderdiği kemik iletimiyle. Kafatası kemiklerin bas frekansları güçlendirdiği için kendi sesini hep daha tok ve derin algılarsın. Ama kayıtta, kemik iletimi devreden çıkar ve başkalarının duyduğu o gerçek sesine yüzleşirsin. Peki sen kayıtlarda kendi sesini dinlemeye alışabildin mi, yoksa duyunca hemen kapatıyor musun? Yorumlarda buluşalım.
 💬 Peki sen kendi sesini kayıtlarda dinlemeye alışabildin mi, yoksa duyunca hâlâ hemen kapatıyor musun? Yorumlarda buluşalım! 👇
@@ -3845,35 +3847,43 @@
 #bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="E56" s="8" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="F56" s="8" t="inlineStr">
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t>bilgidozu, shorts, nörobilim, insan bedeni, psikoloji, bilim</t>
         </is>
       </c>
-      <c r="G56" s="8" t="inlineStr">
+      <c r="G56" s="3" t="inlineStr">
         <is>
           <t>Peki sen kendi sesini kayıtlarda dinlemeye alışabildin mi, yoksa duyunca hâlâ hemen kapatıyor musun? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H56" s="8" t="inlineStr">
+      <c r="H56" s="3" t="inlineStr">
         <is>
           <t>Nörobilim ve İnsan Bedeni</t>
         </is>
       </c>
-      <c r="I56" s="8" t="inlineStr">
+      <c r="I56" s="3" t="inlineStr">
         <is>
           <t>Journal of Voice / Wikipedia — Bone Conduction (Kafatası Kemik İletimi): https://en.wikipedia.org/wiki/Bone_conduction</t>
         </is>
       </c>
-      <c r="J56" s="8" t="n"/>
-      <c r="K56" s="8" t="n"/>
-      <c r="L56" s="8" t="n"/>
-      <c r="M56" s="8" t="n"/>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>https://youtu.be/aat1STZfbps</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29 21:11</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="n"/>
+      <c r="M56" s="3" t="n"/>
     </row>
     <row r="57" ht="42" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
@@ -4041,22 +4051,22 @@
       <c r="M59" s="8" t="n"/>
     </row>
     <row r="60" ht="42" customHeight="1">
-      <c r="A60" s="7" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>video_100.mp4</t>
         </is>
       </c>
-      <c r="C60" s="8" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>Utandığında Neden Sadece Yüzün ve Kulakların Kızarır? 😳 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D60" s="8" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>Herkesin içinde bir anda utandığında neden kolların değil de sadece yanakların ve kulakların alev alev kızarır? Üstelik sakın kızarma dedikçe daha da kıpkırmızı olursun. Charles Darwin'in tüm duyguların en insaniye olanı dediği bu tepki vücudunun gizli dürüstlük mekanizmasıdır. Utandığın saniye beynin ani bir adrenalin salgılar ve sadece yüzündeki özel kılcal damarlar genişleyerek cildinin altına sıcak kan hücum eder. Evrimsel olarak bu tek kelime etmeden çevrendekilere hata yaptım ve farkındayım demenin sessiz yoludur. Peki sen utandığında sakin kalabilenlerden misin, yoksa saniyesinde kızaranlardan mı? Yorumlarda buluşalım.
 💬 Peki sen utandığında rengini belli etmeden sakin kalabilenlerden misin, yoksa saniyesinde pancar gibi kızaranlardan mı? Yorumlarda buluşalım! 👇
@@ -4065,53 +4075,61 @@
 #bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="E60" s="8" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="F60" s="8" t="inlineStr">
+      <c r="F60" s="3" t="inlineStr">
         <is>
           <t>bilgidozu, shorts, nörobilim, insan bedeni, psikoloji, bilim</t>
         </is>
       </c>
-      <c r="G60" s="8" t="inlineStr">
+      <c r="G60" s="3" t="inlineStr">
         <is>
           <t>Peki sen utandığında rengini belli etmeden sakin kalabilenlerden misin, yoksa saniyesinde pancar gibi kızaranlardan mı? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H60" s="8" t="inlineStr">
+      <c r="H60" s="3" t="inlineStr">
         <is>
           <t>Nörobilim ve İnsan Bedeni</t>
         </is>
       </c>
-      <c r="I60" s="8" t="inlineStr">
+      <c r="I60" s="3" t="inlineStr">
         <is>
           <t>Charles Darwin / Wikipedia — Blushing Physiology (Yüz Kızarması Mekanizması): https://en.wikipedia.org/wiki/Blushing</t>
         </is>
       </c>
-      <c r="J60" s="8" t="n"/>
-      <c r="K60" s="8" t="n"/>
-      <c r="L60" s="8" t="n"/>
-      <c r="M60" s="8" t="n"/>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>https://youtu.be/j8J7rqtyyFg</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28 19:37</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="n"/>
+      <c r="M60" s="3" t="n"/>
     </row>
     <row r="61" ht="42" customHeight="1">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>video_86.mp4</t>
         </is>
       </c>
-      <c r="C61" s="8" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>Vücudundaki Hücrelerin Yarısından Fazlası Aslında Bakteri! 🦠 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D61" s="8" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>İnsan bedeninde yaklaşık 30 trilyon insan hücresine karşılık 38 trilyondan fazla dost bakteri hücresi yaşar.
 Peki vücudunuzda kendi hücrelerinizden daha fazla bakteri yaşaması size nasıl hissettiriyor? Yorumlara yazın! 👇
@@ -4120,35 +4138,43 @@
 #bilgidozu #shorts #insanvücudu #bilim #biyoloji</t>
         </is>
       </c>
-      <c r="E61" s="8" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #insanvücudu #bilim #biyoloji</t>
         </is>
       </c>
-      <c r="F61" s="8" t="inlineStr">
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>bilgi dozu, insan vücudu, bakteri, biyoloji, bilim, shorts</t>
         </is>
       </c>
-      <c r="G61" s="8" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr">
         <is>
           <t>Peki vücudunuzda kendi hücrelerinizden daha fazla bakteri yaşaması size nasıl hissettiriyor? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H61" s="8" t="inlineStr">
+      <c r="H61" s="3" t="inlineStr">
         <is>
           <t>İnsan Vücudu ve Psikoloji</t>
         </is>
       </c>
-      <c r="I61" s="8" t="inlineStr">
+      <c r="I61" s="3" t="inlineStr">
         <is>
           <t>PLOS Biology (Sender et al., 2016) — Revised Estimates for Human &amp; Bacteria Cells: https://journals.plos.org/plosbiology/article?id=10.1371/journal.pbio.1002533</t>
         </is>
       </c>
-      <c r="J61" s="8" t="n"/>
-      <c r="K61" s="8" t="n"/>
-      <c r="L61" s="8" t="n"/>
-      <c r="M61" s="8" t="n"/>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Bn5vzNjsnWo</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28 21:10</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="n"/>
+      <c r="M61" s="3" t="n"/>
     </row>
     <row r="62" ht="42" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
@@ -4206,22 +4232,22 @@
       <c r="M62" s="8" t="n"/>
     </row>
     <row r="63" ht="42" customHeight="1">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>video_83.mp4</t>
         </is>
       </c>
-      <c r="C63" s="8" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>Sevdiğin Birine Bakınca Göz Bebeğin Neden Otomatik Büyür? 👀 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D63" s="8" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>Hoşlandığımız birine baktığımızda dopamin ve oksitosin etkisiyle sempatik sinir sistemi göz bebeklerimizi istemsizce büyütür.
 Siz konuşurken karşınızdakinin göz bebeklerine dikkat eder misiniz? Yorumlara yazın! 👇
@@ -4230,35 +4256,43 @@
 #bilgidozu #shorts #psikoloji #insanvücudu #bilim</t>
         </is>
       </c>
-      <c r="E63" s="8" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #psikoloji #insanvücudu #bilim</t>
         </is>
       </c>
-      <c r="F63" s="8" t="inlineStr">
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>bilgi dozu, psikoloji, göz bebeği, insan vücudu, bilim, shorts</t>
         </is>
       </c>
-      <c r="G63" s="8" t="inlineStr">
+      <c r="G63" s="3" t="inlineStr">
         <is>
           <t>Siz konuşurken karşınızdakinin göz bebeklerine dikkat eder misiniz? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H63" s="8" t="inlineStr">
+      <c r="H63" s="3" t="inlineStr">
         <is>
           <t>İnsan Vücudu ve Psikoloji</t>
         </is>
       </c>
-      <c r="I63" s="8" t="inlineStr">
+      <c r="I63" s="3" t="inlineStr">
         <is>
           <t>Hess &amp; Polt (1960) / Wikipedia — Pupillometry Research: https://en.wikipedia.org/wiki/Pupillometry</t>
         </is>
       </c>
-      <c r="J63" s="8" t="n"/>
-      <c r="K63" s="8" t="n"/>
-      <c r="L63" s="8" t="n"/>
-      <c r="M63" s="8" t="n"/>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>https://youtu.be/0vGKrBpJh0Q</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28 14:07</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="n"/>
+      <c r="M63" s="3" t="n"/>
     </row>
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="7" t="inlineStr">
@@ -4682,7 +4716,7 @@
         </is>
       </c>
       <c r="L70" s="3" t="n">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="M70" s="3" t="n"/>
     </row>
@@ -7451,22 +7485,22 @@
       <c r="M121" s="8" t="n"/>
     </row>
     <row r="122" ht="42" customHeight="1">
-      <c r="A122" s="7" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B122" s="7" t="inlineStr">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>video_108.mp4</t>
         </is>
       </c>
-      <c r="C122" s="8" t="inlineStr">
+      <c r="C122" s="3" t="inlineStr">
         <is>
           <t>Voynich El Yazması: 600 Yıldır Kimsenin Okuyamadığı Şifreli Kitap! 📜 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D122" s="8" t="inlineStr">
+      <c r="D122" s="3" t="inlineStr">
         <is>
           <t>Dünyanın en iyi şifre çözücüleri, dilbilimcileri ve yapay zekâları bir araya geldi ama altı yüz yıllık bu kitabın tek bir cümlesini bile okuyamadı: Voynich El Yazması.
 💬 Peki sence bu kitap unutulmuş gizli bir bilimin şifreli kaydı mı, yoksa tarihin en zekice kurgulanmış bilmecesi mi? Yorumlarda buluşalım! 👇
@@ -7475,35 +7509,43 @@
 #bilgidozu #shorts #tarih #arkeoloji #bilim</t>
         </is>
       </c>
-      <c r="E122" s="8" t="inlineStr">
+      <c r="E122" s="3" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #arkeoloji #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F122" s="8" t="inlineStr">
+      <c r="F122" s="3" t="inlineStr">
         <is>
           <t>bilgi dozu, antik mühendislik, tarih, arkeoloji, gizemli yapılar, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G122" s="8" t="inlineStr">
+      <c r="G122" s="3" t="inlineStr">
         <is>
           <t>Peki sence bu kitap unutulmuş gizli bir bilimin şifreli kaydı mı, yoksa tarihin en zekice kurgulanmış bilmecesi mi? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H122" s="8" t="inlineStr">
+      <c r="H122" s="3" t="inlineStr">
         <is>
           <t>Tarih ve Antik Mühendislik</t>
         </is>
       </c>
-      <c r="I122" s="8" t="inlineStr">
+      <c r="I122" s="3" t="inlineStr">
         <is>
           <t>Yale Beinecke Library / Wikipedia — Voynich Manuscript (Voynich El Yazması): https://en.wikipedia.org/wiki/Voynich_manuscript</t>
         </is>
       </c>
-      <c r="J122" s="8" t="n"/>
-      <c r="K122" s="8" t="n"/>
-      <c r="L122" s="8" t="n"/>
-      <c r="M122" s="8" t="n"/>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>https://youtu.be/7DG1etjQlR4</t>
+        </is>
+      </c>
+      <c r="K122" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28 10:58</t>
+        </is>
+      </c>
+      <c r="L122" s="3" t="n"/>
+      <c r="M122" s="3" t="n"/>
     </row>
     <row r="123" ht="42" customHeight="1">
       <c r="A123" s="7" t="inlineStr">
@@ -7753,7 +7795,7 @@
         </is>
       </c>
       <c r="L126" s="3" t="n">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="M126" s="3" t="n"/>
     </row>
@@ -7829,7 +7871,7 @@
         </is>
       </c>
       <c r="L127" s="3" t="n">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="M127" s="3" t="n"/>
     </row>
@@ -7904,27 +7946,27 @@
         </is>
       </c>
       <c r="L128" s="3" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="M128" s="3" t="n"/>
     </row>
     <row r="129" ht="42" customHeight="1">
-      <c r="A129" s="10" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B129" s="10" t="inlineStr">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>video_135.mp4</t>
         </is>
       </c>
-      <c r="C129" s="11" t="inlineStr">
+      <c r="C129" s="3" t="inlineStr">
         <is>
           <t>Güneşe Dönünce Hapşırıyor musun? Bu Bir Refleks: ACHOO! ☀️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D129" s="11" t="inlineStr">
+      <c r="D129" s="3" t="inlineStr">
         <is>
           <t>Güneşli havada hapşırıyorsan bu bir alerji değil: fotik hapşırma refleksi, yani ACHOO. Toplumun yaklaşık %18–%35'inde var.
 📍 BÖLÜMLER
@@ -7943,35 +7985,43 @@
 #bilgidozu #shorts #ACHOO #hapşırma #genetik</t>
         </is>
       </c>
-      <c r="E129" s="11" t="inlineStr">
+      <c r="E129" s="3" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #ACHOO #hapşırma #genetik</t>
         </is>
       </c>
-      <c r="F129" s="11" t="inlineStr">
+      <c r="F129" s="3" t="inlineStr">
         <is>
           <t>bilgidozu, shorts, ACHOO, fotik hapşırma, güneş hapşırması, hapşırma refleksi, genetik, otozomal dominant, insan vücudu, bilgi dozu</t>
         </is>
       </c>
-      <c r="G129" s="11" t="inlineStr">
+      <c r="G129" s="3" t="inlineStr">
         <is>
           <t>Güneşte hapşırıyorsan 1 yaz, hiç tepki vermeyen 2 yazsın! 👇</t>
         </is>
       </c>
-      <c r="H129" s="11" t="inlineStr">
+      <c r="H129" s="3" t="inlineStr">
         <is>
           <t>İnsan Vücudu ve Beyin</t>
         </is>
       </c>
-      <c r="I129" s="11" t="inlineStr">
+      <c r="I129" s="3" t="inlineStr">
         <is>
           <t>Nature Scientific Reports (2019) &amp; Cleveland Clinic JM</t>
         </is>
       </c>
-      <c r="J129" s="11" t="n"/>
-      <c r="K129" s="11" t="n"/>
-      <c r="L129" s="11" t="n"/>
-      <c r="M129" s="11" t="n"/>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>https://youtu.be/LGXmOwTtGOw</t>
+        </is>
+      </c>
+      <c r="K129" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28 01:00</t>
+        </is>
+      </c>
+      <c r="L129" s="3" t="n"/>
+      <c r="M129" s="3" t="n"/>
     </row>
     <row r="130" ht="42" customHeight="1">
       <c r="A130" s="10" t="inlineStr">
@@ -8845,31 +8895,28 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
+      <c r="A144" s="12" t="inlineStr">
         <is>
           <t>YÜKLENDİ</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
+      <c r="B144" s="12" t="inlineStr">
         <is>
           <t>video_157.mp4</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
+      <c r="C144" s="13" t="inlineStr">
         <is>
           <t>Üçgen ve Açı Kelimelerini Atatürk'ün Bizzat Türettiğini Biliyor muydun? 🇹🇷 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
+      <c r="D144" s="13" t="inlineStr">
         <is>
           <t>Bugün okulda tek nefeste söylediğin üçgen, kare, açı ve artı kelimelerini kimin oturup türettiğini hiç düşündün mü? Bin dokuz yüz otuz altı kışında Atatürk masa başına geçti ve adını bile koymadığı kırk dört sayfalık Geometri kitabını yazdı.
 📍 BÖLÜMLER
-00:00 Üçgen, kare ve açi adini — Ki̇m türetti̇ bi̇li̇yor musun?
-00:08 Cumhuri̇yet'ten önce üçgen: — Ezberi̇ zor ağir teri̇mler!
-00:17 1936 kişi i̇si̇msi̇z eser: — 44 sayfalik geometri̇ ki̇tabi!
-00:26 Arti, eksi̇, çap, uzay: — Bi̇li̇m di̇li̇ tertemi̇z oldu!
-00:37 29 eki̇m'i̇n gerçek ruhu: — Akil ve bi̇li̇m devri̇mi̇!
-00:46 103. yilimiz kutlu olsun! — Yoruma yaz &amp; taki̇p et!
+00:00 Üçgen, kare ve açi adini — Kim türetti biliyor musun?
+00:17 1936 kişi isimsiz eser: — 44 sayfalik geometri kitabi!
+00:37 29 ekim'in gerçek ruhu: — Akil ve bilim devrimi!
 📊 Kaynaklar:
 • Kaynak: Türk Dil Kurumu &amp; Kültür Bakanlığı Geometri Kılavuzu (1937)
 • https://tdk.gov.tr/
@@ -8878,43 +8925,1458 @@
 #bilgidozu #shorts #29ekim #cumhuriyetbayramı #bilim #tarih</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
+      <c r="E144" s="13" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #29ekim #cumhuriyetbayramı #bilim #tarih</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
+      <c r="F144" s="13" t="inlineStr">
         <is>
           <t>bilgidozu, shorts, 29 ekim, cumhuriyet bayramı, atatürk geometri kitabı, üçgen kelimesini kim buldu, bilim tarihi, türkçe matematik terimleri, bilgi dozu</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
+      <c r="G144" s="13" t="inlineStr">
         <is>
           <t>Üçgen, açı, uzay, köşegen, artı, eksi... Senin en sevdiğin Türkçe bilim kelimesi hangisi? 29 Ekim Cumhuriyet Bayramımız kutlu olsun! 👇</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
+      <c r="H144" s="13" t="inlineStr">
         <is>
           <t>29 Ekim Özel — Bilim Tarihi</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr">
+      <c r="I144" s="13" t="inlineStr">
         <is>
           <t>Türk Dil Kurumu (TDK) &amp; Kültür Bakanlığı Geometri Kılavuzu (1937)</t>
         </is>
       </c>
-      <c r="J144" t="inlineStr">
+      <c r="J144" s="13" t="inlineStr">
         <is>
           <t>https://youtu.be/t2lphcITKXs</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
+      <c r="K144" s="13" t="inlineStr">
         <is>
           <t>2026-10-29 19:30</t>
         </is>
       </c>
-      <c r="L144" t="n">
-        <v>36</v>
+      <c r="L144" s="13" t="n"/>
+      <c r="M144" s="13" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>video_148.mp4</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Karanlık Odaya Girince Gözün Gece Görüşünü 20 Dakikada Nasıl Açar? 👁️ #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Aydınlıktan karanlık bir odaya girdiğinde ilk saniye hiçbir şey göremezken dakikalar içinde gece görüşün nasıl açılır? Göz arkasında gündüz çalışan koni hücreleri karanlıkta susar; nöbeti yüz yirmi milyon çubuk hücresi devralır.
+📍 BÖLÜMLER
+00:00 Işık kapanınca gözün — Neden önce kör olur?
+00:18 Gizli kimyasal yakıt: — Rodopsin pigmenti!
+00:36 Tek telefon ışığı — Sayacı sıfırlar!
+📊 Kaynaklar:
+• American Academy of Ophthalmology &amp; Harvard Ophthalmology
+• https://www.aao.org/eye-health/anatomy/photoreceptors
+🖼️ Görseller temsilîdir (AI bilimsel canlandırma).
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+#bilgidozu #shorts #göz #insanvücudu #bilim</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #göz #insanvücudu #bilim</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, karanlıkta göz nasıl alışır, gece görüşü, rodopsin, göz anatomisi, insan vücudu, bilim, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Bu gece ışığı kapattığında ilk saniye ile üçüncü dakika arasındaki farkı test et, gördüğün değişimi yoruma bırak! 👇</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>İnsan Vücudu ve Beyin</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>American Academy of Ophthalmology &amp; Harvard Ophthalmology</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>video_149.mp4</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Nane Şekeri Ağzını Gerçekte Soğutmaz: Beynini Nasıl Kandırır? 🌿 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Keskin bir nane şekeri attığında ağzının içi buz kesmiş gibi ferahlar; peki nane sıcaklığı gerçekten düşürür mü? Ağzına hassas termometre koysan sıcaklık hiç düşmez; çünkü ortada kusursuz bir kimyasal illüzyon vardır.
+📍 BÖLÜMLER
+00:00 Nane ağzını gerçekten — Soğutuyor mu?
+00:18 Nobel ödüllü keşif: — Sahte soğuk anahtarı!
+00:36 Üstüne su içince — Neden iki kat çarpar?
+📊 Kaynaklar:
+• Nobel Prize in Physiology or Medicine (David Julius, 2021)
+• https://www.nobelprize.org/prizes/medicine/2021/press-release/
+🖼️ Görseller temsilîdir (AI bilimsel canlandırma).
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+#bilgidozu #shorts #bilim #beyin #insanvücudu</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #bilim #beyin #insanvücudu</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, nane neden serinletir, mentol soğuk hissi, trpm8 reseptörü, nobel tıp, beyin hilesi, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Naneli sakız üstüne su içip yüzünü buruşturan o arkadaşına bunu gönder, sebebini öğrensin! 👇</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>İnsan Vücudu ve Beyin</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Nobel Prize in Physiology or Medicine (David Julius, 2021)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>video_150.mp4</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Sabah Uyandığında Boyun Geceye Göre Neden 2 Santim Daha Uzun Çıkar? 📏 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Sabah yataktan kalktığın an boyunu ölçsen, geceye göre iki santimetre daha uzun çıktığını biliyor muydun? Sırrı omurga kemiklerinin arasına dizilmiş yirmi üç adet jelatinimsi yastıkçıkta, yani esnek omurga disklerinde gizlidir.
+📍 BÖLÜMLER
+00:00 Sabah uyanınca boyun — Gerçekten uzuyor mu?
+00:17 Gün boyu yerçekimi — Sünger gibi sıkar!
+00:35 Uzaydaki astronotlar — 5 santim bile uzar!
+📊 Kaynaklar:
+• Cleveland Clinic &amp; NASA Spine Decompression Research
+• https://my.clevelandclinic.org/health/body/22460-intervertebral-disc
+🖼️ Görseller temsilîdir (AI bilimsel canlandırma).
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+#bilgidozu #shorts #insanvücudu #omurga #bilim</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #insanvücudu #omurga #bilim</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, sabah boy neden uzun çıkar, omurga diskleri, uzayda astronot boyu, insan vücudu, anatomi, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Sabah uyanır uyanmaz ve gece yatmadan duvara işaret koyup ölçmeyi dene, farkı yoruma yaz! 👇</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>İnsan Vücudu ve Beyin</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Cleveland Clinic &amp; NASA Spine Decompression Research</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>uzun_video_17.mp4</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Karanlıkta Gözümüz Gece Görüşünü Nasıl Açar? Korsan Bandı ve Rodopsin Sırrı 👁️ #bilgidozu</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Aydınlıktan karanlık bir odaya girdiğinde ilk saniye hiçbir şey göremezken dakikalar içinde gece görüşün nasıl açılır? Peki eski denizcilerin ve korsanların taktığı meşhur göz bandının bu yirmi dakikalık kimyayla doğrudan bağlantılı olduğunu biliyor muydun? Güneşli güverteden karanlık gemi altına inen bir denizci yirmi dakika kör kalmayı göze alamazdı. Bir gözünü bantla sürekli karanlıkta hazır tutuyor, alt kata indiği saniye bandı diğer göze kaydırıp anında net görüyordu.
+📍 BÖLÜMLER
+00:00 Işık kapanınca gözün — Neden önce kör olur?
+00:16 Gizli kimyasal yakıt: — Rodopsin pigmenti!
+00:32 Tek telefon ışığı — Sayacı sıfırlar!
+01:06 Denizaltılarda neden — Kırmızı ışık yanar?
+01:27 Soluk yıldızı görmek için — Tam üstüne bakma!
+01:47 Yıldız taktiğini dene! — Yoruma yaz &amp; takip et!
+📊 Kaynaklar:
+• American Academy of Ophthalmology &amp; Naval Aerospace Medical Inst.
+• https://www.aao.org/eye-health/anatomy/photoreceptors
+🖼️ Görseller temsilîdir (AI bilimsel canlandırma).
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+#bilgidozu #göz #beyin #insanvücudu #bilim</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>#bilgidozu #göz #beyin #insanvücudu #bilim</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>bilgidozu, karanlıkta gece görüşü, göz karanlığa nasıl alışır, rodopsin nedir, korsanlar neden göz bandı takar, kırmızı ışık gece görüşü, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Korsanların göz bandı taktiğini daha önce duymuş muydun, yoksa yaralı olduklarını mı sanıyordun? Yoruma yaz! 👇</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>İnsan Vücudu ve Beyin</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>American Academy of Ophthalmology &amp; Naval Aerospace Medical Inst.</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>video_148.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>video_151.mp4</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Odaya Girince Buraya Neden Gelmiştim Diye Unutmanın Bilimsel Sırrı! 🚪 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>İçeriden bir şey almaya mutfağa gidip kapıdan adım attığın saniye ben buraya neden gelmiştim diye kalakalman neden olur? Merak etme, hafızan zayıflamıyor; Notre Dame Üniversitesi bilimcileri bu olaya kapı eşiği etkisi adını verdi.
+📍 BÖLÜMLER
+00:00 Mutfağa girince — Neden bir anda unutursun?
+00:17 Beyin anıları bölüm — Dosyalarına ayırır!
+00:35 Eski odaya dönünce — Neden hemen akla gelir?
+📊 Kaynaklar:
+• Univ. of Notre Dame (Radvansky et al., 2011) Q. J. Exp. Psychol.
+• https://news.nd.edu/news/walking-through-doorways-causes-forgetting-new-research-shows/
+🖼️ Görseller temsilîdir (AI bilimsel canlandırma).
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+#bilgidozu #shorts #beyin #hafıza #psikoloji #bilim</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #beyin #hafıza #psikoloji #bilim</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, odaya girince unutmak, kapı eşiği etkisi, doorway effect, unutkanlık neden olur, beyin hafıza, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Mutfağa gidip elinde bambaşka bir şeyle döndüğün en komik anını yoruma yaz! 👇</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>İnsan Vücudu ve Beyin</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Univ. of Notre Dame (Radvansky et al., 2011) Q. J. Exp. Psychol.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>video_152.mp4</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>İlk Yudum Su Daha Kana Karışmadan Susuzluğunu Nasıl Anında Keser? 💧 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>İçtiğin suyun mideden kana karışması on beş dakikayı bulur; peki nasıl daha ilk yudumda susuzluğun anında kesilir? Kanındaki su azalıp tuz yoğunluğu yükseldiğinde beynindeki özel osmoreseptör nöronları aralıksız susuzluk alarmı çalmaya başlar.
+📍 BÖLÜMLER
+00:00 Suyun kana karışması — 15 dakika sürer ama...
+00:18 15 dakika bekleseydi — Fazla su içerdin!
+00:36 Soğuk su alarmı — Daha hızlı susturur!
+📊 Kaynaklar:
+• UCSF (Zimmerman &amp; Knight, 2016) Nature
+• https://www.ucsf.edu/news/2016/08/403796/thirst-neurons-anticipate-future-hydration-needs
+🖼️ Görseller temsilîdir (AI bilimsel canlandırma).
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+#bilgidozu #shorts #su #beyin #insanvücudu #bilim</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #su #beyin #insanvücudu #bilim</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, su içince susuzluk nasıl geçer, beyin susuzluk merkezi, osmoreseptör, insan vücudu, bilim, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Çok susadığında soğuk suyun o ilk yudumdaki ani ferahlığını sen de yaşıyor musun? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>İnsan Vücudu ve Beyin</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>UCSF (Zimmerman &amp; Knight, 2016) Nature</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>video_153.mp4</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Spordan Ertesi Gün Çıkan Kas Ağrısının Sebebi Laktik Asit Değilmiş! 💪 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Uzun aradan sonra spor yaptığında ertesi sabah merdiven bile inememene yol açan o hamlama ağrısını hâlâ laktik asit mi sanıyorsun? Spor bilimi bu efsaneyi çürüttü; çünkü oluşan laktik asit, antrenmandan sonraki bir saat içinde tamamen temizlenir.
+📍 BÖLÜMLER
+00:00 Spordan ertesi gün — Kaslar neden sızlar?
+00:18 Gerçek sebep: — Mikroskobik lif çatlakları!
+00:36 Bir sonraki antrenmanda — Kas daha dayanıklı!
+📊 Kaynaklar:
+• American College of Sports Medicine &amp; Sports Medicine Journal
+• https://www.acsm.org/
+🖼️ Görseller temsilîdir (AI bilimsel canlandırma).
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+#bilgidozu #shorts #spor #kas #insanvücudu #bilim</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #spor #kas #insanvücudu #bilim</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, kas ağrısı neden olur, hamlama sebebi, laktik asit efsanesi, doms nedir, spor bilimi, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Uzun aradan sonra spora dönüp merdiven inemediğin o gün en çok hangi kasın ağrımıştı? Yoruma yaz! 👇</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>İnsan Vücudu ve Beyin</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>American College of Sports Medicine &amp; Sports Medicine Journal</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>uzun_video_18.mp4</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Odaya Girince Ne Alacağını Neden Unutursun? Kapı Eşiği Etkisi ve Beyin 🚪 #bilgidozu</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>İçeriden bir şey almaya mutfağa gidip kapıdan adım attığın saniye ben buraya neden gelmiştim diye kalakalman neden olur? Bilim insanları unutmanın yürüyerek geçen süreden mi yoksa kapıdan mı kaynaklandığını ölçmek için sanal gerçeklik testi kurdu. Aynı mesafeyi düz ve büyük bir salonda yürüyen gönüllüler nesneleri net hatırlarken, aynı mesafede tek bir kapıdan geçenlerin hata oranı iki katına çıktı. Yani hafızayı sıfırlayan şey adımların değil, mekân sınırını geçmekti.
+📍 BÖLÜMLER
+00:00 Mutfağa girince — Neden bir anda unutursun?
+00:16 Beyin anıları bölüm — Dosyalarına ayırır!
+00:32 Eski odaya dönünce — Neden hemen akla gelir?
+01:04 Telefonda sekme açmak: — Dijital kapı eşiği!
+01:20 Unutmamak için 3 saniyelik — Beyin kilitleme tekniği!
+01:40 Telefonda da yaşıyor musun? — Yoruma yaz &amp; takip et!
+📊 Kaynaklar:
+• Univ. of Notre Dame (Radvansky, 2011) &amp; Bond University (2021)
+• https://news.nd.edu/news/walking-through-doorways-causes-forgetting-new-research-shows/
+🖼️ Görseller temsilîdir (AI bilimsel canlandırma).
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+#bilgidozu #beyin #hafıza #psikoloji #bilim</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>#bilgidozu #beyin #hafıza #psikoloji #bilim</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>bilgidozu, kapı eşiği etkisi, odaya girince unutmak, doorway effect, çalışma belleği, dijital unutkanlık, beyin sırları, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Telefon ekranında yeni sekme açınca ne arayacağını unuttuğun da oluyor mu? Yoruma yaz! 👇</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>İnsan Vücudu ve Beyin</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Univ. of Notre Dame (Radvansky, 2011) &amp; Bond University (2021)</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>video_151.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>video_154.mp4</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Kesilen Elma Dakikalar İçinde Neden Kararır: Gizli Savunma Zırhı! 🍏 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Bembeyaz kestiğin bir elma dilimi tabakta birkaç dakika beklediğinde neden bozulmuş gibi hızla kahverengiye döner? Gördüğün o renk değişimi çürüme değildir; aslında elmanın yaralanan dokusunu mikroplardan korumak için ördüğü kimyasal bir zırhtır.
+📍 BÖLÜMLER
+00:00 Kesilen elma neden — Dakikalarda kararır?
+00:17 Bıçak hücreyi kesince — Oksijenle birleşir!
+00:35 Bir damla limon — Enzimi nasıl durdurur?
+📊 Kaynaklar:
+• Journal of Agricultural and Food Chemistry &amp; Scientific American
+• https://www.scientificamerican.com/article/why-do-apple-slices-turn-brown-after-being-cut/
+🖼️ Görseller temsilîdir (AI bilimsel canlandırma).
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+#bilgidozu #shorts #kimya #bilim #ilginçbilgiler</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #kimya #bilim #ilginçbilgiler</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, kesilen elma neden kararır, elmaya limon sıkmak, polifenol oksidaz, kimya, günlük bilim, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Dilimlenmiş elmayı kararmasın diye limonla mı saklıyorsun, yoksa başka bir yöntemin mi var? Yoruma yaz! 👇</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Doğa ve Kimya</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Journal of Agricultural and Food Chemistry &amp; Scientific American</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>video_155.mp4</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Buzun Üzeri Neden Kaygandır: Eksi Derecede Bile Akan Gizli Katman! 🧊 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Düz betonda rahatça yürürken katı buza bastığın saniye ayağının neden sabun gibi kaydığını düşündün mü? Yıllarca ayakkabı basıncının buzu erittiği anlatıldı; oysa insan ağırlığının oluşturduğu basınç buzu eritmeye asla yetmez.
+📍 BÖLÜMLER
+00:00 Taş ve cam kuruyken — Buz neden kaygandır?
+00:17 Amsterdam keşfi: — Gevşek yüzey atomları!
+00:36 -7 derece en kaygan an: — Aşırı soğukta azalır!
+📊 Kaynaklar:
+• Univ. of Amsterdam (Weber &amp; Bonn, 2018) J. Phys. Chem. Lett.
+• https://iop.uva.nl/content/news/2018/05/why-is-ice-slippery.html
+🖼️ Görseller temsilîdir (AI bilimsel canlandırma).
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+#bilgidozu #shorts #fizik #buz #bilim #ilginçbilgiler</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #fizik #buz #bilim #ilginçbilgiler</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, buz neden kaygandır, buz üstünde neden kayılır, su molekülleri, fizik sırları, bilim, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Kışın düz yolda yürürken bile kaymayı başaran o arkadaşına bunu gönder! 👇</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Fizik ve Bilim</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Univ. of Amsterdam (Weber &amp; Bonn, 2018) J. Phys. Chem. Lett.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>video_156.mp4</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Havuç Gece Görüşünü Güçlendirir Efsanesi Nasıl Gizli Radar Oyunu Çıktı? 🥕 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Çok havuç yersen karanlıkta kedi gibi görürsün sözünü hep duyarız; peki bu gerçek mi yoksa askeri bir sır mı? Havuçtaki A vitamini göz sağlığını korur; fakat eksiklik yoksa fazlası sağlıklı göze ekstra gece görüşü vermez.
+📍 BÖLÜMLER
+00:00 Bol havuç yemek gece — Görüşünü açar mı?
+00:18 1940 gece gökyüzünde — Gizli radar icadı!
+00:37 80 yıldır süren — En başarılı kampanya!
+📊 Kaynaklar:
+• Smithsonian Magazine &amp; Imperial War Museums Archives
+• https://www.smithsonianmag.com/arts-culture/a-wwii-propaganda-campaign-popularized-the-myth-that-carrots-help-you-see-in-the-dark-28812484/
+🖼️ Görseller temsilîdir (AI bilimsel canlandırma).
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+#bilgidozu #shorts #tarih #bilim #efsaneler #ilginçbilgiler</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #tarih #bilim #efsaneler #ilginçbilgiler</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, havuç göze iyi gelir mi, havuç gece görüşü efsanesi, ikinci dünya savaşı radar sırrı, bilim tarihi, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Çocukken doğru sanıp büyüyünce şaşırdığın başka hangi meşhur efsane var? Yoruma bırak! 👇</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Bilim Tarihi ve Efsaneler</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Smithsonian Magazine &amp; Imperial War Museums Archives</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>uzun_video_19.mp4</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Buz Neden Kaygandır? 150 Yıllık Fizik Tartışmasını Çözen Molekül Sırrı 🧊 #bilgidozu</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Düz betonda rahatça yürürken katı buza bastığın saniye ayağının neden sabun gibi kaydığını düşündün mü? Buzun yüzeyindeki bu görünmez hareketli katmanı ilk hisseden bilim insanı bin sekiz yüz elli yılında ünlü fizikçi Michael Faraday olmuştu. İki buz küpünü birbirine hafifçe bastırdığında aralarındaki o ince hareketli katman artık dış yüzey olmaktan çıkıp anında donuyor ve iki küp tek parça halinde birbirine kaynıyordu.
+📍 BÖLÜMLER
+00:00 Taş ve cam kuruyken — Buz neden kaygandır?
+00:17 Amsterdam keşfi: — Gevşek yüzey atomları!
+00:36 -7 derece en kaygan an: — Aşırı soğukta azalır!
+01:09 Paten bıçağı buzda — Saniyede nasıl süzülür?
+01:27 Su doğadaki kuralları — Bozan tek sıvıdır!
+01:44 Suyun en ilginç özelliği ne? — Yoruma yaz &amp; takip et!
+📊 Kaynaklar:
+• Univ. of Amsterdam (Bonn, 2018) &amp; Physical Review X
+• https://iop.uva.nl/content/news/2018/05/why-is-ice-slippery.html
+🖼️ Görseller temsilîdir (AI bilimsel canlandırma).
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+#bilgidozu #fizik #buz #bilim #keşif</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>#bilgidozu #fizik #buz #bilim #keşif</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>bilgidozu, buz neden kaygandır, faraday buz deneyi, paten buzda nasıl kayar, suyun ilginç özellikleri, fizik bilimi, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Suyun donunca genleşmesi mi yoksa buzun kayganlığı mı sence daha şaşırtıcı? Yoruma yaz! 👇</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Fizik ve Bilim</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Univ. of Amsterdam (Bonn, 2018) &amp; Physical Review X</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>video_155.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>video_158.mp4</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Ağlamamak İçin Kendini Tuttuğunda Boğazına Neden Yumru Oturur? 😢 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Ağlamamak için kendini zor tuttuğun an boğazına koca bir yumru oturmuş gibi yutkunmakta neden zorlanırsın? Yoğun üzüntü başladığında beynin tıpkı tehlike anındaki gibi savaş ya da kaç sistemini devreye sokup daha çok oksijen ister.
+📍 BÖLÜMLER
+00:00 Gözyaşını tuttuğun an — Boğazın neden düğümlenir?
+00:16 Ses telleri arasındaki — Nefes kapısı açılır!
+00:35 Ortada hiçbir cisim yok: — Kas çatışması yumru gibi!
+📊 Kaynaklar:
+• Cleveland Clinic &amp; Journal of Voice (Autonomic Laryngeal Physiology)
+• https://my.clevelandclinic.org/health/symptoms/globus-sensation
+🖼️ Görseller temsilîdir (AI bilimsel canlandırma).
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+#bilgidozu #shorts #insanvücudu #beyin #psikoloji #bilim</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #insanvücudu #beyin #psikoloji #bilim</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, boğaz düğümlenmesi neden olur, ağlarken boğazda yumru hissi, globus hissi, insan vücudu, beyin, bilim, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Boğazının en son düğümlendiği o an bir film sahnesi miydi yoksa gerçek hayat mı? Yoruma bırak! 👇</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>İnsan Vücudu ve Beyin</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Cleveland Clinic &amp; Journal of Voice (Autonomic Laryngeal Physiology)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>video_159.mp4</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Aynı Kelimeyi 20 Kez Söyleyince Neden Anlamı Bir Anda Silinir? 🧠 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Her gün kullandığın kapı kelimesini yirmi kez üst üste söylediğinde neden bir anda tuhaf bir sese dönüşür? Normalde bir kelimeyi duyduğun salisede beyin kabuğundaki nöron ağı o sesi hafızandaki anlamıyla birleştirir.
+📍 BÖLÜMLER
+00:00 Bildiğin kelime 20 saniyede — Neden yabancı dile döner?
+00:15 Peş peşe ateşlenen hücre — Enerji korumaya geçer!
+00:33 Kulak sesi duyar ama — Anlam köprüsü susar!
+📊 Kaynaklar:
+• McGill University (Jakobovits James, 1962) &amp; Psychological Science
+• https://www.apa.org/pubs/journals/xge
+🖼️ Görseller temsilîdir (AI bilimsel canlandırma).
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+#bilgidozu #shorts #beyin #psikoloji #nörobilim #bilim</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #beyin #psikoloji #nörobilim #bilim</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, kelimeyi tekrarlayınca anlamsız gelmesi, anlamsal doygunluk, semantic satiation, beyin sırları, psikoloji, bilim, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Şu an 'kaşık' ya da 'kapı' kelimesini 15 kez üst üste fısılda; kaçıncı tekrarda yabancılaştı? Yoruma yaz! 👇</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Beyin ve Psikoloji</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>McGill University (Jakobovits James, 1962) &amp; Psychological Science</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>video_160.mp4</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Gece Yatakta Tek Ayağını Yorgandan Çıkarınca Neden Hemen Uykun Gelir? 🦶 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Gece yatakta dönerken tek ayağını yorganın dışına çıkardığın an neden saniyeler içinde ferahlayıp uyursun? Beyninin uyku şalterini açması için iç vücut sıcaklığının bir derece düşmesi şarttır; kalın yorgan ise ısıyı hapseder.
+📍 BÖLÜMLER
+00:00 Tek ayağı yorgandan çıkarmak — Neden anında uyutur?
+00:17 Ayak tabanında gizli — Özel radyatör damarlar!
+00:35 Serinleyen kan beyne — Uyku sinyalini verir!
+📊 Kaynaklar:
+• National Sleep Foundation &amp; Northumbria Univ. Sleep Research
+• https://www.sleepfoundation.org/bedroom-environment/touch/what-temperature-should-your-bedroom-be
+🖼️ Görseller temsilîdir (AI bilimsel canlandırma).
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+#bilgidozu #shorts #uyku #insanvücudu #beyin #bilim</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #uyku #insanvücudu #beyin #bilim</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, uyurken ayağı yorgandan çıkarmak, hızlı uyuma tekniği, vücut sıcaklığı uyku, insan vücudu, bilim, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Sen de yaz kış demeden tek ayağını yorganın dışına çıkaranlardan mısın? Yoruma yaz! 👇</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>İnsan Vücudu ve Beyin</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>National Sleep Foundation &amp; Northumbria Univ. Sleep Research</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>uzun_video_20.mp4</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Ağlarken Boğazımız Neden Düğümlenir? Beynin Gizli Glottis Savaşı ve Çözümü 😢 #bilgidozu</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Ağlamamak için kendini zor tuttuğun an boğazına koca bir yumru oturmuş gibi yutkunmakta neden zorlanırsın? Peki ağlamak yerine kendini sıktığında bu düğüm neden iki kat büyür? Çünkü gözyaşını durdurmak için yüz, çene ve boyun çevresindeki yirmiden fazla yardımcı kası aynı anda kasarsın. Gırtlağı askıda tutan bu dış kaslar gerildikçe içerideki nefes kapısının hareket alanı iyice daralır ve basınç hissi zirveye çıkar.
+📍 BÖLÜMLER
+00:00 Gözyaşını tuttuğun an — Boğazın neden düğümlenir?
+00:16 Ses telleri arasındaki — Nefes kapısı açılır!
+00:34 Ortada hiçbir cisim yok: — Kas çatışması yumru gibi!
+01:05 Tek yudum ılık su — Sinir kilidini nasıl açar?
+01:27 Ağlamak zayıflık değil: — Kimyasal boşaltım sistemi!
+01:47 Seni en çok ne duygulandırır? — Yoruma yaz &amp; abone ol!
+📊 Kaynaklar:
+• Cleveland Clinic &amp; Journal of Voice (Autonomic Laryngeal Physiology)
+• https://my.clevelandclinic.org/health/symptoms/globus-sensation
+🖼️ Görseller temsilîdir (AI bilimsel canlandırma).
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+#bilgidozu #insanvücudu #beyin #psikoloji #bilim</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>#bilgidozu #insanvücudu #beyin #psikoloji #bilim</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>bilgidozu, boğaz düğümlenmesi neden olur, ağlarken boğazda yumru, globus pharyngeus, glottis nedir, vagus siniri, insan vücudu, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Boğazın düğümlendiğinde bir yudum ılık su taktiğini biliyor muydun, yoksa yutkunmaya mı çalışıyordun? Yoruma yaz! 👇</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>İnsan Vücudu ve Beyin</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Cleveland Clinic &amp; Journal of Voice (Autonomic Laryngeal Physiology)</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>video_158.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>video_161.mp4</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Saate İlk Baktığın Saniye Neden Donmuş Gibi Daha Uzun Sürer? ⏱️ #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Gözünü aniden duvar saatine çevirdiğin ilk an saniye ibresinin bozulmuş gibi daha uzun beklediğini fark ettin mi? Gözün saate hızla sıçrarken görüntü bulanıklaşmasın diye beynin yaklaşık elli milisaniye boyunca kaydı kapatır.
+📍 BÖLÜMLER
+00:00 Saate ilk baktığın an — Saniye neden donakalır?
+00:16 Karanlık boşluğu örtmek için — Geriye dönük montaj!
+00:35 Aynada kendi gözünün — Hareketini göremezsin!
+📊 Kaynaklar:
+• University College London (Yarrow et al., Nature 2001)
+• https://www.nature.com/articles/35104551
+🖼️ Görseller temsilîdir (AI bilimsel canlandırma).
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+#bilgidozu #shorts #beyin #zaman #psikoloji #bilim</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #beyin #zaman #psikoloji #bilim</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, durmuş saat yanılsaması, kronostaz nedir, saate bakınca saniyenin durması, beyin zaman algısı, nörobilim, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Bu videodan hemen sonra bir saate ya da telefon sayacına hızla gözünü çevirip ilk saniyeyi dene; fark ettin mi? 👇</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Beyin ve Psikoloji</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>University College London (Yarrow et al., Nature 2001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>video_162.mp4</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Çok Tuzlu Çekirdek Yediğinde Dudakların Neden Kuruyup Büzüşür? 🧂 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Bir avuç tuzlu çekirdek yediğinde dudaklarının kuruyup beyazladığını ve büzüştüğünü hiç fark ettin mi? Ağız içini kaplayan yumuşak hücrelerin üzerine yoğun tuz yapıştığında fiziğin ozmoz yasası saniyede devreye girer.
+📍 BÖLÜMLER
+00:00 Tuzlu çekirdek yiyince — Dudaklar neden büzüşür?
+00:16 Hücre içindeki saf su — Dışarı doğru emilir!
+00:35 Bir bardak saf suyla — Denge geri kurulur!
+📊 Kaynaklar:
+• Nature Neuroscience (Oka et al., High-Salt Taste Receptors) &amp; NIH
+• https://www.nih.gov/news-events/nih-research-matters/how-tongue-detects-high-salt-levels
+🖼️ Görseller temsilîdir (AI bilimsel canlandırma).
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+#bilgidozu #shorts #biyoloji #insanvücudu #kimya #bilim</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #biyoloji #insanvücudu #kimya #bilim</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, tuzlu çekirdek dudak büzüşmesi, tuz neden susatır, ozmoz nedir, insan vücudu, biyoloji, bilim, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Çekirdek çitlemeye başlayınca dudakların beyazlayana kadar duramayan arkadaşını etiketle veya ona gönder! 👇</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Biyoloji ve Vücut</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Nature Neuroscience (Oka et al., High-Salt Taste Receptors) &amp; NIH</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>video_163.mp4</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Üzgün Olmasan Bile Her 5 Dakikada Bir Neden Fark Etmeden İç Çekersin? 🫁 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Hiçbir derdin yokken otururken göğsünün neden her beş dakikada bir kendiliğinden derin iç çektiğini biliyor musun? Akciğerlerindeki beş yüz milyon minik hava keseciği normal sığ nefeslerde ıslak balon gibi yavaşça söner.
+📍 BÖLÜMLER
+00:00 Üzgün olmadığın halde — Neden derin iç çekersin?
+00:17 Beyin sapındaki saat: — Saatte 12 kez ateşlenir!
+00:36 Stresi 10 saniyede kesen — Çift nefes tekniği!
+📊 Kaynaklar:
+• Nature (Li, Feldman &amp; Krasnow, UCLA &amp; Stanford Medicine)
+• https://med.stanford.edu/news/all-news/2016/02/study-pinpoints-brain-circuitry-that-causes-sighing.html
+🖼️ Görseller temsilîdir (AI bilimsel canlandırma).
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+#bilgidozu #shorts #akciğer #nefes #insanvücudu #bilim</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #akciğer #nefes #insanvücudu #bilim</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, neden iç çekeriz, fizyolojik iç çekiş, akciğer alveol, stanford nefes tekniği, insan vücudu, bilim, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Şimdi burnundan üst üste iki kısa nefes çekip ağzından yavaşça ver; o anlık rahatlamayı hissettin mi? 👇</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>İnsan Vücudu ve Beyin</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Nature (Li, Feldman &amp; Krasnow, UCLA &amp; Stanford Medicine)</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>uzun_video_21.mp4</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Saate İlk Baktığında Saniye Neden Donar? Beynin Zamanı Geriye Saran Hilesi ⏱️ #bilgidozu</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Gözünü aniden duvar saatine çevirdiğin ilk an saniye ibresinin bozulmuş gibi daha uzun beklediğini fark ettin mi? İnsan gözü çevreyi tararken saniyede üç kez hızlı sıçrama yapar; yani uyanık olduğun tek bir günde yaklaşık yüz elli bin kez görüntün kesilir. Toplamda günde kırk dakikadan fazla görsel karanlıkta kalırsın ama beynin kurgu masası gibi boşlukları geriye dönük doldurduğu için dünyayı kesintisiz bir film sanırsın.
+📍 BÖLÜMLER
+00:00 Saate ilk baktığın an — Saniye neden donakalır?
+00:15 Karanlık boşluğu örtmek için — Geriye dönük montaj!
+00:32 Aynada kendi gözünün — Hareketini göremezsin!
+01:02 Sadece gözde değil: — Ses ve dokunmada da olur!
+01:19 80 milisaniye geriden: — Geçmişi şimdi sanıyorsun!
+01:41 Ayna testini denedin mi? — Yoruma yaz &amp; abone ol!
+📊 Kaynaklar:
+• University College London (Yarrow et al., Nature 2001) &amp; Salk Institute
+• https://www.nature.com/articles/35104551
+🖼️ Görseller temsilîdir (AI bilimsel canlandırma).
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+#bilgidozu #beyin #zaman #nörobilim #bilim</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>#bilgidozu #beyin #zaman #nörobilim #bilim</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>bilgidozu, durmuş saat yanılsaması, kronostaz, beynin zaman algısı, aynada göz hareketini görememek, nörobilim, psikoloji, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Aynada sağ gözünden sol gözüne bakarken hareketi yakalamayı denedin mi? Sonucu yoruma yaz! 👇</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Beyin ve Psikoloji</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>University College London (Yarrow et al., Nature 2001) &amp; Salk Institute</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>video_161.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>video_164.mp4</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Tıka Basa Doysan Bile Tatlıya Neden Her Zaman Yer Açılır? 🍰 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Akşam yemeğinde tek lokma bile yiyemeyecek kadar doyduğun halde masaya tatlı geldiği an midende nasıl mucizevi yer açılır? Şaka sandığımız tatlı için ayrı mide sözü gerçek çıktı; Max Planck Enstitüsü bu gizli şalterin tam beyinde olduğunu kanıtladı.
+📍 BÖLÜMLER
+00:00 Tek lokma yiyemeyecekken — Tatlıya nasıl yer açılır?
+00:19 Tokluk nöronları yemekte — Artık doydun diyor!
+00:38 Atalarımızdan kalan — Hızlı enerji kodu!
+📊 Kaynaklar:
+• Max Planck Institute for Metabolism Research (Science, 2025)
+• https://www.mpg.de/24159607/0211-neur-dessert-stomach-emerges-in-the-brain-153735-x
+🖼️ Görseller temsilîdir (AI bilimsel canlandırma).
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+#bilgidozu #shorts #beyin #tatlı #insanvücudu #bilim</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #beyin #tatlı #insanvücudu #bilim</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, tokken neden tatlı isteriz, tatlı midesi gerçek mi, yemekten sonra tatlı krizi, beyin ve iştah, bilim, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Yemekten sonra ne kadar tok olursan ol asla hayır diyemediğin o tatlı hangisi? Yoruma yaz! 👇</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>İnsan Vücudu ve Beyin</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Max Planck Institute for Metabolism Research (Science, 2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>video_165.mp4</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Kuru Kum Dağılırken Yüzde 1 Su Kumdan Kaleyi Nasıl Taş Gibi Tutar? 🏰 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Sahilde kuru kum parmaklarının arasından su gibi akarken, biraz ıslattığında nasıl metrelerce yüksek kale gibi dimdik durur? Kuma az miktarda su eklediğinde su damlacıkları kum tanelerinin arasına yerleşip görünmez kapiler sıvı köprüleri kurar.
+📍 BÖLÜMLER
+00:00 Kuru kum akıp giderken — Islak kum nasıl taşlaşır?
+00:19 Yüzey gerilimi taneleri — Vantuz gibi çeker!
+00:38 Fazla su köprüyü yıkar: — Kale çamur olup çöker!
+📊 Kaynaklar:
+• Univ. of Amsterdam (Fall &amp; Bonn, Nature Scientific Reports)
+• https://www.nature.com/articles/srep00549
+🖼️ Görseller temsilîdir (AI bilimsel canlandırma).
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+#bilgidozu #shorts #fizik #doğa #keşif #bilim</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #fizik #doğa #keşif #bilim</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, ıslak kum neden yapışır, kumdan kale fiziği, kapiler sıvı köprüsü, yüzey gerilimi, fizik bilimi, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Sahilde kumdan kale yaparken senin de kulelerin fazla sudan çökmüş müydü? Yoruma yaz! 👇</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Fizik ve Bilim</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Univ. of Amsterdam (Fall &amp; Bonn, Nature Scientific Reports)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>video_166.mp4</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Okulda Öğretilen Dil Tat Haritası Nasıl 100 Yıllık Çeviri Hatası Çıktı? 👅 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Okulda yıllarca ezberletilen dilin ucu tatlıyı, arkası acıyı alır haritasının koca bir hata olduğunu biliyor muydun? Bin dokuz yüz birde Alman bilimci David Hänig dilin her yerinin tat aldığını, sadece ufak farklar olduğunu yazdı.
+📍 BÖLÜMLER
+00:00 Okulda öğretilen dil haritası — Tamamen yanlış çıktı!
+00:17 1942 grafik çevirisinde — Efsane nasıl doğdu?
+00:36 Tek saniyelik kanıt: — Dilinin ucuna kahve değdir!
+📊 Kaynaklar:
+• Nature (Chandrashekar et al., 2006) &amp; Smithsonian Science
+• https://www.smithsonianmag.com/science-nature/neat-and-tidy-map-tastes-tongue-you-learned-school-all-wrong-180963407/
+🖼️ Görseller temsilîdir (AI bilimsel canlandırma).
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+#bilgidozu #shorts #efsaneler #insanvücudu #bilim #tarih</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #efsaneler #insanvücudu #bilim #tarih</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, dil tat haritası yanlış mı, dilin ucu tatlı alır efsanesi, umami nedir, bilim efsaneleri, insan vücudu, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Okulda sana da 'dilin ucu tatlı, yanları ekşi alır' şeması çizdirilmiş miydi? Yoruma yaz! 👇</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Bilim Tarihi ve Efsaneler</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Nature (Chandrashekar et al., 2006) &amp; Smithsonian Science</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>uzun_video_22.mp4</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Tokken Neden Tatlı İsteriz? Beyindeki 'Tatlı Midesi' Şalterinin 2025 Bilimsel Kanıtı 🍰 #bilgidozu</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Akşam yemeğinde tek lokma bile yiyemeyecek kadar doyduğun halde masaya tatlı geldiği an midende nasıl mucizevi yer açılır? Tatlı krizinin arkasındaki ikinci büyük güç Oxford Üniversitesi'nden Edmund Rolls'un tanımladığı duyusal özgül tokluktur. Beynin tek tip tuzlu yemekten sıkıldığında miden tam dolmasa bile o tada karşı fren yapar; fakat önüne bambaşka koku ve dokuda tatlı bir tabak geldiğinde iştah sayacı sıfırlanır.
+📍 BÖLÜMLER
+00:00 Tek lokma yiyemeyecekken — Tatlıya nasıl yer açılır?
+00:18 Tokluk nöronları yemekte — Artık doydun diyor!
+00:36 Atalarımızdan kalan — Hızlı enerji kodu!
+01:06 Daha ilk lokmadan önce — Görmek bile şalteri açar!
+01:28 Tatlı krizini kandıran — 15 dakika kuralı!
+01:51 15 dakika kuralını dene! — Yoruma yaz &amp; abone ol!
+📊 Kaynaklar:
+• Max Planck Institute (Minère et al., Science 2025) &amp; Oxford University
+• https://www.mpg.de/24159607/0211-neur-dessert-stomach-emerges-in-the-brain-153735-x
+🖼️ Görseller temsilîdir (AI bilimsel canlandırma).
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+#bilgidozu #beyin #beslenme #insanvücudu #bilim</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>#bilgidozu #beyin #beslenme #insanvücudu #bilim</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>bilgidozu, yemekten sonra tatlı isteği neden olur, tatlı midesi gerçek mi, max planck tatlı araştırması, duyusal özgül tokluk, beyin, bilgi dozu</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Yemekten hemen sonra tatlı arayanlardan mısın yoksa çayla geçiştirebilenlerden mi? Yoruma yaz! 👇</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>İnsan Vücudu ve Beyin</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Max Planck Institute (Minère et al., Science 2025) &amp; Oxford University</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>video_164.mp4</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/bilgidozu_yukleme_tablosu.xlsx
+++ b/bilgidozu_yukleme_tablosu.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DRIVE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ISCILER" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UYARILAR" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="DRIVE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ISCILER" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="UYARILAR" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>3</v>
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>1</v>
@@ -1313,7 +1313,7 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>1</v>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="L19" s="3" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="M19" s="3" t="n"/>
     </row>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="L38" s="3" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M38" s="3" t="n">
         <v>1</v>
@@ -2882,7 +2882,7 @@
         </is>
       </c>
       <c r="L39" s="3" t="n">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>1</v>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="L43" s="3" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M43" s="3" t="n"/>
     </row>
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="L45" s="3" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="M45" s="3" t="n"/>
     </row>
@@ -3882,7 +3882,9 @@
           <t>2026-10-29 21:11</t>
         </is>
       </c>
-      <c r="L56" s="3" t="n"/>
+      <c r="L56" s="3" t="n">
+        <v>167</v>
+      </c>
       <c r="M56" s="3" t="n"/>
     </row>
     <row r="57" ht="42" customHeight="1">
@@ -4110,7 +4112,9 @@
           <t>2026-10-28 19:37</t>
         </is>
       </c>
-      <c r="L60" s="3" t="n"/>
+      <c r="L60" s="3" t="n">
+        <v>514</v>
+      </c>
       <c r="M60" s="3" t="n"/>
     </row>
     <row r="61" ht="42" customHeight="1">
@@ -4173,7 +4177,9 @@
           <t>2026-10-28 21:10</t>
         </is>
       </c>
-      <c r="L61" s="3" t="n"/>
+      <c r="L61" s="3" t="n">
+        <v>218</v>
+      </c>
       <c r="M61" s="3" t="n"/>
     </row>
     <row r="62" ht="42" customHeight="1">
@@ -4291,7 +4297,9 @@
           <t>2026-10-28 14:07</t>
         </is>
       </c>
-      <c r="L63" s="3" t="n"/>
+      <c r="L63" s="3" t="n">
+        <v>134</v>
+      </c>
       <c r="M63" s="3" t="n"/>
     </row>
     <row r="64" ht="42" customHeight="1">
@@ -4716,7 +4724,7 @@
         </is>
       </c>
       <c r="L70" s="3" t="n">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="M70" s="3" t="n"/>
     </row>
@@ -7544,7 +7552,9 @@
           <t>2026-10-28 10:58</t>
         </is>
       </c>
-      <c r="L122" s="3" t="n"/>
+      <c r="L122" s="3" t="n">
+        <v>127</v>
+      </c>
       <c r="M122" s="3" t="n"/>
     </row>
     <row r="123" ht="42" customHeight="1">
@@ -7718,7 +7728,7 @@
         </is>
       </c>
       <c r="L125" s="3" t="n">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="M125" s="3" t="n"/>
     </row>
@@ -7795,7 +7805,7 @@
         </is>
       </c>
       <c r="L126" s="3" t="n">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="M126" s="3" t="n"/>
     </row>
@@ -7871,7 +7881,7 @@
         </is>
       </c>
       <c r="L127" s="3" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="M127" s="3" t="n"/>
     </row>
@@ -7946,7 +7956,7 @@
         </is>
       </c>
       <c r="L128" s="3" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="M128" s="3" t="n"/>
     </row>
@@ -8020,7 +8030,9 @@
           <t>2026-10-28 01:00</t>
         </is>
       </c>
-      <c r="L129" s="3" t="n"/>
+      <c r="L129" s="3" t="n">
+        <v>145</v>
+      </c>
       <c r="M129" s="3" t="n"/>
     </row>
     <row r="130" ht="42" customHeight="1">
@@ -8960,7 +8972,9 @@
           <t>2026-10-29 19:30</t>
         </is>
       </c>
-      <c r="L144" s="13" t="n"/>
+      <c r="L144" s="13" t="n">
+        <v>59</v>
+      </c>
       <c r="M144" s="13" t="n"/>
     </row>
     <row r="145">
